--- a/artfynd/A 1625-2025 artfynd.xlsx
+++ b/artfynd/A 1625-2025 artfynd.xlsx
@@ -2886,10 +2886,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122715870</v>
+        <v>122720959</v>
       </c>
       <c r="B21" t="n">
-        <v>79844</v>
+        <v>78762</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2902,34 +2902,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Finnbodarna, Finnbodarna, Jmt</t>
+          <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>520265</v>
+        <v>519917</v>
       </c>
       <c r="R21" t="n">
-        <v>7035574</v>
+        <v>7035339</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2964,6 +2964,11 @@
           <t>2025-02-23</t>
         </is>
       </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Långväxta bålar på flertalet granar.</t>
+        </is>
+      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
@@ -2972,6 +2977,31 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM21" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -2988,10 +3018,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122716329</v>
+        <v>122715569</v>
       </c>
       <c r="B22" t="n">
-        <v>79843</v>
+        <v>78762</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3004,42 +3034,37 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Finnbodarna, Finnbodarna, Jmt</t>
+          <t>Djupmyren, Djupmyren, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>520374</v>
+        <v>520115</v>
       </c>
       <c r="R22" t="n">
-        <v>7035511</v>
+        <v>7035562</v>
       </c>
       <c r="S22" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3073,7 +3098,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>På gran intill en gammal lunglavssälg.</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3125,10 +3150,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122716303</v>
+        <v>122715870</v>
       </c>
       <c r="B23" t="n">
-        <v>57478</v>
+        <v>79844</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3141,39 +3166,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Finnbodarna, Hammerdal, Finnbodarna, Hammerdal, Jmt</t>
+          <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>520250</v>
+        <v>520265</v>
       </c>
       <c r="R23" t="n">
-        <v>7035363</v>
+        <v>7035574</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3206,11 +3226,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-02-23</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3237,10 +3252,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122719829</v>
+        <v>122717873</v>
       </c>
       <c r="B24" t="n">
-        <v>57478</v>
+        <v>79843</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3253,27 +3268,27 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3282,13 +3297,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>519930</v>
+        <v>520033</v>
       </c>
       <c r="R24" t="n">
-        <v>7035181</v>
+        <v>7035301</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3320,11 +3335,6 @@
           <t>2025-02-23</t>
         </is>
       </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
@@ -3333,6 +3343,31 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
+      </c>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM24" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
@@ -3349,10 +3384,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122717343</v>
+        <v>122715790</v>
       </c>
       <c r="B25" t="n">
-        <v>57478</v>
+        <v>79843</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3365,39 +3400,39 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Spejkmyren, Spejkmyren, Jmt</t>
+          <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>520034</v>
+        <v>520267</v>
       </c>
       <c r="R25" t="n">
-        <v>7035339</v>
+        <v>7035581</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3430,11 +3465,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-02-23</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3461,10 +3491,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122720959</v>
+        <v>122716329</v>
       </c>
       <c r="B26" t="n">
-        <v>78762</v>
+        <v>79843</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3477,37 +3507,42 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Spejkmyren, Spejkmyren, Jmt</t>
+          <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>519917</v>
+        <v>520374</v>
       </c>
       <c r="R26" t="n">
-        <v>7035339</v>
+        <v>7035511</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3541,7 +3576,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Långväxta bålar på flertalet granar.</t>
+          <t>På gran intill en gammal lunglavssälg.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3593,10 +3628,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122715569</v>
+        <v>122717952</v>
       </c>
       <c r="B27" t="n">
-        <v>78762</v>
+        <v>57494</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3609,34 +3644,43 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Djupmyren, Djupmyren, Jmt</t>
+          <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>520115</v>
+        <v>519951</v>
       </c>
       <c r="R27" t="n">
-        <v>7035562</v>
+        <v>7035320</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3671,11 +3715,6 @@
           <t>2025-02-23</t>
         </is>
       </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
-        </is>
-      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
@@ -3684,31 +3723,6 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
-      </c>
-      <c r="AH27" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ27" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK27" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM27" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO27" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
@@ -3725,10 +3739,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122717873</v>
+        <v>122720368</v>
       </c>
       <c r="B28" t="n">
-        <v>79843</v>
+        <v>57478</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3741,27 +3755,27 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>med soral</t>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -3770,13 +3784,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>520033</v>
+        <v>519852</v>
       </c>
       <c r="R28" t="n">
-        <v>7035301</v>
+        <v>7035392</v>
       </c>
       <c r="S28" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3808,6 +3822,11 @@
           <t>2025-02-23</t>
         </is>
       </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
@@ -3816,31 +3835,6 @@
       </c>
       <c r="AG28" t="b">
         <v>0</v>
-      </c>
-      <c r="AH28" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ28" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK28" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM28" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO28" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
@@ -3857,10 +3851,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122715790</v>
+        <v>122716303</v>
       </c>
       <c r="B29" t="n">
-        <v>79843</v>
+        <v>57478</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3873,39 +3867,39 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Finnbodarna, Finnbodarna, Jmt</t>
+          <t>Finnbodarna, Hammerdal, Finnbodarna, Hammerdal, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>520267</v>
+        <v>520250</v>
       </c>
       <c r="R29" t="n">
-        <v>7035581</v>
+        <v>7035363</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3938,6 +3932,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-02-23</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3964,10 +3963,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122717952</v>
+        <v>122719829</v>
       </c>
       <c r="B30" t="n">
-        <v>57494</v>
+        <v>57478</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3980,16 +3979,16 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -3997,14 +3996,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -4013,10 +4008,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>519951</v>
+        <v>519930</v>
       </c>
       <c r="R30" t="n">
-        <v>7035320</v>
+        <v>7035181</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4049,6 +4044,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-02-23</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4075,7 +4075,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122720368</v>
+        <v>122717343</v>
       </c>
       <c r="B31" t="n">
         <v>57478</v>
@@ -4120,10 +4120,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>519852</v>
+        <v>520034</v>
       </c>
       <c r="R31" t="n">
-        <v>7035392</v>
+        <v>7035339</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -5971,10 +5971,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122719648</v>
+        <v>122716443</v>
       </c>
       <c r="B47" t="n">
-        <v>57478</v>
+        <v>78762</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5987,39 +5987,48 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Spejkmyren, Spejkmyren, Jmt</t>
+          <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>519939</v>
+        <v>520251</v>
       </c>
       <c r="R47" t="n">
-        <v>7035194</v>
+        <v>7035394</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6056,7 +6065,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Garnlavsrikt</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6083,10 +6092,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122716443</v>
+        <v>122715766</v>
       </c>
       <c r="B48" t="n">
-        <v>78762</v>
+        <v>90958</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6099,48 +6108,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>520251</v>
+        <v>520252</v>
       </c>
       <c r="R48" t="n">
-        <v>7035394</v>
+        <v>7035591</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6173,11 +6168,6 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-02-23</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Garnlavsrikt</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6204,10 +6194,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122715766</v>
+        <v>122719648</v>
       </c>
       <c r="B49" t="n">
-        <v>90958</v>
+        <v>57478</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6220,34 +6210,39 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Finnbodarna, Finnbodarna, Jmt</t>
+          <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>520252</v>
+        <v>519939</v>
       </c>
       <c r="R49" t="n">
-        <v>7035591</v>
+        <v>7035194</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6280,6 +6275,11 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-02-23</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6417,10 +6417,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122720548</v>
+        <v>122720558</v>
       </c>
       <c r="B51" t="n">
-        <v>90958</v>
+        <v>57494</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6433,34 +6433,39 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>519847</v>
+        <v>519949</v>
       </c>
       <c r="R51" t="n">
-        <v>7035432</v>
+        <v>7035254</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6495,6 +6500,11 @@
           <t>2025-02-23</t>
         </is>
       </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Äldre hackspår i stambasen.</t>
+        </is>
+      </c>
       <c r="AD51" t="b">
         <v>0</v>
       </c>
@@ -6503,6 +6513,31 @@
       </c>
       <c r="AG51" t="b">
         <v>0</v>
+      </c>
+      <c r="AH51" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ51" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK51" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM51" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO51" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
@@ -6519,10 +6554,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122720558</v>
+        <v>122716673</v>
       </c>
       <c r="B52" t="n">
-        <v>57494</v>
+        <v>57478</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6535,16 +6570,16 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -6564,10 +6599,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>519949</v>
+        <v>520108</v>
       </c>
       <c r="R52" t="n">
-        <v>7035254</v>
+        <v>7035462</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6604,7 +6639,7 @@
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>Äldre hackspår i stambasen.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6615,31 +6650,6 @@
       </c>
       <c r="AG52" t="b">
         <v>0</v>
-      </c>
-      <c r="AH52" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ52" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK52" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM52" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO52" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
@@ -6656,10 +6666,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122716673</v>
+        <v>122717616</v>
       </c>
       <c r="B53" t="n">
-        <v>57478</v>
+        <v>78762</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6672,39 +6682,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>520108</v>
+        <v>520019</v>
       </c>
       <c r="R53" t="n">
-        <v>7035462</v>
+        <v>7035352</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6741,7 +6746,7 @@
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6752,6 +6757,31 @@
       </c>
       <c r="AG53" t="b">
         <v>0</v>
+      </c>
+      <c r="AH53" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ53" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK53" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM53" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO53" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
@@ -6768,7 +6798,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122717616</v>
+        <v>122721333</v>
       </c>
       <c r="B54" t="n">
         <v>78762</v>
@@ -6808,13 +6838,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>520019</v>
+        <v>519906</v>
       </c>
       <c r="R54" t="n">
-        <v>7035352</v>
+        <v>7035389</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6848,7 +6878,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>Rikligt.</t>
+          <t>Ymnigt på flera granar.</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6900,10 +6930,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122721333</v>
+        <v>122720548</v>
       </c>
       <c r="B55" t="n">
-        <v>78762</v>
+        <v>90958</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6916,21 +6946,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6940,13 +6970,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>519906</v>
+        <v>519847</v>
       </c>
       <c r="R55" t="n">
-        <v>7035389</v>
+        <v>7035432</v>
       </c>
       <c r="S55" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6978,11 +7008,6 @@
           <t>2025-02-23</t>
         </is>
       </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Ymnigt på flera granar.</t>
-        </is>
-      </c>
       <c r="AD55" t="b">
         <v>0</v>
       </c>
@@ -6991,31 +7016,6 @@
       </c>
       <c r="AG55" t="b">
         <v>0</v>
-      </c>
-      <c r="AH55" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ55" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK55" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM55" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO55" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
@@ -7032,10 +7032,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122716234</v>
+        <v>122716269</v>
       </c>
       <c r="B56" t="n">
-        <v>79843</v>
+        <v>57478</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -7048,34 +7048,39 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Finnbodarna, Finnbodarna, Jmt</t>
+          <t>Finnbodarna, Hammerdal, Finnbodarna, Hammerdal, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>520362</v>
+        <v>520256</v>
       </c>
       <c r="R56" t="n">
-        <v>7035500</v>
+        <v>7035380</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7112,7 +7117,7 @@
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>På en klen gran intill en gammal sälg med lunglav.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7123,31 +7128,6 @@
       </c>
       <c r="AG56" t="b">
         <v>0</v>
-      </c>
-      <c r="AH56" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ56" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK56" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM56" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO56" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
@@ -7266,10 +7246,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122717294</v>
+        <v>122716234</v>
       </c>
       <c r="B58" t="n">
-        <v>90958</v>
+        <v>79843</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7282,34 +7262,34 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Spejkmyren, Spejkmyren, Jmt</t>
+          <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>520013</v>
+        <v>520362</v>
       </c>
       <c r="R58" t="n">
-        <v>7035340</v>
+        <v>7035500</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7344,6 +7324,11 @@
           <t>2025-02-23</t>
         </is>
       </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>På en klen gran intill en gammal sälg med lunglav.</t>
+        </is>
+      </c>
       <c r="AD58" t="b">
         <v>0</v>
       </c>
@@ -7352,6 +7337,31 @@
       </c>
       <c r="AG58" t="b">
         <v>0</v>
+      </c>
+      <c r="AH58" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ58" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK58" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM58" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO58" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
@@ -7368,10 +7378,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122716269</v>
+        <v>122717294</v>
       </c>
       <c r="B59" t="n">
-        <v>57478</v>
+        <v>90958</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7384,39 +7394,34 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Finnbodarna, Hammerdal, Finnbodarna, Hammerdal, Jmt</t>
+          <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>520256</v>
+        <v>520013</v>
       </c>
       <c r="R59" t="n">
-        <v>7035380</v>
+        <v>7035340</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7449,11 +7454,6 @@
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-02-23</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7480,10 +7480,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122720823</v>
+        <v>122715795</v>
       </c>
       <c r="B60" t="n">
-        <v>57478</v>
+        <v>79843</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7496,56 +7496,37 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K60" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L60" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Spejkmyren, Spejkmyren, Jmt</t>
+          <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>519842</v>
+        <v>520214</v>
       </c>
       <c r="R60" t="n">
-        <v>7035388</v>
+        <v>7035599</v>
       </c>
       <c r="S60" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7579,7 +7560,7 @@
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>Trummande</t>
+          <t>På en klen gran intill en lunglavssälg.</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7590,6 +7571,31 @@
       </c>
       <c r="AG60" t="b">
         <v>0</v>
+      </c>
+      <c r="AH60" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ60" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK60" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM60" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO60" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
@@ -7606,10 +7612,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122715795</v>
+        <v>122720823</v>
       </c>
       <c r="B61" t="n">
-        <v>79843</v>
+        <v>57478</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7622,37 +7628,56 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Finnbodarna, Finnbodarna, Jmt</t>
+          <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>520214</v>
+        <v>519842</v>
       </c>
       <c r="R61" t="n">
-        <v>7035599</v>
+        <v>7035388</v>
       </c>
       <c r="S61" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7686,7 +7711,7 @@
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>På en klen gran intill en lunglavssälg.</t>
+          <t>Trummande</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7697,31 +7722,6 @@
       </c>
       <c r="AG61" t="b">
         <v>0</v>
-      </c>
-      <c r="AH61" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ61" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK61" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM61" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO61" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
@@ -7992,10 +7992,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122717488</v>
+        <v>122717164</v>
       </c>
       <c r="B64" t="n">
-        <v>79843</v>
+        <v>78762</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -8008,21 +8008,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -8032,10 +8032,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>520000</v>
+        <v>520120</v>
       </c>
       <c r="R64" t="n">
-        <v>7035297</v>
+        <v>7035405</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -8078,6 +8078,31 @@
       </c>
       <c r="AG64" t="b">
         <v>0</v>
+      </c>
+      <c r="AH64" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ64" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK64" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM64" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO64" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
@@ -8094,10 +8119,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122717164</v>
+        <v>122717488</v>
       </c>
       <c r="B65" t="n">
-        <v>78762</v>
+        <v>79843</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -8110,21 +8135,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -8134,10 +8159,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>520120</v>
+        <v>520000</v>
       </c>
       <c r="R65" t="n">
-        <v>7035405</v>
+        <v>7035297</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -8180,31 +8205,6 @@
       </c>
       <c r="AG65" t="b">
         <v>0</v>
-      </c>
-      <c r="AH65" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ65" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK65" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM65" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO65" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
@@ -8221,10 +8221,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122715779</v>
+        <v>122715648</v>
       </c>
       <c r="B66" t="n">
-        <v>79843</v>
+        <v>57478</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -8237,42 +8237,42 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="K66" t="inlineStr">
-        <is>
-          <t>med soral</t>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Finnbodarna, Finnbodarna, Jmt</t>
+          <t>Finnbodarna, Hammerdal, Finnbodarna, Hammerdal, Jmt</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>520223</v>
+        <v>520219</v>
       </c>
       <c r="R66" t="n">
-        <v>7035609</v>
+        <v>7035597</v>
       </c>
       <c r="S66" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -8304,6 +8304,11 @@
           <t>2025-02-23</t>
         </is>
       </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD66" t="b">
         <v>0</v>
       </c>
@@ -8312,31 +8317,6 @@
       </c>
       <c r="AG66" t="b">
         <v>0</v>
-      </c>
-      <c r="AH66" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ66" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK66" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM66" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO66" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
@@ -8353,7 +8333,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>122715648</v>
+        <v>122717636</v>
       </c>
       <c r="B67" t="n">
         <v>57478</v>
@@ -8394,14 +8374,14 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Finnbodarna, Hammerdal, Finnbodarna, Hammerdal, Jmt</t>
+          <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>520219</v>
+        <v>519970</v>
       </c>
       <c r="R67" t="n">
-        <v>7035597</v>
+        <v>7035297</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8465,10 +8445,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>122717636</v>
+        <v>122716682</v>
       </c>
       <c r="B68" t="n">
-        <v>57478</v>
+        <v>57631</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8481,27 +8461,31 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>par i lämplig häckbiotop</t>
         </is>
       </c>
       <c r="P68" t="inlineStr">
@@ -8510,10 +8494,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>519970</v>
+        <v>520101</v>
       </c>
       <c r="R68" t="n">
-        <v>7035297</v>
+        <v>7035453</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8546,11 +8530,6 @@
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-02-23</t>
-        </is>
-      </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8577,10 +8556,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>122716682</v>
+        <v>122715779</v>
       </c>
       <c r="B69" t="n">
-        <v>57631</v>
+        <v>79843</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8593,46 +8572,42 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>par i lämplig häckbiotop</t>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Spejkmyren, Spejkmyren, Jmt</t>
+          <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>520101</v>
+        <v>520223</v>
       </c>
       <c r="R69" t="n">
-        <v>7035453</v>
+        <v>7035609</v>
       </c>
       <c r="S69" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8672,6 +8647,31 @@
       </c>
       <c r="AG69" t="b">
         <v>0</v>
+      </c>
+      <c r="AH69" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ69" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK69" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM69" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO69" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
@@ -10706,10 +10706,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>122717446</v>
+        <v>122715778</v>
       </c>
       <c r="B87" t="n">
-        <v>90958</v>
+        <v>79843</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -10722,34 +10722,39 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Spejkmyren, Spejkmyren, Jmt</t>
+          <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>520006</v>
+        <v>520259</v>
       </c>
       <c r="R87" t="n">
-        <v>7035303</v>
+        <v>7035574</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10808,10 +10813,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>122720427</v>
+        <v>122717446</v>
       </c>
       <c r="B88" t="n">
-        <v>57478</v>
+        <v>90958</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -10824,39 +10829,34 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
-      <c r="M88" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P88" t="inlineStr">
         <is>
           <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>519846</v>
+        <v>520006</v>
       </c>
       <c r="R88" t="n">
-        <v>7035407</v>
+        <v>7035303</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10889,11 +10889,6 @@
       <c r="AA88" t="inlineStr">
         <is>
           <t>2025-02-23</t>
-        </is>
-      </c>
-      <c r="AC88" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10920,10 +10915,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>122715778</v>
+        <v>122720427</v>
       </c>
       <c r="B89" t="n">
-        <v>79843</v>
+        <v>57478</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -10936,39 +10931,39 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
-      <c r="K89" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Finnbodarna, Finnbodarna, Jmt</t>
+          <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>520259</v>
+        <v>519846</v>
       </c>
       <c r="R89" t="n">
-        <v>7035574</v>
+        <v>7035407</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -11001,6 +10996,11 @@
       <c r="AA89" t="inlineStr">
         <is>
           <t>2025-02-23</t>
+        </is>
+      </c>
+      <c r="AC89" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD89" t="b">

--- a/artfynd/A 1625-2025 artfynd.xlsx
+++ b/artfynd/A 1625-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122716160</v>
+        <v>122719697</v>
       </c>
       <c r="B2" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -711,17 +711,17 @@
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Finnbodarna, Finnbodarna, Jmt</t>
+          <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>520349</v>
+        <v>520026</v>
       </c>
       <c r="R2" t="n">
-        <v>7035517</v>
+        <v>7035233</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -802,10 +802,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122715573</v>
+        <v>122715669</v>
       </c>
       <c r="B3" t="n">
-        <v>79844</v>
+        <v>79847</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -818,34 +818,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>520214</v>
+        <v>520221</v>
       </c>
       <c r="R3" t="n">
-        <v>7035583</v>
+        <v>7035600</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -904,10 +909,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122715757</v>
+        <v>122715949</v>
       </c>
       <c r="B4" t="n">
-        <v>78762</v>
+        <v>79847</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -920,21 +925,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -944,10 +949,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>520234</v>
+        <v>520254</v>
       </c>
       <c r="R4" t="n">
-        <v>7035595</v>
+        <v>7035555</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -982,11 +987,6 @@
           <t>2025-02-23</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -995,31 +995,6 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1036,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122715775</v>
+        <v>122717164</v>
       </c>
       <c r="B5" t="n">
-        <v>79843</v>
+        <v>78766</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1052,39 +1027,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Finnbodarna, Finnbodarna, Jmt</t>
+          <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>520252</v>
+        <v>520120</v>
       </c>
       <c r="R5" t="n">
-        <v>7035576</v>
+        <v>7035405</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1119,11 +1089,6 @@
           <t>2025-02-23</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>På björk</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1132,6 +1097,31 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1148,10 +1138,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122715949</v>
+        <v>122720469</v>
       </c>
       <c r="B6" t="n">
-        <v>79843</v>
+        <v>78766</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1164,34 +1154,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Finnbodarna, Finnbodarna, Jmt</t>
+          <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>520254</v>
+        <v>519996</v>
       </c>
       <c r="R6" t="n">
-        <v>7035555</v>
+        <v>7035241</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1234,6 +1224,31 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1250,10 +1265,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122720474</v>
+        <v>122715795</v>
       </c>
       <c r="B7" t="n">
-        <v>57494</v>
+        <v>79847</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1266,51 +1281,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Spejkmyren, Spejkmyren, Jmt</t>
+          <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>519848</v>
+        <v>520214</v>
       </c>
       <c r="R7" t="n">
-        <v>7035394</v>
+        <v>7035599</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1342,6 +1343,11 @@
           <t>2025-02-23</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>På en klen gran intill en lunglavssälg.</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1350,6 +1356,31 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1366,10 +1397,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122715801</v>
+        <v>122719554</v>
       </c>
       <c r="B8" t="n">
-        <v>79844</v>
+        <v>57478</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1382,34 +1413,44 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Finnbodarna, Finnbodarna, Jmt</t>
+          <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>520266</v>
+        <v>519981</v>
       </c>
       <c r="R8" t="n">
-        <v>7035582</v>
+        <v>7035221</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1444,6 +1485,11 @@
           <t>2025-02-23</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Äldre ringhack som bedöms vara 5 - 10 år gamla.</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1452,6 +1498,31 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1468,10 +1539,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122720629</v>
+        <v>122715780</v>
       </c>
       <c r="B9" t="n">
-        <v>78762</v>
+        <v>79847</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1484,34 +1555,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Spejkmyren, Spejkmyren, Jmt</t>
+          <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>519935</v>
+        <v>520259</v>
       </c>
       <c r="R9" t="n">
-        <v>7035246</v>
+        <v>7035569</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1548,7 +1619,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>På björk</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1559,31 +1630,6 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1600,10 +1646,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122716850</v>
+        <v>122715779</v>
       </c>
       <c r="B10" t="n">
-        <v>90958</v>
+        <v>79847</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1616,37 +1662,42 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Spejkmyren, Spejkmyren, Jmt</t>
+          <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>520101</v>
+        <v>520223</v>
       </c>
       <c r="R10" t="n">
-        <v>7035388</v>
+        <v>7035609</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1686,6 +1737,31 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1702,10 +1778,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122716387</v>
+        <v>122717284</v>
       </c>
       <c r="B11" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1718,42 +1794,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Finnbodarna, Hammerdal, Finnbodarna, Hammerdal, Jmt</t>
+          <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>520278</v>
+        <v>520031</v>
       </c>
       <c r="R11" t="n">
-        <v>7035397</v>
+        <v>7035353</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1787,7 +1858,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Långväxta bålar på flertalet granar.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1798,6 +1869,31 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -1814,10 +1910,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122717359</v>
+        <v>122716850</v>
       </c>
       <c r="B12" t="n">
-        <v>79843</v>
+        <v>90962</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1830,21 +1926,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1854,10 +1950,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>520030</v>
+        <v>520101</v>
       </c>
       <c r="R12" t="n">
-        <v>7035341</v>
+        <v>7035388</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1916,10 +2012,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122716757</v>
+        <v>122720823</v>
       </c>
       <c r="B13" t="n">
-        <v>78762</v>
+        <v>57478</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1932,37 +2028,56 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Finnbodarna, Finnbodarna, Jmt</t>
+          <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>520316</v>
+        <v>519842</v>
       </c>
       <c r="R13" t="n">
-        <v>7035491</v>
+        <v>7035388</v>
       </c>
       <c r="S13" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1994,6 +2109,11 @@
           <t>2025-02-23</t>
         </is>
       </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Trummande</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -2002,31 +2122,6 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AH13" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
@@ -2043,10 +2138,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122716427</v>
+        <v>122716801</v>
       </c>
       <c r="B14" t="n">
-        <v>78763</v>
+        <v>57631</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2059,37 +2154,46 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>230405</v>
+        <v>103021</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Finnbodarna, Finnbodarna, Jmt</t>
+          <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>520388</v>
+        <v>520083</v>
       </c>
       <c r="R14" t="n">
-        <v>7035490</v>
+        <v>7035403</v>
       </c>
       <c r="S14" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2121,11 +2225,6 @@
           <t>2025-02-23</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2134,31 +2233,6 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
-      </c>
-      <c r="AH14" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ14" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK14" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
@@ -2175,10 +2249,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122716293</v>
+        <v>122715778</v>
       </c>
       <c r="B15" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2191,39 +2265,39 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Finnbodarna, Hammerdal, Finnbodarna, Hammerdal, Jmt</t>
+          <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>520249</v>
+        <v>520259</v>
       </c>
       <c r="R15" t="n">
-        <v>7035364</v>
+        <v>7035574</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2256,11 +2330,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-02-23</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2287,10 +2356,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122716216</v>
+        <v>122718013</v>
       </c>
       <c r="B16" t="n">
-        <v>79843</v>
+        <v>57478</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2303,39 +2372,39 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>med soral</t>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Finnbodarna, Finnbodarna, Jmt</t>
+          <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>520368</v>
+        <v>519948</v>
       </c>
       <c r="R16" t="n">
-        <v>7035513</v>
+        <v>7035313</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2372,7 +2441,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>På en gammal grovbarkad sälg.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2383,31 +2452,6 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
-      </c>
-      <c r="AH16" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
@@ -2424,10 +2468,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122715836</v>
+        <v>122720368</v>
       </c>
       <c r="B17" t="n">
-        <v>79843</v>
+        <v>57478</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2440,39 +2484,39 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Finnbodarna, Finnbodarna, Jmt</t>
+          <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>520269</v>
+        <v>519852</v>
       </c>
       <c r="R17" t="n">
-        <v>7035574</v>
+        <v>7035392</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2505,6 +2549,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-02-23</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2531,10 +2580,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122715841</v>
+        <v>122717873</v>
       </c>
       <c r="B18" t="n">
-        <v>79843</v>
+        <v>79847</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2572,17 +2621,17 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Finnbodarna, Finnbodarna, Jmt</t>
+          <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>520229</v>
+        <v>520033</v>
       </c>
       <c r="R18" t="n">
-        <v>7035608</v>
+        <v>7035301</v>
       </c>
       <c r="S18" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2614,11 +2663,6 @@
           <t>2025-02-23</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>På en björk.</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -2635,12 +2679,12 @@
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>björkar</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
@@ -2650,7 +2694,7 @@
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Betula</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2668,10 +2712,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122715868</v>
+        <v>122717468</v>
       </c>
       <c r="B19" t="n">
-        <v>79843</v>
+        <v>57494</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2684,39 +2728,43 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Finnbodarna, Finnbodarna, Jmt</t>
+          <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>520265</v>
+        <v>520020</v>
       </c>
       <c r="R19" t="n">
-        <v>7035574</v>
+        <v>7035330</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2775,10 +2823,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122717468</v>
+        <v>122715573</v>
       </c>
       <c r="B20" t="n">
-        <v>57494</v>
+        <v>79848</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2791,43 +2839,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>2081</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Spejkmyren, Spejkmyren, Jmt</t>
+          <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>520020</v>
+        <v>520214</v>
       </c>
       <c r="R20" t="n">
-        <v>7035330</v>
+        <v>7035583</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2886,10 +2925,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122720959</v>
+        <v>122717952</v>
       </c>
       <c r="B21" t="n">
-        <v>78762</v>
+        <v>57494</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2902,34 +2941,43 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>519917</v>
+        <v>519951</v>
       </c>
       <c r="R21" t="n">
-        <v>7035339</v>
+        <v>7035320</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2964,11 +3012,6 @@
           <t>2025-02-23</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Långväxta bålar på flertalet granar.</t>
-        </is>
-      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
@@ -2977,31 +3020,6 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
-      </c>
-      <c r="AH21" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -3018,10 +3036,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122715569</v>
+        <v>122715757</v>
       </c>
       <c r="B22" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3054,14 +3072,14 @@
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Djupmyren, Djupmyren, Jmt</t>
+          <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>520115</v>
+        <v>520234</v>
       </c>
       <c r="R22" t="n">
-        <v>7035562</v>
+        <v>7035595</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3150,10 +3168,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122715870</v>
+        <v>122720065</v>
       </c>
       <c r="B23" t="n">
-        <v>79844</v>
+        <v>78766</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3166,37 +3184,37 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Finnbodarna, Finnbodarna, Jmt</t>
+          <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>520265</v>
+        <v>520062</v>
       </c>
       <c r="R23" t="n">
-        <v>7035574</v>
+        <v>7035232</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3236,6 +3254,31 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM23" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
@@ -3252,10 +3295,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122717873</v>
+        <v>122719371</v>
       </c>
       <c r="B24" t="n">
-        <v>79843</v>
+        <v>78766</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3268,39 +3311,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>520033</v>
+        <v>519943</v>
       </c>
       <c r="R24" t="n">
-        <v>7035301</v>
+        <v>7035270</v>
       </c>
       <c r="S24" t="n">
         <v>8</v>
@@ -3351,22 +3389,22 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK24" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM24" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3384,10 +3422,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122715790</v>
+        <v>122715648</v>
       </c>
       <c r="B25" t="n">
-        <v>79843</v>
+        <v>57478</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3400,39 +3438,39 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Finnbodarna, Finnbodarna, Jmt</t>
+          <t>Finnbodarna, Hammerdal, Finnbodarna, Hammerdal, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>520267</v>
+        <v>520219</v>
       </c>
       <c r="R25" t="n">
-        <v>7035581</v>
+        <v>7035597</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3465,6 +3503,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-02-23</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3491,10 +3534,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122716329</v>
+        <v>122717359</v>
       </c>
       <c r="B26" t="n">
-        <v>79843</v>
+        <v>79847</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3525,24 +3568,19 @@
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Finnbodarna, Finnbodarna, Jmt</t>
+          <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>520374</v>
+        <v>520030</v>
       </c>
       <c r="R26" t="n">
-        <v>7035511</v>
+        <v>7035341</v>
       </c>
       <c r="S26" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3574,11 +3612,6 @@
           <t>2025-02-23</t>
         </is>
       </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>På gran intill en gammal lunglavssälg.</t>
-        </is>
-      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
@@ -3587,31 +3620,6 @@
       </c>
       <c r="AG26" t="b">
         <v>0</v>
-      </c>
-      <c r="AH26" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ26" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK26" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM26" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO26" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
@@ -3628,10 +3636,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122717952</v>
+        <v>122715836</v>
       </c>
       <c r="B27" t="n">
-        <v>57494</v>
+        <v>79847</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3644,43 +3652,39 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Spejkmyren, Spejkmyren, Jmt</t>
+          <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>519951</v>
+        <v>520269</v>
       </c>
       <c r="R27" t="n">
-        <v>7035320</v>
+        <v>7035574</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3739,10 +3743,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122720368</v>
+        <v>122715775</v>
       </c>
       <c r="B28" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3755,39 +3759,39 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Spejkmyren, Spejkmyren, Jmt</t>
+          <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>519852</v>
+        <v>520252</v>
       </c>
       <c r="R28" t="n">
-        <v>7035392</v>
+        <v>7035576</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3824,7 +3828,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>På björk</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3851,10 +3855,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122716303</v>
+        <v>122715756</v>
       </c>
       <c r="B29" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3867,39 +3871,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Finnbodarna, Hammerdal, Finnbodarna, Hammerdal, Jmt</t>
+          <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>520250</v>
+        <v>520256</v>
       </c>
       <c r="R29" t="n">
-        <v>7035363</v>
+        <v>7035593</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3932,11 +3931,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-02-23</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3963,7 +3957,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122719829</v>
+        <v>122719614</v>
       </c>
       <c r="B30" t="n">
         <v>57478</v>
@@ -3999,7 +3993,7 @@
       <c r="I30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -4048,7 +4042,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Färska och äldre ringhack på samma gran.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4075,7 +4069,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122717343</v>
+        <v>122716293</v>
       </c>
       <c r="B31" t="n">
         <v>57478</v>
@@ -4116,14 +4110,14 @@
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Spejkmyren, Spejkmyren, Jmt</t>
+          <t>Finnbodarna, Hammerdal, Finnbodarna, Hammerdal, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>520034</v>
+        <v>520249</v>
       </c>
       <c r="R31" t="n">
-        <v>7035339</v>
+        <v>7035364</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4187,10 +4181,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122720686</v>
+        <v>122717446</v>
       </c>
       <c r="B32" t="n">
-        <v>78762</v>
+        <v>90962</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4203,21 +4197,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4227,10 +4221,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>519903</v>
+        <v>520006</v>
       </c>
       <c r="R32" t="n">
-        <v>7035224</v>
+        <v>7035303</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4273,31 +4267,6 @@
       </c>
       <c r="AG32" t="b">
         <v>0</v>
-      </c>
-      <c r="AH32" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ32" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK32" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM32" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO32" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
@@ -4314,10 +4283,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122715978</v>
+        <v>122720686</v>
       </c>
       <c r="B33" t="n">
-        <v>79843</v>
+        <v>78766</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4330,39 +4299,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Finnbodarna, Finnbodarna, Jmt</t>
+          <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>520243</v>
+        <v>519903</v>
       </c>
       <c r="R33" t="n">
-        <v>7035552</v>
+        <v>7035224</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4405,6 +4369,31 @@
       </c>
       <c r="AG33" t="b">
         <v>0</v>
+      </c>
+      <c r="AH33" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM33" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
@@ -4421,10 +4410,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122720327</v>
+        <v>122716329</v>
       </c>
       <c r="B34" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4437,42 +4426,42 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Spejkmyren, Spejkmyren, Jmt</t>
+          <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>519838</v>
+        <v>520374</v>
       </c>
       <c r="R34" t="n">
-        <v>7035393</v>
+        <v>7035511</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4506,7 +4495,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>På gran intill en gammal lunglavssälg.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4517,6 +4506,31 @@
       </c>
       <c r="AG34" t="b">
         <v>0</v>
+      </c>
+      <c r="AH34" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ34" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK34" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM34" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO34" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
@@ -4533,10 +4547,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122720889</v>
+        <v>122715677</v>
       </c>
       <c r="B35" t="n">
-        <v>57478</v>
+        <v>79848</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4549,39 +4563,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Spejkmyren, Spejkmyren, Jmt</t>
+          <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>519841</v>
+        <v>520221</v>
       </c>
       <c r="R35" t="n">
-        <v>7035390</v>
+        <v>7035600</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4618,7 +4627,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4645,10 +4654,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122716964</v>
+        <v>122716443</v>
       </c>
       <c r="B36" t="n">
-        <v>90958</v>
+        <v>78766</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4661,34 +4670,48 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Spejkmyren, Spejkmyren, Jmt</t>
+          <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>520115</v>
+        <v>520251</v>
       </c>
       <c r="R36" t="n">
-        <v>7035402</v>
+        <v>7035394</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4721,6 +4744,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-02-23</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Garnlavsrikt</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4747,10 +4775,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122720065</v>
+        <v>122720959</v>
       </c>
       <c r="B37" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4787,13 +4815,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>520062</v>
+        <v>519917</v>
       </c>
       <c r="R37" t="n">
-        <v>7035232</v>
+        <v>7035339</v>
       </c>
       <c r="S37" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4823,6 +4851,11 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-02-23</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Långväxta bålar på flertalet granar.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4874,10 +4907,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122715934</v>
+        <v>122715790</v>
       </c>
       <c r="B38" t="n">
-        <v>78762</v>
+        <v>79847</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4890,37 +4923,42 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>520303</v>
+        <v>520267</v>
       </c>
       <c r="R38" t="n">
-        <v>7035598</v>
+        <v>7035581</v>
       </c>
       <c r="S38" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4952,11 +4990,6 @@
           <t>2025-02-23</t>
         </is>
       </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
-        </is>
-      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
@@ -4965,31 +4998,6 @@
       </c>
       <c r="AG38" t="b">
         <v>0</v>
-      </c>
-      <c r="AH38" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ38" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK38" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM38" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO38" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
@@ -5006,10 +5014,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122715756</v>
+        <v>122716303</v>
       </c>
       <c r="B39" t="n">
-        <v>79843</v>
+        <v>57478</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5022,34 +5030,39 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Finnbodarna, Finnbodarna, Jmt</t>
+          <t>Finnbodarna, Hammerdal, Finnbodarna, Hammerdal, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>520256</v>
+        <v>520250</v>
       </c>
       <c r="R39" t="n">
-        <v>7035593</v>
+        <v>7035363</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5082,6 +5095,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-02-23</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5108,7 +5126,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122716645</v>
+        <v>122720889</v>
       </c>
       <c r="B40" t="n">
         <v>57478</v>
@@ -5153,10 +5171,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>520129</v>
+        <v>519841</v>
       </c>
       <c r="R40" t="n">
-        <v>7035444</v>
+        <v>7035390</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5220,10 +5238,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122716295</v>
+        <v>122720427</v>
       </c>
       <c r="B41" t="n">
-        <v>79843</v>
+        <v>57478</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5236,39 +5254,39 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Finnbodarna, Finnbodarna, Jmt</t>
+          <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>520378</v>
+        <v>519846</v>
       </c>
       <c r="R41" t="n">
-        <v>7035512</v>
+        <v>7035407</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5305,7 +5323,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Ymnig påväxt på en grovbarkad gammal sälg. Fertila bålar med apothecier.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5316,31 +5334,6 @@
       </c>
       <c r="AG41" t="b">
         <v>0</v>
-      </c>
-      <c r="AH41" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ41" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK41" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM41" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO41" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
@@ -5357,10 +5350,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122716392</v>
+        <v>122716673</v>
       </c>
       <c r="B42" t="n">
-        <v>79844</v>
+        <v>57478</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5373,42 +5366,42 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>med soral</t>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Finnbodarna, Finnbodarna, Jmt</t>
+          <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>520385</v>
+        <v>520108</v>
       </c>
       <c r="R42" t="n">
-        <v>7035518</v>
+        <v>7035462</v>
       </c>
       <c r="S42" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5442,7 +5435,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>På gran intill en gammal sälg.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5453,31 +5446,6 @@
       </c>
       <c r="AG42" t="b">
         <v>0</v>
-      </c>
-      <c r="AH42" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ42" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK42" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM42" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO42" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
@@ -5494,10 +5462,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122720469</v>
+        <v>122721463</v>
       </c>
       <c r="B43" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5534,10 +5502,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>519996</v>
+        <v>519841</v>
       </c>
       <c r="R43" t="n">
-        <v>7035241</v>
+        <v>7035417</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5570,6 +5538,11 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-02-23</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5621,10 +5594,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122717284</v>
+        <v>122721333</v>
       </c>
       <c r="B44" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5661,13 +5634,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>520031</v>
+        <v>519906</v>
       </c>
       <c r="R44" t="n">
-        <v>7035353</v>
+        <v>7035389</v>
       </c>
       <c r="S44" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5701,7 +5674,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Långväxta bålar på flertalet granar.</t>
+          <t>Ymnigt på flera granar.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5753,10 +5726,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122716801</v>
+        <v>122715569</v>
       </c>
       <c r="B45" t="n">
-        <v>57631</v>
+        <v>78766</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5769,43 +5742,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>par i lämplig häckbiotop</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Spejkmyren, Spejkmyren, Jmt</t>
+          <t>Djupmyren, Djupmyren, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>520083</v>
+        <v>520115</v>
       </c>
       <c r="R45" t="n">
-        <v>7035403</v>
+        <v>7035562</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5840,6 +5804,11 @@
           <t>2025-02-23</t>
         </is>
       </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
+        </is>
+      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
@@ -5848,6 +5817,31 @@
       </c>
       <c r="AG45" t="b">
         <v>0</v>
+      </c>
+      <c r="AH45" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ45" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK45" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM45" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO45" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
@@ -5864,10 +5858,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122715677</v>
+        <v>122717488</v>
       </c>
       <c r="B46" t="n">
-        <v>79844</v>
+        <v>79847</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5880,34 +5874,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Finnbodarna, Finnbodarna, Jmt</t>
+          <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>520221</v>
+        <v>520000</v>
       </c>
       <c r="R46" t="n">
-        <v>7035600</v>
+        <v>7035297</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5940,11 +5934,6 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-02-23</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>På gran</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5971,10 +5960,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122716443</v>
+        <v>122716269</v>
       </c>
       <c r="B47" t="n">
-        <v>78762</v>
+        <v>57478</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5987,48 +5976,39 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Finnbodarna, Finnbodarna, Jmt</t>
+          <t>Finnbodarna, Hammerdal, Finnbodarna, Hammerdal, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>520251</v>
+        <v>520256</v>
       </c>
       <c r="R47" t="n">
-        <v>7035394</v>
+        <v>7035380</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6065,7 +6045,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Garnlavsrikt</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6092,10 +6072,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122715766</v>
+        <v>122720281</v>
       </c>
       <c r="B48" t="n">
-        <v>90958</v>
+        <v>57478</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6108,34 +6088,39 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Finnbodarna, Finnbodarna, Jmt</t>
+          <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>520252</v>
+        <v>519850</v>
       </c>
       <c r="R48" t="n">
-        <v>7035591</v>
+        <v>7035373</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6168,6 +6153,11 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-02-23</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6194,7 +6184,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122719648</v>
+        <v>122717636</v>
       </c>
       <c r="B49" t="n">
         <v>57478</v>
@@ -6239,10 +6229,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>519939</v>
+        <v>519970</v>
       </c>
       <c r="R49" t="n">
-        <v>7035194</v>
+        <v>7035297</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6306,10 +6296,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122719979</v>
+        <v>122716387</v>
       </c>
       <c r="B50" t="n">
-        <v>57631</v>
+        <v>57478</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6322,43 +6312,39 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="M50" t="inlineStr">
         <is>
-          <t>par i lämplig häckbiotop</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Spejkmyren, Spejkmyren, Jmt</t>
+          <t>Finnbodarna, Hammerdal, Finnbodarna, Hammerdal, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>519946</v>
+        <v>520278</v>
       </c>
       <c r="R50" t="n">
-        <v>7035240</v>
+        <v>7035397</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6391,6 +6377,11 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-02-23</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6417,10 +6408,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122720558</v>
+        <v>122715953</v>
       </c>
       <c r="B51" t="n">
-        <v>57494</v>
+        <v>79848</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6433,39 +6424,34 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100049</v>
+        <v>2081</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Spejkmyren, Spejkmyren, Jmt</t>
+          <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>519949</v>
+        <v>520254</v>
       </c>
       <c r="R51" t="n">
-        <v>7035254</v>
+        <v>7035555</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6500,11 +6486,6 @@
           <t>2025-02-23</t>
         </is>
       </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Äldre hackspår i stambasen.</t>
-        </is>
-      </c>
       <c r="AD51" t="b">
         <v>0</v>
       </c>
@@ -6513,31 +6494,6 @@
       </c>
       <c r="AG51" t="b">
         <v>0</v>
-      </c>
-      <c r="AH51" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ51" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK51" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM51" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO51" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
@@ -6554,10 +6510,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122716673</v>
+        <v>122716682</v>
       </c>
       <c r="B52" t="n">
-        <v>57478</v>
+        <v>57631</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6570,27 +6526,31 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>par i lämplig häckbiotop</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
@@ -6599,10 +6559,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>520108</v>
+        <v>520101</v>
       </c>
       <c r="R52" t="n">
-        <v>7035462</v>
+        <v>7035453</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6635,11 +6595,6 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-02-23</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6666,10 +6621,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122717616</v>
+        <v>122719875</v>
       </c>
       <c r="B53" t="n">
-        <v>78762</v>
+        <v>57478</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6682,34 +6637,39 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>520019</v>
+        <v>519983</v>
       </c>
       <c r="R53" t="n">
-        <v>7035352</v>
+        <v>7035206</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6746,7 +6706,7 @@
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>Rikligt.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6757,31 +6717,6 @@
       </c>
       <c r="AG53" t="b">
         <v>0</v>
-      </c>
-      <c r="AH53" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ53" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK53" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM53" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO53" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
@@ -6798,10 +6733,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122721333</v>
+        <v>122719979</v>
       </c>
       <c r="B54" t="n">
-        <v>78762</v>
+        <v>57631</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6814,37 +6749,46 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>519906</v>
+        <v>519946</v>
       </c>
       <c r="R54" t="n">
-        <v>7035389</v>
+        <v>7035240</v>
       </c>
       <c r="S54" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6876,11 +6820,6 @@
           <t>2025-02-23</t>
         </is>
       </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Ymnigt på flera granar.</t>
-        </is>
-      </c>
       <c r="AD54" t="b">
         <v>0</v>
       </c>
@@ -6889,31 +6828,6 @@
       </c>
       <c r="AG54" t="b">
         <v>0</v>
-      </c>
-      <c r="AH54" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ54" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK54" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM54" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO54" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
@@ -6930,10 +6844,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122720548</v>
+        <v>122716427</v>
       </c>
       <c r="B55" t="n">
-        <v>90958</v>
+        <v>78767</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6946,37 +6860,37 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>5432</v>
+        <v>230405</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Spejkmyren, Spejkmyren, Jmt</t>
+          <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>519847</v>
+        <v>520388</v>
       </c>
       <c r="R55" t="n">
-        <v>7035432</v>
+        <v>7035490</v>
       </c>
       <c r="S55" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -7008,6 +6922,11 @@
           <t>2025-02-23</t>
         </is>
       </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
+        </is>
+      </c>
       <c r="AD55" t="b">
         <v>0</v>
       </c>
@@ -7016,6 +6935,31 @@
       </c>
       <c r="AG55" t="b">
         <v>0</v>
+      </c>
+      <c r="AH55" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ55" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK55" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM55" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO55" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
@@ -7032,10 +6976,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122716269</v>
+        <v>122721035</v>
       </c>
       <c r="B56" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -7048,42 +6992,37 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Finnbodarna, Hammerdal, Finnbodarna, Hammerdal, Jmt</t>
+          <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>520256</v>
+        <v>519897</v>
       </c>
       <c r="R56" t="n">
-        <v>7035380</v>
+        <v>7035374</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -7115,11 +7054,6 @@
           <t>2025-02-23</t>
         </is>
       </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD56" t="b">
         <v>0</v>
       </c>
@@ -7128,6 +7062,31 @@
       </c>
       <c r="AG56" t="b">
         <v>0</v>
+      </c>
+      <c r="AH56" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ56" t="inlineStr">
+        <is>
+          <t>garnlav</t>
+        </is>
+      </c>
+      <c r="AK56" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="AM56" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO56" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Alectoria sarmentosa</t>
+        </is>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
@@ -7144,10 +7103,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122715874</v>
+        <v>122715999</v>
       </c>
       <c r="B57" t="n">
-        <v>79872</v>
+        <v>78766</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -7156,25 +7115,25 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -7184,13 +7143,13 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>520265</v>
+        <v>520311</v>
       </c>
       <c r="R57" t="n">
-        <v>7035574</v>
+        <v>7035566</v>
       </c>
       <c r="S57" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -7230,6 +7189,31 @@
       </c>
       <c r="AG57" t="b">
         <v>0</v>
+      </c>
+      <c r="AH57" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ57" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK57" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM57" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO57" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
@@ -7246,10 +7230,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122716234</v>
+        <v>122720629</v>
       </c>
       <c r="B58" t="n">
-        <v>79843</v>
+        <v>78766</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7262,34 +7246,34 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Finnbodarna, Finnbodarna, Jmt</t>
+          <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>520362</v>
+        <v>519935</v>
       </c>
       <c r="R58" t="n">
-        <v>7035500</v>
+        <v>7035246</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7326,7 +7310,7 @@
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>På en klen gran intill en gammal sälg med lunglav.</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7378,10 +7362,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122717294</v>
+        <v>122720327</v>
       </c>
       <c r="B59" t="n">
-        <v>90958</v>
+        <v>57478</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7394,34 +7378,39 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>520013</v>
+        <v>519838</v>
       </c>
       <c r="R59" t="n">
-        <v>7035340</v>
+        <v>7035393</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7454,6 +7443,11 @@
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-02-23</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7480,10 +7474,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122715795</v>
+        <v>122715978</v>
       </c>
       <c r="B60" t="n">
-        <v>79843</v>
+        <v>79847</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7514,19 +7508,24 @@
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>520214</v>
+        <v>520243</v>
       </c>
       <c r="R60" t="n">
-        <v>7035599</v>
+        <v>7035552</v>
       </c>
       <c r="S60" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7558,11 +7557,6 @@
           <t>2025-02-23</t>
         </is>
       </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>På en klen gran intill en lunglavssälg.</t>
-        </is>
-      </c>
       <c r="AD60" t="b">
         <v>0</v>
       </c>
@@ -7571,31 +7565,6 @@
       </c>
       <c r="AG60" t="b">
         <v>0</v>
-      </c>
-      <c r="AH60" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ60" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK60" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM60" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO60" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
@@ -7612,10 +7581,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122720823</v>
+        <v>122716295</v>
       </c>
       <c r="B61" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7628,53 +7597,39 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
       <c r="K61" t="inlineStr">
         <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L61" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Spejkmyren, Spejkmyren, Jmt</t>
+          <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>519842</v>
+        <v>520378</v>
       </c>
       <c r="R61" t="n">
-        <v>7035388</v>
+        <v>7035512</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7711,7 +7666,7 @@
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>Trummande</t>
+          <t>Ymnig påväxt på en grovbarkad gammal sälg. Fertila bålar med apothecier.</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7722,6 +7677,31 @@
       </c>
       <c r="AG61" t="b">
         <v>0</v>
+      </c>
+      <c r="AH61" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ61" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK61" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM61" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO61" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
@@ -7738,10 +7718,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122719554</v>
+        <v>122715502</v>
       </c>
       <c r="B62" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7754,47 +7734,42 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N62" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Spejkmyren, Spejkmyren, Jmt</t>
+          <t>Djupmyren, Djupmyren, Jmt</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>519981</v>
+        <v>520110</v>
       </c>
       <c r="R62" t="n">
-        <v>7035221</v>
+        <v>7035585</v>
       </c>
       <c r="S62" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7828,7 +7803,7 @@
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>Äldre ringhack som bedöms vara 5 - 10 år gamla.</t>
+          <t>Gott om långväxt garnlav på många granar. Vissa bålar är här fertila.</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7857,12 +7832,12 @@
       </c>
       <c r="AM62" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO62" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT62" t="inlineStr"/>
@@ -7880,10 +7855,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122719533</v>
+        <v>122716757</v>
       </c>
       <c r="B63" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7896,42 +7871,37 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Spejkmyren, Spejkmyren, Jmt</t>
+          <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>519948</v>
+        <v>520316</v>
       </c>
       <c r="R63" t="n">
-        <v>7035187</v>
+        <v>7035491</v>
       </c>
       <c r="S63" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7963,11 +7933,6 @@
           <t>2025-02-23</t>
         </is>
       </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD63" t="b">
         <v>0</v>
       </c>
@@ -7976,6 +7941,31 @@
       </c>
       <c r="AG63" t="b">
         <v>0</v>
+      </c>
+      <c r="AH63" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ63" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK63" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM63" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO63" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
@@ -7992,10 +7982,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122717164</v>
+        <v>122720558</v>
       </c>
       <c r="B64" t="n">
-        <v>78762</v>
+        <v>57494</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -8008,34 +7998,39 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
           <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>520120</v>
+        <v>519949</v>
       </c>
       <c r="R64" t="n">
-        <v>7035405</v>
+        <v>7035254</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -8070,6 +8065,11 @@
           <t>2025-02-23</t>
         </is>
       </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Äldre hackspår i stambasen.</t>
+        </is>
+      </c>
       <c r="AD64" t="b">
         <v>0</v>
       </c>
@@ -8096,12 +8096,12 @@
       </c>
       <c r="AM64" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO64" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT64" t="inlineStr"/>
@@ -8119,10 +8119,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122717488</v>
+        <v>122716645</v>
       </c>
       <c r="B65" t="n">
-        <v>79843</v>
+        <v>57478</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -8135,34 +8135,39 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>520000</v>
+        <v>520129</v>
       </c>
       <c r="R65" t="n">
-        <v>7035297</v>
+        <v>7035444</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -8195,6 +8200,11 @@
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-02-23</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8221,10 +8231,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122715648</v>
+        <v>122715841</v>
       </c>
       <c r="B66" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -8237,42 +8247,42 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Finnbodarna, Hammerdal, Finnbodarna, Hammerdal, Jmt</t>
+          <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>520219</v>
+        <v>520229</v>
       </c>
       <c r="R66" t="n">
-        <v>7035597</v>
+        <v>7035608</v>
       </c>
       <c r="S66" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -8306,7 +8316,7 @@
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>På en björk.</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8317,6 +8327,31 @@
       </c>
       <c r="AG66" t="b">
         <v>0</v>
+      </c>
+      <c r="AH66" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ66" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK66" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AM66" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO66" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Betula</t>
+        </is>
       </c>
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
@@ -8333,10 +8368,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>122717636</v>
+        <v>122717294</v>
       </c>
       <c r="B67" t="n">
-        <v>57478</v>
+        <v>90962</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8349,39 +8384,34 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>519970</v>
+        <v>520013</v>
       </c>
       <c r="R67" t="n">
-        <v>7035297</v>
+        <v>7035340</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8414,11 +8444,6 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-02-23</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8445,10 +8470,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>122716682</v>
+        <v>122717616</v>
       </c>
       <c r="B68" t="n">
-        <v>57631</v>
+        <v>78766</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8461,43 +8486,34 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>par i lämplig häckbiotop</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>520101</v>
+        <v>520019</v>
       </c>
       <c r="R68" t="n">
-        <v>7035453</v>
+        <v>7035352</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8532,6 +8548,11 @@
           <t>2025-02-23</t>
         </is>
       </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Rikligt.</t>
+        </is>
+      </c>
       <c r="AD68" t="b">
         <v>0</v>
       </c>
@@ -8540,6 +8561,31 @@
       </c>
       <c r="AG68" t="b">
         <v>0</v>
+      </c>
+      <c r="AH68" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ68" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK68" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM68" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO68" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
@@ -8556,10 +8602,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>122715779</v>
+        <v>122715849</v>
       </c>
       <c r="B69" t="n">
-        <v>79843</v>
+        <v>79876</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8568,46 +8614,41 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="K69" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>520223</v>
+        <v>520268</v>
       </c>
       <c r="R69" t="n">
-        <v>7035609</v>
+        <v>7035575</v>
       </c>
       <c r="S69" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8647,31 +8688,6 @@
       </c>
       <c r="AG69" t="b">
         <v>0</v>
-      </c>
-      <c r="AH69" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ69" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK69" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM69" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO69" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
@@ -8688,10 +8704,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>122720281</v>
+        <v>122720474</v>
       </c>
       <c r="B70" t="n">
-        <v>57478</v>
+        <v>57494</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8704,16 +8720,16 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -8721,10 +8737,19 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I70" t="inlineStr"/>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P70" t="inlineStr">
@@ -8733,10 +8758,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>519850</v>
+        <v>519848</v>
       </c>
       <c r="R70" t="n">
-        <v>7035373</v>
+        <v>7035394</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8769,11 +8794,6 @@
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-02-23</t>
-        </is>
-      </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8800,7 +8820,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>122720454</v>
+        <v>122719533</v>
       </c>
       <c r="B71" t="n">
         <v>57478</v>
@@ -8845,10 +8865,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>519849</v>
+        <v>519948</v>
       </c>
       <c r="R71" t="n">
-        <v>7035406</v>
+        <v>7035187</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8912,10 +8932,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>122715953</v>
+        <v>122715934</v>
       </c>
       <c r="B72" t="n">
-        <v>79844</v>
+        <v>78766</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8928,21 +8948,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8952,13 +8972,13 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>520254</v>
+        <v>520303</v>
       </c>
       <c r="R72" t="n">
-        <v>7035555</v>
+        <v>7035598</v>
       </c>
       <c r="S72" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8990,6 +9010,11 @@
           <t>2025-02-23</t>
         </is>
       </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
+        </is>
+      </c>
       <c r="AD72" t="b">
         <v>0</v>
       </c>
@@ -8998,6 +9023,31 @@
       </c>
       <c r="AG72" t="b">
         <v>0</v>
+      </c>
+      <c r="AH72" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ72" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK72" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM72" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO72" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
@@ -9014,10 +9064,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>122721463</v>
+        <v>122720869</v>
       </c>
       <c r="B73" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -9054,10 +9104,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>519841</v>
+        <v>519960</v>
       </c>
       <c r="R73" t="n">
-        <v>7035417</v>
+        <v>7035342</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -9090,11 +9140,6 @@
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-02-23</t>
-        </is>
-      </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -9146,10 +9191,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>122715669</v>
+        <v>122715571</v>
       </c>
       <c r="B74" t="n">
-        <v>79843</v>
+        <v>79847</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -9180,21 +9225,16 @@
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
-      <c r="K74" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P74" t="inlineStr">
         <is>
           <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>520221</v>
+        <v>520216</v>
       </c>
       <c r="R74" t="n">
-        <v>7035600</v>
+        <v>7035583</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -9253,10 +9293,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>122715849</v>
+        <v>122716234</v>
       </c>
       <c r="B75" t="n">
-        <v>79872</v>
+        <v>79847</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -9265,25 +9305,25 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -9293,10 +9333,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>520268</v>
+        <v>520362</v>
       </c>
       <c r="R75" t="n">
-        <v>7035575</v>
+        <v>7035500</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -9331,6 +9371,11 @@
           <t>2025-02-23</t>
         </is>
       </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>På en klen gran intill en gammal sälg med lunglav.</t>
+        </is>
+      </c>
       <c r="AD75" t="b">
         <v>0</v>
       </c>
@@ -9339,6 +9384,31 @@
       </c>
       <c r="AG75" t="b">
         <v>0</v>
+      </c>
+      <c r="AH75" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK75" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM75" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO75" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
@@ -9355,10 +9425,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>122715780</v>
+        <v>122716392</v>
       </c>
       <c r="B76" t="n">
-        <v>79843</v>
+        <v>79848</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -9371,37 +9441,42 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P76" t="inlineStr">
         <is>
           <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>520259</v>
+        <v>520385</v>
       </c>
       <c r="R76" t="n">
-        <v>7035569</v>
+        <v>7035518</v>
       </c>
       <c r="S76" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -9435,7 +9510,7 @@
       </c>
       <c r="AC76" t="inlineStr">
         <is>
-          <t>På björk</t>
+          <t>På gran intill en gammal sälg.</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9446,6 +9521,31 @@
       </c>
       <c r="AG76" t="b">
         <v>0</v>
+      </c>
+      <c r="AH76" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ76" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK76" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM76" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO76" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
@@ -9462,10 +9562,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>122717929</v>
+        <v>122719648</v>
       </c>
       <c r="B77" t="n">
-        <v>79872</v>
+        <v>57478</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -9474,31 +9574,31 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
-      <c r="K77" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P77" t="inlineStr">
@@ -9507,13 +9607,13 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>520029</v>
+        <v>519939</v>
       </c>
       <c r="R77" t="n">
-        <v>7035292</v>
+        <v>7035194</v>
       </c>
       <c r="S77" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -9545,6 +9645,11 @@
           <t>2025-02-23</t>
         </is>
       </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD77" t="b">
         <v>0</v>
       </c>
@@ -9553,31 +9658,6 @@
       </c>
       <c r="AG77" t="b">
         <v>0</v>
-      </c>
-      <c r="AH77" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ77" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK77" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM77" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO77" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
@@ -9594,10 +9674,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>122719371</v>
+        <v>122716547</v>
       </c>
       <c r="B78" t="n">
-        <v>78762</v>
+        <v>98261</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -9606,38 +9686,52 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>504</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Spejkmyren, Spejkmyren, Jmt</t>
+          <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>519943</v>
+        <v>520386</v>
       </c>
       <c r="R78" t="n">
-        <v>7035270</v>
+        <v>7035492</v>
       </c>
       <c r="S78" t="n">
         <v>8</v>
@@ -9672,6 +9766,11 @@
           <t>2025-02-23</t>
         </is>
       </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>En vinterståndare på till synes fuktig mark i en lucka.</t>
+        </is>
+      </c>
       <c r="AD78" t="b">
         <v>0</v>
       </c>
@@ -9684,26 +9783,6 @@
       <c r="AH78" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ78" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK78" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM78" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO78" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT78" t="inlineStr"/>
@@ -9721,10 +9800,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>122719697</v>
+        <v>122716160</v>
       </c>
       <c r="B79" t="n">
-        <v>78762</v>
+        <v>78766</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -9757,17 +9836,17 @@
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Spejkmyren, Spejkmyren, Jmt</t>
+          <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>520026</v>
+        <v>520349</v>
       </c>
       <c r="R79" t="n">
-        <v>7035233</v>
+        <v>7035517</v>
       </c>
       <c r="S79" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -9848,10 +9927,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>122715571</v>
+        <v>122716216</v>
       </c>
       <c r="B80" t="n">
-        <v>79843</v>
+        <v>79847</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -9882,16 +9961,21 @@
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P80" t="inlineStr">
         <is>
           <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>520216</v>
+        <v>520368</v>
       </c>
       <c r="R80" t="n">
-        <v>7035583</v>
+        <v>7035513</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9926,6 +10010,11 @@
           <t>2025-02-23</t>
         </is>
       </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>På en gammal grovbarkad sälg.</t>
+        </is>
+      </c>
       <c r="AD80" t="b">
         <v>0</v>
       </c>
@@ -9934,6 +10023,31 @@
       </c>
       <c r="AG80" t="b">
         <v>0</v>
+      </c>
+      <c r="AH80" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ80" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK80" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM80" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO80" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
@@ -9950,10 +10064,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>122720869</v>
+        <v>122715874</v>
       </c>
       <c r="B81" t="n">
-        <v>78762</v>
+        <v>79876</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9962,38 +10076,38 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Spejkmyren, Spejkmyren, Jmt</t>
+          <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>519960</v>
+        <v>520265</v>
       </c>
       <c r="R81" t="n">
-        <v>7035342</v>
+        <v>7035574</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -10036,31 +10150,6 @@
       </c>
       <c r="AG81" t="b">
         <v>0</v>
-      </c>
-      <c r="AH81" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ81" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK81" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM81" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO81" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
@@ -10077,10 +10166,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>122716547</v>
+        <v>122715801</v>
       </c>
       <c r="B82" t="n">
-        <v>98253</v>
+        <v>79848</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -10089,55 +10178,41 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>504</v>
+        <v>2081</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J82" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K82" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
           <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>520386</v>
+        <v>520266</v>
       </c>
       <c r="R82" t="n">
-        <v>7035492</v>
+        <v>7035582</v>
       </c>
       <c r="S82" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -10169,11 +10244,6 @@
           <t>2025-02-23</t>
         </is>
       </c>
-      <c r="AC82" t="inlineStr">
-        <is>
-          <t>En vinterståndare på till synes fuktig mark i en lucka.</t>
-        </is>
-      </c>
       <c r="AD82" t="b">
         <v>0</v>
       </c>
@@ -10182,11 +10252,6 @@
       </c>
       <c r="AG82" t="b">
         <v>0</v>
-      </c>
-      <c r="AH82" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
@@ -10203,10 +10268,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>122721035</v>
+        <v>122717343</v>
       </c>
       <c r="B83" t="n">
-        <v>78762</v>
+        <v>57478</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -10219,37 +10284,42 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P83" t="inlineStr">
         <is>
           <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>519897</v>
+        <v>520034</v>
       </c>
       <c r="R83" t="n">
-        <v>7035374</v>
+        <v>7035339</v>
       </c>
       <c r="S83" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -10281,6 +10351,11 @@
           <t>2025-02-23</t>
         </is>
       </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD83" t="b">
         <v>0</v>
       </c>
@@ -10289,31 +10364,6 @@
       </c>
       <c r="AG83" t="b">
         <v>0</v>
-      </c>
-      <c r="AH83" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ83" t="inlineStr">
-        <is>
-          <t>garnlav</t>
-        </is>
-      </c>
-      <c r="AK83" t="inlineStr">
-        <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="AM83" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO83" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Alectoria sarmentosa</t>
-        </is>
       </c>
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
@@ -10330,10 +10380,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>122715502</v>
+        <v>122716964</v>
       </c>
       <c r="B84" t="n">
-        <v>78762</v>
+        <v>90962</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -10346,42 +10396,37 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
-      <c r="K84" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Djupmyren, Djupmyren, Jmt</t>
+          <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>520110</v>
+        <v>520115</v>
       </c>
       <c r="R84" t="n">
-        <v>7035585</v>
+        <v>7035402</v>
       </c>
       <c r="S84" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -10413,11 +10458,6 @@
           <t>2025-02-23</t>
         </is>
       </c>
-      <c r="AC84" t="inlineStr">
-        <is>
-          <t>Gott om långväxt garnlav på många granar. Vissa bålar är här fertila.</t>
-        </is>
-      </c>
       <c r="AD84" t="b">
         <v>0</v>
       </c>
@@ -10426,31 +10466,6 @@
       </c>
       <c r="AG84" t="b">
         <v>0</v>
-      </c>
-      <c r="AH84" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ84" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK84" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM84" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO84" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
@@ -10467,10 +10482,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>122715999</v>
+        <v>122715868</v>
       </c>
       <c r="B85" t="n">
-        <v>78762</v>
+        <v>79847</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -10483,37 +10498,42 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P85" t="inlineStr">
         <is>
           <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>520311</v>
+        <v>520265</v>
       </c>
       <c r="R85" t="n">
-        <v>7035566</v>
+        <v>7035574</v>
       </c>
       <c r="S85" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -10553,31 +10573,6 @@
       </c>
       <c r="AG85" t="b">
         <v>0</v>
-      </c>
-      <c r="AH85" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ85" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK85" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM85" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO85" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
@@ -10594,7 +10589,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>122719875</v>
+        <v>122720454</v>
       </c>
       <c r="B86" t="n">
         <v>57478</v>
@@ -10639,10 +10634,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>519983</v>
+        <v>519849</v>
       </c>
       <c r="R86" t="n">
-        <v>7035206</v>
+        <v>7035406</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -10706,10 +10701,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>122715778</v>
+        <v>122720548</v>
       </c>
       <c r="B87" t="n">
-        <v>79843</v>
+        <v>90962</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -10722,39 +10717,34 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
-      <c r="K87" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Finnbodarna, Finnbodarna, Jmt</t>
+          <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>520259</v>
+        <v>519847</v>
       </c>
       <c r="R87" t="n">
-        <v>7035574</v>
+        <v>7035432</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10813,10 +10803,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>122717446</v>
+        <v>122715766</v>
       </c>
       <c r="B88" t="n">
-        <v>90958</v>
+        <v>90962</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -10849,14 +10839,14 @@
       <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Spejkmyren, Spejkmyren, Jmt</t>
+          <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>520006</v>
+        <v>520252</v>
       </c>
       <c r="R88" t="n">
-        <v>7035303</v>
+        <v>7035591</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10915,10 +10905,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>122720427</v>
+        <v>122717929</v>
       </c>
       <c r="B89" t="n">
-        <v>57478</v>
+        <v>79876</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -10927,31 +10917,31 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
-      <c r="M89" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P89" t="inlineStr">
@@ -10960,13 +10950,13 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>519846</v>
+        <v>520029</v>
       </c>
       <c r="R89" t="n">
-        <v>7035407</v>
+        <v>7035292</v>
       </c>
       <c r="S89" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -10998,11 +10988,6 @@
           <t>2025-02-23</t>
         </is>
       </c>
-      <c r="AC89" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD89" t="b">
         <v>0</v>
       </c>
@@ -11011,6 +10996,31 @@
       </c>
       <c r="AG89" t="b">
         <v>0</v>
+      </c>
+      <c r="AH89" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ89" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK89" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM89" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO89" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
@@ -11027,10 +11037,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>122718013</v>
+        <v>122715870</v>
       </c>
       <c r="B90" t="n">
-        <v>57478</v>
+        <v>79848</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -11043,39 +11053,34 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
-      <c r="M90" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Spejkmyren, Spejkmyren, Jmt</t>
+          <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>519948</v>
+        <v>520265</v>
       </c>
       <c r="R90" t="n">
-        <v>7035313</v>
+        <v>7035574</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -11108,11 +11113,6 @@
       <c r="AA90" t="inlineStr">
         <is>
           <t>2025-02-23</t>
-        </is>
-      </c>
-      <c r="AC90" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD90" t="b">

--- a/artfynd/A 1625-2025 artfynd.xlsx
+++ b/artfynd/A 1625-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122719697</v>
+        <v>122715669</v>
       </c>
       <c r="B2" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,37 +691,42 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Spejkmyren, Spejkmyren, Jmt</t>
+          <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>520026</v>
+        <v>520221</v>
       </c>
       <c r="R2" t="n">
-        <v>7035233</v>
+        <v>7035600</v>
       </c>
       <c r="S2" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -761,31 +766,6 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -802,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122715669</v>
+        <v>122715949</v>
       </c>
       <c r="B3" t="n">
         <v>79847</v>
@@ -836,21 +816,16 @@
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>520221</v>
+        <v>520254</v>
       </c>
       <c r="R3" t="n">
-        <v>7035600</v>
+        <v>7035555</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -909,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122715949</v>
+        <v>122719697</v>
       </c>
       <c r="B4" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -925,37 +900,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Finnbodarna, Finnbodarna, Jmt</t>
+          <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>520254</v>
+        <v>520026</v>
       </c>
       <c r="R4" t="n">
-        <v>7035555</v>
+        <v>7035233</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -995,6 +970,31 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1539,10 +1539,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122715780</v>
+        <v>122717284</v>
       </c>
       <c r="B9" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1555,37 +1555,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Finnbodarna, Finnbodarna, Jmt</t>
+          <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>520259</v>
+        <v>520031</v>
       </c>
       <c r="R9" t="n">
-        <v>7035569</v>
+        <v>7035353</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1619,7 +1619,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>På björk</t>
+          <t>Långväxta bålar på flertalet granar.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1630,6 +1630,31 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1646,7 +1671,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122715779</v>
+        <v>122715780</v>
       </c>
       <c r="B10" t="n">
         <v>79847</v>
@@ -1680,24 +1705,19 @@
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>520223</v>
+        <v>520259</v>
       </c>
       <c r="R10" t="n">
-        <v>7035609</v>
+        <v>7035569</v>
       </c>
       <c r="S10" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1729,6 +1749,11 @@
           <t>2025-02-23</t>
         </is>
       </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>På björk</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1737,31 +1762,6 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1778,10 +1778,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122717284</v>
+        <v>122715779</v>
       </c>
       <c r="B11" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1794,34 +1794,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Spejkmyren, Spejkmyren, Jmt</t>
+          <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>520031</v>
+        <v>520223</v>
       </c>
       <c r="R11" t="n">
-        <v>7035353</v>
+        <v>7035609</v>
       </c>
       <c r="S11" t="n">
         <v>9</v>
@@ -1856,11 +1861,6 @@
           <t>2025-02-23</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Långväxta bålar på flertalet granar.</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1877,22 +1877,22 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -2823,10 +2823,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122715573</v>
+        <v>122715757</v>
       </c>
       <c r="B20" t="n">
-        <v>79848</v>
+        <v>78766</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2839,21 +2839,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2863,10 +2863,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>520214</v>
+        <v>520234</v>
       </c>
       <c r="R20" t="n">
-        <v>7035583</v>
+        <v>7035595</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2901,6 +2901,11 @@
           <t>2025-02-23</t>
         </is>
       </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
+        </is>
+      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
@@ -2909,6 +2914,31 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM20" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
@@ -2925,10 +2955,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122717952</v>
+        <v>122720065</v>
       </c>
       <c r="B21" t="n">
-        <v>57494</v>
+        <v>78766</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2941,46 +2971,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>519951</v>
+        <v>520062</v>
       </c>
       <c r="R21" t="n">
-        <v>7035320</v>
+        <v>7035232</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3020,6 +3041,31 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM21" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -3036,10 +3082,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122715757</v>
+        <v>122715573</v>
       </c>
       <c r="B22" t="n">
-        <v>78766</v>
+        <v>79848</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3052,21 +3098,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3076,10 +3122,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>520234</v>
+        <v>520214</v>
       </c>
       <c r="R22" t="n">
-        <v>7035595</v>
+        <v>7035583</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3114,11 +3160,6 @@
           <t>2025-02-23</t>
         </is>
       </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
-        </is>
-      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
@@ -3127,31 +3168,6 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
-      </c>
-      <c r="AH22" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -3168,10 +3184,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122720065</v>
+        <v>122717952</v>
       </c>
       <c r="B23" t="n">
-        <v>78766</v>
+        <v>57494</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3184,37 +3200,46 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>520062</v>
+        <v>519951</v>
       </c>
       <c r="R23" t="n">
-        <v>7035232</v>
+        <v>7035320</v>
       </c>
       <c r="S23" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3254,31 +3279,6 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
-      </c>
-      <c r="AH23" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
@@ -3295,10 +3295,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122719371</v>
+        <v>122715648</v>
       </c>
       <c r="B24" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3311,37 +3311,42 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Spejkmyren, Spejkmyren, Jmt</t>
+          <t>Finnbodarna, Hammerdal, Finnbodarna, Hammerdal, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>519943</v>
+        <v>520219</v>
       </c>
       <c r="R24" t="n">
-        <v>7035270</v>
+        <v>7035597</v>
       </c>
       <c r="S24" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3373,6 +3378,11 @@
           <t>2025-02-23</t>
         </is>
       </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
@@ -3381,31 +3391,6 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
-      </c>
-      <c r="AH24" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ24" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK24" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
@@ -3422,10 +3407,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122715648</v>
+        <v>122717359</v>
       </c>
       <c r="B25" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3438,39 +3423,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Finnbodarna, Hammerdal, Finnbodarna, Hammerdal, Jmt</t>
+          <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>520219</v>
+        <v>520030</v>
       </c>
       <c r="R25" t="n">
-        <v>7035597</v>
+        <v>7035341</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3503,11 +3483,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-02-23</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3534,7 +3509,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122717359</v>
+        <v>122715836</v>
       </c>
       <c r="B26" t="n">
         <v>79847</v>
@@ -3568,16 +3543,21 @@
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Spejkmyren, Spejkmyren, Jmt</t>
+          <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>520030</v>
+        <v>520269</v>
       </c>
       <c r="R26" t="n">
-        <v>7035341</v>
+        <v>7035574</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3636,7 +3616,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122715836</v>
+        <v>122715775</v>
       </c>
       <c r="B27" t="n">
         <v>79847</v>
@@ -3681,10 +3661,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>520269</v>
+        <v>520252</v>
       </c>
       <c r="R27" t="n">
-        <v>7035574</v>
+        <v>7035576</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3717,6 +3697,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-02-23</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>På björk</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3743,7 +3728,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122715775</v>
+        <v>122715756</v>
       </c>
       <c r="B28" t="n">
         <v>79847</v>
@@ -3777,21 +3762,16 @@
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>520252</v>
+        <v>520256</v>
       </c>
       <c r="R28" t="n">
-        <v>7035576</v>
+        <v>7035593</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3824,11 +3804,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-02-23</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>På björk</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3855,10 +3830,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122715756</v>
+        <v>122719371</v>
       </c>
       <c r="B29" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3871,37 +3846,37 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Finnbodarna, Finnbodarna, Jmt</t>
+          <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>520256</v>
+        <v>519943</v>
       </c>
       <c r="R29" t="n">
-        <v>7035593</v>
+        <v>7035270</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3941,6 +3916,31 @@
       </c>
       <c r="AG29" t="b">
         <v>0</v>
+      </c>
+      <c r="AH29" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM29" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
@@ -3957,10 +3957,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122719614</v>
+        <v>122717446</v>
       </c>
       <c r="B30" t="n">
-        <v>57478</v>
+        <v>90962</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3973,39 +3973,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>519930</v>
+        <v>520006</v>
       </c>
       <c r="R30" t="n">
-        <v>7035181</v>
+        <v>7035303</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4038,11 +4033,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-02-23</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Färska och äldre ringhack på samma gran.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4069,10 +4059,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122716293</v>
+        <v>122716329</v>
       </c>
       <c r="B31" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4085,42 +4075,42 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Finnbodarna, Hammerdal, Finnbodarna, Hammerdal, Jmt</t>
+          <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>520249</v>
+        <v>520374</v>
       </c>
       <c r="R31" t="n">
-        <v>7035364</v>
+        <v>7035511</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4154,7 +4144,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>På gran intill en gammal lunglavssälg.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4165,6 +4155,31 @@
       </c>
       <c r="AG31" t="b">
         <v>0</v>
+      </c>
+      <c r="AH31" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM31" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
@@ -4181,10 +4196,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122717446</v>
+        <v>122719614</v>
       </c>
       <c r="B32" t="n">
-        <v>90962</v>
+        <v>57478</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4197,34 +4212,39 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>520006</v>
+        <v>519930</v>
       </c>
       <c r="R32" t="n">
-        <v>7035303</v>
+        <v>7035181</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4257,6 +4277,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-02-23</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Färska och äldre ringhack på samma gran.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4283,10 +4308,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122720686</v>
+        <v>122716293</v>
       </c>
       <c r="B33" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4299,34 +4324,39 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Spejkmyren, Spejkmyren, Jmt</t>
+          <t>Finnbodarna, Hammerdal, Finnbodarna, Hammerdal, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>519903</v>
+        <v>520249</v>
       </c>
       <c r="R33" t="n">
-        <v>7035224</v>
+        <v>7035364</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4361,6 +4391,11 @@
           <t>2025-02-23</t>
         </is>
       </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
@@ -4369,31 +4404,6 @@
       </c>
       <c r="AG33" t="b">
         <v>0</v>
-      </c>
-      <c r="AH33" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ33" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK33" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO33" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
@@ -4410,10 +4420,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122716329</v>
+        <v>122720686</v>
       </c>
       <c r="B34" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4426,42 +4436,37 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Finnbodarna, Finnbodarna, Jmt</t>
+          <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>520374</v>
+        <v>519903</v>
       </c>
       <c r="R34" t="n">
-        <v>7035511</v>
+        <v>7035224</v>
       </c>
       <c r="S34" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4491,11 +4496,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-02-23</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>På gran intill en gammal lunglavssälg.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -5462,10 +5462,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122721463</v>
+        <v>122716269</v>
       </c>
       <c r="B43" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5478,34 +5478,39 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Spejkmyren, Spejkmyren, Jmt</t>
+          <t>Finnbodarna, Hammerdal, Finnbodarna, Hammerdal, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>519841</v>
+        <v>520256</v>
       </c>
       <c r="R43" t="n">
-        <v>7035417</v>
+        <v>7035380</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5542,7 +5547,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5553,31 +5558,6 @@
       </c>
       <c r="AG43" t="b">
         <v>0</v>
-      </c>
-      <c r="AH43" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ43" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK43" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM43" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO43" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
@@ -5594,10 +5574,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122721333</v>
+        <v>122720281</v>
       </c>
       <c r="B44" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5610,37 +5590,42 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>519906</v>
+        <v>519850</v>
       </c>
       <c r="R44" t="n">
-        <v>7035389</v>
+        <v>7035373</v>
       </c>
       <c r="S44" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5674,7 +5659,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Ymnigt på flera granar.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5685,31 +5670,6 @@
       </c>
       <c r="AG44" t="b">
         <v>0</v>
-      </c>
-      <c r="AH44" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ44" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK44" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM44" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO44" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
@@ -5726,10 +5686,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122715569</v>
+        <v>122717636</v>
       </c>
       <c r="B45" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5742,34 +5702,39 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Djupmyren, Djupmyren, Jmt</t>
+          <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>520115</v>
+        <v>519970</v>
       </c>
       <c r="R45" t="n">
-        <v>7035562</v>
+        <v>7035297</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5806,7 +5771,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5817,31 +5782,6 @@
       </c>
       <c r="AG45" t="b">
         <v>0</v>
-      </c>
-      <c r="AH45" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ45" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK45" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM45" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO45" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
@@ -5858,10 +5798,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122717488</v>
+        <v>122716387</v>
       </c>
       <c r="B46" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5874,34 +5814,39 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Spejkmyren, Spejkmyren, Jmt</t>
+          <t>Finnbodarna, Hammerdal, Finnbodarna, Hammerdal, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>520000</v>
+        <v>520278</v>
       </c>
       <c r="R46" t="n">
-        <v>7035297</v>
+        <v>7035397</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5934,6 +5879,11 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-02-23</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5960,10 +5910,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122716269</v>
+        <v>122716682</v>
       </c>
       <c r="B47" t="n">
-        <v>57478</v>
+        <v>57631</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5976,39 +5926,43 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>par i lämplig häckbiotop</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Finnbodarna, Hammerdal, Finnbodarna, Hammerdal, Jmt</t>
+          <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>520256</v>
+        <v>520101</v>
       </c>
       <c r="R47" t="n">
-        <v>7035380</v>
+        <v>7035453</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6041,11 +5995,6 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-02-23</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6072,10 +6021,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122720281</v>
+        <v>122721463</v>
       </c>
       <c r="B48" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6088,39 +6037,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>519850</v>
+        <v>519841</v>
       </c>
       <c r="R48" t="n">
-        <v>7035373</v>
+        <v>7035417</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6157,7 +6101,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6168,6 +6112,31 @@
       </c>
       <c r="AG48" t="b">
         <v>0</v>
+      </c>
+      <c r="AH48" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ48" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK48" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM48" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO48" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
@@ -6184,10 +6153,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122717636</v>
+        <v>122721333</v>
       </c>
       <c r="B49" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6200,42 +6169,37 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>519970</v>
+        <v>519906</v>
       </c>
       <c r="R49" t="n">
-        <v>7035297</v>
+        <v>7035389</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6269,7 +6233,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ymnigt på flera granar.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6280,6 +6244,31 @@
       </c>
       <c r="AG49" t="b">
         <v>0</v>
+      </c>
+      <c r="AH49" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ49" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK49" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM49" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO49" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
@@ -6296,10 +6285,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122716387</v>
+        <v>122715569</v>
       </c>
       <c r="B50" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6312,39 +6301,34 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Finnbodarna, Hammerdal, Finnbodarna, Hammerdal, Jmt</t>
+          <t>Djupmyren, Djupmyren, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>520278</v>
+        <v>520115</v>
       </c>
       <c r="R50" t="n">
-        <v>7035397</v>
+        <v>7035562</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6381,7 +6365,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6392,6 +6376,31 @@
       </c>
       <c r="AG50" t="b">
         <v>0</v>
+      </c>
+      <c r="AH50" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ50" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK50" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM50" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO50" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
@@ -6408,10 +6417,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122715953</v>
+        <v>122717488</v>
       </c>
       <c r="B51" t="n">
-        <v>79848</v>
+        <v>79847</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6424,34 +6433,34 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Finnbodarna, Finnbodarna, Jmt</t>
+          <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>520254</v>
+        <v>520000</v>
       </c>
       <c r="R51" t="n">
-        <v>7035555</v>
+        <v>7035297</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6510,10 +6519,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122716682</v>
+        <v>122715953</v>
       </c>
       <c r="B52" t="n">
-        <v>57631</v>
+        <v>79848</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6526,43 +6535,34 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>103021</v>
+        <v>2081</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>par i lämplig häckbiotop</t>
-        </is>
-      </c>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Spejkmyren, Spejkmyren, Jmt</t>
+          <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>520101</v>
+        <v>520254</v>
       </c>
       <c r="R52" t="n">
-        <v>7035453</v>
+        <v>7035555</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -9674,10 +9674,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>122716547</v>
+        <v>122716216</v>
       </c>
       <c r="B78" t="n">
-        <v>98261</v>
+        <v>79847</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -9686,40 +9686,31 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>504</v>
+        <v>6458</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J78" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
       <c r="K78" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P78" t="inlineStr">
@@ -9728,13 +9719,13 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>520386</v>
+        <v>520368</v>
       </c>
       <c r="R78" t="n">
-        <v>7035492</v>
+        <v>7035513</v>
       </c>
       <c r="S78" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -9768,7 +9759,7 @@
       </c>
       <c r="AC78" t="inlineStr">
         <is>
-          <t>En vinterståndare på till synes fuktig mark i en lucka.</t>
+          <t>På en gammal grovbarkad sälg.</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9783,6 +9774,26 @@
       <c r="AH78" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ78" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK78" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM78" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO78" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT78" t="inlineStr"/>
@@ -9800,10 +9811,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>122716160</v>
+        <v>122715874</v>
       </c>
       <c r="B79" t="n">
-        <v>78766</v>
+        <v>79876</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -9812,25 +9823,25 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -9840,10 +9851,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>520349</v>
+        <v>520265</v>
       </c>
       <c r="R79" t="n">
-        <v>7035517</v>
+        <v>7035574</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9886,31 +9897,6 @@
       </c>
       <c r="AG79" t="b">
         <v>0</v>
-      </c>
-      <c r="AH79" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ79" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK79" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM79" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO79" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
@@ -9927,10 +9913,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>122716216</v>
+        <v>122715801</v>
       </c>
       <c r="B80" t="n">
-        <v>79847</v>
+        <v>79848</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -9943,39 +9929,34 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
-      <c r="K80" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P80" t="inlineStr">
         <is>
           <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>520368</v>
+        <v>520266</v>
       </c>
       <c r="R80" t="n">
-        <v>7035513</v>
+        <v>7035582</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -10010,11 +9991,6 @@
           <t>2025-02-23</t>
         </is>
       </c>
-      <c r="AC80" t="inlineStr">
-        <is>
-          <t>På en gammal grovbarkad sälg.</t>
-        </is>
-      </c>
       <c r="AD80" t="b">
         <v>0</v>
       </c>
@@ -10023,31 +9999,6 @@
       </c>
       <c r="AG80" t="b">
         <v>0</v>
-      </c>
-      <c r="AH80" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ80" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK80" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM80" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO80" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
@@ -10064,10 +10015,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>122715874</v>
+        <v>122717343</v>
       </c>
       <c r="B81" t="n">
-        <v>79876</v>
+        <v>57478</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -10076,38 +10027,43 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Finnbodarna, Finnbodarna, Jmt</t>
+          <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>520265</v>
+        <v>520034</v>
       </c>
       <c r="R81" t="n">
-        <v>7035574</v>
+        <v>7035339</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -10140,6 +10096,11 @@
       <c r="AA81" t="inlineStr">
         <is>
           <t>2025-02-23</t>
+        </is>
+      </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -10166,10 +10127,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>122715801</v>
+        <v>122716547</v>
       </c>
       <c r="B82" t="n">
-        <v>79848</v>
+        <v>98261</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -10178,41 +10139,55 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>2081</v>
+        <v>504</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P82" t="inlineStr">
         <is>
           <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>520266</v>
+        <v>520386</v>
       </c>
       <c r="R82" t="n">
-        <v>7035582</v>
+        <v>7035492</v>
       </c>
       <c r="S82" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -10244,6 +10219,11 @@
           <t>2025-02-23</t>
         </is>
       </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>En vinterståndare på till synes fuktig mark i en lucka.</t>
+        </is>
+      </c>
       <c r="AD82" t="b">
         <v>0</v>
       </c>
@@ -10252,6 +10232,11 @@
       </c>
       <c r="AG82" t="b">
         <v>0</v>
+      </c>
+      <c r="AH82" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
@@ -10268,10 +10253,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>122717343</v>
+        <v>122716160</v>
       </c>
       <c r="B83" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -10284,39 +10269,34 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
-      <c r="M83" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Spejkmyren, Spejkmyren, Jmt</t>
+          <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>520034</v>
+        <v>520349</v>
       </c>
       <c r="R83" t="n">
-        <v>7035339</v>
+        <v>7035517</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -10351,11 +10331,6 @@
           <t>2025-02-23</t>
         </is>
       </c>
-      <c r="AC83" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD83" t="b">
         <v>0</v>
       </c>
@@ -10364,6 +10339,31 @@
       </c>
       <c r="AG83" t="b">
         <v>0</v>
+      </c>
+      <c r="AH83" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ83" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK83" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM83" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO83" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">

--- a/artfynd/A 1625-2025 artfynd.xlsx
+++ b/artfynd/A 1625-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122715669</v>
+        <v>122715801</v>
       </c>
       <c r="B2" t="n">
-        <v>79847</v>
+        <v>79848</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,39 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>520221</v>
+        <v>520266</v>
       </c>
       <c r="R2" t="n">
-        <v>7035600</v>
+        <v>7035582</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -782,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122715949</v>
+        <v>122717359</v>
       </c>
       <c r="B3" t="n">
         <v>79847</v>
@@ -818,14 +813,14 @@
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Finnbodarna, Finnbodarna, Jmt</t>
+          <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>520254</v>
+        <v>520030</v>
       </c>
       <c r="R3" t="n">
-        <v>7035555</v>
+        <v>7035341</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -884,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122719697</v>
+        <v>122720823</v>
       </c>
       <c r="B4" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,37 +895,56 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>520026</v>
+        <v>519842</v>
       </c>
       <c r="R4" t="n">
-        <v>7035233</v>
+        <v>7035388</v>
       </c>
       <c r="S4" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -962,6 +976,11 @@
           <t>2025-02-23</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Trummande</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -970,31 +989,6 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1011,10 +1005,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122717164</v>
+        <v>122720327</v>
       </c>
       <c r="B5" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1027,34 +1021,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>520120</v>
+        <v>519838</v>
       </c>
       <c r="R5" t="n">
-        <v>7035405</v>
+        <v>7035393</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1089,6 +1088,11 @@
           <t>2025-02-23</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1097,31 +1101,6 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1138,10 +1117,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122720469</v>
+        <v>122716303</v>
       </c>
       <c r="B6" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1154,34 +1133,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Spejkmyren, Spejkmyren, Jmt</t>
+          <t>Finnbodarna, Hammerdal, Finnbodarna, Hammerdal, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>519996</v>
+        <v>520250</v>
       </c>
       <c r="R6" t="n">
-        <v>7035241</v>
+        <v>7035363</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1216,6 +1200,11 @@
           <t>2025-02-23</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1224,31 +1213,6 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1265,10 +1229,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122715795</v>
+        <v>122716387</v>
       </c>
       <c r="B7" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1281,37 +1245,42 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Finnbodarna, Finnbodarna, Jmt</t>
+          <t>Finnbodarna, Hammerdal, Finnbodarna, Hammerdal, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>520214</v>
+        <v>520278</v>
       </c>
       <c r="R7" t="n">
-        <v>7035599</v>
+        <v>7035397</v>
       </c>
       <c r="S7" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1345,7 +1314,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>På en klen gran intill en lunglavssälg.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1356,31 +1325,6 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1397,10 +1341,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122719554</v>
+        <v>122716427</v>
       </c>
       <c r="B8" t="n">
-        <v>57478</v>
+        <v>78767</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1413,47 +1357,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>230405</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Spejkmyren, Spejkmyren, Jmt</t>
+          <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>519981</v>
+        <v>520388</v>
       </c>
       <c r="R8" t="n">
-        <v>7035221</v>
+        <v>7035490</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1487,7 +1421,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Äldre ringhack som bedöms vara 5 - 10 år gamla.</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1516,12 +1450,12 @@
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1539,7 +1473,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122717284</v>
+        <v>122720629</v>
       </c>
       <c r="B9" t="n">
         <v>78766</v>
@@ -1579,13 +1513,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>520031</v>
+        <v>519935</v>
       </c>
       <c r="R9" t="n">
-        <v>7035353</v>
+        <v>7035246</v>
       </c>
       <c r="S9" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1619,7 +1553,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Långväxta bålar på flertalet granar.</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1671,10 +1605,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122715780</v>
+        <v>122721035</v>
       </c>
       <c r="B10" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1687,37 +1621,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Finnbodarna, Finnbodarna, Jmt</t>
+          <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>520259</v>
+        <v>519897</v>
       </c>
       <c r="R10" t="n">
-        <v>7035569</v>
+        <v>7035374</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1749,11 +1683,6 @@
           <t>2025-02-23</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>På björk</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1762,6 +1691,31 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>garnlav</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Alectoria sarmentosa</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1778,10 +1732,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122715779</v>
+        <v>122717468</v>
       </c>
       <c r="B11" t="n">
-        <v>79847</v>
+        <v>57494</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1794,42 +1748,46 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>med soral</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Finnbodarna, Finnbodarna, Jmt</t>
+          <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>520223</v>
+        <v>520020</v>
       </c>
       <c r="R11" t="n">
-        <v>7035609</v>
+        <v>7035330</v>
       </c>
       <c r="S11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1869,31 +1827,6 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -1910,10 +1843,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122716850</v>
+        <v>122720281</v>
       </c>
       <c r="B12" t="n">
-        <v>90962</v>
+        <v>57478</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1926,34 +1859,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>520101</v>
+        <v>519850</v>
       </c>
       <c r="R12" t="n">
-        <v>7035388</v>
+        <v>7035373</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1986,6 +1924,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-02-23</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2012,7 +1955,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122720823</v>
+        <v>122719533</v>
       </c>
       <c r="B13" t="n">
         <v>57478</v>
@@ -2045,24 +1988,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -2071,10 +2000,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>519842</v>
+        <v>519948</v>
       </c>
       <c r="R13" t="n">
-        <v>7035388</v>
+        <v>7035187</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2111,7 +2040,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Trummande</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2249,10 +2178,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122715778</v>
+        <v>122716645</v>
       </c>
       <c r="B15" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2265,39 +2194,39 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Finnbodarna, Finnbodarna, Jmt</t>
+          <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>520259</v>
+        <v>520129</v>
       </c>
       <c r="R15" t="n">
-        <v>7035574</v>
+        <v>7035444</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2330,6 +2259,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-02-23</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2356,7 +2290,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122718013</v>
+        <v>122715648</v>
       </c>
       <c r="B16" t="n">
         <v>57478</v>
@@ -2397,14 +2331,14 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Spejkmyren, Spejkmyren, Jmt</t>
+          <t>Finnbodarna, Hammerdal, Finnbodarna, Hammerdal, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>519948</v>
+        <v>520219</v>
       </c>
       <c r="R16" t="n">
-        <v>7035313</v>
+        <v>7035597</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2468,7 +2402,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122720368</v>
+        <v>122719875</v>
       </c>
       <c r="B17" t="n">
         <v>57478</v>
@@ -2513,10 +2447,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>519852</v>
+        <v>519983</v>
       </c>
       <c r="R17" t="n">
-        <v>7035392</v>
+        <v>7035206</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2580,10 +2514,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122717873</v>
+        <v>122715849</v>
       </c>
       <c r="B18" t="n">
-        <v>79847</v>
+        <v>79876</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2592,46 +2526,41 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Spejkmyren, Spejkmyren, Jmt</t>
+          <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>520033</v>
+        <v>520268</v>
       </c>
       <c r="R18" t="n">
-        <v>7035301</v>
+        <v>7035575</v>
       </c>
       <c r="S18" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2671,31 +2600,6 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
-      </c>
-      <c r="AH18" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2712,10 +2616,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122717468</v>
+        <v>122716850</v>
       </c>
       <c r="B19" t="n">
-        <v>57494</v>
+        <v>90962</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2728,43 +2632,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>520020</v>
+        <v>520101</v>
       </c>
       <c r="R19" t="n">
-        <v>7035330</v>
+        <v>7035388</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2823,10 +2718,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122715757</v>
+        <v>122717989</v>
       </c>
       <c r="B20" t="n">
-        <v>78766</v>
+        <v>57494</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2839,34 +2734,43 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Finnbodarna, Finnbodarna, Jmt</t>
+          <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>520234</v>
+        <v>519951</v>
       </c>
       <c r="R20" t="n">
-        <v>7035595</v>
+        <v>7035320</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2903,7 +2807,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Trummande</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2914,31 +2818,6 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
-      </c>
-      <c r="AH20" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
@@ -2955,7 +2834,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122720065</v>
+        <v>122715757</v>
       </c>
       <c r="B21" t="n">
         <v>78766</v>
@@ -2991,17 +2870,17 @@
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Spejkmyren, Spejkmyren, Jmt</t>
+          <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>520062</v>
+        <v>520234</v>
       </c>
       <c r="R21" t="n">
-        <v>7035232</v>
+        <v>7035595</v>
       </c>
       <c r="S21" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3031,6 +2910,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-02-23</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3082,10 +2966,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122715573</v>
+        <v>122716216</v>
       </c>
       <c r="B22" t="n">
-        <v>79848</v>
+        <v>79847</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3098,34 +2982,39 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>520214</v>
+        <v>520368</v>
       </c>
       <c r="R22" t="n">
-        <v>7035583</v>
+        <v>7035513</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3160,6 +3049,11 @@
           <t>2025-02-23</t>
         </is>
       </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>På en gammal grovbarkad sälg.</t>
+        </is>
+      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
@@ -3168,6 +3062,31 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM22" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -3184,10 +3103,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122717952</v>
+        <v>122715669</v>
       </c>
       <c r="B23" t="n">
-        <v>57494</v>
+        <v>79847</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3200,43 +3119,39 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Spejkmyren, Spejkmyren, Jmt</t>
+          <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>519951</v>
+        <v>520221</v>
       </c>
       <c r="R23" t="n">
-        <v>7035320</v>
+        <v>7035600</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3295,10 +3210,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122715648</v>
+        <v>122715775</v>
       </c>
       <c r="B24" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3311,39 +3226,39 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Finnbodarna, Hammerdal, Finnbodarna, Hammerdal, Jmt</t>
+          <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>520219</v>
+        <v>520252</v>
       </c>
       <c r="R24" t="n">
-        <v>7035597</v>
+        <v>7035576</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3380,7 +3295,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>På björk</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3407,10 +3322,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122717359</v>
+        <v>122715766</v>
       </c>
       <c r="B25" t="n">
-        <v>79847</v>
+        <v>90962</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3423,34 +3338,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Spejkmyren, Spejkmyren, Jmt</t>
+          <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>520030</v>
+        <v>520252</v>
       </c>
       <c r="R25" t="n">
-        <v>7035341</v>
+        <v>7035591</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3509,10 +3424,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122715836</v>
+        <v>122717294</v>
       </c>
       <c r="B26" t="n">
-        <v>79847</v>
+        <v>90962</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3525,39 +3440,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Finnbodarna, Finnbodarna, Jmt</t>
+          <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>520269</v>
+        <v>520013</v>
       </c>
       <c r="R26" t="n">
-        <v>7035574</v>
+        <v>7035340</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3616,10 +3526,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122715775</v>
+        <v>122717446</v>
       </c>
       <c r="B27" t="n">
-        <v>79847</v>
+        <v>90962</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3632,39 +3542,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Finnbodarna, Finnbodarna, Jmt</t>
+          <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>520252</v>
+        <v>520006</v>
       </c>
       <c r="R27" t="n">
-        <v>7035576</v>
+        <v>7035303</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3697,11 +3602,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-02-23</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>På björk</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3728,10 +3628,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122715756</v>
+        <v>122720065</v>
       </c>
       <c r="B28" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3744,37 +3644,37 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Finnbodarna, Finnbodarna, Jmt</t>
+          <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>520256</v>
+        <v>520062</v>
       </c>
       <c r="R28" t="n">
-        <v>7035593</v>
+        <v>7035232</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3814,6 +3714,31 @@
       </c>
       <c r="AG28" t="b">
         <v>0</v>
+      </c>
+      <c r="AH28" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM28" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
@@ -3830,10 +3755,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122719371</v>
+        <v>122715949</v>
       </c>
       <c r="B29" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3846,37 +3771,37 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Spejkmyren, Spejkmyren, Jmt</t>
+          <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>519943</v>
+        <v>520254</v>
       </c>
       <c r="R29" t="n">
-        <v>7035270</v>
+        <v>7035555</v>
       </c>
       <c r="S29" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3916,31 +3841,6 @@
       </c>
       <c r="AG29" t="b">
         <v>0</v>
-      </c>
-      <c r="AH29" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ29" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK29" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM29" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO29" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
@@ -3957,10 +3857,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122717446</v>
+        <v>122717164</v>
       </c>
       <c r="B30" t="n">
-        <v>90962</v>
+        <v>78766</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3973,21 +3873,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3997,10 +3897,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>520006</v>
+        <v>520120</v>
       </c>
       <c r="R30" t="n">
-        <v>7035303</v>
+        <v>7035405</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4043,6 +3943,31 @@
       </c>
       <c r="AG30" t="b">
         <v>0</v>
+      </c>
+      <c r="AH30" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM30" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
@@ -4059,10 +3984,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122716329</v>
+        <v>122719554</v>
       </c>
       <c r="B31" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4075,42 +4000,47 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>med soral</t>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Finnbodarna, Finnbodarna, Jmt</t>
+          <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>520374</v>
+        <v>519981</v>
       </c>
       <c r="R31" t="n">
-        <v>7035511</v>
+        <v>7035221</v>
       </c>
       <c r="S31" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4144,7 +4074,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>På gran intill en gammal lunglavssälg.</t>
+          <t>Äldre ringhack som bedöms vara 5 - 10 år gamla.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4173,12 +4103,12 @@
       </c>
       <c r="AM31" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4196,10 +4126,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122719614</v>
+        <v>122715870</v>
       </c>
       <c r="B32" t="n">
-        <v>57478</v>
+        <v>79848</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4212,39 +4142,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Spejkmyren, Spejkmyren, Jmt</t>
+          <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>519930</v>
+        <v>520265</v>
       </c>
       <c r="R32" t="n">
-        <v>7035181</v>
+        <v>7035574</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4277,11 +4202,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-02-23</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Färska och äldre ringhack på samma gran.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4308,10 +4228,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122716293</v>
+        <v>122715778</v>
       </c>
       <c r="B33" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4324,39 +4244,39 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Finnbodarna, Hammerdal, Finnbodarna, Hammerdal, Jmt</t>
+          <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>520249</v>
+        <v>520259</v>
       </c>
       <c r="R33" t="n">
-        <v>7035364</v>
+        <v>7035574</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4389,11 +4309,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-02-23</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4420,7 +4335,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122720686</v>
+        <v>122717616</v>
       </c>
       <c r="B34" t="n">
         <v>78766</v>
@@ -4460,10 +4375,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>519903</v>
+        <v>520019</v>
       </c>
       <c r="R34" t="n">
-        <v>7035224</v>
+        <v>7035352</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4496,6 +4411,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-02-23</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4547,10 +4467,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122715677</v>
+        <v>122716234</v>
       </c>
       <c r="B35" t="n">
-        <v>79848</v>
+        <v>79847</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4563,21 +4483,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4587,10 +4507,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>520221</v>
+        <v>520362</v>
       </c>
       <c r="R35" t="n">
-        <v>7035600</v>
+        <v>7035500</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4627,7 +4547,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>På gran</t>
+          <t>På en klen gran intill en gammal sälg med lunglav.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4638,6 +4558,31 @@
       </c>
       <c r="AG35" t="b">
         <v>0</v>
+      </c>
+      <c r="AH35" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ35" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK35" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM35" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO35" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
@@ -4654,10 +4599,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122716443</v>
+        <v>122716673</v>
       </c>
       <c r="B36" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4670,48 +4615,39 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Finnbodarna, Finnbodarna, Jmt</t>
+          <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>520251</v>
+        <v>520108</v>
       </c>
       <c r="R36" t="n">
-        <v>7035394</v>
+        <v>7035462</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4748,7 +4684,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Garnlavsrikt</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4775,10 +4711,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122720959</v>
+        <v>122717636</v>
       </c>
       <c r="B37" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4791,34 +4727,39 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>519917</v>
+        <v>519970</v>
       </c>
       <c r="R37" t="n">
-        <v>7035339</v>
+        <v>7035297</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4855,7 +4796,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Långväxta bålar på flertalet granar.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4866,31 +4807,6 @@
       </c>
       <c r="AG37" t="b">
         <v>0</v>
-      </c>
-      <c r="AH37" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ37" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK37" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM37" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO37" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
@@ -4907,10 +4823,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122715790</v>
+        <v>122720427</v>
       </c>
       <c r="B38" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4923,39 +4839,39 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Finnbodarna, Finnbodarna, Jmt</t>
+          <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>520267</v>
+        <v>519846</v>
       </c>
       <c r="R38" t="n">
-        <v>7035581</v>
+        <v>7035407</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4988,6 +4904,11 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-02-23</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5014,7 +4935,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122716303</v>
+        <v>122716293</v>
       </c>
       <c r="B39" t="n">
         <v>57478</v>
@@ -5059,10 +4980,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>520250</v>
+        <v>520249</v>
       </c>
       <c r="R39" t="n">
-        <v>7035363</v>
+        <v>7035364</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5126,10 +5047,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122720889</v>
+        <v>122720869</v>
       </c>
       <c r="B40" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5142,39 +5063,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>519841</v>
+        <v>519960</v>
       </c>
       <c r="R40" t="n">
-        <v>7035390</v>
+        <v>7035342</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5209,11 +5125,6 @@
           <t>2025-02-23</t>
         </is>
       </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
@@ -5222,6 +5133,31 @@
       </c>
       <c r="AG40" t="b">
         <v>0</v>
+      </c>
+      <c r="AH40" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ40" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK40" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM40" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO40" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
@@ -5238,10 +5174,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122720427</v>
+        <v>122715999</v>
       </c>
       <c r="B41" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5254,42 +5190,37 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Spejkmyren, Spejkmyren, Jmt</t>
+          <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>519846</v>
+        <v>520311</v>
       </c>
       <c r="R41" t="n">
-        <v>7035407</v>
+        <v>7035566</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5321,11 +5252,6 @@
           <t>2025-02-23</t>
         </is>
       </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
@@ -5334,6 +5260,31 @@
       </c>
       <c r="AG41" t="b">
         <v>0</v>
+      </c>
+      <c r="AH41" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ41" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK41" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM41" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO41" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
@@ -5350,10 +5301,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122716673</v>
+        <v>122715779</v>
       </c>
       <c r="B42" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5366,42 +5317,42 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Spejkmyren, Spejkmyren, Jmt</t>
+          <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>520108</v>
+        <v>520223</v>
       </c>
       <c r="R42" t="n">
-        <v>7035462</v>
+        <v>7035609</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5433,11 +5384,6 @@
           <t>2025-02-23</t>
         </is>
       </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
@@ -5446,6 +5392,31 @@
       </c>
       <c r="AG42" t="b">
         <v>0</v>
+      </c>
+      <c r="AH42" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ42" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK42" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM42" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO42" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
@@ -5462,10 +5433,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122716269</v>
+        <v>122717488</v>
       </c>
       <c r="B43" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5478,39 +5449,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Finnbodarna, Hammerdal, Finnbodarna, Hammerdal, Jmt</t>
+          <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>520256</v>
+        <v>520000</v>
       </c>
       <c r="R43" t="n">
-        <v>7035380</v>
+        <v>7035297</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5543,11 +5509,6 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-02-23</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5574,10 +5535,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122720281</v>
+        <v>122717284</v>
       </c>
       <c r="B44" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5590,42 +5551,37 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>519850</v>
+        <v>520031</v>
       </c>
       <c r="R44" t="n">
-        <v>7035373</v>
+        <v>7035353</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5659,7 +5615,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Långväxta bålar på flertalet granar.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5670,6 +5626,31 @@
       </c>
       <c r="AG44" t="b">
         <v>0</v>
+      </c>
+      <c r="AH44" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ44" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK44" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM44" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO44" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
@@ -5686,10 +5667,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122717636</v>
+        <v>122715934</v>
       </c>
       <c r="B45" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5702,42 +5683,37 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Spejkmyren, Spejkmyren, Jmt</t>
+          <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>519970</v>
+        <v>520303</v>
       </c>
       <c r="R45" t="n">
-        <v>7035297</v>
+        <v>7035598</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5771,7 +5747,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5782,6 +5758,31 @@
       </c>
       <c r="AG45" t="b">
         <v>0</v>
+      </c>
+      <c r="AH45" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ45" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK45" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM45" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO45" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
@@ -5798,7 +5799,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122716387</v>
+        <v>122716269</v>
       </c>
       <c r="B46" t="n">
         <v>57478</v>
@@ -5843,10 +5844,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>520278</v>
+        <v>520256</v>
       </c>
       <c r="R46" t="n">
-        <v>7035397</v>
+        <v>7035380</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5910,10 +5911,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122716682</v>
+        <v>122720889</v>
       </c>
       <c r="B47" t="n">
-        <v>57631</v>
+        <v>57478</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5926,31 +5927,27 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="M47" t="inlineStr">
         <is>
-          <t>par i lämplig häckbiotop</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
@@ -5959,10 +5956,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>520101</v>
+        <v>519841</v>
       </c>
       <c r="R47" t="n">
-        <v>7035453</v>
+        <v>7035390</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5995,6 +5992,11 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-02-23</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6021,10 +6023,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122721463</v>
+        <v>122720368</v>
       </c>
       <c r="B48" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6037,34 +6039,39 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>519841</v>
+        <v>519852</v>
       </c>
       <c r="R48" t="n">
-        <v>7035417</v>
+        <v>7035392</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6101,7 +6108,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6112,31 +6119,6 @@
       </c>
       <c r="AG48" t="b">
         <v>0</v>
-      </c>
-      <c r="AH48" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ48" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK48" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM48" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO48" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
@@ -6153,10 +6135,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122721333</v>
+        <v>122720558</v>
       </c>
       <c r="B49" t="n">
-        <v>78766</v>
+        <v>57494</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6169,37 +6151,42 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>519906</v>
+        <v>519949</v>
       </c>
       <c r="R49" t="n">
-        <v>7035389</v>
+        <v>7035254</v>
       </c>
       <c r="S49" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6233,7 +6220,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Ymnigt på flera granar.</t>
+          <t>Äldre hackspår i stambasen.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6262,12 +6249,12 @@
       </c>
       <c r="AM49" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO49" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT49" t="inlineStr"/>
@@ -6285,7 +6272,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122715569</v>
+        <v>122716757</v>
       </c>
       <c r="B50" t="n">
         <v>78766</v>
@@ -6321,17 +6308,17 @@
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Djupmyren, Djupmyren, Jmt</t>
+          <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>520115</v>
+        <v>520316</v>
       </c>
       <c r="R50" t="n">
-        <v>7035562</v>
+        <v>7035491</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6361,11 +6348,6 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-02-23</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6417,7 +6399,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122717488</v>
+        <v>122715836</v>
       </c>
       <c r="B51" t="n">
         <v>79847</v>
@@ -6451,16 +6433,21 @@
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Spejkmyren, Spejkmyren, Jmt</t>
+          <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>520000</v>
+        <v>520269</v>
       </c>
       <c r="R51" t="n">
-        <v>7035297</v>
+        <v>7035574</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6519,10 +6506,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122715953</v>
+        <v>122719979</v>
       </c>
       <c r="B52" t="n">
-        <v>79848</v>
+        <v>57631</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6535,34 +6522,43 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>2081</v>
+        <v>103021</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Finnbodarna, Finnbodarna, Jmt</t>
+          <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>520254</v>
+        <v>519946</v>
       </c>
       <c r="R52" t="n">
-        <v>7035555</v>
+        <v>7035240</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6621,10 +6617,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122719875</v>
+        <v>122719697</v>
       </c>
       <c r="B53" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6637,42 +6633,37 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>519983</v>
+        <v>520026</v>
       </c>
       <c r="R53" t="n">
-        <v>7035206</v>
+        <v>7035233</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6704,11 +6695,6 @@
           <t>2025-02-23</t>
         </is>
       </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD53" t="b">
         <v>0</v>
       </c>
@@ -6717,6 +6703,31 @@
       </c>
       <c r="AG53" t="b">
         <v>0</v>
+      </c>
+      <c r="AH53" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ53" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK53" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM53" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO53" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
@@ -6733,10 +6744,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122719979</v>
+        <v>122720686</v>
       </c>
       <c r="B54" t="n">
-        <v>57631</v>
+        <v>78766</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6749,43 +6760,34 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>par i lämplig häckbiotop</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>519946</v>
+        <v>519903</v>
       </c>
       <c r="R54" t="n">
-        <v>7035240</v>
+        <v>7035224</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6828,6 +6830,31 @@
       </c>
       <c r="AG54" t="b">
         <v>0</v>
+      </c>
+      <c r="AH54" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ54" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK54" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM54" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO54" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
@@ -6844,10 +6871,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122716427</v>
+        <v>122721333</v>
       </c>
       <c r="B55" t="n">
-        <v>78767</v>
+        <v>78766</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6860,16 +6887,16 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>230405</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -6880,17 +6907,17 @@
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Finnbodarna, Finnbodarna, Jmt</t>
+          <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>520388</v>
+        <v>519906</v>
       </c>
       <c r="R55" t="n">
-        <v>7035490</v>
+        <v>7035389</v>
       </c>
       <c r="S55" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6924,7 +6951,7 @@
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Ymnigt på flera granar.</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6976,7 +7003,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122721035</v>
+        <v>122715569</v>
       </c>
       <c r="B56" t="n">
         <v>78766</v>
@@ -7012,17 +7039,17 @@
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Spejkmyren, Spejkmyren, Jmt</t>
+          <t>Djupmyren, Djupmyren, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>519897</v>
+        <v>520115</v>
       </c>
       <c r="R56" t="n">
-        <v>7035374</v>
+        <v>7035562</v>
       </c>
       <c r="S56" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -7054,6 +7081,11 @@
           <t>2025-02-23</t>
         </is>
       </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
+        </is>
+      </c>
       <c r="AD56" t="b">
         <v>0</v>
       </c>
@@ -7070,12 +7102,12 @@
       </c>
       <c r="AJ56" t="inlineStr">
         <is>
-          <t>garnlav</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM56" t="inlineStr">
@@ -7085,7 +7117,7 @@
       </c>
       <c r="AO56" t="inlineStr">
         <is>
-          <t>Branch on living tree # Alectoria sarmentosa</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT56" t="inlineStr"/>
@@ -7103,10 +7135,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122715999</v>
+        <v>122720474</v>
       </c>
       <c r="B57" t="n">
-        <v>78766</v>
+        <v>57494</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -7119,37 +7151,51 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Finnbodarna, Finnbodarna, Jmt</t>
+          <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>520311</v>
+        <v>519848</v>
       </c>
       <c r="R57" t="n">
-        <v>7035566</v>
+        <v>7035394</v>
       </c>
       <c r="S57" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -7189,31 +7235,6 @@
       </c>
       <c r="AG57" t="b">
         <v>0</v>
-      </c>
-      <c r="AH57" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ57" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK57" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM57" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO57" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
@@ -7230,10 +7251,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122720629</v>
+        <v>122716682</v>
       </c>
       <c r="B58" t="n">
-        <v>78766</v>
+        <v>57631</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7246,34 +7267,43 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>519935</v>
+        <v>520101</v>
       </c>
       <c r="R58" t="n">
-        <v>7035246</v>
+        <v>7035453</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7308,11 +7338,6 @@
           <t>2025-02-23</t>
         </is>
       </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
-        </is>
-      </c>
       <c r="AD58" t="b">
         <v>0</v>
       </c>
@@ -7321,31 +7346,6 @@
       </c>
       <c r="AG58" t="b">
         <v>0</v>
-      </c>
-      <c r="AH58" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ58" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK58" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM58" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO58" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
@@ -7362,10 +7362,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122720327</v>
+        <v>122715756</v>
       </c>
       <c r="B59" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7378,39 +7378,34 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Spejkmyren, Spejkmyren, Jmt</t>
+          <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>519838</v>
+        <v>520256</v>
       </c>
       <c r="R59" t="n">
-        <v>7035393</v>
+        <v>7035593</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7443,11 +7438,6 @@
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-02-23</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7474,7 +7464,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122715978</v>
+        <v>122715868</v>
       </c>
       <c r="B60" t="n">
         <v>79847</v>
@@ -7519,10 +7509,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>520243</v>
+        <v>520265</v>
       </c>
       <c r="R60" t="n">
-        <v>7035552</v>
+        <v>7035574</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7581,10 +7571,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122716295</v>
+        <v>122716547</v>
       </c>
       <c r="B61" t="n">
-        <v>79847</v>
+        <v>98261</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7593,31 +7583,40 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6458</v>
+        <v>504</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
@@ -7626,13 +7625,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>520378</v>
+        <v>520386</v>
       </c>
       <c r="R61" t="n">
-        <v>7035512</v>
+        <v>7035492</v>
       </c>
       <c r="S61" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7666,7 +7665,7 @@
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>Ymnig påväxt på en grovbarkad gammal sälg. Fertila bålar med apothecier.</t>
+          <t>En vinterståndare på till synes fuktig mark i en lucka.</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7681,26 +7680,6 @@
       <c r="AH61" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ61" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK61" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM61" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO61" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT61" t="inlineStr"/>
@@ -7718,10 +7697,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122715502</v>
+        <v>122715571</v>
       </c>
       <c r="B62" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7734,42 +7713,37 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="K62" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Djupmyren, Djupmyren, Jmt</t>
+          <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>520110</v>
+        <v>520216</v>
       </c>
       <c r="R62" t="n">
-        <v>7035585</v>
+        <v>7035583</v>
       </c>
       <c r="S62" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7801,11 +7775,6 @@
           <t>2025-02-23</t>
         </is>
       </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>Gott om långväxt garnlav på många granar. Vissa bålar är här fertila.</t>
-        </is>
-      </c>
       <c r="AD62" t="b">
         <v>0</v>
       </c>
@@ -7814,31 +7783,6 @@
       </c>
       <c r="AG62" t="b">
         <v>0</v>
-      </c>
-      <c r="AH62" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ62" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK62" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM62" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO62" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
@@ -7855,10 +7799,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122716757</v>
+        <v>122715841</v>
       </c>
       <c r="B63" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7871,37 +7815,42 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>520316</v>
+        <v>520229</v>
       </c>
       <c r="R63" t="n">
-        <v>7035491</v>
+        <v>7035608</v>
       </c>
       <c r="S63" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7933,6 +7882,11 @@
           <t>2025-02-23</t>
         </is>
       </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>På en björk.</t>
+        </is>
+      </c>
       <c r="AD63" t="b">
         <v>0</v>
       </c>
@@ -7949,22 +7903,22 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>björkar</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Betula</t>
         </is>
       </c>
       <c r="AM63" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO63" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Betula</t>
         </is>
       </c>
       <c r="AT63" t="inlineStr"/>
@@ -7982,10 +7936,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122720558</v>
+        <v>122715677</v>
       </c>
       <c r="B64" t="n">
-        <v>57494</v>
+        <v>79848</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7998,39 +7952,34 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100049</v>
+        <v>2081</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Spejkmyren, Spejkmyren, Jmt</t>
+          <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>519949</v>
+        <v>520221</v>
       </c>
       <c r="R64" t="n">
-        <v>7035254</v>
+        <v>7035600</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -8067,7 +8016,7 @@
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>Äldre hackspår i stambasen.</t>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8078,31 +8027,6 @@
       </c>
       <c r="AG64" t="b">
         <v>0</v>
-      </c>
-      <c r="AH64" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ64" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK64" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM64" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO64" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
@@ -8119,10 +8043,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122716645</v>
+        <v>122720469</v>
       </c>
       <c r="B65" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -8135,39 +8059,34 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>520129</v>
+        <v>519996</v>
       </c>
       <c r="R65" t="n">
-        <v>7035444</v>
+        <v>7035241</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -8202,11 +8121,6 @@
           <t>2025-02-23</t>
         </is>
       </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD65" t="b">
         <v>0</v>
       </c>
@@ -8215,6 +8129,31 @@
       </c>
       <c r="AG65" t="b">
         <v>0</v>
+      </c>
+      <c r="AH65" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ65" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK65" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM65" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO65" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
@@ -8231,7 +8170,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122715841</v>
+        <v>122715795</v>
       </c>
       <c r="B66" t="n">
         <v>79847</v>
@@ -8265,24 +8204,19 @@
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="K66" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>520229</v>
+        <v>520214</v>
       </c>
       <c r="R66" t="n">
-        <v>7035608</v>
+        <v>7035599</v>
       </c>
       <c r="S66" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -8316,7 +8250,7 @@
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>På en björk.</t>
+          <t>På en klen gran intill en lunglavssälg.</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8335,22 +8269,22 @@
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
-          <t>björkar</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK66" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM66" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO66" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Betula</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT66" t="inlineStr"/>
@@ -8368,10 +8302,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>122717294</v>
+        <v>122719648</v>
       </c>
       <c r="B67" t="n">
-        <v>90962</v>
+        <v>57478</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8384,34 +8318,39 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>520013</v>
+        <v>519939</v>
       </c>
       <c r="R67" t="n">
-        <v>7035340</v>
+        <v>7035194</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8444,6 +8383,11 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-02-23</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8470,7 +8414,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>122717616</v>
+        <v>122719371</v>
       </c>
       <c r="B68" t="n">
         <v>78766</v>
@@ -8510,13 +8454,13 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>520019</v>
+        <v>519943</v>
       </c>
       <c r="R68" t="n">
-        <v>7035352</v>
+        <v>7035270</v>
       </c>
       <c r="S68" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8546,11 +8490,6 @@
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-02-23</t>
-        </is>
-      </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8602,10 +8541,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>122715849</v>
+        <v>122716160</v>
       </c>
       <c r="B69" t="n">
-        <v>79876</v>
+        <v>78766</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8614,25 +8553,25 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8642,10 +8581,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>520268</v>
+        <v>520349</v>
       </c>
       <c r="R69" t="n">
-        <v>7035575</v>
+        <v>7035517</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8688,6 +8627,31 @@
       </c>
       <c r="AG69" t="b">
         <v>0</v>
+      </c>
+      <c r="AH69" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ69" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK69" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM69" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO69" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
@@ -8704,10 +8668,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>122720474</v>
+        <v>122715978</v>
       </c>
       <c r="B70" t="n">
-        <v>57494</v>
+        <v>79847</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8720,48 +8684,39 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L70" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>födosökande</t>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Spejkmyren, Spejkmyren, Jmt</t>
+          <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>519848</v>
+        <v>520243</v>
       </c>
       <c r="R70" t="n">
-        <v>7035394</v>
+        <v>7035552</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8820,10 +8775,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>122719533</v>
+        <v>122716329</v>
       </c>
       <c r="B71" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8836,42 +8791,42 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Spejkmyren, Spejkmyren, Jmt</t>
+          <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>519948</v>
+        <v>520374</v>
       </c>
       <c r="R71" t="n">
-        <v>7035187</v>
+        <v>7035511</v>
       </c>
       <c r="S71" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8905,7 +8860,7 @@
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>På gran intill en gammal lunglavssälg.</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8916,6 +8871,31 @@
       </c>
       <c r="AG71" t="b">
         <v>0</v>
+      </c>
+      <c r="AH71" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ71" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK71" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM71" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO71" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
@@ -8932,10 +8912,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>122715934</v>
+        <v>122716392</v>
       </c>
       <c r="B72" t="n">
-        <v>78766</v>
+        <v>79848</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8948,37 +8928,42 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>520303</v>
+        <v>520385</v>
       </c>
       <c r="R72" t="n">
-        <v>7035598</v>
+        <v>7035518</v>
       </c>
       <c r="S72" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -9012,7 +8997,7 @@
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>På gran intill en gammal sälg.</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -9064,10 +9049,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>122720869</v>
+        <v>122719829</v>
       </c>
       <c r="B73" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -9080,34 +9065,39 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P73" t="inlineStr">
         <is>
           <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>519960</v>
+        <v>519930</v>
       </c>
       <c r="R73" t="n">
-        <v>7035342</v>
+        <v>7035181</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -9142,6 +9132,11 @@
           <t>2025-02-23</t>
         </is>
       </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD73" t="b">
         <v>0</v>
       </c>
@@ -9150,31 +9145,6 @@
       </c>
       <c r="AG73" t="b">
         <v>0</v>
-      </c>
-      <c r="AH73" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ73" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK73" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM73" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO73" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
@@ -9191,10 +9161,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>122715571</v>
+        <v>122720454</v>
       </c>
       <c r="B74" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -9207,34 +9177,39 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Finnbodarna, Finnbodarna, Jmt</t>
+          <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>520216</v>
+        <v>519849</v>
       </c>
       <c r="R74" t="n">
-        <v>7035583</v>
+        <v>7035406</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -9267,6 +9242,11 @@
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-02-23</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9293,10 +9273,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>122716234</v>
+        <v>122715953</v>
       </c>
       <c r="B75" t="n">
-        <v>79847</v>
+        <v>79848</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -9309,21 +9289,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -9333,10 +9313,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>520362</v>
+        <v>520254</v>
       </c>
       <c r="R75" t="n">
-        <v>7035500</v>
+        <v>7035555</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -9371,11 +9351,6 @@
           <t>2025-02-23</t>
         </is>
       </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>På en klen gran intill en gammal sälg med lunglav.</t>
-        </is>
-      </c>
       <c r="AD75" t="b">
         <v>0</v>
       </c>
@@ -9384,31 +9359,6 @@
       </c>
       <c r="AG75" t="b">
         <v>0</v>
-      </c>
-      <c r="AH75" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ75" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK75" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM75" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO75" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
@@ -9425,10 +9375,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>122716392</v>
+        <v>122715502</v>
       </c>
       <c r="B76" t="n">
-        <v>79848</v>
+        <v>78766</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -9441,42 +9391,42 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
       <c r="K76" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Finnbodarna, Finnbodarna, Jmt</t>
+          <t>Djupmyren, Djupmyren, Jmt</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>520385</v>
+        <v>520110</v>
       </c>
       <c r="R76" t="n">
-        <v>7035518</v>
+        <v>7035585</v>
       </c>
       <c r="S76" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -9510,7 +9460,7 @@
       </c>
       <c r="AC76" t="inlineStr">
         <is>
-          <t>På gran intill en gammal sälg.</t>
+          <t>Gott om långväxt garnlav på många granar. Vissa bålar är här fertila.</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9562,10 +9512,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>122719648</v>
+        <v>122716295</v>
       </c>
       <c r="B77" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -9578,39 +9528,39 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
-      <c r="M77" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Spejkmyren, Spejkmyren, Jmt</t>
+          <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>519939</v>
+        <v>520378</v>
       </c>
       <c r="R77" t="n">
-        <v>7035194</v>
+        <v>7035512</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9647,7 +9597,7 @@
       </c>
       <c r="AC77" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ymnig påväxt på en grovbarkad gammal sälg. Fertila bålar med apothecier.</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9658,6 +9608,31 @@
       </c>
       <c r="AG77" t="b">
         <v>0</v>
+      </c>
+      <c r="AH77" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ77" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK77" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM77" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO77" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
@@ -9674,10 +9649,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>122716216</v>
+        <v>122717343</v>
       </c>
       <c r="B78" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -9690,39 +9665,39 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
-      <c r="K78" t="inlineStr">
-        <is>
-          <t>med soral</t>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Finnbodarna, Finnbodarna, Jmt</t>
+          <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>520368</v>
+        <v>520034</v>
       </c>
       <c r="R78" t="n">
-        <v>7035513</v>
+        <v>7035339</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9759,7 +9734,7 @@
       </c>
       <c r="AC78" t="inlineStr">
         <is>
-          <t>På en gammal grovbarkad sälg.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9770,31 +9745,6 @@
       </c>
       <c r="AG78" t="b">
         <v>0</v>
-      </c>
-      <c r="AH78" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ78" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK78" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM78" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO78" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
@@ -9811,10 +9761,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>122715874</v>
+        <v>122720959</v>
       </c>
       <c r="B79" t="n">
-        <v>79876</v>
+        <v>78766</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -9823,38 +9773,38 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Finnbodarna, Finnbodarna, Jmt</t>
+          <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>520265</v>
+        <v>519917</v>
       </c>
       <c r="R79" t="n">
-        <v>7035574</v>
+        <v>7035339</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9889,6 +9839,11 @@
           <t>2025-02-23</t>
         </is>
       </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>Långväxta bålar på flertalet granar.</t>
+        </is>
+      </c>
       <c r="AD79" t="b">
         <v>0</v>
       </c>
@@ -9897,6 +9852,31 @@
       </c>
       <c r="AG79" t="b">
         <v>0</v>
+      </c>
+      <c r="AH79" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ79" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK79" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM79" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO79" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
@@ -9913,10 +9893,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>122715801</v>
+        <v>122717873</v>
       </c>
       <c r="B80" t="n">
-        <v>79848</v>
+        <v>79847</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -9929,37 +9909,42 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Finnbodarna, Finnbodarna, Jmt</t>
+          <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>520266</v>
+        <v>520033</v>
       </c>
       <c r="R80" t="n">
-        <v>7035582</v>
+        <v>7035301</v>
       </c>
       <c r="S80" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -9999,6 +9984,31 @@
       </c>
       <c r="AG80" t="b">
         <v>0</v>
+      </c>
+      <c r="AH80" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ80" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK80" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM80" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO80" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
@@ -10015,10 +10025,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>122717343</v>
+        <v>122721463</v>
       </c>
       <c r="B81" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -10031,39 +10041,34 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
-      <c r="M81" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P81" t="inlineStr">
         <is>
           <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>520034</v>
+        <v>519841</v>
       </c>
       <c r="R81" t="n">
-        <v>7035339</v>
+        <v>7035417</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -10100,7 +10105,7 @@
       </c>
       <c r="AC81" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -10111,6 +10116,31 @@
       </c>
       <c r="AG81" t="b">
         <v>0</v>
+      </c>
+      <c r="AH81" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ81" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK81" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM81" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO81" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
@@ -10127,10 +10157,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>122716547</v>
+        <v>122716964</v>
       </c>
       <c r="B82" t="n">
-        <v>98261</v>
+        <v>90962</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -10139,55 +10169,41 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>504</v>
+        <v>5432</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J82" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K82" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Finnbodarna, Finnbodarna, Jmt</t>
+          <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>520386</v>
+        <v>520115</v>
       </c>
       <c r="R82" t="n">
-        <v>7035492</v>
+        <v>7035402</v>
       </c>
       <c r="S82" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -10219,11 +10235,6 @@
           <t>2025-02-23</t>
         </is>
       </c>
-      <c r="AC82" t="inlineStr">
-        <is>
-          <t>En vinterståndare på till synes fuktig mark i en lucka.</t>
-        </is>
-      </c>
       <c r="AD82" t="b">
         <v>0</v>
       </c>
@@ -10232,11 +10243,6 @@
       </c>
       <c r="AG82" t="b">
         <v>0</v>
-      </c>
-      <c r="AH82" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
@@ -10253,10 +10259,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>122716160</v>
+        <v>122717929</v>
       </c>
       <c r="B83" t="n">
-        <v>78766</v>
+        <v>79876</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -10265,41 +10271,46 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Finnbodarna, Finnbodarna, Jmt</t>
+          <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>520349</v>
+        <v>520029</v>
       </c>
       <c r="R83" t="n">
-        <v>7035517</v>
+        <v>7035292</v>
       </c>
       <c r="S83" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -10347,22 +10358,22 @@
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK83" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM83" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO83" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT83" t="inlineStr"/>
@@ -10380,10 +10391,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>122716964</v>
+        <v>122715573</v>
       </c>
       <c r="B84" t="n">
-        <v>90962</v>
+        <v>79848</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -10396,34 +10407,34 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>5432</v>
+        <v>2081</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Spejkmyren, Spejkmyren, Jmt</t>
+          <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>520115</v>
+        <v>520214</v>
       </c>
       <c r="R84" t="n">
-        <v>7035402</v>
+        <v>7035583</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -10482,7 +10493,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>122715868</v>
+        <v>122715790</v>
       </c>
       <c r="B85" t="n">
         <v>79847</v>
@@ -10527,10 +10538,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>520265</v>
+        <v>520267</v>
       </c>
       <c r="R85" t="n">
-        <v>7035574</v>
+        <v>7035581</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -10589,10 +10600,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>122720454</v>
+        <v>122715780</v>
       </c>
       <c r="B86" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -10605,39 +10616,34 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
-      <c r="M86" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Spejkmyren, Spejkmyren, Jmt</t>
+          <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>519849</v>
+        <v>520259</v>
       </c>
       <c r="R86" t="n">
-        <v>7035406</v>
+        <v>7035569</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -10674,7 +10680,7 @@
       </c>
       <c r="AC86" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>På björk</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10803,10 +10809,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>122715766</v>
+        <v>122716443</v>
       </c>
       <c r="B88" t="n">
-        <v>90962</v>
+        <v>78766</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -10819,34 +10825,48 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P88" t="inlineStr">
         <is>
           <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>520252</v>
+        <v>520251</v>
       </c>
       <c r="R88" t="n">
-        <v>7035591</v>
+        <v>7035394</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10879,6 +10899,11 @@
       <c r="AA88" t="inlineStr">
         <is>
           <t>2025-02-23</t>
+        </is>
+      </c>
+      <c r="AC88" t="inlineStr">
+        <is>
+          <t>Garnlavsrikt</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10905,7 +10930,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>122717929</v>
+        <v>122715874</v>
       </c>
       <c r="B89" t="n">
         <v>79876</v>
@@ -10939,24 +10964,19 @@
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
-      <c r="K89" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Spejkmyren, Spejkmyren, Jmt</t>
+          <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>520029</v>
+        <v>520265</v>
       </c>
       <c r="R89" t="n">
-        <v>7035292</v>
+        <v>7035574</v>
       </c>
       <c r="S89" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -10996,31 +11016,6 @@
       </c>
       <c r="AG89" t="b">
         <v>0</v>
-      </c>
-      <c r="AH89" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ89" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK89" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM89" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO89" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
@@ -11037,10 +11032,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>122715870</v>
+        <v>122718013</v>
       </c>
       <c r="B90" t="n">
-        <v>79848</v>
+        <v>57478</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -11053,34 +11048,39 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Finnbodarna, Finnbodarna, Jmt</t>
+          <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>520265</v>
+        <v>519948</v>
       </c>
       <c r="R90" t="n">
-        <v>7035574</v>
+        <v>7035313</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -11113,6 +11113,11 @@
       <c r="AA90" t="inlineStr">
         <is>
           <t>2025-02-23</t>
+        </is>
+      </c>
+      <c r="AC90" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD90" t="b">

--- a/artfynd/A 1625-2025 artfynd.xlsx
+++ b/artfynd/A 1625-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122715801</v>
+        <v>122717873</v>
       </c>
       <c r="B2" t="n">
-        <v>79848</v>
+        <v>79847</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,37 +691,42 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Finnbodarna, Finnbodarna, Jmt</t>
+          <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>520266</v>
+        <v>520033</v>
       </c>
       <c r="R2" t="n">
-        <v>7035582</v>
+        <v>7035301</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -761,6 +766,31 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -777,10 +807,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122717359</v>
+        <v>122719875</v>
       </c>
       <c r="B3" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,34 +823,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>520030</v>
+        <v>519983</v>
       </c>
       <c r="R3" t="n">
-        <v>7035341</v>
+        <v>7035206</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -853,6 +888,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-02-23</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -879,10 +919,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122720823</v>
+        <v>122715502</v>
       </c>
       <c r="B4" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,56 +935,42 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Spejkmyren, Spejkmyren, Jmt</t>
+          <t>Djupmyren, Djupmyren, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>519842</v>
+        <v>520110</v>
       </c>
       <c r="R4" t="n">
-        <v>7035388</v>
+        <v>7035585</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -978,7 +1004,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Trummande</t>
+          <t>Gott om långväxt garnlav på många granar. Vissa bålar är här fertila.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -989,6 +1015,31 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1005,10 +1056,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122720327</v>
+        <v>122721333</v>
       </c>
       <c r="B5" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1021,42 +1072,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>519838</v>
+        <v>519906</v>
       </c>
       <c r="R5" t="n">
-        <v>7035393</v>
+        <v>7035389</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1090,7 +1136,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ymnigt på flera granar.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1101,6 +1147,31 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1117,10 +1188,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122716303</v>
+        <v>122717468</v>
       </c>
       <c r="B6" t="n">
-        <v>57478</v>
+        <v>57494</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1133,16 +1204,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1150,22 +1221,26 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Finnbodarna, Hammerdal, Finnbodarna, Hammerdal, Jmt</t>
+          <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>520250</v>
+        <v>520020</v>
       </c>
       <c r="R6" t="n">
-        <v>7035363</v>
+        <v>7035330</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1198,11 +1273,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-02-23</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1229,10 +1299,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122716387</v>
+        <v>122720629</v>
       </c>
       <c r="B7" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1245,39 +1315,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Finnbodarna, Hammerdal, Finnbodarna, Hammerdal, Jmt</t>
+          <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>520278</v>
+        <v>519935</v>
       </c>
       <c r="R7" t="n">
-        <v>7035397</v>
+        <v>7035246</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1314,7 +1379,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1325,6 +1390,31 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1341,10 +1431,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122716427</v>
+        <v>122716303</v>
       </c>
       <c r="B8" t="n">
-        <v>78767</v>
+        <v>57478</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1357,37 +1447,42 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>230405</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Finnbodarna, Finnbodarna, Jmt</t>
+          <t>Finnbodarna, Hammerdal, Finnbodarna, Hammerdal, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>520388</v>
+        <v>520250</v>
       </c>
       <c r="R8" t="n">
-        <v>7035490</v>
+        <v>7035363</v>
       </c>
       <c r="S8" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1421,7 +1516,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1432,31 +1527,6 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1473,10 +1543,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122720629</v>
+        <v>122715874</v>
       </c>
       <c r="B9" t="n">
-        <v>78766</v>
+        <v>79876</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1485,38 +1555,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Spejkmyren, Spejkmyren, Jmt</t>
+          <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>519935</v>
+        <v>520265</v>
       </c>
       <c r="R9" t="n">
-        <v>7035246</v>
+        <v>7035574</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1551,11 +1621,6 @@
           <t>2025-02-23</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
@@ -1564,31 +1629,6 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1605,10 +1645,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122721035</v>
+        <v>122715836</v>
       </c>
       <c r="B10" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1621,37 +1661,42 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Spejkmyren, Spejkmyren, Jmt</t>
+          <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>519897</v>
+        <v>520269</v>
       </c>
       <c r="R10" t="n">
-        <v>7035374</v>
+        <v>7035574</v>
       </c>
       <c r="S10" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1691,31 +1736,6 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>garnlav</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Alectoria sarmentosa</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1732,10 +1752,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122717468</v>
+        <v>122715779</v>
       </c>
       <c r="B11" t="n">
-        <v>57494</v>
+        <v>79847</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1748,46 +1768,42 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Spejkmyren, Spejkmyren, Jmt</t>
+          <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>520020</v>
+        <v>520223</v>
       </c>
       <c r="R11" t="n">
-        <v>7035330</v>
+        <v>7035609</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1827,6 +1843,31 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -1843,10 +1884,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122720281</v>
+        <v>122715949</v>
       </c>
       <c r="B12" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1859,39 +1900,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Spejkmyren, Spejkmyren, Jmt</t>
+          <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>519850</v>
+        <v>520254</v>
       </c>
       <c r="R12" t="n">
-        <v>7035373</v>
+        <v>7035555</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1924,11 +1960,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-02-23</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1955,10 +1986,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122719533</v>
+        <v>122719979</v>
       </c>
       <c r="B13" t="n">
-        <v>57478</v>
+        <v>57631</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1971,27 +2002,31 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>par i lämplig häckbiotop</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -2000,10 +2035,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>519948</v>
+        <v>519946</v>
       </c>
       <c r="R13" t="n">
-        <v>7035187</v>
+        <v>7035240</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2036,11 +2071,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-02-23</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2067,10 +2097,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122716801</v>
+        <v>122716269</v>
       </c>
       <c r="B14" t="n">
-        <v>57631</v>
+        <v>57478</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2083,43 +2113,39 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>par i lämplig häckbiotop</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Spejkmyren, Spejkmyren, Jmt</t>
+          <t>Finnbodarna, Hammerdal, Finnbodarna, Hammerdal, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>520083</v>
+        <v>520256</v>
       </c>
       <c r="R14" t="n">
-        <v>7035403</v>
+        <v>7035380</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2152,6 +2178,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-02-23</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2178,10 +2209,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122716645</v>
+        <v>122721463</v>
       </c>
       <c r="B15" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2194,39 +2225,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>520129</v>
+        <v>519841</v>
       </c>
       <c r="R15" t="n">
-        <v>7035444</v>
+        <v>7035417</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2263,7 +2289,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2274,6 +2300,31 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM15" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
@@ -2290,10 +2341,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122715648</v>
+        <v>122719371</v>
       </c>
       <c r="B16" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2306,42 +2357,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Finnbodarna, Hammerdal, Finnbodarna, Hammerdal, Jmt</t>
+          <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>520219</v>
+        <v>519943</v>
       </c>
       <c r="R16" t="n">
-        <v>7035597</v>
+        <v>7035270</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2373,11 +2419,6 @@
           <t>2025-02-23</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
@@ -2386,6 +2427,31 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM16" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
@@ -2402,10 +2468,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122719875</v>
+        <v>122716850</v>
       </c>
       <c r="B17" t="n">
-        <v>57478</v>
+        <v>90962</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2418,39 +2484,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>519983</v>
+        <v>520101</v>
       </c>
       <c r="R17" t="n">
-        <v>7035206</v>
+        <v>7035388</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2483,11 +2544,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-02-23</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2514,10 +2570,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122715849</v>
+        <v>122716160</v>
       </c>
       <c r="B18" t="n">
-        <v>79876</v>
+        <v>78766</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2526,25 +2582,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2554,10 +2610,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>520268</v>
+        <v>520349</v>
       </c>
       <c r="R18" t="n">
-        <v>7035575</v>
+        <v>7035517</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2600,6 +2656,31 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM18" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2616,10 +2697,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122716850</v>
+        <v>122716757</v>
       </c>
       <c r="B19" t="n">
-        <v>90962</v>
+        <v>78766</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2632,37 +2713,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Spejkmyren, Spejkmyren, Jmt</t>
+          <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>520101</v>
+        <v>520316</v>
       </c>
       <c r="R19" t="n">
-        <v>7035388</v>
+        <v>7035491</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2702,6 +2783,31 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM19" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -2718,10 +2824,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122717989</v>
+        <v>122720469</v>
       </c>
       <c r="B20" t="n">
-        <v>57494</v>
+        <v>78766</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2734,43 +2840,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>519951</v>
+        <v>519996</v>
       </c>
       <c r="R20" t="n">
-        <v>7035320</v>
+        <v>7035241</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2805,11 +2902,6 @@
           <t>2025-02-23</t>
         </is>
       </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Trummande</t>
-        </is>
-      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
@@ -2818,6 +2910,31 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM20" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
@@ -2834,10 +2951,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122715757</v>
+        <v>122715790</v>
       </c>
       <c r="B21" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2850,34 +2967,39 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>520234</v>
+        <v>520267</v>
       </c>
       <c r="R21" t="n">
-        <v>7035595</v>
+        <v>7035581</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2912,11 +3034,6 @@
           <t>2025-02-23</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
-        </is>
-      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
@@ -2925,31 +3042,6 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
-      </c>
-      <c r="AH21" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -2966,7 +3058,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122716216</v>
+        <v>122715795</v>
       </c>
       <c r="B22" t="n">
         <v>79847</v>
@@ -3000,24 +3092,19 @@
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>520368</v>
+        <v>520214</v>
       </c>
       <c r="R22" t="n">
-        <v>7035513</v>
+        <v>7035599</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3051,7 +3138,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>På en gammal grovbarkad sälg.</t>
+          <t>På en klen gran intill en lunglavssälg.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3070,22 +3157,22 @@
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT22" t="inlineStr"/>
@@ -3103,10 +3190,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122715669</v>
+        <v>122716387</v>
       </c>
       <c r="B23" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3119,39 +3206,39 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Finnbodarna, Finnbodarna, Jmt</t>
+          <t>Finnbodarna, Hammerdal, Finnbodarna, Hammerdal, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>520221</v>
+        <v>520278</v>
       </c>
       <c r="R23" t="n">
-        <v>7035600</v>
+        <v>7035397</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3184,6 +3271,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-02-23</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3210,10 +3302,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122715775</v>
+        <v>122716293</v>
       </c>
       <c r="B24" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3226,39 +3318,39 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Finnbodarna, Finnbodarna, Jmt</t>
+          <t>Finnbodarna, Hammerdal, Finnbodarna, Hammerdal, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>520252</v>
+        <v>520249</v>
       </c>
       <c r="R24" t="n">
-        <v>7035576</v>
+        <v>7035364</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3295,7 +3387,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>På björk</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3322,10 +3414,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122715766</v>
+        <v>122716673</v>
       </c>
       <c r="B25" t="n">
-        <v>90962</v>
+        <v>57478</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3338,34 +3430,39 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Finnbodarna, Finnbodarna, Jmt</t>
+          <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>520252</v>
+        <v>520108</v>
       </c>
       <c r="R25" t="n">
-        <v>7035591</v>
+        <v>7035462</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3398,6 +3495,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-02-23</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3424,10 +3526,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122717294</v>
+        <v>122720889</v>
       </c>
       <c r="B26" t="n">
-        <v>90962</v>
+        <v>57478</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3440,34 +3542,39 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>520013</v>
+        <v>519841</v>
       </c>
       <c r="R26" t="n">
-        <v>7035340</v>
+        <v>7035390</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3500,6 +3607,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-02-23</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3526,10 +3638,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122717446</v>
+        <v>122715953</v>
       </c>
       <c r="B27" t="n">
-        <v>90962</v>
+        <v>79848</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3542,34 +3654,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5432</v>
+        <v>2081</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Spejkmyren, Spejkmyren, Jmt</t>
+          <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>520006</v>
+        <v>520254</v>
       </c>
       <c r="R27" t="n">
-        <v>7035303</v>
+        <v>7035555</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3628,10 +3740,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122720065</v>
+        <v>122716682</v>
       </c>
       <c r="B28" t="n">
-        <v>78766</v>
+        <v>57631</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3644,37 +3756,46 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>520062</v>
+        <v>520101</v>
       </c>
       <c r="R28" t="n">
-        <v>7035232</v>
+        <v>7035453</v>
       </c>
       <c r="S28" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3714,31 +3835,6 @@
       </c>
       <c r="AG28" t="b">
         <v>0</v>
-      </c>
-      <c r="AH28" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ28" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK28" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM28" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO28" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
@@ -3755,10 +3851,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122715949</v>
+        <v>122719697</v>
       </c>
       <c r="B29" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3771,37 +3867,37 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Finnbodarna, Finnbodarna, Jmt</t>
+          <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>520254</v>
+        <v>520026</v>
       </c>
       <c r="R29" t="n">
-        <v>7035555</v>
+        <v>7035233</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3841,6 +3937,31 @@
       </c>
       <c r="AG29" t="b">
         <v>0</v>
+      </c>
+      <c r="AH29" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM29" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
@@ -3857,10 +3978,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122717164</v>
+        <v>122715677</v>
       </c>
       <c r="B30" t="n">
-        <v>78766</v>
+        <v>79848</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3873,34 +3994,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Spejkmyren, Spejkmyren, Jmt</t>
+          <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>520120</v>
+        <v>520221</v>
       </c>
       <c r="R30" t="n">
-        <v>7035405</v>
+        <v>7035600</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3935,6 +4056,11 @@
           <t>2025-02-23</t>
         </is>
       </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>På gran</t>
+        </is>
+      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
@@ -3943,31 +4069,6 @@
       </c>
       <c r="AG30" t="b">
         <v>0</v>
-      </c>
-      <c r="AH30" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ30" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK30" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM30" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO30" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
@@ -3984,10 +4085,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122719554</v>
+        <v>122716329</v>
       </c>
       <c r="B31" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4000,47 +4101,42 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Spejkmyren, Spejkmyren, Jmt</t>
+          <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>519981</v>
+        <v>520374</v>
       </c>
       <c r="R31" t="n">
-        <v>7035221</v>
+        <v>7035511</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4074,7 +4170,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Äldre ringhack som bedöms vara 5 - 10 år gamla.</t>
+          <t>På gran intill en gammal lunglavssälg.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4103,12 +4199,12 @@
       </c>
       <c r="AM31" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4126,10 +4222,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122715870</v>
+        <v>122715868</v>
       </c>
       <c r="B32" t="n">
-        <v>79848</v>
+        <v>79847</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4142,24 +4238,29 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Finnbodarna, Finnbodarna, Jmt</t>
@@ -4228,7 +4329,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122715778</v>
+        <v>122717488</v>
       </c>
       <c r="B33" t="n">
         <v>79847</v>
@@ -4262,21 +4363,16 @@
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Finnbodarna, Finnbodarna, Jmt</t>
+          <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>520259</v>
+        <v>520000</v>
       </c>
       <c r="R33" t="n">
-        <v>7035574</v>
+        <v>7035297</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4335,10 +4431,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122717616</v>
+        <v>122715780</v>
       </c>
       <c r="B34" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4351,34 +4447,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Spejkmyren, Spejkmyren, Jmt</t>
+          <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>520019</v>
+        <v>520259</v>
       </c>
       <c r="R34" t="n">
-        <v>7035352</v>
+        <v>7035569</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4415,7 +4511,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Rikligt.</t>
+          <t>På björk</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4426,31 +4522,6 @@
       </c>
       <c r="AG34" t="b">
         <v>0</v>
-      </c>
-      <c r="AH34" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ34" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK34" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM34" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO34" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
@@ -4467,10 +4538,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122716234</v>
+        <v>122720281</v>
       </c>
       <c r="B35" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4483,34 +4554,39 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Finnbodarna, Finnbodarna, Jmt</t>
+          <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>520362</v>
+        <v>519850</v>
       </c>
       <c r="R35" t="n">
-        <v>7035500</v>
+        <v>7035373</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4547,7 +4623,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>På en klen gran intill en gammal sälg med lunglav.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4558,31 +4634,6 @@
       </c>
       <c r="AG35" t="b">
         <v>0</v>
-      </c>
-      <c r="AH35" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ35" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK35" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM35" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO35" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
@@ -4599,10 +4650,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122716673</v>
+        <v>122716964</v>
       </c>
       <c r="B36" t="n">
-        <v>57478</v>
+        <v>90962</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4615,39 +4666,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>520108</v>
+        <v>520115</v>
       </c>
       <c r="R36" t="n">
-        <v>7035462</v>
+        <v>7035402</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4680,11 +4726,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-02-23</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4711,10 +4752,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122717636</v>
+        <v>122715934</v>
       </c>
       <c r="B37" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4727,42 +4768,37 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Spejkmyren, Spejkmyren, Jmt</t>
+          <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>519970</v>
+        <v>520303</v>
       </c>
       <c r="R37" t="n">
-        <v>7035297</v>
+        <v>7035598</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4796,7 +4832,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4807,6 +4843,31 @@
       </c>
       <c r="AG37" t="b">
         <v>0</v>
+      </c>
+      <c r="AH37" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ37" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK37" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM37" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO37" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
@@ -4823,10 +4884,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122720427</v>
+        <v>122715978</v>
       </c>
       <c r="B38" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4839,39 +4900,39 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Spejkmyren, Spejkmyren, Jmt</t>
+          <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>519846</v>
+        <v>520243</v>
       </c>
       <c r="R38" t="n">
-        <v>7035407</v>
+        <v>7035552</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4904,11 +4965,6 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-02-23</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4935,7 +4991,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122716293</v>
+        <v>122715648</v>
       </c>
       <c r="B39" t="n">
         <v>57478</v>
@@ -4980,10 +5036,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>520249</v>
+        <v>520219</v>
       </c>
       <c r="R39" t="n">
-        <v>7035364</v>
+        <v>7035597</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5047,10 +5103,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122720869</v>
+        <v>122717929</v>
       </c>
       <c r="B40" t="n">
-        <v>78766</v>
+        <v>79876</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5059,41 +5115,46 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>519960</v>
+        <v>520029</v>
       </c>
       <c r="R40" t="n">
-        <v>7035342</v>
+        <v>7035292</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5141,22 +5202,22 @@
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK40" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM40" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO40" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -5174,10 +5235,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122715999</v>
+        <v>122715841</v>
       </c>
       <c r="B41" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5190,37 +5251,42 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>520311</v>
+        <v>520229</v>
       </c>
       <c r="R41" t="n">
-        <v>7035566</v>
+        <v>7035608</v>
       </c>
       <c r="S41" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5252,6 +5318,11 @@
           <t>2025-02-23</t>
         </is>
       </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>På en björk.</t>
+        </is>
+      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
@@ -5268,22 +5339,22 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>björkar</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Betula</t>
         </is>
       </c>
       <c r="AM41" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO41" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Betula</t>
         </is>
       </c>
       <c r="AT41" t="inlineStr"/>
@@ -5301,10 +5372,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122715779</v>
+        <v>122720548</v>
       </c>
       <c r="B42" t="n">
-        <v>79847</v>
+        <v>90962</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5317,42 +5388,37 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Finnbodarna, Finnbodarna, Jmt</t>
+          <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>520223</v>
+        <v>519847</v>
       </c>
       <c r="R42" t="n">
-        <v>7035609</v>
+        <v>7035432</v>
       </c>
       <c r="S42" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5392,31 +5458,6 @@
       </c>
       <c r="AG42" t="b">
         <v>0</v>
-      </c>
-      <c r="AH42" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ42" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK42" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM42" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO42" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
@@ -5433,10 +5474,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122717488</v>
+        <v>122717294</v>
       </c>
       <c r="B43" t="n">
-        <v>79847</v>
+        <v>90962</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5449,21 +5490,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5473,10 +5514,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>520000</v>
+        <v>520013</v>
       </c>
       <c r="R43" t="n">
-        <v>7035297</v>
+        <v>7035340</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5535,7 +5576,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122717284</v>
+        <v>122715757</v>
       </c>
       <c r="B44" t="n">
         <v>78766</v>
@@ -5571,17 +5612,17 @@
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Spejkmyren, Spejkmyren, Jmt</t>
+          <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>520031</v>
+        <v>520234</v>
       </c>
       <c r="R44" t="n">
-        <v>7035353</v>
+        <v>7035595</v>
       </c>
       <c r="S44" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5615,7 +5656,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Långväxta bålar på flertalet granar.</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5667,10 +5708,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122715934</v>
+        <v>122715870</v>
       </c>
       <c r="B45" t="n">
-        <v>78766</v>
+        <v>79848</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5683,21 +5724,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5707,13 +5748,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>520303</v>
+        <v>520265</v>
       </c>
       <c r="R45" t="n">
-        <v>7035598</v>
+        <v>7035574</v>
       </c>
       <c r="S45" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5745,11 +5786,6 @@
           <t>2025-02-23</t>
         </is>
       </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
-        </is>
-      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
@@ -5758,31 +5794,6 @@
       </c>
       <c r="AG45" t="b">
         <v>0</v>
-      </c>
-      <c r="AH45" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ45" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK45" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM45" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO45" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
@@ -5799,7 +5810,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122716269</v>
+        <v>122719648</v>
       </c>
       <c r="B46" t="n">
         <v>57478</v>
@@ -5840,14 +5851,14 @@
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Finnbodarna, Hammerdal, Finnbodarna, Hammerdal, Jmt</t>
+          <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>520256</v>
+        <v>519939</v>
       </c>
       <c r="R46" t="n">
-        <v>7035380</v>
+        <v>7035194</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5911,10 +5922,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122720889</v>
+        <v>122715766</v>
       </c>
       <c r="B47" t="n">
-        <v>57478</v>
+        <v>90962</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5927,39 +5938,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Spejkmyren, Spejkmyren, Jmt</t>
+          <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>519841</v>
+        <v>520252</v>
       </c>
       <c r="R47" t="n">
-        <v>7035390</v>
+        <v>7035591</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5992,11 +5998,6 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-02-23</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6023,10 +6024,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122720368</v>
+        <v>122716392</v>
       </c>
       <c r="B48" t="n">
-        <v>57478</v>
+        <v>79848</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6039,42 +6040,42 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Spejkmyren, Spejkmyren, Jmt</t>
+          <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>519852</v>
+        <v>520385</v>
       </c>
       <c r="R48" t="n">
-        <v>7035392</v>
+        <v>7035518</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6108,7 +6109,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>På gran intill en gammal sälg.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6119,6 +6120,31 @@
       </c>
       <c r="AG48" t="b">
         <v>0</v>
+      </c>
+      <c r="AH48" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ48" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK48" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM48" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO48" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
@@ -6135,10 +6161,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122720558</v>
+        <v>122715756</v>
       </c>
       <c r="B49" t="n">
-        <v>57494</v>
+        <v>79847</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6151,39 +6177,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Spejkmyren, Spejkmyren, Jmt</t>
+          <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>519949</v>
+        <v>520256</v>
       </c>
       <c r="R49" t="n">
-        <v>7035254</v>
+        <v>7035593</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6218,11 +6239,6 @@
           <t>2025-02-23</t>
         </is>
       </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Äldre hackspår i stambasen.</t>
-        </is>
-      </c>
       <c r="AD49" t="b">
         <v>0</v>
       </c>
@@ -6231,31 +6247,6 @@
       </c>
       <c r="AG49" t="b">
         <v>0</v>
-      </c>
-      <c r="AH49" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ49" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK49" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM49" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO49" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
@@ -6272,10 +6263,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122716757</v>
+        <v>122720327</v>
       </c>
       <c r="B50" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6288,37 +6279,42 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Finnbodarna, Finnbodarna, Jmt</t>
+          <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>520316</v>
+        <v>519838</v>
       </c>
       <c r="R50" t="n">
-        <v>7035491</v>
+        <v>7035393</v>
       </c>
       <c r="S50" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6350,6 +6346,11 @@
           <t>2025-02-23</t>
         </is>
       </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD50" t="b">
         <v>0</v>
       </c>
@@ -6358,31 +6359,6 @@
       </c>
       <c r="AG50" t="b">
         <v>0</v>
-      </c>
-      <c r="AH50" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ50" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK50" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM50" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO50" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
@@ -6399,10 +6375,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122715836</v>
+        <v>122720368</v>
       </c>
       <c r="B51" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6415,39 +6391,39 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Finnbodarna, Finnbodarna, Jmt</t>
+          <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>520269</v>
+        <v>519852</v>
       </c>
       <c r="R51" t="n">
-        <v>7035574</v>
+        <v>7035392</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6480,6 +6456,11 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-02-23</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6506,10 +6487,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122719979</v>
+        <v>122720823</v>
       </c>
       <c r="B52" t="n">
-        <v>57631</v>
+        <v>57478</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6522,31 +6503,41 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>hona</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>par i lämplig häckbiotop</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
@@ -6555,10 +6546,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>519946</v>
+        <v>519842</v>
       </c>
       <c r="R52" t="n">
-        <v>7035240</v>
+        <v>7035388</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6591,6 +6582,11 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-02-23</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Trummande</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6617,10 +6613,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122719697</v>
+        <v>122720558</v>
       </c>
       <c r="B53" t="n">
-        <v>78766</v>
+        <v>57494</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6633,37 +6629,42 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>520026</v>
+        <v>519949</v>
       </c>
       <c r="R53" t="n">
-        <v>7035233</v>
+        <v>7035254</v>
       </c>
       <c r="S53" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6695,6 +6696,11 @@
           <t>2025-02-23</t>
         </is>
       </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Äldre hackspår i stambasen.</t>
+        </is>
+      </c>
       <c r="AD53" t="b">
         <v>0</v>
       </c>
@@ -6721,12 +6727,12 @@
       </c>
       <c r="AM53" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO53" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT53" t="inlineStr"/>
@@ -6744,10 +6750,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122720686</v>
+        <v>122715669</v>
       </c>
       <c r="B54" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6760,34 +6766,39 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Spejkmyren, Spejkmyren, Jmt</t>
+          <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>519903</v>
+        <v>520221</v>
       </c>
       <c r="R54" t="n">
-        <v>7035224</v>
+        <v>7035600</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6830,31 +6841,6 @@
       </c>
       <c r="AG54" t="b">
         <v>0</v>
-      </c>
-      <c r="AH54" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ54" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK54" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM54" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO54" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
@@ -6871,10 +6857,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122721333</v>
+        <v>122716295</v>
       </c>
       <c r="B55" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6887,37 +6873,42 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Spejkmyren, Spejkmyren, Jmt</t>
+          <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>519906</v>
+        <v>520378</v>
       </c>
       <c r="R55" t="n">
-        <v>7035389</v>
+        <v>7035512</v>
       </c>
       <c r="S55" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6951,7 +6942,7 @@
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>Ymnigt på flera granar.</t>
+          <t>Ymnig påväxt på en grovbarkad gammal sälg. Fertila bålar med apothecier.</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6970,22 +6961,22 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM55" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO55" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT55" t="inlineStr"/>
@@ -7003,7 +6994,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122715569</v>
+        <v>122716443</v>
       </c>
       <c r="B56" t="n">
         <v>78766</v>
@@ -7036,17 +7027,31 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I56" t="inlineStr"/>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Djupmyren, Djupmyren, Jmt</t>
+          <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>520115</v>
+        <v>520251</v>
       </c>
       <c r="R56" t="n">
-        <v>7035562</v>
+        <v>7035394</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7083,7 +7088,7 @@
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Garnlavsrikt</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7094,31 +7099,6 @@
       </c>
       <c r="AG56" t="b">
         <v>0</v>
-      </c>
-      <c r="AH56" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ56" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK56" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM56" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO56" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
@@ -7135,10 +7115,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122720474</v>
+        <v>122720869</v>
       </c>
       <c r="B57" t="n">
-        <v>57494</v>
+        <v>78766</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -7151,48 +7131,34 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L57" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>519848</v>
+        <v>519960</v>
       </c>
       <c r="R57" t="n">
-        <v>7035394</v>
+        <v>7035342</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7235,6 +7201,31 @@
       </c>
       <c r="AG57" t="b">
         <v>0</v>
+      </c>
+      <c r="AH57" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ57" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK57" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM57" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO57" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
@@ -7251,10 +7242,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122716682</v>
+        <v>122715999</v>
       </c>
       <c r="B58" t="n">
-        <v>57631</v>
+        <v>78766</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7267,46 +7258,37 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>par i lämplig häckbiotop</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Spejkmyren, Spejkmyren, Jmt</t>
+          <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>520101</v>
+        <v>520311</v>
       </c>
       <c r="R58" t="n">
-        <v>7035453</v>
+        <v>7035566</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7346,6 +7328,31 @@
       </c>
       <c r="AG58" t="b">
         <v>0</v>
+      </c>
+      <c r="AH58" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ58" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK58" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM58" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO58" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
@@ -7362,10 +7369,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122715756</v>
+        <v>122720454</v>
       </c>
       <c r="B59" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7378,34 +7385,39 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Finnbodarna, Finnbodarna, Jmt</t>
+          <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>520256</v>
+        <v>519849</v>
       </c>
       <c r="R59" t="n">
-        <v>7035593</v>
+        <v>7035406</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7438,6 +7450,11 @@
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-02-23</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7464,10 +7481,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122715868</v>
+        <v>122721035</v>
       </c>
       <c r="B60" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7480,42 +7497,37 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="K60" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Finnbodarna, Finnbodarna, Jmt</t>
+          <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>520265</v>
+        <v>519897</v>
       </c>
       <c r="R60" t="n">
-        <v>7035574</v>
+        <v>7035374</v>
       </c>
       <c r="S60" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7555,6 +7567,31 @@
       </c>
       <c r="AG60" t="b">
         <v>0</v>
+      </c>
+      <c r="AH60" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ60" t="inlineStr">
+        <is>
+          <t>garnlav</t>
+        </is>
+      </c>
+      <c r="AK60" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="AM60" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO60" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Alectoria sarmentosa</t>
+        </is>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
@@ -7571,10 +7608,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122716547</v>
+        <v>122715849</v>
       </c>
       <c r="B61" t="n">
-        <v>98261</v>
+        <v>79876</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7587,51 +7624,37 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>504</v>
+        <v>6462</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K61" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>520386</v>
+        <v>520268</v>
       </c>
       <c r="R61" t="n">
-        <v>7035492</v>
+        <v>7035575</v>
       </c>
       <c r="S61" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7663,11 +7686,6 @@
           <t>2025-02-23</t>
         </is>
       </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>En vinterståndare på till synes fuktig mark i en lucka.</t>
-        </is>
-      </c>
       <c r="AD61" t="b">
         <v>0</v>
       </c>
@@ -7676,11 +7694,6 @@
       </c>
       <c r="AG61" t="b">
         <v>0</v>
-      </c>
-      <c r="AH61" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
@@ -7697,7 +7710,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122715571</v>
+        <v>122717359</v>
       </c>
       <c r="B62" t="n">
         <v>79847</v>
@@ -7733,14 +7746,14 @@
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Finnbodarna, Finnbodarna, Jmt</t>
+          <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>520216</v>
+        <v>520030</v>
       </c>
       <c r="R62" t="n">
-        <v>7035583</v>
+        <v>7035341</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7799,7 +7812,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122715841</v>
+        <v>122716234</v>
       </c>
       <c r="B63" t="n">
         <v>79847</v>
@@ -7833,24 +7846,19 @@
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="K63" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>520229</v>
+        <v>520362</v>
       </c>
       <c r="R63" t="n">
-        <v>7035608</v>
+        <v>7035500</v>
       </c>
       <c r="S63" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7884,7 +7892,7 @@
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>På en björk.</t>
+          <t>På en klen gran intill en gammal sälg med lunglav.</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7903,22 +7911,22 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>björkar</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM63" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO63" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Betula</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT63" t="inlineStr"/>
@@ -7936,10 +7944,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122715677</v>
+        <v>122718013</v>
       </c>
       <c r="B64" t="n">
-        <v>79848</v>
+        <v>57478</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7952,34 +7960,39 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Finnbodarna, Finnbodarna, Jmt</t>
+          <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>520221</v>
+        <v>519948</v>
       </c>
       <c r="R64" t="n">
-        <v>7035600</v>
+        <v>7035313</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -8016,7 +8029,7 @@
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>På gran</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8043,10 +8056,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122720469</v>
+        <v>122717343</v>
       </c>
       <c r="B65" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -8059,34 +8072,39 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>519996</v>
+        <v>520034</v>
       </c>
       <c r="R65" t="n">
-        <v>7035241</v>
+        <v>7035339</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -8121,6 +8139,11 @@
           <t>2025-02-23</t>
         </is>
       </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD65" t="b">
         <v>0</v>
       </c>
@@ -8129,31 +8152,6 @@
       </c>
       <c r="AG65" t="b">
         <v>0</v>
-      </c>
-      <c r="AH65" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ65" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK65" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM65" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO65" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
@@ -8170,10 +8168,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122715795</v>
+        <v>122719554</v>
       </c>
       <c r="B66" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -8186,37 +8184,47 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Finnbodarna, Finnbodarna, Jmt</t>
+          <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>520214</v>
+        <v>519981</v>
       </c>
       <c r="R66" t="n">
-        <v>7035599</v>
+        <v>7035221</v>
       </c>
       <c r="S66" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -8250,7 +8258,7 @@
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>På en klen gran intill en lunglavssälg.</t>
+          <t>Äldre ringhack som bedöms vara 5 - 10 år gamla.</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8279,12 +8287,12 @@
       </c>
       <c r="AM66" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO66" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT66" t="inlineStr"/>
@@ -8302,10 +8310,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>122719648</v>
+        <v>122715801</v>
       </c>
       <c r="B67" t="n">
-        <v>57478</v>
+        <v>79848</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8318,39 +8326,34 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Spejkmyren, Spejkmyren, Jmt</t>
+          <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>519939</v>
+        <v>520266</v>
       </c>
       <c r="R67" t="n">
-        <v>7035194</v>
+        <v>7035582</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8383,11 +8386,6 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-02-23</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8414,10 +8412,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>122719371</v>
+        <v>122717989</v>
       </c>
       <c r="B68" t="n">
-        <v>78766</v>
+        <v>57494</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8430,37 +8428,46 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>519943</v>
+        <v>519951</v>
       </c>
       <c r="R68" t="n">
-        <v>7035270</v>
+        <v>7035320</v>
       </c>
       <c r="S68" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8492,6 +8499,11 @@
           <t>2025-02-23</t>
         </is>
       </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Trummande</t>
+        </is>
+      </c>
       <c r="AD68" t="b">
         <v>0</v>
       </c>
@@ -8500,31 +8512,6 @@
       </c>
       <c r="AG68" t="b">
         <v>0</v>
-      </c>
-      <c r="AH68" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ68" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK68" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM68" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO68" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
@@ -8541,10 +8528,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>122716160</v>
+        <v>122719829</v>
       </c>
       <c r="B69" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8557,34 +8544,39 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Finnbodarna, Finnbodarna, Jmt</t>
+          <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>520349</v>
+        <v>519930</v>
       </c>
       <c r="R69" t="n">
-        <v>7035517</v>
+        <v>7035181</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8619,6 +8611,11 @@
           <t>2025-02-23</t>
         </is>
       </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD69" t="b">
         <v>0</v>
       </c>
@@ -8627,31 +8624,6 @@
       </c>
       <c r="AG69" t="b">
         <v>0</v>
-      </c>
-      <c r="AH69" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ69" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK69" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM69" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO69" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
@@ -8668,10 +8640,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>122715978</v>
+        <v>122716801</v>
       </c>
       <c r="B70" t="n">
-        <v>79847</v>
+        <v>57631</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8684,39 +8656,43 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr"/>
-      <c r="K70" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
         </is>
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Finnbodarna, Finnbodarna, Jmt</t>
+          <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>520243</v>
+        <v>520083</v>
       </c>
       <c r="R70" t="n">
-        <v>7035552</v>
+        <v>7035403</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8775,10 +8751,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>122716329</v>
+        <v>122717164</v>
       </c>
       <c r="B71" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8791,42 +8767,37 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="K71" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Finnbodarna, Finnbodarna, Jmt</t>
+          <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>520374</v>
+        <v>520120</v>
       </c>
       <c r="R71" t="n">
-        <v>7035511</v>
+        <v>7035405</v>
       </c>
       <c r="S71" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8856,11 +8827,6 @@
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-02-23</t>
-        </is>
-      </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>På gran intill en gammal lunglavssälg.</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8912,10 +8878,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>122716392</v>
+        <v>122719533</v>
       </c>
       <c r="B72" t="n">
-        <v>79848</v>
+        <v>57478</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8928,42 +8894,42 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="K72" t="inlineStr">
-        <is>
-          <t>med soral</t>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Finnbodarna, Finnbodarna, Jmt</t>
+          <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>520385</v>
+        <v>519948</v>
       </c>
       <c r="R72" t="n">
-        <v>7035518</v>
+        <v>7035187</v>
       </c>
       <c r="S72" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8997,7 +8963,7 @@
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>På gran intill en gammal sälg.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -9008,31 +8974,6 @@
       </c>
       <c r="AG72" t="b">
         <v>0</v>
-      </c>
-      <c r="AH72" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ72" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK72" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM72" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO72" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
@@ -9049,10 +8990,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>122719829</v>
+        <v>122715775</v>
       </c>
       <c r="B73" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -9065,39 +9006,39 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Spejkmyren, Spejkmyren, Jmt</t>
+          <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>519930</v>
+        <v>520252</v>
       </c>
       <c r="R73" t="n">
-        <v>7035181</v>
+        <v>7035576</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -9134,7 +9075,7 @@
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>På björk</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -9161,10 +9102,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>122720454</v>
+        <v>122715778</v>
       </c>
       <c r="B74" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -9177,39 +9118,39 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
-      <c r="M74" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Spejkmyren, Spejkmyren, Jmt</t>
+          <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>519849</v>
+        <v>520259</v>
       </c>
       <c r="R74" t="n">
-        <v>7035406</v>
+        <v>7035574</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -9242,11 +9183,6 @@
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-02-23</t>
-        </is>
-      </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9273,7 +9209,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>122715953</v>
+        <v>122715573</v>
       </c>
       <c r="B75" t="n">
         <v>79848</v>
@@ -9313,10 +9249,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>520254</v>
+        <v>520214</v>
       </c>
       <c r="R75" t="n">
-        <v>7035555</v>
+        <v>7035583</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -9375,7 +9311,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>122715502</v>
+        <v>122720686</v>
       </c>
       <c r="B76" t="n">
         <v>78766</v>
@@ -9409,24 +9345,19 @@
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
-      <c r="K76" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Djupmyren, Djupmyren, Jmt</t>
+          <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>520110</v>
+        <v>519903</v>
       </c>
       <c r="R76" t="n">
-        <v>7035585</v>
+        <v>7035224</v>
       </c>
       <c r="S76" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -9456,11 +9387,6 @@
       <c r="AA76" t="inlineStr">
         <is>
           <t>2025-02-23</t>
-        </is>
-      </c>
-      <c r="AC76" t="inlineStr">
-        <is>
-          <t>Gott om långväxt garnlav på många granar. Vissa bålar är här fertila.</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9512,10 +9438,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>122716295</v>
+        <v>122720474</v>
       </c>
       <c r="B77" t="n">
-        <v>79847</v>
+        <v>57494</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -9528,39 +9454,48 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr"/>
-      <c r="K77" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Finnbodarna, Finnbodarna, Jmt</t>
+          <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>520378</v>
+        <v>519848</v>
       </c>
       <c r="R77" t="n">
-        <v>7035512</v>
+        <v>7035394</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9595,11 +9530,6 @@
           <t>2025-02-23</t>
         </is>
       </c>
-      <c r="AC77" t="inlineStr">
-        <is>
-          <t>Ymnig påväxt på en grovbarkad gammal sälg. Fertila bålar med apothecier.</t>
-        </is>
-      </c>
       <c r="AD77" t="b">
         <v>0</v>
       </c>
@@ -9608,31 +9538,6 @@
       </c>
       <c r="AG77" t="b">
         <v>0</v>
-      </c>
-      <c r="AH77" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ77" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK77" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM77" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO77" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
@@ -9649,10 +9554,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>122717343</v>
+        <v>122717446</v>
       </c>
       <c r="B78" t="n">
-        <v>57478</v>
+        <v>90962</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -9665,39 +9570,34 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
-      <c r="M78" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P78" t="inlineStr">
         <is>
           <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>520034</v>
+        <v>520006</v>
       </c>
       <c r="R78" t="n">
-        <v>7035339</v>
+        <v>7035303</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9730,11 +9630,6 @@
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-02-23</t>
-        </is>
-      </c>
-      <c r="AC78" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9761,7 +9656,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>122720959</v>
+        <v>122717616</v>
       </c>
       <c r="B79" t="n">
         <v>78766</v>
@@ -9801,10 +9696,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>519917</v>
+        <v>520019</v>
       </c>
       <c r="R79" t="n">
-        <v>7035339</v>
+        <v>7035352</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9841,7 +9736,7 @@
       </c>
       <c r="AC79" t="inlineStr">
         <is>
-          <t>Långväxta bålar på flertalet granar.</t>
+          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9893,7 +9788,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>122717873</v>
+        <v>122715571</v>
       </c>
       <c r="B80" t="n">
         <v>79847</v>
@@ -9927,24 +9822,19 @@
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
-      <c r="K80" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Spejkmyren, Spejkmyren, Jmt</t>
+          <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>520033</v>
+        <v>520216</v>
       </c>
       <c r="R80" t="n">
-        <v>7035301</v>
+        <v>7035583</v>
       </c>
       <c r="S80" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -9984,31 +9874,6 @@
       </c>
       <c r="AG80" t="b">
         <v>0</v>
-      </c>
-      <c r="AH80" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ80" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK80" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM80" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO80" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
@@ -10025,10 +9890,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>122721463</v>
+        <v>122716216</v>
       </c>
       <c r="B81" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -10041,34 +9906,39 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Spejkmyren, Spejkmyren, Jmt</t>
+          <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>519841</v>
+        <v>520368</v>
       </c>
       <c r="R81" t="n">
-        <v>7035417</v>
+        <v>7035513</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -10105,7 +9975,7 @@
       </c>
       <c r="AC81" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>På en gammal grovbarkad sälg.</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -10124,22 +9994,22 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK81" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM81" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO81" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT81" t="inlineStr"/>
@@ -10157,10 +10027,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>122716964</v>
+        <v>122717636</v>
       </c>
       <c r="B82" t="n">
-        <v>90962</v>
+        <v>57478</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -10173,34 +10043,39 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P82" t="inlineStr">
         <is>
           <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>520115</v>
+        <v>519970</v>
       </c>
       <c r="R82" t="n">
-        <v>7035402</v>
+        <v>7035297</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -10233,6 +10108,11 @@
       <c r="AA82" t="inlineStr">
         <is>
           <t>2025-02-23</t>
+        </is>
+      </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -10259,10 +10139,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>122717929</v>
+        <v>122716547</v>
       </c>
       <c r="B83" t="n">
-        <v>79876</v>
+        <v>98263</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -10275,42 +10155,51 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6462</v>
+        <v>504</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Spejkmyren, Spejkmyren, Jmt</t>
+          <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>520029</v>
+        <v>520386</v>
       </c>
       <c r="R83" t="n">
-        <v>7035292</v>
+        <v>7035492</v>
       </c>
       <c r="S83" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -10342,6 +10231,11 @@
           <t>2025-02-23</t>
         </is>
       </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>En vinterståndare på till synes fuktig mark i en lucka.</t>
+        </is>
+      </c>
       <c r="AD83" t="b">
         <v>0</v>
       </c>
@@ -10354,26 +10248,6 @@
       <c r="AH83" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ83" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK83" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM83" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO83" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT83" t="inlineStr"/>
@@ -10391,10 +10265,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>122715573</v>
+        <v>122720065</v>
       </c>
       <c r="B84" t="n">
-        <v>79848</v>
+        <v>78766</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -10407,37 +10281,37 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Finnbodarna, Finnbodarna, Jmt</t>
+          <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>520214</v>
+        <v>520062</v>
       </c>
       <c r="R84" t="n">
-        <v>7035583</v>
+        <v>7035232</v>
       </c>
       <c r="S84" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -10477,6 +10351,31 @@
       </c>
       <c r="AG84" t="b">
         <v>0</v>
+      </c>
+      <c r="AH84" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ84" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK84" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM84" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO84" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
@@ -10493,10 +10392,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>122715790</v>
+        <v>122717284</v>
       </c>
       <c r="B85" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -10509,42 +10408,37 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
-      <c r="K85" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Finnbodarna, Finnbodarna, Jmt</t>
+          <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>520267</v>
+        <v>520031</v>
       </c>
       <c r="R85" t="n">
-        <v>7035581</v>
+        <v>7035353</v>
       </c>
       <c r="S85" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -10576,6 +10470,11 @@
           <t>2025-02-23</t>
         </is>
       </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>Långväxta bålar på flertalet granar.</t>
+        </is>
+      </c>
       <c r="AD85" t="b">
         <v>0</v>
       </c>
@@ -10584,6 +10483,31 @@
       </c>
       <c r="AG85" t="b">
         <v>0</v>
+      </c>
+      <c r="AH85" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ85" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK85" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM85" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO85" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
@@ -10600,10 +10524,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>122715780</v>
+        <v>122720959</v>
       </c>
       <c r="B86" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -10616,34 +10540,34 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Finnbodarna, Finnbodarna, Jmt</t>
+          <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>520259</v>
+        <v>519917</v>
       </c>
       <c r="R86" t="n">
-        <v>7035569</v>
+        <v>7035339</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -10680,7 +10604,7 @@
       </c>
       <c r="AC86" t="inlineStr">
         <is>
-          <t>På björk</t>
+          <t>Långväxta bålar på flertalet granar.</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10691,6 +10615,31 @@
       </c>
       <c r="AG86" t="b">
         <v>0</v>
+      </c>
+      <c r="AH86" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ86" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK86" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM86" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO86" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
@@ -10707,10 +10656,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>122720548</v>
+        <v>122716645</v>
       </c>
       <c r="B87" t="n">
-        <v>90962</v>
+        <v>57478</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -10723,34 +10672,39 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P87" t="inlineStr">
         <is>
           <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>519847</v>
+        <v>520129</v>
       </c>
       <c r="R87" t="n">
-        <v>7035432</v>
+        <v>7035444</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10783,6 +10737,11 @@
       <c r="AA87" t="inlineStr">
         <is>
           <t>2025-02-23</t>
+        </is>
+      </c>
+      <c r="AC87" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10809,10 +10768,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>122716443</v>
+        <v>122716427</v>
       </c>
       <c r="B88" t="n">
-        <v>78766</v>
+        <v>78767</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -10825,16 +10784,16 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6425</v>
+        <v>230405</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -10842,34 +10801,20 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I88" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
-      <c r="J88" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K88" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
           <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>520251</v>
+        <v>520388</v>
       </c>
       <c r="R88" t="n">
-        <v>7035394</v>
+        <v>7035490</v>
       </c>
       <c r="S88" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -10903,7 +10848,7 @@
       </c>
       <c r="AC88" t="inlineStr">
         <is>
-          <t>Garnlavsrikt</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10914,6 +10859,31 @@
       </c>
       <c r="AG88" t="b">
         <v>0</v>
+      </c>
+      <c r="AH88" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ88" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK88" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM88" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO88" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
@@ -10930,10 +10900,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>122715874</v>
+        <v>122715569</v>
       </c>
       <c r="B89" t="n">
-        <v>79876</v>
+        <v>78766</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -10942,38 +10912,38 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Finnbodarna, Finnbodarna, Jmt</t>
+          <t>Djupmyren, Djupmyren, Jmt</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>520265</v>
+        <v>520115</v>
       </c>
       <c r="R89" t="n">
-        <v>7035574</v>
+        <v>7035562</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -11008,6 +10978,11 @@
           <t>2025-02-23</t>
         </is>
       </c>
+      <c r="AC89" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
+        </is>
+      </c>
       <c r="AD89" t="b">
         <v>0</v>
       </c>
@@ -11016,6 +10991,31 @@
       </c>
       <c r="AG89" t="b">
         <v>0</v>
+      </c>
+      <c r="AH89" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ89" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK89" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM89" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO89" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
@@ -11032,7 +11032,7 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>122718013</v>
+        <v>122720427</v>
       </c>
       <c r="B90" t="n">
         <v>57478</v>
@@ -11068,7 +11068,7 @@
       <c r="I90" t="inlineStr"/>
       <c r="M90" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P90" t="inlineStr">
@@ -11077,10 +11077,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>519948</v>
+        <v>519846</v>
       </c>
       <c r="R90" t="n">
-        <v>7035313</v>
+        <v>7035407</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>

--- a/artfynd/A 1625-2025 artfynd.xlsx
+++ b/artfynd/A 1625-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122717873</v>
+        <v>122715502</v>
       </c>
       <c r="B2" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,42 +691,42 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Spejkmyren, Spejkmyren, Jmt</t>
+          <t>Djupmyren, Djupmyren, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>520033</v>
+        <v>520110</v>
       </c>
       <c r="R2" t="n">
-        <v>7035301</v>
+        <v>7035585</v>
       </c>
       <c r="S2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -758,6 +758,11 @@
           <t>2025-02-23</t>
         </is>
       </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Gott om långväxt garnlav på många granar. Vissa bålar är här fertila.</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -774,22 +779,22 @@
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -807,10 +812,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122719875</v>
+        <v>122721333</v>
       </c>
       <c r="B3" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -823,42 +828,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>519983</v>
+        <v>519906</v>
       </c>
       <c r="R3" t="n">
-        <v>7035206</v>
+        <v>7035389</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ymnigt på flera granar.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -903,6 +903,31 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -919,10 +944,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122715502</v>
+        <v>122717873</v>
       </c>
       <c r="B4" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -935,42 +960,42 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Djupmyren, Djupmyren, Jmt</t>
+          <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>520110</v>
+        <v>520033</v>
       </c>
       <c r="R4" t="n">
-        <v>7035585</v>
+        <v>7035301</v>
       </c>
       <c r="S4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1002,11 +1027,6 @@
           <t>2025-02-23</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Gott om långväxt garnlav på många granar. Vissa bålar är här fertila.</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1023,22 +1043,22 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1056,10 +1076,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122721333</v>
+        <v>122719875</v>
       </c>
       <c r="B5" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1072,37 +1092,42 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>519906</v>
+        <v>519983</v>
       </c>
       <c r="R5" t="n">
-        <v>7035389</v>
+        <v>7035206</v>
       </c>
       <c r="S5" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1136,7 +1161,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ymnigt på flera granar.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1147,31 +1172,6 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1299,10 +1299,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122720629</v>
+        <v>122715874</v>
       </c>
       <c r="B7" t="n">
-        <v>78766</v>
+        <v>79876</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1311,38 +1311,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Spejkmyren, Spejkmyren, Jmt</t>
+          <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>519935</v>
+        <v>520265</v>
       </c>
       <c r="R7" t="n">
-        <v>7035246</v>
+        <v>7035574</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1377,11 +1377,6 @@
           <t>2025-02-23</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1390,31 +1385,6 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1431,10 +1401,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122716303</v>
+        <v>122720629</v>
       </c>
       <c r="B8" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1447,39 +1417,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Finnbodarna, Hammerdal, Finnbodarna, Hammerdal, Jmt</t>
+          <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>520250</v>
+        <v>519935</v>
       </c>
       <c r="R8" t="n">
-        <v>7035363</v>
+        <v>7035246</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1516,7 +1481,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1527,6 +1492,31 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1543,10 +1533,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122715874</v>
+        <v>122715836</v>
       </c>
       <c r="B9" t="n">
-        <v>79876</v>
+        <v>79847</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1555,35 +1545,40 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>520265</v>
+        <v>520269</v>
       </c>
       <c r="R9" t="n">
         <v>7035574</v>
@@ -1645,7 +1640,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122715836</v>
+        <v>122715779</v>
       </c>
       <c r="B10" t="n">
         <v>79847</v>
@@ -1681,7 +1676,7 @@
       <c r="I10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1690,13 +1685,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>520269</v>
+        <v>520223</v>
       </c>
       <c r="R10" t="n">
-        <v>7035574</v>
+        <v>7035609</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1736,6 +1731,31 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1752,7 +1772,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122715779</v>
+        <v>122715949</v>
       </c>
       <c r="B11" t="n">
         <v>79847</v>
@@ -1786,24 +1806,19 @@
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>520223</v>
+        <v>520254</v>
       </c>
       <c r="R11" t="n">
-        <v>7035609</v>
+        <v>7035555</v>
       </c>
       <c r="S11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1843,31 +1858,6 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -1884,10 +1874,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122715949</v>
+        <v>122716303</v>
       </c>
       <c r="B12" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1900,34 +1890,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Finnbodarna, Finnbodarna, Jmt</t>
+          <t>Finnbodarna, Hammerdal, Finnbodarna, Hammerdal, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>520254</v>
+        <v>520250</v>
       </c>
       <c r="R12" t="n">
-        <v>7035555</v>
+        <v>7035363</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1960,6 +1955,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-02-23</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2209,7 +2209,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122721463</v>
+        <v>122719371</v>
       </c>
       <c r="B15" t="n">
         <v>78766</v>
@@ -2249,13 +2249,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>519841</v>
+        <v>519943</v>
       </c>
       <c r="R15" t="n">
-        <v>7035417</v>
+        <v>7035270</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2285,11 +2285,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-02-23</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2341,7 +2336,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122719371</v>
+        <v>122721463</v>
       </c>
       <c r="B16" t="n">
         <v>78766</v>
@@ -2381,13 +2376,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>519943</v>
+        <v>519841</v>
       </c>
       <c r="R16" t="n">
-        <v>7035270</v>
+        <v>7035417</v>
       </c>
       <c r="S16" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2417,6 +2412,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-02-23</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -6161,10 +6161,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122715756</v>
+        <v>122720327</v>
       </c>
       <c r="B49" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6177,34 +6177,39 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Finnbodarna, Finnbodarna, Jmt</t>
+          <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>520256</v>
+        <v>519838</v>
       </c>
       <c r="R49" t="n">
-        <v>7035593</v>
+        <v>7035393</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6237,6 +6242,11 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-02-23</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6263,7 +6273,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122720327</v>
+        <v>122720368</v>
       </c>
       <c r="B50" t="n">
         <v>57478</v>
@@ -6308,10 +6318,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>519838</v>
+        <v>519852</v>
       </c>
       <c r="R50" t="n">
-        <v>7035393</v>
+        <v>7035392</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6375,7 +6385,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122720368</v>
+        <v>122720823</v>
       </c>
       <c r="B51" t="n">
         <v>57478</v>
@@ -6408,10 +6418,24 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I51" t="inlineStr"/>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
@@ -6420,10 +6444,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>519852</v>
+        <v>519842</v>
       </c>
       <c r="R51" t="n">
-        <v>7035392</v>
+        <v>7035388</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6460,7 +6484,7 @@
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Trummande</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6487,10 +6511,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122720823</v>
+        <v>122720558</v>
       </c>
       <c r="B52" t="n">
-        <v>57478</v>
+        <v>57494</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6503,16 +6527,16 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -6520,24 +6544,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L52" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="M52" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
@@ -6546,10 +6556,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>519842</v>
+        <v>519949</v>
       </c>
       <c r="R52" t="n">
-        <v>7035388</v>
+        <v>7035254</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6586,7 +6596,7 @@
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>Trummande</t>
+          <t>Äldre hackspår i stambasen.</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6597,6 +6607,31 @@
       </c>
       <c r="AG52" t="b">
         <v>0</v>
+      </c>
+      <c r="AH52" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ52" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK52" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM52" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO52" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
@@ -6613,10 +6648,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122720558</v>
+        <v>122715756</v>
       </c>
       <c r="B53" t="n">
-        <v>57494</v>
+        <v>79847</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6629,39 +6664,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Spejkmyren, Spejkmyren, Jmt</t>
+          <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>519949</v>
+        <v>520256</v>
       </c>
       <c r="R53" t="n">
-        <v>7035254</v>
+        <v>7035593</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6696,11 +6726,6 @@
           <t>2025-02-23</t>
         </is>
       </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Äldre hackspår i stambasen.</t>
-        </is>
-      </c>
       <c r="AD53" t="b">
         <v>0</v>
       </c>
@@ -6709,31 +6734,6 @@
       </c>
       <c r="AG53" t="b">
         <v>0</v>
-      </c>
-      <c r="AH53" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ53" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK53" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM53" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO53" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
@@ -6750,10 +6750,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122715669</v>
+        <v>122716443</v>
       </c>
       <c r="B54" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6766,24 +6766,33 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K54" t="inlineStr">
         <is>
           <t>med apothecier</t>
@@ -6795,10 +6804,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>520221</v>
+        <v>520251</v>
       </c>
       <c r="R54" t="n">
-        <v>7035600</v>
+        <v>7035394</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6831,6 +6840,11 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-02-23</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Garnlavsrikt</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6857,10 +6871,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122716295</v>
+        <v>122720869</v>
       </c>
       <c r="B55" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6873,39 +6887,34 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Finnbodarna, Finnbodarna, Jmt</t>
+          <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>520378</v>
+        <v>519960</v>
       </c>
       <c r="R55" t="n">
-        <v>7035512</v>
+        <v>7035342</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6940,11 +6949,6 @@
           <t>2025-02-23</t>
         </is>
       </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Ymnig påväxt på en grovbarkad gammal sälg. Fertila bålar med apothecier.</t>
-        </is>
-      </c>
       <c r="AD55" t="b">
         <v>0</v>
       </c>
@@ -6961,22 +6965,22 @@
       </c>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM55" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO55" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT55" t="inlineStr"/>
@@ -6994,7 +6998,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122716443</v>
+        <v>122715999</v>
       </c>
       <c r="B56" t="n">
         <v>78766</v>
@@ -7027,34 +7031,20 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>520251</v>
+        <v>520311</v>
       </c>
       <c r="R56" t="n">
-        <v>7035394</v>
+        <v>7035566</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -7086,11 +7076,6 @@
           <t>2025-02-23</t>
         </is>
       </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Garnlavsrikt</t>
-        </is>
-      </c>
       <c r="AD56" t="b">
         <v>0</v>
       </c>
@@ -7099,6 +7084,31 @@
       </c>
       <c r="AG56" t="b">
         <v>0</v>
+      </c>
+      <c r="AH56" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ56" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK56" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM56" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO56" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
@@ -7115,10 +7125,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122720869</v>
+        <v>122720454</v>
       </c>
       <c r="B57" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -7131,34 +7141,39 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>519960</v>
+        <v>519849</v>
       </c>
       <c r="R57" t="n">
-        <v>7035342</v>
+        <v>7035406</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7193,6 +7208,11 @@
           <t>2025-02-23</t>
         </is>
       </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD57" t="b">
         <v>0</v>
       </c>
@@ -7201,31 +7221,6 @@
       </c>
       <c r="AG57" t="b">
         <v>0</v>
-      </c>
-      <c r="AH57" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ57" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK57" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM57" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO57" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
@@ -7242,10 +7237,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122715999</v>
+        <v>122715669</v>
       </c>
       <c r="B58" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7258,37 +7253,42 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>520311</v>
+        <v>520221</v>
       </c>
       <c r="R58" t="n">
-        <v>7035566</v>
+        <v>7035600</v>
       </c>
       <c r="S58" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7328,31 +7328,6 @@
       </c>
       <c r="AG58" t="b">
         <v>0</v>
-      </c>
-      <c r="AH58" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ58" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK58" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM58" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO58" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
@@ -7369,10 +7344,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122720454</v>
+        <v>122716295</v>
       </c>
       <c r="B59" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7385,39 +7360,39 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Spejkmyren, Spejkmyren, Jmt</t>
+          <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>519849</v>
+        <v>520378</v>
       </c>
       <c r="R59" t="n">
-        <v>7035406</v>
+        <v>7035512</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7454,7 +7429,7 @@
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ymnig påväxt på en grovbarkad gammal sälg. Fertila bålar med apothecier.</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7465,6 +7440,31 @@
       </c>
       <c r="AG59" t="b">
         <v>0</v>
+      </c>
+      <c r="AH59" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ59" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK59" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM59" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO59" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
@@ -7608,10 +7608,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122715849</v>
+        <v>122717359</v>
       </c>
       <c r="B61" t="n">
-        <v>79876</v>
+        <v>79847</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7620,38 +7620,38 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Finnbodarna, Finnbodarna, Jmt</t>
+          <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>520268</v>
+        <v>520030</v>
       </c>
       <c r="R61" t="n">
-        <v>7035575</v>
+        <v>7035341</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7710,7 +7710,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122717359</v>
+        <v>122716234</v>
       </c>
       <c r="B62" t="n">
         <v>79847</v>
@@ -7746,14 +7746,14 @@
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Spejkmyren, Spejkmyren, Jmt</t>
+          <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>520030</v>
+        <v>520362</v>
       </c>
       <c r="R62" t="n">
-        <v>7035341</v>
+        <v>7035500</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7788,6 +7788,11 @@
           <t>2025-02-23</t>
         </is>
       </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>På en klen gran intill en gammal sälg med lunglav.</t>
+        </is>
+      </c>
       <c r="AD62" t="b">
         <v>0</v>
       </c>
@@ -7796,6 +7801,31 @@
       </c>
       <c r="AG62" t="b">
         <v>0</v>
+      </c>
+      <c r="AH62" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ62" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK62" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM62" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO62" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
@@ -7812,10 +7842,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122716234</v>
+        <v>122715849</v>
       </c>
       <c r="B63" t="n">
-        <v>79847</v>
+        <v>79876</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7824,25 +7854,25 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7852,10 +7882,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>520362</v>
+        <v>520268</v>
       </c>
       <c r="R63" t="n">
-        <v>7035500</v>
+        <v>7035575</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7890,11 +7920,6 @@
           <t>2025-02-23</t>
         </is>
       </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>På en klen gran intill en gammal sälg med lunglav.</t>
-        </is>
-      </c>
       <c r="AD63" t="b">
         <v>0</v>
       </c>
@@ -7903,31 +7928,6 @@
       </c>
       <c r="AG63" t="b">
         <v>0</v>
-      </c>
-      <c r="AH63" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ63" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK63" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM63" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO63" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
@@ -7944,10 +7944,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122718013</v>
+        <v>122715801</v>
       </c>
       <c r="B64" t="n">
-        <v>57478</v>
+        <v>79848</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7960,39 +7960,34 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Spejkmyren, Spejkmyren, Jmt</t>
+          <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>519948</v>
+        <v>520266</v>
       </c>
       <c r="R64" t="n">
-        <v>7035313</v>
+        <v>7035582</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -8025,11 +8020,6 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-02-23</t>
-        </is>
-      </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8056,7 +8046,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122717343</v>
+        <v>122718013</v>
       </c>
       <c r="B65" t="n">
         <v>57478</v>
@@ -8101,10 +8091,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>520034</v>
+        <v>519948</v>
       </c>
       <c r="R65" t="n">
-        <v>7035339</v>
+        <v>7035313</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -8168,7 +8158,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122719554</v>
+        <v>122717343</v>
       </c>
       <c r="B66" t="n">
         <v>57478</v>
@@ -8207,21 +8197,16 @@
           <t>äldre spår</t>
         </is>
       </c>
-      <c r="N66" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>519981</v>
+        <v>520034</v>
       </c>
       <c r="R66" t="n">
-        <v>7035221</v>
+        <v>7035339</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -8258,7 +8243,7 @@
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>Äldre ringhack som bedöms vara 5 - 10 år gamla.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8269,31 +8254,6 @@
       </c>
       <c r="AG66" t="b">
         <v>0</v>
-      </c>
-      <c r="AH66" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ66" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK66" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM66" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO66" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
@@ -8310,10 +8270,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>122715801</v>
+        <v>122719554</v>
       </c>
       <c r="B67" t="n">
-        <v>79848</v>
+        <v>57478</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8326,34 +8286,44 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Finnbodarna, Finnbodarna, Jmt</t>
+          <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>520266</v>
+        <v>519981</v>
       </c>
       <c r="R67" t="n">
-        <v>7035582</v>
+        <v>7035221</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8388,6 +8358,11 @@
           <t>2025-02-23</t>
         </is>
       </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Äldre ringhack som bedöms vara 5 - 10 år gamla.</t>
+        </is>
+      </c>
       <c r="AD67" t="b">
         <v>0</v>
       </c>
@@ -8396,6 +8371,31 @@
       </c>
       <c r="AG67" t="b">
         <v>0</v>
+      </c>
+      <c r="AH67" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ67" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK67" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM67" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO67" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
@@ -9209,10 +9209,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>122715573</v>
+        <v>122720686</v>
       </c>
       <c r="B75" t="n">
-        <v>79848</v>
+        <v>78766</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -9225,34 +9225,34 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Finnbodarna, Finnbodarna, Jmt</t>
+          <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>520214</v>
+        <v>519903</v>
       </c>
       <c r="R75" t="n">
-        <v>7035583</v>
+        <v>7035224</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -9295,6 +9295,31 @@
       </c>
       <c r="AG75" t="b">
         <v>0</v>
+      </c>
+      <c r="AH75" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK75" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM75" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO75" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
@@ -9311,10 +9336,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>122720686</v>
+        <v>122715573</v>
       </c>
       <c r="B76" t="n">
-        <v>78766</v>
+        <v>79848</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -9327,34 +9352,34 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Spejkmyren, Spejkmyren, Jmt</t>
+          <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>519903</v>
+        <v>520214</v>
       </c>
       <c r="R76" t="n">
-        <v>7035224</v>
+        <v>7035583</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -9397,31 +9422,6 @@
       </c>
       <c r="AG76" t="b">
         <v>0</v>
-      </c>
-      <c r="AH76" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ76" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK76" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM76" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO76" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
@@ -9554,10 +9554,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>122717446</v>
+        <v>122717636</v>
       </c>
       <c r="B78" t="n">
-        <v>90962</v>
+        <v>57478</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -9570,34 +9570,39 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P78" t="inlineStr">
         <is>
           <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>520006</v>
+        <v>519970</v>
       </c>
       <c r="R78" t="n">
-        <v>7035303</v>
+        <v>7035297</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9630,6 +9635,11 @@
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-02-23</t>
+        </is>
+      </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9656,10 +9666,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>122717616</v>
+        <v>122717446</v>
       </c>
       <c r="B79" t="n">
-        <v>78766</v>
+        <v>90962</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -9672,21 +9682,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -9696,10 +9706,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>520019</v>
+        <v>520006</v>
       </c>
       <c r="R79" t="n">
-        <v>7035352</v>
+        <v>7035303</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9734,11 +9744,6 @@
           <t>2025-02-23</t>
         </is>
       </c>
-      <c r="AC79" t="inlineStr">
-        <is>
-          <t>Rikligt.</t>
-        </is>
-      </c>
       <c r="AD79" t="b">
         <v>0</v>
       </c>
@@ -9747,31 +9752,6 @@
       </c>
       <c r="AG79" t="b">
         <v>0</v>
-      </c>
-      <c r="AH79" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ79" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK79" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM79" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO79" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
@@ -9788,10 +9768,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>122715571</v>
+        <v>122717616</v>
       </c>
       <c r="B80" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -9804,34 +9784,34 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Finnbodarna, Finnbodarna, Jmt</t>
+          <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>520216</v>
+        <v>520019</v>
       </c>
       <c r="R80" t="n">
-        <v>7035583</v>
+        <v>7035352</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9866,6 +9846,11 @@
           <t>2025-02-23</t>
         </is>
       </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>Rikligt.</t>
+        </is>
+      </c>
       <c r="AD80" t="b">
         <v>0</v>
       </c>
@@ -9874,6 +9859,31 @@
       </c>
       <c r="AG80" t="b">
         <v>0</v>
+      </c>
+      <c r="AH80" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ80" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK80" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM80" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO80" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
@@ -9890,7 +9900,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>122716216</v>
+        <v>122715571</v>
       </c>
       <c r="B81" t="n">
         <v>79847</v>
@@ -9924,21 +9934,16 @@
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
-      <c r="K81" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P81" t="inlineStr">
         <is>
           <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>520368</v>
+        <v>520216</v>
       </c>
       <c r="R81" t="n">
-        <v>7035513</v>
+        <v>7035583</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9973,11 +9978,6 @@
           <t>2025-02-23</t>
         </is>
       </c>
-      <c r="AC81" t="inlineStr">
-        <is>
-          <t>På en gammal grovbarkad sälg.</t>
-        </is>
-      </c>
       <c r="AD81" t="b">
         <v>0</v>
       </c>
@@ -9986,31 +9986,6 @@
       </c>
       <c r="AG81" t="b">
         <v>0</v>
-      </c>
-      <c r="AH81" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ81" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK81" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM81" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO81" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
@@ -10027,10 +10002,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>122717636</v>
+        <v>122716216</v>
       </c>
       <c r="B82" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -10043,39 +10018,39 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Spejkmyren, Spejkmyren, Jmt</t>
+          <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>519970</v>
+        <v>520368</v>
       </c>
       <c r="R82" t="n">
-        <v>7035297</v>
+        <v>7035513</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -10112,7 +10087,7 @@
       </c>
       <c r="AC82" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>På en gammal grovbarkad sälg.</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -10123,6 +10098,31 @@
       </c>
       <c r="AG82" t="b">
         <v>0</v>
+      </c>
+      <c r="AH82" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ82" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK82" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM82" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO82" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">

--- a/artfynd/A 1625-2025 artfynd.xlsx
+++ b/artfynd/A 1625-2025 artfynd.xlsx
@@ -1076,10 +1076,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122719875</v>
+        <v>122717468</v>
       </c>
       <c r="B5" t="n">
-        <v>57478</v>
+        <v>57494</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1092,16 +1092,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1109,10 +1109,14 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1121,10 +1125,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>519983</v>
+        <v>520020</v>
       </c>
       <c r="R5" t="n">
-        <v>7035206</v>
+        <v>7035330</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1157,11 +1161,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-02-23</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1188,10 +1187,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122717468</v>
+        <v>122719875</v>
       </c>
       <c r="B6" t="n">
-        <v>57494</v>
+        <v>57478</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1204,16 +1203,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1221,14 +1220,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1237,10 +1232,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>520020</v>
+        <v>519983</v>
       </c>
       <c r="R6" t="n">
-        <v>7035330</v>
+        <v>7035206</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1273,6 +1268,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-02-23</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -3638,10 +3638,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122715953</v>
+        <v>122716682</v>
       </c>
       <c r="B27" t="n">
-        <v>79848</v>
+        <v>57631</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3654,34 +3654,43 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2081</v>
+        <v>103021</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Finnbodarna, Finnbodarna, Jmt</t>
+          <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>520254</v>
+        <v>520101</v>
       </c>
       <c r="R27" t="n">
-        <v>7035555</v>
+        <v>7035453</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3740,10 +3749,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122716682</v>
+        <v>122715953</v>
       </c>
       <c r="B28" t="n">
-        <v>57631</v>
+        <v>79848</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3756,43 +3765,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>103021</v>
+        <v>2081</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>par i lämplig häckbiotop</t>
-        </is>
-      </c>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Spejkmyren, Spejkmyren, Jmt</t>
+          <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>520101</v>
+        <v>520254</v>
       </c>
       <c r="R28" t="n">
-        <v>7035453</v>
+        <v>7035555</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4752,10 +4752,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122715934</v>
+        <v>122715978</v>
       </c>
       <c r="B37" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4768,37 +4768,42 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>520303</v>
+        <v>520243</v>
       </c>
       <c r="R37" t="n">
-        <v>7035598</v>
+        <v>7035552</v>
       </c>
       <c r="S37" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4830,11 +4835,6 @@
           <t>2025-02-23</t>
         </is>
       </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
-        </is>
-      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
@@ -4843,31 +4843,6 @@
       </c>
       <c r="AG37" t="b">
         <v>0</v>
-      </c>
-      <c r="AH37" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ37" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK37" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM37" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO37" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
@@ -4884,10 +4859,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122715978</v>
+        <v>122715934</v>
       </c>
       <c r="B38" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4900,42 +4875,37 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>520243</v>
+        <v>520303</v>
       </c>
       <c r="R38" t="n">
-        <v>7035552</v>
+        <v>7035598</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4967,6 +4937,11 @@
           <t>2025-02-23</t>
         </is>
       </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
+        </is>
+      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
@@ -4975,6 +4950,31 @@
       </c>
       <c r="AG38" t="b">
         <v>0</v>
+      </c>
+      <c r="AH38" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ38" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK38" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM38" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO38" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
@@ -7608,10 +7608,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122717359</v>
+        <v>122715849</v>
       </c>
       <c r="B61" t="n">
-        <v>79847</v>
+        <v>79876</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7620,38 +7620,38 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Spejkmyren, Spejkmyren, Jmt</t>
+          <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>520030</v>
+        <v>520268</v>
       </c>
       <c r="R61" t="n">
-        <v>7035341</v>
+        <v>7035575</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7710,7 +7710,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122716234</v>
+        <v>122717359</v>
       </c>
       <c r="B62" t="n">
         <v>79847</v>
@@ -7746,14 +7746,14 @@
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Finnbodarna, Finnbodarna, Jmt</t>
+          <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>520362</v>
+        <v>520030</v>
       </c>
       <c r="R62" t="n">
-        <v>7035500</v>
+        <v>7035341</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7788,11 +7788,6 @@
           <t>2025-02-23</t>
         </is>
       </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>På en klen gran intill en gammal sälg med lunglav.</t>
-        </is>
-      </c>
       <c r="AD62" t="b">
         <v>0</v>
       </c>
@@ -7801,31 +7796,6 @@
       </c>
       <c r="AG62" t="b">
         <v>0</v>
-      </c>
-      <c r="AH62" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ62" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK62" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM62" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO62" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
@@ -7842,10 +7812,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122715849</v>
+        <v>122716234</v>
       </c>
       <c r="B63" t="n">
-        <v>79876</v>
+        <v>79847</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7854,25 +7824,25 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7882,10 +7852,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>520268</v>
+        <v>520362</v>
       </c>
       <c r="R63" t="n">
-        <v>7035575</v>
+        <v>7035500</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7920,6 +7890,11 @@
           <t>2025-02-23</t>
         </is>
       </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>På en klen gran intill en gammal sälg med lunglav.</t>
+        </is>
+      </c>
       <c r="AD63" t="b">
         <v>0</v>
       </c>
@@ -7928,6 +7903,31 @@
       </c>
       <c r="AG63" t="b">
         <v>0</v>
+      </c>
+      <c r="AH63" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ63" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK63" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM63" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO63" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
@@ -7944,10 +7944,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122715801</v>
+        <v>122718013</v>
       </c>
       <c r="B64" t="n">
-        <v>79848</v>
+        <v>57478</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7960,34 +7960,39 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Finnbodarna, Finnbodarna, Jmt</t>
+          <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>520266</v>
+        <v>519948</v>
       </c>
       <c r="R64" t="n">
-        <v>7035582</v>
+        <v>7035313</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -8020,6 +8025,11 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-02-23</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8046,7 +8056,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122718013</v>
+        <v>122717343</v>
       </c>
       <c r="B65" t="n">
         <v>57478</v>
@@ -8091,10 +8101,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>519948</v>
+        <v>520034</v>
       </c>
       <c r="R65" t="n">
-        <v>7035313</v>
+        <v>7035339</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -8158,7 +8168,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122717343</v>
+        <v>122719554</v>
       </c>
       <c r="B66" t="n">
         <v>57478</v>
@@ -8197,16 +8207,21 @@
           <t>äldre spår</t>
         </is>
       </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>520034</v>
+        <v>519981</v>
       </c>
       <c r="R66" t="n">
-        <v>7035339</v>
+        <v>7035221</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -8243,7 +8258,7 @@
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Äldre ringhack som bedöms vara 5 - 10 år gamla.</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8254,6 +8269,31 @@
       </c>
       <c r="AG66" t="b">
         <v>0</v>
+      </c>
+      <c r="AH66" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ66" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK66" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM66" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO66" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
@@ -8270,10 +8310,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>122719554</v>
+        <v>122715801</v>
       </c>
       <c r="B67" t="n">
-        <v>57478</v>
+        <v>79848</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8286,44 +8326,34 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N67" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Spejkmyren, Spejkmyren, Jmt</t>
+          <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>519981</v>
+        <v>520266</v>
       </c>
       <c r="R67" t="n">
-        <v>7035221</v>
+        <v>7035582</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8358,11 +8388,6 @@
           <t>2025-02-23</t>
         </is>
       </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>Äldre ringhack som bedöms vara 5 - 10 år gamla.</t>
-        </is>
-      </c>
       <c r="AD67" t="b">
         <v>0</v>
       </c>
@@ -8371,31 +8396,6 @@
       </c>
       <c r="AG67" t="b">
         <v>0</v>
-      </c>
-      <c r="AH67" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ67" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK67" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM67" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO67" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
@@ -8528,10 +8528,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>122719829</v>
+        <v>122716801</v>
       </c>
       <c r="B69" t="n">
-        <v>57478</v>
+        <v>57631</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8544,27 +8544,31 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>par i lämplig häckbiotop</t>
         </is>
       </c>
       <c r="P69" t="inlineStr">
@@ -8573,10 +8577,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>519930</v>
+        <v>520083</v>
       </c>
       <c r="R69" t="n">
-        <v>7035181</v>
+        <v>7035403</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8609,11 +8613,6 @@
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-02-23</t>
-        </is>
-      </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8640,10 +8639,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>122716801</v>
+        <v>122719829</v>
       </c>
       <c r="B70" t="n">
-        <v>57631</v>
+        <v>57478</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8656,31 +8655,27 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
       <c r="M70" t="inlineStr">
         <is>
-          <t>par i lämplig häckbiotop</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P70" t="inlineStr">
@@ -8689,10 +8684,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>520083</v>
+        <v>519930</v>
       </c>
       <c r="R70" t="n">
-        <v>7035403</v>
+        <v>7035181</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8725,6 +8720,11 @@
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-02-23</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD70" t="b">

--- a/artfynd/A 1625-2025 artfynd.xlsx
+++ b/artfynd/A 1625-2025 artfynd.xlsx
@@ -4752,10 +4752,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122715978</v>
+        <v>122715934</v>
       </c>
       <c r="B37" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4768,42 +4768,37 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>520243</v>
+        <v>520303</v>
       </c>
       <c r="R37" t="n">
-        <v>7035552</v>
+        <v>7035598</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4835,6 +4830,11 @@
           <t>2025-02-23</t>
         </is>
       </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
+        </is>
+      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
@@ -4843,6 +4843,31 @@
       </c>
       <c r="AG37" t="b">
         <v>0</v>
+      </c>
+      <c r="AH37" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ37" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK37" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM37" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO37" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
@@ -4859,10 +4884,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122715934</v>
+        <v>122715978</v>
       </c>
       <c r="B38" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4875,37 +4900,42 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>520303</v>
+        <v>520243</v>
       </c>
       <c r="R38" t="n">
-        <v>7035598</v>
+        <v>7035552</v>
       </c>
       <c r="S38" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4937,11 +4967,6 @@
           <t>2025-02-23</t>
         </is>
       </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
-        </is>
-      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
@@ -4950,31 +4975,6 @@
       </c>
       <c r="AG38" t="b">
         <v>0</v>
-      </c>
-      <c r="AH38" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ38" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK38" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM38" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO38" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
@@ -9209,10 +9209,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>122720686</v>
+        <v>122715573</v>
       </c>
       <c r="B75" t="n">
-        <v>78766</v>
+        <v>79848</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -9225,34 +9225,34 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Spejkmyren, Spejkmyren, Jmt</t>
+          <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>519903</v>
+        <v>520214</v>
       </c>
       <c r="R75" t="n">
-        <v>7035224</v>
+        <v>7035583</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -9295,31 +9295,6 @@
       </c>
       <c r="AG75" t="b">
         <v>0</v>
-      </c>
-      <c r="AH75" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ75" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK75" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM75" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO75" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
@@ -9336,10 +9311,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>122715573</v>
+        <v>122720686</v>
       </c>
       <c r="B76" t="n">
-        <v>79848</v>
+        <v>78766</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -9352,34 +9327,34 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Finnbodarna, Finnbodarna, Jmt</t>
+          <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>520214</v>
+        <v>519903</v>
       </c>
       <c r="R76" t="n">
-        <v>7035583</v>
+        <v>7035224</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -9422,6 +9397,31 @@
       </c>
       <c r="AG76" t="b">
         <v>0</v>
+      </c>
+      <c r="AH76" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ76" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK76" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM76" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO76" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
@@ -9554,10 +9554,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>122717636</v>
+        <v>122717446</v>
       </c>
       <c r="B78" t="n">
-        <v>57478</v>
+        <v>90962</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -9570,39 +9570,34 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
-      <c r="M78" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P78" t="inlineStr">
         <is>
           <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>519970</v>
+        <v>520006</v>
       </c>
       <c r="R78" t="n">
-        <v>7035297</v>
+        <v>7035303</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9635,11 +9630,6 @@
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-02-23</t>
-        </is>
-      </c>
-      <c r="AC78" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9666,10 +9656,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>122717446</v>
+        <v>122717616</v>
       </c>
       <c r="B79" t="n">
-        <v>90962</v>
+        <v>78766</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -9682,21 +9672,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -9706,10 +9696,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>520006</v>
+        <v>520019</v>
       </c>
       <c r="R79" t="n">
-        <v>7035303</v>
+        <v>7035352</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9744,6 +9734,11 @@
           <t>2025-02-23</t>
         </is>
       </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>Rikligt.</t>
+        </is>
+      </c>
       <c r="AD79" t="b">
         <v>0</v>
       </c>
@@ -9752,6 +9747,31 @@
       </c>
       <c r="AG79" t="b">
         <v>0</v>
+      </c>
+      <c r="AH79" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ79" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK79" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM79" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO79" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
@@ -9768,10 +9788,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>122717616</v>
+        <v>122715571</v>
       </c>
       <c r="B80" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -9784,34 +9804,34 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Spejkmyren, Spejkmyren, Jmt</t>
+          <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>520019</v>
+        <v>520216</v>
       </c>
       <c r="R80" t="n">
-        <v>7035352</v>
+        <v>7035583</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9846,11 +9866,6 @@
           <t>2025-02-23</t>
         </is>
       </c>
-      <c r="AC80" t="inlineStr">
-        <is>
-          <t>Rikligt.</t>
-        </is>
-      </c>
       <c r="AD80" t="b">
         <v>0</v>
       </c>
@@ -9859,31 +9874,6 @@
       </c>
       <c r="AG80" t="b">
         <v>0</v>
-      </c>
-      <c r="AH80" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ80" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK80" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM80" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO80" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
@@ -9900,7 +9890,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>122715571</v>
+        <v>122716216</v>
       </c>
       <c r="B81" t="n">
         <v>79847</v>
@@ -9934,16 +9924,21 @@
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P81" t="inlineStr">
         <is>
           <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>520216</v>
+        <v>520368</v>
       </c>
       <c r="R81" t="n">
-        <v>7035583</v>
+        <v>7035513</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9978,6 +9973,11 @@
           <t>2025-02-23</t>
         </is>
       </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>På en gammal grovbarkad sälg.</t>
+        </is>
+      </c>
       <c r="AD81" t="b">
         <v>0</v>
       </c>
@@ -9986,6 +9986,31 @@
       </c>
       <c r="AG81" t="b">
         <v>0</v>
+      </c>
+      <c r="AH81" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ81" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK81" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM81" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO81" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
@@ -10002,10 +10027,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>122716216</v>
+        <v>122717636</v>
       </c>
       <c r="B82" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -10018,39 +10043,39 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
-      <c r="K82" t="inlineStr">
-        <is>
-          <t>med soral</t>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Finnbodarna, Finnbodarna, Jmt</t>
+          <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>520368</v>
+        <v>519970</v>
       </c>
       <c r="R82" t="n">
-        <v>7035513</v>
+        <v>7035297</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -10087,7 +10112,7 @@
       </c>
       <c r="AC82" t="inlineStr">
         <is>
-          <t>På en gammal grovbarkad sälg.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -10098,31 +10123,6 @@
       </c>
       <c r="AG82" t="b">
         <v>0</v>
-      </c>
-      <c r="AH82" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ82" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK82" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM82" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO82" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">

--- a/artfynd/A 1625-2025 artfynd.xlsx
+++ b/artfynd/A 1625-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122715502</v>
+        <v>122715870</v>
       </c>
       <c r="B2" t="n">
-        <v>78766</v>
+        <v>79848</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,42 +691,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Djupmyren, Djupmyren, Jmt</t>
+          <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>520110</v>
+        <v>520265</v>
       </c>
       <c r="R2" t="n">
-        <v>7035585</v>
+        <v>7035574</v>
       </c>
       <c r="S2" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -758,11 +753,6 @@
           <t>2025-02-23</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Gott om långväxt garnlav på många granar. Vissa bålar är här fertila.</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -771,31 +761,6 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -812,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122721333</v>
+        <v>122715669</v>
       </c>
       <c r="B3" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -828,37 +793,42 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Spejkmyren, Spejkmyren, Jmt</t>
+          <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>519906</v>
+        <v>520221</v>
       </c>
       <c r="R3" t="n">
-        <v>7035389</v>
+        <v>7035600</v>
       </c>
       <c r="S3" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -890,11 +860,6 @@
           <t>2025-02-23</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ymnigt på flera granar.</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -903,31 +868,6 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -1076,10 +1016,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122717468</v>
+        <v>122717488</v>
       </c>
       <c r="B5" t="n">
-        <v>57494</v>
+        <v>79847</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1092,43 +1032,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>520020</v>
+        <v>520000</v>
       </c>
       <c r="R5" t="n">
-        <v>7035330</v>
+        <v>7035297</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1187,10 +1118,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122719875</v>
+        <v>122717929</v>
       </c>
       <c r="B6" t="n">
-        <v>57478</v>
+        <v>79876</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1199,31 +1130,31 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1232,13 +1163,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>519983</v>
+        <v>520029</v>
       </c>
       <c r="R6" t="n">
-        <v>7035206</v>
+        <v>7035292</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1270,11 +1201,6 @@
           <t>2025-02-23</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1283,6 +1209,31 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1299,10 +1250,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122715874</v>
+        <v>122717468</v>
       </c>
       <c r="B7" t="n">
-        <v>79876</v>
+        <v>57494</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1311,38 +1262,47 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6462</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Finnbodarna, Finnbodarna, Jmt</t>
+          <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>520265</v>
+        <v>520020</v>
       </c>
       <c r="R7" t="n">
-        <v>7035574</v>
+        <v>7035330</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1401,10 +1361,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122720629</v>
+        <v>122719875</v>
       </c>
       <c r="B8" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1417,34 +1377,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>519935</v>
+        <v>519983</v>
       </c>
       <c r="R8" t="n">
-        <v>7035246</v>
+        <v>7035206</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1481,7 +1446,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1492,31 +1457,6 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1533,10 +1473,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122715836</v>
+        <v>122715573</v>
       </c>
       <c r="B9" t="n">
-        <v>79847</v>
+        <v>79848</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1549,39 +1489,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>520269</v>
+        <v>520214</v>
       </c>
       <c r="R9" t="n">
-        <v>7035574</v>
+        <v>7035583</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1640,10 +1575,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122715779</v>
+        <v>122716160</v>
       </c>
       <c r="B10" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1656,42 +1591,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>520223</v>
+        <v>520349</v>
       </c>
       <c r="R10" t="n">
-        <v>7035609</v>
+        <v>7035517</v>
       </c>
       <c r="S10" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1739,22 +1669,22 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1772,10 +1702,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122715949</v>
+        <v>122716269</v>
       </c>
       <c r="B11" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1788,34 +1718,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Finnbodarna, Finnbodarna, Jmt</t>
+          <t>Finnbodarna, Hammerdal, Finnbodarna, Hammerdal, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>520254</v>
+        <v>520256</v>
       </c>
       <c r="R11" t="n">
-        <v>7035555</v>
+        <v>7035380</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1848,6 +1783,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-02-23</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1874,7 +1814,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122716303</v>
+        <v>122720281</v>
       </c>
       <c r="B12" t="n">
         <v>57478</v>
@@ -1915,14 +1855,14 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Finnbodarna, Hammerdal, Finnbodarna, Hammerdal, Jmt</t>
+          <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>520250</v>
+        <v>519850</v>
       </c>
       <c r="R12" t="n">
-        <v>7035363</v>
+        <v>7035373</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1986,10 +1926,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122719979</v>
+        <v>122716387</v>
       </c>
       <c r="B13" t="n">
-        <v>57631</v>
+        <v>57478</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2002,43 +1942,39 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>par i lämplig häckbiotop</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Spejkmyren, Spejkmyren, Jmt</t>
+          <t>Finnbodarna, Hammerdal, Finnbodarna, Hammerdal, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>519946</v>
+        <v>520278</v>
       </c>
       <c r="R13" t="n">
-        <v>7035240</v>
+        <v>7035397</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2071,6 +2007,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-02-23</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2097,10 +2038,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122716269</v>
+        <v>122720469</v>
       </c>
       <c r="B14" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2113,39 +2054,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Finnbodarna, Hammerdal, Finnbodarna, Hammerdal, Jmt</t>
+          <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>520256</v>
+        <v>519996</v>
       </c>
       <c r="R14" t="n">
-        <v>7035380</v>
+        <v>7035241</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2180,11 +2116,6 @@
           <t>2025-02-23</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2193,6 +2124,31 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM14" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
@@ -2209,10 +2165,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122719371</v>
+        <v>122715766</v>
       </c>
       <c r="B15" t="n">
-        <v>78766</v>
+        <v>90962</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2225,37 +2181,37 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Spejkmyren, Spejkmyren, Jmt</t>
+          <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>519943</v>
+        <v>520252</v>
       </c>
       <c r="R15" t="n">
-        <v>7035270</v>
+        <v>7035591</v>
       </c>
       <c r="S15" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2295,31 +2251,6 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
-      </c>
-      <c r="AH15" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
@@ -2336,10 +2267,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122721463</v>
+        <v>122716801</v>
       </c>
       <c r="B16" t="n">
-        <v>78766</v>
+        <v>57631</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2352,34 +2283,43 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>519841</v>
+        <v>520083</v>
       </c>
       <c r="R16" t="n">
-        <v>7035417</v>
+        <v>7035403</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2414,11 +2354,6 @@
           <t>2025-02-23</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
@@ -2427,31 +2362,6 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
-      </c>
-      <c r="AH16" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
@@ -2468,7 +2378,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122716850</v>
+        <v>122717294</v>
       </c>
       <c r="B17" t="n">
         <v>90962</v>
@@ -2508,10 +2418,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>520101</v>
+        <v>520013</v>
       </c>
       <c r="R17" t="n">
-        <v>7035388</v>
+        <v>7035340</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2570,10 +2480,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122716160</v>
+        <v>122715953</v>
       </c>
       <c r="B18" t="n">
-        <v>78766</v>
+        <v>79848</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2586,21 +2496,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2610,10 +2520,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>520349</v>
+        <v>520254</v>
       </c>
       <c r="R18" t="n">
-        <v>7035517</v>
+        <v>7035555</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2656,31 +2566,6 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
-      </c>
-      <c r="AH18" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2697,10 +2582,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122716757</v>
+        <v>122719829</v>
       </c>
       <c r="B19" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2713,37 +2598,42 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Finnbodarna, Finnbodarna, Jmt</t>
+          <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>520316</v>
+        <v>519930</v>
       </c>
       <c r="R19" t="n">
-        <v>7035491</v>
+        <v>7035181</v>
       </c>
       <c r="S19" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2775,6 +2665,11 @@
           <t>2025-02-23</t>
         </is>
       </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -2783,31 +2678,6 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
-      </c>
-      <c r="AH19" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -2824,10 +2694,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122720469</v>
+        <v>122719533</v>
       </c>
       <c r="B20" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2840,34 +2710,39 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>519996</v>
+        <v>519948</v>
       </c>
       <c r="R20" t="n">
-        <v>7035241</v>
+        <v>7035187</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2902,6 +2777,11 @@
           <t>2025-02-23</t>
         </is>
       </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
@@ -2910,31 +2790,6 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
-      </c>
-      <c r="AH20" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
@@ -2951,10 +2806,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122715790</v>
+        <v>122720454</v>
       </c>
       <c r="B21" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2967,39 +2822,39 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Finnbodarna, Finnbodarna, Jmt</t>
+          <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>520267</v>
+        <v>519849</v>
       </c>
       <c r="R21" t="n">
-        <v>7035581</v>
+        <v>7035406</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3032,6 +2887,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-02-23</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3058,7 +2918,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122715795</v>
+        <v>122715571</v>
       </c>
       <c r="B22" t="n">
         <v>79847</v>
@@ -3098,13 +2958,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>520214</v>
+        <v>520216</v>
       </c>
       <c r="R22" t="n">
-        <v>7035599</v>
+        <v>7035583</v>
       </c>
       <c r="S22" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3136,11 +2996,6 @@
           <t>2025-02-23</t>
         </is>
       </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>På en klen gran intill en lunglavssälg.</t>
-        </is>
-      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
@@ -3149,31 +3004,6 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
-      </c>
-      <c r="AH22" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -3190,7 +3020,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122716387</v>
+        <v>122717636</v>
       </c>
       <c r="B23" t="n">
         <v>57478</v>
@@ -3231,14 +3061,14 @@
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Finnbodarna, Hammerdal, Finnbodarna, Hammerdal, Jmt</t>
+          <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>520278</v>
+        <v>519970</v>
       </c>
       <c r="R23" t="n">
-        <v>7035397</v>
+        <v>7035297</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3302,10 +3132,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122716293</v>
+        <v>122715841</v>
       </c>
       <c r="B24" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3318,42 +3148,42 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Finnbodarna, Hammerdal, Finnbodarna, Hammerdal, Jmt</t>
+          <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>520249</v>
+        <v>520229</v>
       </c>
       <c r="R24" t="n">
-        <v>7035364</v>
+        <v>7035608</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3387,7 +3217,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>På en björk.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3398,6 +3228,31 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
+      </c>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AM24" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Betula</t>
+        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
@@ -3414,10 +3269,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122716673</v>
+        <v>122716295</v>
       </c>
       <c r="B25" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3430,39 +3285,39 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Spejkmyren, Spejkmyren, Jmt</t>
+          <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>520108</v>
+        <v>520378</v>
       </c>
       <c r="R25" t="n">
-        <v>7035462</v>
+        <v>7035512</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3499,7 +3354,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ymnig påväxt på en grovbarkad gammal sälg. Fertila bålar med apothecier.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3510,6 +3365,31 @@
       </c>
       <c r="AG25" t="b">
         <v>0</v>
+      </c>
+      <c r="AH25" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM25" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
@@ -3638,10 +3518,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122716682</v>
+        <v>122719554</v>
       </c>
       <c r="B27" t="n">
-        <v>57631</v>
+        <v>57478</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3654,31 +3534,32 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
-          <t>par i lämplig häckbiotop</t>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -3687,10 +3568,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>520101</v>
+        <v>519981</v>
       </c>
       <c r="R27" t="n">
-        <v>7035453</v>
+        <v>7035221</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3725,6 +3606,11 @@
           <t>2025-02-23</t>
         </is>
       </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Äldre ringhack som bedöms vara 5 - 10 år gamla.</t>
+        </is>
+      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
@@ -3733,6 +3619,31 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
+      </c>
+      <c r="AH27" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM27" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
@@ -3749,10 +3660,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122715953</v>
+        <v>122716682</v>
       </c>
       <c r="B28" t="n">
-        <v>79848</v>
+        <v>57631</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3765,34 +3676,43 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>2081</v>
+        <v>103021</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Finnbodarna, Finnbodarna, Jmt</t>
+          <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>520254</v>
+        <v>520101</v>
       </c>
       <c r="R28" t="n">
-        <v>7035555</v>
+        <v>7035453</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3851,7 +3771,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122719697</v>
+        <v>122720629</v>
       </c>
       <c r="B29" t="n">
         <v>78766</v>
@@ -3891,13 +3811,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>520026</v>
+        <v>519935</v>
       </c>
       <c r="R29" t="n">
-        <v>7035233</v>
+        <v>7035246</v>
       </c>
       <c r="S29" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3927,6 +3847,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-02-23</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3978,10 +3903,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122715677</v>
+        <v>122715836</v>
       </c>
       <c r="B30" t="n">
-        <v>79848</v>
+        <v>79847</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3994,34 +3919,39 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>520221</v>
+        <v>520269</v>
       </c>
       <c r="R30" t="n">
-        <v>7035600</v>
+        <v>7035574</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4054,11 +3984,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-02-23</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>På gran</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4085,7 +4010,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122716329</v>
+        <v>122715775</v>
       </c>
       <c r="B31" t="n">
         <v>79847</v>
@@ -4121,7 +4046,7 @@
       <c r="I31" t="inlineStr"/>
       <c r="K31" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -4130,13 +4055,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>520374</v>
+        <v>520252</v>
       </c>
       <c r="R31" t="n">
-        <v>7035511</v>
+        <v>7035576</v>
       </c>
       <c r="S31" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4170,7 +4095,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>På gran intill en gammal lunglavssälg.</t>
+          <t>På björk</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4181,31 +4106,6 @@
       </c>
       <c r="AG31" t="b">
         <v>0</v>
-      </c>
-      <c r="AH31" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ31" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK31" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM31" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO31" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
@@ -4222,7 +4122,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122715868</v>
+        <v>122715790</v>
       </c>
       <c r="B32" t="n">
         <v>79847</v>
@@ -4267,10 +4167,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>520265</v>
+        <v>520267</v>
       </c>
       <c r="R32" t="n">
-        <v>7035574</v>
+        <v>7035581</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4329,10 +4229,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122717488</v>
+        <v>122720368</v>
       </c>
       <c r="B33" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4345,34 +4245,39 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>520000</v>
+        <v>519852</v>
       </c>
       <c r="R33" t="n">
-        <v>7035297</v>
+        <v>7035392</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4405,6 +4310,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-02-23</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4431,10 +4341,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122715780</v>
+        <v>122717343</v>
       </c>
       <c r="B34" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4447,34 +4357,39 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Finnbodarna, Finnbodarna, Jmt</t>
+          <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>520259</v>
+        <v>520034</v>
       </c>
       <c r="R34" t="n">
-        <v>7035569</v>
+        <v>7035339</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4511,7 +4426,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>På björk</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4538,10 +4453,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122720281</v>
+        <v>122715801</v>
       </c>
       <c r="B35" t="n">
-        <v>57478</v>
+        <v>79848</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4554,39 +4469,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Spejkmyren, Spejkmyren, Jmt</t>
+          <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>519850</v>
+        <v>520266</v>
       </c>
       <c r="R35" t="n">
-        <v>7035373</v>
+        <v>7035582</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4619,11 +4529,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-02-23</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4650,7 +4555,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122716964</v>
+        <v>122720548</v>
       </c>
       <c r="B36" t="n">
         <v>90962</v>
@@ -4690,10 +4595,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>520115</v>
+        <v>519847</v>
       </c>
       <c r="R36" t="n">
-        <v>7035402</v>
+        <v>7035432</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4752,7 +4657,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122715934</v>
+        <v>122721035</v>
       </c>
       <c r="B37" t="n">
         <v>78766</v>
@@ -4788,17 +4693,17 @@
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Finnbodarna, Finnbodarna, Jmt</t>
+          <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>520303</v>
+        <v>519897</v>
       </c>
       <c r="R37" t="n">
-        <v>7035598</v>
+        <v>7035374</v>
       </c>
       <c r="S37" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4830,11 +4735,6 @@
           <t>2025-02-23</t>
         </is>
       </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
-        </is>
-      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
@@ -4851,12 +4751,12 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>garnlav</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="AM37" t="inlineStr">
@@ -4866,7 +4766,7 @@
       </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Branch on living tree # Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -4884,10 +4784,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122715978</v>
+        <v>122721333</v>
       </c>
       <c r="B38" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4900,42 +4800,37 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Finnbodarna, Finnbodarna, Jmt</t>
+          <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>520243</v>
+        <v>519906</v>
       </c>
       <c r="R38" t="n">
-        <v>7035552</v>
+        <v>7035389</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4967,6 +4862,11 @@
           <t>2025-02-23</t>
         </is>
       </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Ymnigt på flera granar.</t>
+        </is>
+      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
@@ -4975,6 +4875,31 @@
       </c>
       <c r="AG38" t="b">
         <v>0</v>
+      </c>
+      <c r="AH38" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ38" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK38" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM38" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO38" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
@@ -4991,10 +4916,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122715648</v>
+        <v>122715569</v>
       </c>
       <c r="B39" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5007,39 +4932,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Finnbodarna, Hammerdal, Finnbodarna, Hammerdal, Jmt</t>
+          <t>Djupmyren, Djupmyren, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>520219</v>
+        <v>520115</v>
       </c>
       <c r="R39" t="n">
-        <v>7035597</v>
+        <v>7035562</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5076,7 +4996,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5087,6 +5007,31 @@
       </c>
       <c r="AG39" t="b">
         <v>0</v>
+      </c>
+      <c r="AH39" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ39" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK39" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM39" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO39" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
@@ -5103,10 +5048,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122717929</v>
+        <v>122720558</v>
       </c>
       <c r="B40" t="n">
-        <v>79876</v>
+        <v>57494</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5115,31 +5060,31 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6462</v>
+        <v>100049</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
@@ -5148,13 +5093,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>520029</v>
+        <v>519949</v>
       </c>
       <c r="R40" t="n">
-        <v>7035292</v>
+        <v>7035254</v>
       </c>
       <c r="S40" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5186,6 +5131,11 @@
           <t>2025-02-23</t>
         </is>
       </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Äldre hackspår i stambasen.</t>
+        </is>
+      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
@@ -5202,22 +5152,22 @@
       </c>
       <c r="AJ40" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK40" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM40" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO40" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT40" t="inlineStr"/>
@@ -5235,10 +5185,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122715841</v>
+        <v>122718013</v>
       </c>
       <c r="B41" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5251,42 +5201,42 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>med soral</t>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Finnbodarna, Finnbodarna, Jmt</t>
+          <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>520229</v>
+        <v>519948</v>
       </c>
       <c r="R41" t="n">
-        <v>7035608</v>
+        <v>7035313</v>
       </c>
       <c r="S41" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5320,7 +5270,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>På en björk.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5331,31 +5281,6 @@
       </c>
       <c r="AG41" t="b">
         <v>0</v>
-      </c>
-      <c r="AH41" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ41" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK41" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AM41" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO41" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Betula</t>
-        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
@@ -5372,10 +5297,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122720548</v>
+        <v>122715949</v>
       </c>
       <c r="B42" t="n">
-        <v>90962</v>
+        <v>79847</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5388,34 +5313,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Spejkmyren, Spejkmyren, Jmt</t>
+          <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>519847</v>
+        <v>520254</v>
       </c>
       <c r="R42" t="n">
-        <v>7035432</v>
+        <v>7035555</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5474,10 +5399,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122717294</v>
+        <v>122719979</v>
       </c>
       <c r="B43" t="n">
-        <v>90962</v>
+        <v>57631</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5490,34 +5415,43 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>5432</v>
+        <v>103021</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>520013</v>
+        <v>519946</v>
       </c>
       <c r="R43" t="n">
-        <v>7035340</v>
+        <v>7035240</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5576,7 +5510,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122715757</v>
+        <v>122719371</v>
       </c>
       <c r="B44" t="n">
         <v>78766</v>
@@ -5612,17 +5546,17 @@
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Finnbodarna, Finnbodarna, Jmt</t>
+          <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>520234</v>
+        <v>519943</v>
       </c>
       <c r="R44" t="n">
-        <v>7035595</v>
+        <v>7035270</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5652,11 +5586,6 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-02-23</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5708,10 +5637,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122715870</v>
+        <v>122720959</v>
       </c>
       <c r="B45" t="n">
-        <v>79848</v>
+        <v>78766</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5724,34 +5653,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Finnbodarna, Finnbodarna, Jmt</t>
+          <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>520265</v>
+        <v>519917</v>
       </c>
       <c r="R45" t="n">
-        <v>7035574</v>
+        <v>7035339</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5786,6 +5715,11 @@
           <t>2025-02-23</t>
         </is>
       </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Långväxta bålar på flertalet granar.</t>
+        </is>
+      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
@@ -5794,6 +5728,31 @@
       </c>
       <c r="AG45" t="b">
         <v>0</v>
+      </c>
+      <c r="AH45" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ45" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK45" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM45" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO45" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
@@ -5810,10 +5769,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122719648</v>
+        <v>122716850</v>
       </c>
       <c r="B46" t="n">
-        <v>57478</v>
+        <v>90962</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5826,39 +5785,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>519939</v>
+        <v>520101</v>
       </c>
       <c r="R46" t="n">
-        <v>7035194</v>
+        <v>7035388</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5891,11 +5845,6 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-02-23</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5922,10 +5871,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122715766</v>
+        <v>122716293</v>
       </c>
       <c r="B47" t="n">
-        <v>90962</v>
+        <v>57478</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5938,34 +5887,39 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Finnbodarna, Finnbodarna, Jmt</t>
+          <t>Finnbodarna, Hammerdal, Finnbodarna, Hammerdal, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>520252</v>
+        <v>520249</v>
       </c>
       <c r="R47" t="n">
-        <v>7035591</v>
+        <v>7035364</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5998,6 +5952,11 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-02-23</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6024,10 +5983,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122716392</v>
+        <v>122719648</v>
       </c>
       <c r="B48" t="n">
-        <v>79848</v>
+        <v>57478</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6040,42 +5999,42 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>med soral</t>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Finnbodarna, Finnbodarna, Jmt</t>
+          <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>520385</v>
+        <v>519939</v>
       </c>
       <c r="R48" t="n">
-        <v>7035518</v>
+        <v>7035194</v>
       </c>
       <c r="S48" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6109,7 +6068,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>På gran intill en gammal sälg.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6120,31 +6079,6 @@
       </c>
       <c r="AG48" t="b">
         <v>0</v>
-      </c>
-      <c r="AH48" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ48" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK48" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM48" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO48" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
@@ -6161,10 +6095,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122720327</v>
+        <v>122721463</v>
       </c>
       <c r="B49" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6177,39 +6111,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>519838</v>
+        <v>519841</v>
       </c>
       <c r="R49" t="n">
-        <v>7035393</v>
+        <v>7035417</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6246,7 +6175,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6257,6 +6186,31 @@
       </c>
       <c r="AG49" t="b">
         <v>0</v>
+      </c>
+      <c r="AH49" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ49" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK49" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM49" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO49" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
@@ -6273,10 +6227,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122720368</v>
+        <v>122720686</v>
       </c>
       <c r="B50" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6289,39 +6243,34 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>519852</v>
+        <v>519903</v>
       </c>
       <c r="R50" t="n">
-        <v>7035392</v>
+        <v>7035224</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6356,11 +6305,6 @@
           <t>2025-02-23</t>
         </is>
       </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD50" t="b">
         <v>0</v>
       </c>
@@ -6369,6 +6313,31 @@
       </c>
       <c r="AG50" t="b">
         <v>0</v>
+      </c>
+      <c r="AH50" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ50" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK50" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM50" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO50" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
@@ -6385,10 +6354,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122720823</v>
+        <v>122720065</v>
       </c>
       <c r="B51" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6401,56 +6370,37 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L51" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>519842</v>
+        <v>520062</v>
       </c>
       <c r="R51" t="n">
-        <v>7035388</v>
+        <v>7035232</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6482,11 +6432,6 @@
           <t>2025-02-23</t>
         </is>
       </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Trummande</t>
-        </is>
-      </c>
       <c r="AD51" t="b">
         <v>0</v>
       </c>
@@ -6495,6 +6440,31 @@
       </c>
       <c r="AG51" t="b">
         <v>0</v>
+      </c>
+      <c r="AH51" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ51" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK51" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM51" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO51" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
@@ -6511,10 +6481,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122720558</v>
+        <v>122716443</v>
       </c>
       <c r="B52" t="n">
-        <v>57494</v>
+        <v>78766</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6527,39 +6497,48 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Spejkmyren, Spejkmyren, Jmt</t>
+          <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>519949</v>
+        <v>520251</v>
       </c>
       <c r="R52" t="n">
-        <v>7035254</v>
+        <v>7035394</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6596,7 +6575,7 @@
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>Äldre hackspår i stambasen.</t>
+          <t>Garnlavsrikt</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6607,31 +6586,6 @@
       </c>
       <c r="AG52" t="b">
         <v>0</v>
-      </c>
-      <c r="AH52" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ52" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK52" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM52" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO52" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
@@ -6648,7 +6602,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122715756</v>
+        <v>122716216</v>
       </c>
       <c r="B53" t="n">
         <v>79847</v>
@@ -6682,16 +6636,21 @@
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>520256</v>
+        <v>520368</v>
       </c>
       <c r="R53" t="n">
-        <v>7035593</v>
+        <v>7035513</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6726,6 +6685,11 @@
           <t>2025-02-23</t>
         </is>
       </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>På en gammal grovbarkad sälg.</t>
+        </is>
+      </c>
       <c r="AD53" t="b">
         <v>0</v>
       </c>
@@ -6734,6 +6698,31 @@
       </c>
       <c r="AG53" t="b">
         <v>0</v>
+      </c>
+      <c r="AH53" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ53" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK53" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM53" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO53" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
@@ -6750,10 +6739,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122716443</v>
+        <v>122716673</v>
       </c>
       <c r="B54" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6766,48 +6755,39 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Finnbodarna, Finnbodarna, Jmt</t>
+          <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>520251</v>
+        <v>520108</v>
       </c>
       <c r="R54" t="n">
-        <v>7035394</v>
+        <v>7035462</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6844,7 +6824,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>Garnlavsrikt</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6871,7 +6851,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122720869</v>
+        <v>122715757</v>
       </c>
       <c r="B55" t="n">
         <v>78766</v>
@@ -6907,14 +6887,14 @@
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Spejkmyren, Spejkmyren, Jmt</t>
+          <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>519960</v>
+        <v>520234</v>
       </c>
       <c r="R55" t="n">
-        <v>7035342</v>
+        <v>7035595</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6947,6 +6927,11 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-02-23</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6998,7 +6983,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122715999</v>
+        <v>122717284</v>
       </c>
       <c r="B56" t="n">
         <v>78766</v>
@@ -7034,17 +7019,17 @@
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Finnbodarna, Finnbodarna, Jmt</t>
+          <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>520311</v>
+        <v>520031</v>
       </c>
       <c r="R56" t="n">
-        <v>7035566</v>
+        <v>7035353</v>
       </c>
       <c r="S56" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -7074,6 +7059,11 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-02-23</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Långväxta bålar på flertalet granar.</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7125,10 +7115,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122720454</v>
+        <v>122715778</v>
       </c>
       <c r="B57" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -7141,39 +7131,39 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Spejkmyren, Spejkmyren, Jmt</t>
+          <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>519849</v>
+        <v>520259</v>
       </c>
       <c r="R57" t="n">
-        <v>7035406</v>
+        <v>7035574</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7206,11 +7196,6 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-02-23</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7237,7 +7222,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122715669</v>
+        <v>122715756</v>
       </c>
       <c r="B58" t="n">
         <v>79847</v>
@@ -7271,21 +7256,16 @@
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="K58" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>520221</v>
+        <v>520256</v>
       </c>
       <c r="R58" t="n">
-        <v>7035600</v>
+        <v>7035593</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7344,10 +7324,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122716295</v>
+        <v>122720427</v>
       </c>
       <c r="B59" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7360,39 +7340,39 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="K59" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Finnbodarna, Finnbodarna, Jmt</t>
+          <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>520378</v>
+        <v>519846</v>
       </c>
       <c r="R59" t="n">
-        <v>7035512</v>
+        <v>7035407</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7429,7 +7409,7 @@
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>Ymnig påväxt på en grovbarkad gammal sälg. Fertila bålar med apothecier.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7440,31 +7420,6 @@
       </c>
       <c r="AG59" t="b">
         <v>0</v>
-      </c>
-      <c r="AH59" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ59" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK59" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM59" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO59" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
@@ -7481,10 +7436,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122721035</v>
+        <v>122715868</v>
       </c>
       <c r="B60" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7497,37 +7452,42 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Spejkmyren, Spejkmyren, Jmt</t>
+          <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>519897</v>
+        <v>520265</v>
       </c>
       <c r="R60" t="n">
-        <v>7035374</v>
+        <v>7035574</v>
       </c>
       <c r="S60" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7567,31 +7527,6 @@
       </c>
       <c r="AG60" t="b">
         <v>0</v>
-      </c>
-      <c r="AH60" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ60" t="inlineStr">
-        <is>
-          <t>garnlav</t>
-        </is>
-      </c>
-      <c r="AK60" t="inlineStr">
-        <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="AM60" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO60" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Alectoria sarmentosa</t>
-        </is>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
@@ -7608,10 +7543,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122715849</v>
+        <v>122715780</v>
       </c>
       <c r="B61" t="n">
-        <v>79876</v>
+        <v>79847</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7620,25 +7555,25 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7648,10 +7583,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>520268</v>
+        <v>520259</v>
       </c>
       <c r="R61" t="n">
-        <v>7035575</v>
+        <v>7035569</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7684,6 +7619,11 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-02-23</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>På björk</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7710,10 +7650,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122717359</v>
+        <v>122715874</v>
       </c>
       <c r="B62" t="n">
-        <v>79847</v>
+        <v>79876</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7722,38 +7662,38 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Spejkmyren, Spejkmyren, Jmt</t>
+          <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>520030</v>
+        <v>520265</v>
       </c>
       <c r="R62" t="n">
-        <v>7035341</v>
+        <v>7035574</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7812,10 +7752,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122716234</v>
+        <v>122716427</v>
       </c>
       <c r="B63" t="n">
-        <v>79847</v>
+        <v>78767</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7828,21 +7768,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6458</v>
+        <v>230405</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7852,13 +7792,13 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>520362</v>
+        <v>520388</v>
       </c>
       <c r="R63" t="n">
-        <v>7035500</v>
+        <v>7035490</v>
       </c>
       <c r="S63" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7892,7 +7832,7 @@
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>På en klen gran intill en gammal sälg med lunglav.</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7944,10 +7884,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122718013</v>
+        <v>122716234</v>
       </c>
       <c r="B64" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7960,39 +7900,34 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Spejkmyren, Spejkmyren, Jmt</t>
+          <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>519948</v>
+        <v>520362</v>
       </c>
       <c r="R64" t="n">
-        <v>7035313</v>
+        <v>7035500</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -8029,7 +7964,7 @@
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>På en klen gran intill en gammal sälg med lunglav.</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8040,6 +7975,31 @@
       </c>
       <c r="AG64" t="b">
         <v>0</v>
+      </c>
+      <c r="AH64" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ64" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK64" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM64" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO64" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
@@ -8056,10 +8016,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122717343</v>
+        <v>122715779</v>
       </c>
       <c r="B65" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -8072,42 +8032,42 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Spejkmyren, Spejkmyren, Jmt</t>
+          <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>520034</v>
+        <v>520223</v>
       </c>
       <c r="R65" t="n">
-        <v>7035339</v>
+        <v>7035609</v>
       </c>
       <c r="S65" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -8139,11 +8099,6 @@
           <t>2025-02-23</t>
         </is>
       </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD65" t="b">
         <v>0</v>
       </c>
@@ -8152,6 +8107,31 @@
       </c>
       <c r="AG65" t="b">
         <v>0</v>
+      </c>
+      <c r="AH65" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ65" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK65" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM65" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO65" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
@@ -8168,10 +8148,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122719554</v>
+        <v>122715795</v>
       </c>
       <c r="B66" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -8184,47 +8164,37 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N66" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Spejkmyren, Spejkmyren, Jmt</t>
+          <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>519981</v>
+        <v>520214</v>
       </c>
       <c r="R66" t="n">
-        <v>7035221</v>
+        <v>7035599</v>
       </c>
       <c r="S66" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -8258,7 +8228,7 @@
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>Äldre ringhack som bedöms vara 5 - 10 år gamla.</t>
+          <t>På en klen gran intill en lunglavssälg.</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8287,12 +8257,12 @@
       </c>
       <c r="AM66" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO66" t="inlineStr">
         <is>
-          <t>Stem on living tree # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT66" t="inlineStr"/>
@@ -8310,10 +8280,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>122715801</v>
+        <v>122715999</v>
       </c>
       <c r="B67" t="n">
-        <v>79848</v>
+        <v>78766</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8326,21 +8296,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -8350,13 +8320,13 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>520266</v>
+        <v>520311</v>
       </c>
       <c r="R67" t="n">
-        <v>7035582</v>
+        <v>7035566</v>
       </c>
       <c r="S67" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -8396,6 +8366,31 @@
       </c>
       <c r="AG67" t="b">
         <v>0</v>
+      </c>
+      <c r="AH67" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ67" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK67" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM67" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO67" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
@@ -8412,10 +8407,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>122717989</v>
+        <v>122715934</v>
       </c>
       <c r="B68" t="n">
-        <v>57494</v>
+        <v>78766</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8428,46 +8423,37 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Spejkmyren, Spejkmyren, Jmt</t>
+          <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>519951</v>
+        <v>520303</v>
       </c>
       <c r="R68" t="n">
-        <v>7035320</v>
+        <v>7035598</v>
       </c>
       <c r="S68" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8501,7 +8487,7 @@
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>Trummande</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8512,6 +8498,31 @@
       </c>
       <c r="AG68" t="b">
         <v>0</v>
+      </c>
+      <c r="AH68" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ68" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK68" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM68" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO68" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
@@ -8528,10 +8539,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>122716801</v>
+        <v>122717989</v>
       </c>
       <c r="B69" t="n">
-        <v>57631</v>
+        <v>57494</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8544,31 +8555,31 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>par i lämplig häckbiotop</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P69" t="inlineStr">
@@ -8577,10 +8588,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>520083</v>
+        <v>519951</v>
       </c>
       <c r="R69" t="n">
-        <v>7035403</v>
+        <v>7035320</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8613,6 +8624,11 @@
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-02-23</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Trummande</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8639,10 +8655,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>122719829</v>
+        <v>122716547</v>
       </c>
       <c r="B70" t="n">
-        <v>57478</v>
+        <v>98263</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8651,46 +8667,55 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100109</v>
+        <v>504</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr"/>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
         </is>
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Spejkmyren, Spejkmyren, Jmt</t>
+          <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>519930</v>
+        <v>520386</v>
       </c>
       <c r="R70" t="n">
-        <v>7035181</v>
+        <v>7035492</v>
       </c>
       <c r="S70" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8724,7 +8749,7 @@
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>En vinterståndare på till synes fuktig mark i en lucka.</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8735,6 +8760,11 @@
       </c>
       <c r="AG70" t="b">
         <v>0</v>
+      </c>
+      <c r="AH70" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
@@ -8751,7 +8781,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>122717164</v>
+        <v>122716757</v>
       </c>
       <c r="B71" t="n">
         <v>78766</v>
@@ -8787,17 +8817,17 @@
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Spejkmyren, Spejkmyren, Jmt</t>
+          <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>520120</v>
+        <v>520316</v>
       </c>
       <c r="R71" t="n">
-        <v>7035405</v>
+        <v>7035491</v>
       </c>
       <c r="S71" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8878,7 +8908,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>122719533</v>
+        <v>122716645</v>
       </c>
       <c r="B72" t="n">
         <v>57478</v>
@@ -8923,10 +8953,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>519948</v>
+        <v>520129</v>
       </c>
       <c r="R72" t="n">
-        <v>7035187</v>
+        <v>7035444</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8990,10 +9020,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>122715775</v>
+        <v>122720823</v>
       </c>
       <c r="B73" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -9006,39 +9036,53 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Finnbodarna, Finnbodarna, Jmt</t>
+          <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>520252</v>
+        <v>519842</v>
       </c>
       <c r="R73" t="n">
-        <v>7035576</v>
+        <v>7035388</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -9075,7 +9119,7 @@
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>På björk</t>
+          <t>Trummande</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -9102,10 +9146,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>122715778</v>
+        <v>122715648</v>
       </c>
       <c r="B74" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -9118,39 +9162,39 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
-      <c r="K74" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Finnbodarna, Finnbodarna, Jmt</t>
+          <t>Finnbodarna, Hammerdal, Finnbodarna, Hammerdal, Jmt</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>520259</v>
+        <v>520219</v>
       </c>
       <c r="R74" t="n">
-        <v>7035574</v>
+        <v>7035597</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -9183,6 +9227,11 @@
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-02-23</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9209,7 +9258,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>122715573</v>
+        <v>122716392</v>
       </c>
       <c r="B75" t="n">
         <v>79848</v>
@@ -9243,19 +9292,24 @@
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P75" t="inlineStr">
         <is>
           <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>520214</v>
+        <v>520385</v>
       </c>
       <c r="R75" t="n">
-        <v>7035583</v>
+        <v>7035518</v>
       </c>
       <c r="S75" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -9287,6 +9341,11 @@
           <t>2025-02-23</t>
         </is>
       </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>På gran intill en gammal sälg.</t>
+        </is>
+      </c>
       <c r="AD75" t="b">
         <v>0</v>
       </c>
@@ -9295,6 +9354,31 @@
       </c>
       <c r="AG75" t="b">
         <v>0</v>
+      </c>
+      <c r="AH75" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK75" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM75" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO75" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
@@ -9311,7 +9395,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>122720686</v>
+        <v>122715502</v>
       </c>
       <c r="B76" t="n">
         <v>78766</v>
@@ -9345,19 +9429,24 @@
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Spejkmyren, Spejkmyren, Jmt</t>
+          <t>Djupmyren, Djupmyren, Jmt</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>519903</v>
+        <v>520110</v>
       </c>
       <c r="R76" t="n">
-        <v>7035224</v>
+        <v>7035585</v>
       </c>
       <c r="S76" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -9387,6 +9476,11 @@
       <c r="AA76" t="inlineStr">
         <is>
           <t>2025-02-23</t>
+        </is>
+      </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>Gott om långväxt garnlav på många granar. Vissa bålar är här fertila.</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9438,10 +9532,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>122720474</v>
+        <v>122720869</v>
       </c>
       <c r="B77" t="n">
-        <v>57494</v>
+        <v>78766</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -9454,48 +9548,34 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L77" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M77" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
           <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>519848</v>
+        <v>519960</v>
       </c>
       <c r="R77" t="n">
-        <v>7035394</v>
+        <v>7035342</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9538,6 +9618,31 @@
       </c>
       <c r="AG77" t="b">
         <v>0</v>
+      </c>
+      <c r="AH77" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ77" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK77" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM77" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO77" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
@@ -9554,10 +9659,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>122717446</v>
+        <v>122717359</v>
       </c>
       <c r="B78" t="n">
-        <v>90962</v>
+        <v>79847</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -9570,21 +9675,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -9594,10 +9699,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>520006</v>
+        <v>520030</v>
       </c>
       <c r="R78" t="n">
-        <v>7035303</v>
+        <v>7035341</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9656,10 +9761,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>122717616</v>
+        <v>122715978</v>
       </c>
       <c r="B79" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -9672,34 +9777,39 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Spejkmyren, Spejkmyren, Jmt</t>
+          <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>520019</v>
+        <v>520243</v>
       </c>
       <c r="R79" t="n">
-        <v>7035352</v>
+        <v>7035552</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9734,11 +9844,6 @@
           <t>2025-02-23</t>
         </is>
       </c>
-      <c r="AC79" t="inlineStr">
-        <is>
-          <t>Rikligt.</t>
-        </is>
-      </c>
       <c r="AD79" t="b">
         <v>0</v>
       </c>
@@ -9747,31 +9852,6 @@
       </c>
       <c r="AG79" t="b">
         <v>0</v>
-      </c>
-      <c r="AH79" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ79" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK79" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM79" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO79" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
@@ -9788,10 +9868,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>122715571</v>
+        <v>122719697</v>
       </c>
       <c r="B80" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -9804,37 +9884,37 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Finnbodarna, Finnbodarna, Jmt</t>
+          <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>520216</v>
+        <v>520026</v>
       </c>
       <c r="R80" t="n">
-        <v>7035583</v>
+        <v>7035233</v>
       </c>
       <c r="S80" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -9874,6 +9954,31 @@
       </c>
       <c r="AG80" t="b">
         <v>0</v>
+      </c>
+      <c r="AH80" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ80" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK80" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM80" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO80" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
@@ -9890,10 +9995,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>122716216</v>
+        <v>122717616</v>
       </c>
       <c r="B81" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9906,39 +10011,34 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
-      <c r="K81" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Finnbodarna, Finnbodarna, Jmt</t>
+          <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>520368</v>
+        <v>520019</v>
       </c>
       <c r="R81" t="n">
-        <v>7035513</v>
+        <v>7035352</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9975,7 +10075,7 @@
       </c>
       <c r="AC81" t="inlineStr">
         <is>
-          <t>På en gammal grovbarkad sälg.</t>
+          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9994,22 +10094,22 @@
       </c>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK81" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM81" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO81" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT81" t="inlineStr"/>
@@ -10027,10 +10127,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>122717636</v>
+        <v>122720474</v>
       </c>
       <c r="B82" t="n">
-        <v>57478</v>
+        <v>57494</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -10043,16 +10143,16 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -10060,10 +10160,19 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I82" t="inlineStr"/>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P82" t="inlineStr">
@@ -10072,10 +10181,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>519970</v>
+        <v>519848</v>
       </c>
       <c r="R82" t="n">
-        <v>7035297</v>
+        <v>7035394</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -10108,11 +10217,6 @@
       <c r="AA82" t="inlineStr">
         <is>
           <t>2025-02-23</t>
-        </is>
-      </c>
-      <c r="AC82" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -10139,10 +10243,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>122716547</v>
+        <v>122716964</v>
       </c>
       <c r="B83" t="n">
-        <v>98263</v>
+        <v>90962</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -10151,55 +10255,41 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>504</v>
+        <v>5432</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J83" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K83" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Finnbodarna, Finnbodarna, Jmt</t>
+          <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>520386</v>
+        <v>520115</v>
       </c>
       <c r="R83" t="n">
-        <v>7035492</v>
+        <v>7035402</v>
       </c>
       <c r="S83" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -10231,11 +10321,6 @@
           <t>2025-02-23</t>
         </is>
       </c>
-      <c r="AC83" t="inlineStr">
-        <is>
-          <t>En vinterståndare på till synes fuktig mark i en lucka.</t>
-        </is>
-      </c>
       <c r="AD83" t="b">
         <v>0</v>
       </c>
@@ -10244,11 +10329,6 @@
       </c>
       <c r="AG83" t="b">
         <v>0</v>
-      </c>
-      <c r="AH83" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
@@ -10265,10 +10345,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>122720065</v>
+        <v>122717446</v>
       </c>
       <c r="B84" t="n">
-        <v>78766</v>
+        <v>90962</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -10281,21 +10361,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -10305,13 +10385,13 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>520062</v>
+        <v>520006</v>
       </c>
       <c r="R84" t="n">
-        <v>7035232</v>
+        <v>7035303</v>
       </c>
       <c r="S84" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -10351,31 +10431,6 @@
       </c>
       <c r="AG84" t="b">
         <v>0</v>
-      </c>
-      <c r="AH84" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ84" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK84" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM84" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO84" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
@@ -10392,10 +10447,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>122717284</v>
+        <v>122716303</v>
       </c>
       <c r="B85" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -10408,37 +10463,42 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Spejkmyren, Spejkmyren, Jmt</t>
+          <t>Finnbodarna, Hammerdal, Finnbodarna, Hammerdal, Jmt</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>520031</v>
+        <v>520250</v>
       </c>
       <c r="R85" t="n">
-        <v>7035353</v>
+        <v>7035363</v>
       </c>
       <c r="S85" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -10472,7 +10532,7 @@
       </c>
       <c r="AC85" t="inlineStr">
         <is>
-          <t>Långväxta bålar på flertalet granar.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -10483,31 +10543,6 @@
       </c>
       <c r="AG85" t="b">
         <v>0</v>
-      </c>
-      <c r="AH85" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ85" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK85" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM85" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO85" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
@@ -10524,10 +10559,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>122720959</v>
+        <v>122715677</v>
       </c>
       <c r="B86" t="n">
-        <v>78766</v>
+        <v>79848</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -10540,34 +10575,34 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Spejkmyren, Spejkmyren, Jmt</t>
+          <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>519917</v>
+        <v>520221</v>
       </c>
       <c r="R86" t="n">
-        <v>7035339</v>
+        <v>7035600</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -10604,7 +10639,7 @@
       </c>
       <c r="AC86" t="inlineStr">
         <is>
-          <t>Långväxta bålar på flertalet granar.</t>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10615,31 +10650,6 @@
       </c>
       <c r="AG86" t="b">
         <v>0</v>
-      </c>
-      <c r="AH86" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ86" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK86" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM86" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO86" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
@@ -10656,10 +10666,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>122716645</v>
+        <v>122717164</v>
       </c>
       <c r="B87" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -10672,39 +10682,34 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
-      <c r="M87" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P87" t="inlineStr">
         <is>
           <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>520129</v>
+        <v>520120</v>
       </c>
       <c r="R87" t="n">
-        <v>7035444</v>
+        <v>7035405</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10739,11 +10744,6 @@
           <t>2025-02-23</t>
         </is>
       </c>
-      <c r="AC87" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD87" t="b">
         <v>0</v>
       </c>
@@ -10752,6 +10752,31 @@
       </c>
       <c r="AG87" t="b">
         <v>0</v>
+      </c>
+      <c r="AH87" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ87" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK87" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM87" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO87" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
@@ -10768,10 +10793,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>122716427</v>
+        <v>122715849</v>
       </c>
       <c r="B88" t="n">
-        <v>78767</v>
+        <v>79876</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -10780,25 +10805,25 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>230405</v>
+        <v>6462</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -10808,13 +10833,13 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>520388</v>
+        <v>520268</v>
       </c>
       <c r="R88" t="n">
-        <v>7035490</v>
+        <v>7035575</v>
       </c>
       <c r="S88" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -10846,11 +10871,6 @@
           <t>2025-02-23</t>
         </is>
       </c>
-      <c r="AC88" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
-        </is>
-      </c>
       <c r="AD88" t="b">
         <v>0</v>
       </c>
@@ -10859,31 +10879,6 @@
       </c>
       <c r="AG88" t="b">
         <v>0</v>
-      </c>
-      <c r="AH88" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ88" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK88" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM88" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO88" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
@@ -10900,10 +10895,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>122715569</v>
+        <v>122716329</v>
       </c>
       <c r="B89" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -10916,37 +10911,42 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Djupmyren, Djupmyren, Jmt</t>
+          <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>520115</v>
+        <v>520374</v>
       </c>
       <c r="R89" t="n">
-        <v>7035562</v>
+        <v>7035511</v>
       </c>
       <c r="S89" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -10980,7 +10980,7 @@
       </c>
       <c r="AC89" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>På gran intill en gammal lunglavssälg.</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -11032,7 +11032,7 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>122720427</v>
+        <v>122720327</v>
       </c>
       <c r="B90" t="n">
         <v>57478</v>
@@ -11068,7 +11068,7 @@
       <c r="I90" t="inlineStr"/>
       <c r="M90" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P90" t="inlineStr">
@@ -11077,10 +11077,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>519846</v>
+        <v>519838</v>
       </c>
       <c r="R90" t="n">
-        <v>7035407</v>
+        <v>7035393</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>

--- a/artfynd/A 1625-2025 artfynd.xlsx
+++ b/artfynd/A 1625-2025 artfynd.xlsx
@@ -2378,10 +2378,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122717294</v>
+        <v>122715953</v>
       </c>
       <c r="B17" t="n">
-        <v>90962</v>
+        <v>79848</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2394,34 +2394,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5432</v>
+        <v>2081</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Spejkmyren, Spejkmyren, Jmt</t>
+          <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>520013</v>
+        <v>520254</v>
       </c>
       <c r="R17" t="n">
-        <v>7035340</v>
+        <v>7035555</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2480,10 +2480,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122715953</v>
+        <v>122717294</v>
       </c>
       <c r="B18" t="n">
-        <v>79848</v>
+        <v>90962</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2496,34 +2496,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2081</v>
+        <v>5432</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Finnbodarna, Finnbodarna, Jmt</t>
+          <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>520254</v>
+        <v>520013</v>
       </c>
       <c r="R18" t="n">
-        <v>7035555</v>
+        <v>7035340</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -5510,10 +5510,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122719371</v>
+        <v>122716850</v>
       </c>
       <c r="B44" t="n">
-        <v>78766</v>
+        <v>90962</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5526,21 +5526,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5550,13 +5550,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>519943</v>
+        <v>520101</v>
       </c>
       <c r="R44" t="n">
-        <v>7035270</v>
+        <v>7035388</v>
       </c>
       <c r="S44" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5596,31 +5596,6 @@
       </c>
       <c r="AG44" t="b">
         <v>0</v>
-      </c>
-      <c r="AH44" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ44" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK44" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM44" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO44" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
@@ -5637,10 +5612,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122720959</v>
+        <v>122716293</v>
       </c>
       <c r="B45" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5653,34 +5628,39 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Spejkmyren, Spejkmyren, Jmt</t>
+          <t>Finnbodarna, Hammerdal, Finnbodarna, Hammerdal, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>519917</v>
+        <v>520249</v>
       </c>
       <c r="R45" t="n">
-        <v>7035339</v>
+        <v>7035364</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5717,7 +5697,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Långväxta bålar på flertalet granar.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5728,31 +5708,6 @@
       </c>
       <c r="AG45" t="b">
         <v>0</v>
-      </c>
-      <c r="AH45" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ45" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK45" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM45" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO45" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
@@ -5769,10 +5724,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122716850</v>
+        <v>122719648</v>
       </c>
       <c r="B46" t="n">
-        <v>90962</v>
+        <v>57478</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5785,34 +5740,39 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>520101</v>
+        <v>519939</v>
       </c>
       <c r="R46" t="n">
-        <v>7035388</v>
+        <v>7035194</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5845,6 +5805,11 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-02-23</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5871,10 +5836,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122716293</v>
+        <v>122719371</v>
       </c>
       <c r="B47" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5887,42 +5852,37 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Finnbodarna, Hammerdal, Finnbodarna, Hammerdal, Jmt</t>
+          <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>520249</v>
+        <v>519943</v>
       </c>
       <c r="R47" t="n">
-        <v>7035364</v>
+        <v>7035270</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5954,11 +5914,6 @@
           <t>2025-02-23</t>
         </is>
       </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
@@ -5967,6 +5922,31 @@
       </c>
       <c r="AG47" t="b">
         <v>0</v>
+      </c>
+      <c r="AH47" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ47" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK47" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM47" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO47" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
@@ -5983,10 +5963,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122719648</v>
+        <v>122720959</v>
       </c>
       <c r="B48" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5999,39 +5979,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>519939</v>
+        <v>519917</v>
       </c>
       <c r="R48" t="n">
-        <v>7035194</v>
+        <v>7035339</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6068,7 +6043,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Långväxta bålar på flertalet granar.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6079,6 +6054,31 @@
       </c>
       <c r="AG48" t="b">
         <v>0</v>
+      </c>
+      <c r="AH48" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ48" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK48" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM48" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO48" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
@@ -6354,10 +6354,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122720065</v>
+        <v>122716216</v>
       </c>
       <c r="B51" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6370,37 +6370,42 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Spejkmyren, Spejkmyren, Jmt</t>
+          <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>520062</v>
+        <v>520368</v>
       </c>
       <c r="R51" t="n">
-        <v>7035232</v>
+        <v>7035513</v>
       </c>
       <c r="S51" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6432,6 +6437,11 @@
           <t>2025-02-23</t>
         </is>
       </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>På en gammal grovbarkad sälg.</t>
+        </is>
+      </c>
       <c r="AD51" t="b">
         <v>0</v>
       </c>
@@ -6448,22 +6458,22 @@
       </c>
       <c r="AJ51" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK51" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM51" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO51" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT51" t="inlineStr"/>
@@ -6481,7 +6491,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122716443</v>
+        <v>122720065</v>
       </c>
       <c r="B52" t="n">
         <v>78766</v>
@@ -6514,34 +6524,20 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Finnbodarna, Finnbodarna, Jmt</t>
+          <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>520251</v>
+        <v>520062</v>
       </c>
       <c r="R52" t="n">
-        <v>7035394</v>
+        <v>7035232</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6573,11 +6569,6 @@
           <t>2025-02-23</t>
         </is>
       </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Garnlavsrikt</t>
-        </is>
-      </c>
       <c r="AD52" t="b">
         <v>0</v>
       </c>
@@ -6586,6 +6577,31 @@
       </c>
       <c r="AG52" t="b">
         <v>0</v>
+      </c>
+      <c r="AH52" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ52" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK52" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM52" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO52" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
@@ -6602,10 +6618,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122716216</v>
+        <v>122716443</v>
       </c>
       <c r="B53" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6618,27 +6634,36 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
@@ -6647,10 +6672,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>520368</v>
+        <v>520251</v>
       </c>
       <c r="R53" t="n">
-        <v>7035513</v>
+        <v>7035394</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6687,7 +6712,7 @@
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>På en gammal grovbarkad sälg.</t>
+          <t>Garnlavsrikt</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6698,31 +6723,6 @@
       </c>
       <c r="AG53" t="b">
         <v>0</v>
-      </c>
-      <c r="AH53" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ53" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK53" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM53" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO53" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
@@ -9995,10 +9995,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>122717616</v>
+        <v>122715677</v>
       </c>
       <c r="B81" t="n">
-        <v>78766</v>
+        <v>79848</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -10011,34 +10011,34 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Spejkmyren, Spejkmyren, Jmt</t>
+          <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>520019</v>
+        <v>520221</v>
       </c>
       <c r="R81" t="n">
-        <v>7035352</v>
+        <v>7035600</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -10075,7 +10075,7 @@
       </c>
       <c r="AC81" t="inlineStr">
         <is>
-          <t>Rikligt.</t>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -10086,31 +10086,6 @@
       </c>
       <c r="AG81" t="b">
         <v>0</v>
-      </c>
-      <c r="AH81" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ81" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK81" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM81" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO81" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
@@ -10127,10 +10102,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>122720474</v>
+        <v>122717616</v>
       </c>
       <c r="B82" t="n">
-        <v>57494</v>
+        <v>78766</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -10143,48 +10118,34 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L82" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
           <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>519848</v>
+        <v>520019</v>
       </c>
       <c r="R82" t="n">
-        <v>7035394</v>
+        <v>7035352</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -10219,6 +10180,11 @@
           <t>2025-02-23</t>
         </is>
       </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>Rikligt.</t>
+        </is>
+      </c>
       <c r="AD82" t="b">
         <v>0</v>
       </c>
@@ -10227,6 +10193,31 @@
       </c>
       <c r="AG82" t="b">
         <v>0</v>
+      </c>
+      <c r="AH82" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ82" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK82" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM82" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO82" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
@@ -10243,10 +10234,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>122716964</v>
+        <v>122720474</v>
       </c>
       <c r="B83" t="n">
-        <v>90962</v>
+        <v>57494</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -10259,34 +10250,48 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P83" t="inlineStr">
         <is>
           <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>520115</v>
+        <v>519848</v>
       </c>
       <c r="R83" t="n">
-        <v>7035402</v>
+        <v>7035394</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -10345,7 +10350,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>122717446</v>
+        <v>122716964</v>
       </c>
       <c r="B84" t="n">
         <v>90962</v>
@@ -10385,10 +10390,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>520006</v>
+        <v>520115</v>
       </c>
       <c r="R84" t="n">
-        <v>7035303</v>
+        <v>7035402</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -10447,10 +10452,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>122716303</v>
+        <v>122717446</v>
       </c>
       <c r="B85" t="n">
-        <v>57478</v>
+        <v>90962</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -10463,39 +10468,34 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
-      <c r="M85" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Finnbodarna, Hammerdal, Finnbodarna, Hammerdal, Jmt</t>
+          <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>520250</v>
+        <v>520006</v>
       </c>
       <c r="R85" t="n">
-        <v>7035363</v>
+        <v>7035303</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -10528,11 +10528,6 @@
       <c r="AA85" t="inlineStr">
         <is>
           <t>2025-02-23</t>
-        </is>
-      </c>
-      <c r="AC85" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -10559,10 +10554,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>122715677</v>
+        <v>122716303</v>
       </c>
       <c r="B86" t="n">
-        <v>79848</v>
+        <v>57478</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -10575,34 +10570,39 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Finnbodarna, Finnbodarna, Jmt</t>
+          <t>Finnbodarna, Hammerdal, Finnbodarna, Hammerdal, Jmt</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>520221</v>
+        <v>520250</v>
       </c>
       <c r="R86" t="n">
-        <v>7035600</v>
+        <v>7035363</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -10639,7 +10639,7 @@
       </c>
       <c r="AC86" t="inlineStr">
         <is>
-          <t>På gran</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD86" t="b">

--- a/artfynd/A 1625-2025 artfynd.xlsx
+++ b/artfynd/A 1625-2025 artfynd.xlsx
@@ -9395,10 +9395,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>122715502</v>
+        <v>122715978</v>
       </c>
       <c r="B76" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -9411,21 +9411,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -9436,17 +9436,17 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Djupmyren, Djupmyren, Jmt</t>
+          <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>520110</v>
+        <v>520243</v>
       </c>
       <c r="R76" t="n">
-        <v>7035585</v>
+        <v>7035552</v>
       </c>
       <c r="S76" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -9478,11 +9478,6 @@
           <t>2025-02-23</t>
         </is>
       </c>
-      <c r="AC76" t="inlineStr">
-        <is>
-          <t>Gott om långväxt garnlav på många granar. Vissa bålar är här fertila.</t>
-        </is>
-      </c>
       <c r="AD76" t="b">
         <v>0</v>
       </c>
@@ -9491,31 +9486,6 @@
       </c>
       <c r="AG76" t="b">
         <v>0</v>
-      </c>
-      <c r="AH76" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ76" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK76" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM76" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO76" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
@@ -9532,7 +9502,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>122720869</v>
+        <v>122715502</v>
       </c>
       <c r="B77" t="n">
         <v>78766</v>
@@ -9566,19 +9536,24 @@
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Spejkmyren, Spejkmyren, Jmt</t>
+          <t>Djupmyren, Djupmyren, Jmt</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>519960</v>
+        <v>520110</v>
       </c>
       <c r="R77" t="n">
-        <v>7035342</v>
+        <v>7035585</v>
       </c>
       <c r="S77" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -9608,6 +9583,11 @@
       <c r="AA77" t="inlineStr">
         <is>
           <t>2025-02-23</t>
+        </is>
+      </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>Gott om långväxt garnlav på många granar. Vissa bålar är här fertila.</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9659,10 +9639,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>122717359</v>
+        <v>122720869</v>
       </c>
       <c r="B78" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -9675,21 +9655,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -9699,10 +9679,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>520030</v>
+        <v>519960</v>
       </c>
       <c r="R78" t="n">
-        <v>7035341</v>
+        <v>7035342</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9745,6 +9725,31 @@
       </c>
       <c r="AG78" t="b">
         <v>0</v>
+      </c>
+      <c r="AH78" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ78" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK78" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM78" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO78" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
@@ -9761,7 +9766,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>122715978</v>
+        <v>122717359</v>
       </c>
       <c r="B79" t="n">
         <v>79847</v>
@@ -9795,21 +9800,16 @@
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
-      <c r="K79" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Finnbodarna, Finnbodarna, Jmt</t>
+          <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>520243</v>
+        <v>520030</v>
       </c>
       <c r="R79" t="n">
-        <v>7035552</v>
+        <v>7035341</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>

--- a/artfynd/A 1625-2025 artfynd.xlsx
+++ b/artfynd/A 1625-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122715870</v>
+        <v>122720686</v>
       </c>
       <c r="B2" t="n">
-        <v>79848</v>
+        <v>78766</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Finnbodarna, Finnbodarna, Jmt</t>
+          <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>520265</v>
+        <v>519903</v>
       </c>
       <c r="R2" t="n">
-        <v>7035574</v>
+        <v>7035224</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -761,6 +761,31 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -777,10 +802,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122715669</v>
+        <v>122715757</v>
       </c>
       <c r="B3" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,39 +818,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>520221</v>
+        <v>520234</v>
       </c>
       <c r="R3" t="n">
-        <v>7035600</v>
+        <v>7035595</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -860,6 +880,11 @@
           <t>2025-02-23</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -868,6 +893,31 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -884,7 +934,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122717873</v>
+        <v>122715571</v>
       </c>
       <c r="B4" t="n">
         <v>79847</v>
@@ -918,24 +968,19 @@
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Spejkmyren, Spejkmyren, Jmt</t>
+          <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>520033</v>
+        <v>520216</v>
       </c>
       <c r="R4" t="n">
-        <v>7035301</v>
+        <v>7035583</v>
       </c>
       <c r="S4" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -975,31 +1020,6 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1016,7 +1036,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122717488</v>
+        <v>122715778</v>
       </c>
       <c r="B5" t="n">
         <v>79847</v>
@@ -1050,16 +1070,21 @@
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Spejkmyren, Spejkmyren, Jmt</t>
+          <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>520000</v>
+        <v>520259</v>
       </c>
       <c r="R5" t="n">
-        <v>7035297</v>
+        <v>7035574</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1118,10 +1143,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122717929</v>
+        <v>122715677</v>
       </c>
       <c r="B6" t="n">
-        <v>79876</v>
+        <v>79848</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1130,46 +1155,41 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6462</v>
+        <v>2081</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Spejkmyren, Spejkmyren, Jmt</t>
+          <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>520029</v>
+        <v>520221</v>
       </c>
       <c r="R6" t="n">
-        <v>7035292</v>
+        <v>7035600</v>
       </c>
       <c r="S6" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1201,6 +1221,11 @@
           <t>2025-02-23</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>På gran</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1209,31 +1234,6 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1250,10 +1250,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122717468</v>
+        <v>122717359</v>
       </c>
       <c r="B7" t="n">
-        <v>57494</v>
+        <v>79847</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1266,43 +1266,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>520020</v>
+        <v>520030</v>
       </c>
       <c r="R7" t="n">
-        <v>7035330</v>
+        <v>7035341</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1361,7 +1352,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122719875</v>
+        <v>122717343</v>
       </c>
       <c r="B8" t="n">
         <v>57478</v>
@@ -1406,10 +1397,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>519983</v>
+        <v>520034</v>
       </c>
       <c r="R8" t="n">
-        <v>7035206</v>
+        <v>7035339</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1473,10 +1464,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122715573</v>
+        <v>122719875</v>
       </c>
       <c r="B9" t="n">
-        <v>79848</v>
+        <v>57478</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1489,34 +1480,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Finnbodarna, Finnbodarna, Jmt</t>
+          <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>520214</v>
+        <v>519983</v>
       </c>
       <c r="R9" t="n">
-        <v>7035583</v>
+        <v>7035206</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1549,6 +1545,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-02-23</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1575,10 +1576,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122716160</v>
+        <v>122720548</v>
       </c>
       <c r="B10" t="n">
-        <v>78766</v>
+        <v>90970</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1591,34 +1592,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Finnbodarna, Finnbodarna, Jmt</t>
+          <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>520349</v>
+        <v>519847</v>
       </c>
       <c r="R10" t="n">
-        <v>7035517</v>
+        <v>7035432</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1661,31 +1662,6 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1702,10 +1678,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122716269</v>
+        <v>122715999</v>
       </c>
       <c r="B11" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1718,42 +1694,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Finnbodarna, Hammerdal, Finnbodarna, Hammerdal, Jmt</t>
+          <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>520256</v>
+        <v>520311</v>
       </c>
       <c r="R11" t="n">
-        <v>7035380</v>
+        <v>7035566</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1785,11 +1756,6 @@
           <t>2025-02-23</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1798,6 +1764,31 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -1814,10 +1805,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122720281</v>
+        <v>122715836</v>
       </c>
       <c r="B12" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1830,39 +1821,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Spejkmyren, Spejkmyren, Jmt</t>
+          <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>519850</v>
+        <v>520269</v>
       </c>
       <c r="R12" t="n">
-        <v>7035373</v>
+        <v>7035574</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1895,11 +1886,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-02-23</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1926,10 +1912,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122716387</v>
+        <v>122715978</v>
       </c>
       <c r="B13" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1942,39 +1928,39 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Finnbodarna, Hammerdal, Finnbodarna, Hammerdal, Jmt</t>
+          <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>520278</v>
+        <v>520243</v>
       </c>
       <c r="R13" t="n">
-        <v>7035397</v>
+        <v>7035552</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2007,11 +1993,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-02-23</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2038,10 +2019,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122720469</v>
+        <v>122716427</v>
       </c>
       <c r="B14" t="n">
-        <v>78766</v>
+        <v>78767</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2054,16 +2035,16 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>230405</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -2074,17 +2055,17 @@
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Spejkmyren, Spejkmyren, Jmt</t>
+          <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>519996</v>
+        <v>520388</v>
       </c>
       <c r="R14" t="n">
-        <v>7035241</v>
+        <v>7035490</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2114,6 +2095,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-02-23</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2165,10 +2151,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122715766</v>
+        <v>122716645</v>
       </c>
       <c r="B15" t="n">
-        <v>90962</v>
+        <v>57478</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2181,34 +2167,39 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Finnbodarna, Finnbodarna, Jmt</t>
+          <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>520252</v>
+        <v>520129</v>
       </c>
       <c r="R15" t="n">
-        <v>7035591</v>
+        <v>7035444</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2241,6 +2232,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-02-23</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2267,7 +2263,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122716801</v>
+        <v>122716682</v>
       </c>
       <c r="B16" t="n">
         <v>57631</v>
@@ -2316,10 +2312,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>520083</v>
+        <v>520101</v>
       </c>
       <c r="R16" t="n">
-        <v>7035403</v>
+        <v>7035453</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2378,10 +2374,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122715953</v>
+        <v>122715766</v>
       </c>
       <c r="B17" t="n">
-        <v>79848</v>
+        <v>90970</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2394,21 +2390,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2081</v>
+        <v>5432</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2418,10 +2414,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>520254</v>
+        <v>520252</v>
       </c>
       <c r="R17" t="n">
-        <v>7035555</v>
+        <v>7035591</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2480,10 +2476,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122717294</v>
+        <v>122720368</v>
       </c>
       <c r="B18" t="n">
-        <v>90962</v>
+        <v>57478</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2496,34 +2492,39 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>520013</v>
+        <v>519852</v>
       </c>
       <c r="R18" t="n">
-        <v>7035340</v>
+        <v>7035392</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2556,6 +2557,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-02-23</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2582,10 +2588,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122719829</v>
+        <v>122717989</v>
       </c>
       <c r="B19" t="n">
-        <v>57478</v>
+        <v>57494</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2598,16 +2604,16 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2615,10 +2621,14 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2627,10 +2637,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>519930</v>
+        <v>519951</v>
       </c>
       <c r="R19" t="n">
-        <v>7035181</v>
+        <v>7035320</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2667,7 +2677,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Trummande</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2694,7 +2704,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122719533</v>
+        <v>122720327</v>
       </c>
       <c r="B20" t="n">
         <v>57478</v>
@@ -2739,10 +2749,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>519948</v>
+        <v>519838</v>
       </c>
       <c r="R20" t="n">
-        <v>7035187</v>
+        <v>7035393</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2806,10 +2816,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122720454</v>
+        <v>122716964</v>
       </c>
       <c r="B21" t="n">
-        <v>57478</v>
+        <v>90970</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2822,39 +2832,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>519849</v>
+        <v>520115</v>
       </c>
       <c r="R21" t="n">
-        <v>7035406</v>
+        <v>7035402</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2887,11 +2892,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-02-23</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2918,10 +2918,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122715571</v>
+        <v>122715502</v>
       </c>
       <c r="B22" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2934,37 +2934,42 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Finnbodarna, Finnbodarna, Jmt</t>
+          <t>Djupmyren, Djupmyren, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>520216</v>
+        <v>520110</v>
       </c>
       <c r="R22" t="n">
-        <v>7035583</v>
+        <v>7035585</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2996,6 +3001,11 @@
           <t>2025-02-23</t>
         </is>
       </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Gott om långväxt garnlav på många granar. Vissa bålar är här fertila.</t>
+        </is>
+      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
@@ -3004,6 +3014,31 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM22" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -3020,10 +3055,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122717636</v>
+        <v>122720469</v>
       </c>
       <c r="B23" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3036,39 +3071,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>519970</v>
+        <v>519996</v>
       </c>
       <c r="R23" t="n">
-        <v>7035297</v>
+        <v>7035241</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3103,11 +3133,6 @@
           <t>2025-02-23</t>
         </is>
       </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
@@ -3116,6 +3141,31 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM23" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
@@ -3132,7 +3182,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122715841</v>
+        <v>122716329</v>
       </c>
       <c r="B24" t="n">
         <v>79847</v>
@@ -3177,13 +3227,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>520229</v>
+        <v>520374</v>
       </c>
       <c r="R24" t="n">
-        <v>7035608</v>
+        <v>7035511</v>
       </c>
       <c r="S24" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3217,7 +3267,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>På en björk.</t>
+          <t>På gran intill en gammal lunglavssälg.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3236,22 +3286,22 @@
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>björkar</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK24" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM24" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Betula</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT24" t="inlineStr"/>
@@ -3269,10 +3319,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122716295</v>
+        <v>122720558</v>
       </c>
       <c r="B25" t="n">
-        <v>79847</v>
+        <v>57494</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3285,39 +3335,39 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Finnbodarna, Finnbodarna, Jmt</t>
+          <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>520378</v>
+        <v>519949</v>
       </c>
       <c r="R25" t="n">
-        <v>7035512</v>
+        <v>7035254</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3354,7 +3404,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Ymnig påväxt på en grovbarkad gammal sälg. Fertila bålar med apothecier.</t>
+          <t>Äldre hackspår i stambasen.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3373,22 +3423,22 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK25" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3660,10 +3710,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122716682</v>
+        <v>122719829</v>
       </c>
       <c r="B28" t="n">
-        <v>57631</v>
+        <v>57478</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3676,31 +3726,27 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="M28" t="inlineStr">
         <is>
-          <t>par i lämplig häckbiotop</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -3709,10 +3755,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>520101</v>
+        <v>519930</v>
       </c>
       <c r="R28" t="n">
-        <v>7035453</v>
+        <v>7035181</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3745,6 +3791,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-02-23</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3771,7 +3822,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122720629</v>
+        <v>122719697</v>
       </c>
       <c r="B29" t="n">
         <v>78766</v>
@@ -3811,13 +3862,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>519935</v>
+        <v>520026</v>
       </c>
       <c r="R29" t="n">
-        <v>7035246</v>
+        <v>7035233</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3847,11 +3898,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-02-23</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3903,10 +3949,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122715836</v>
+        <v>122717284</v>
       </c>
       <c r="B30" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3919,42 +3965,37 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Finnbodarna, Finnbodarna, Jmt</t>
+          <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>520269</v>
+        <v>520031</v>
       </c>
       <c r="R30" t="n">
-        <v>7035574</v>
+        <v>7035353</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3986,6 +4027,11 @@
           <t>2025-02-23</t>
         </is>
       </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Långväxta bålar på flertalet granar.</t>
+        </is>
+      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
@@ -3994,6 +4040,31 @@
       </c>
       <c r="AG30" t="b">
         <v>0</v>
+      </c>
+      <c r="AH30" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM30" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
@@ -4122,7 +4193,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122715790</v>
+        <v>122715949</v>
       </c>
       <c r="B32" t="n">
         <v>79847</v>
@@ -4156,21 +4227,16 @@
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>520267</v>
+        <v>520254</v>
       </c>
       <c r="R32" t="n">
-        <v>7035581</v>
+        <v>7035555</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4229,10 +4295,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122720368</v>
+        <v>122716757</v>
       </c>
       <c r="B33" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4245,42 +4311,37 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Spejkmyren, Spejkmyren, Jmt</t>
+          <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>519852</v>
+        <v>520316</v>
       </c>
       <c r="R33" t="n">
-        <v>7035392</v>
+        <v>7035491</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4312,11 +4373,6 @@
           <t>2025-02-23</t>
         </is>
       </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
@@ -4325,6 +4381,31 @@
       </c>
       <c r="AG33" t="b">
         <v>0</v>
+      </c>
+      <c r="AH33" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM33" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
@@ -4341,10 +4422,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122717343</v>
+        <v>122715569</v>
       </c>
       <c r="B34" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4357,39 +4438,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Spejkmyren, Spejkmyren, Jmt</t>
+          <t>Djupmyren, Djupmyren, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>520034</v>
+        <v>520115</v>
       </c>
       <c r="R34" t="n">
-        <v>7035339</v>
+        <v>7035562</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4426,7 +4502,7 @@
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4437,6 +4513,31 @@
       </c>
       <c r="AG34" t="b">
         <v>0</v>
+      </c>
+      <c r="AH34" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ34" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK34" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM34" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO34" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
@@ -4453,10 +4554,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122715801</v>
+        <v>122719979</v>
       </c>
       <c r="B35" t="n">
-        <v>79848</v>
+        <v>57631</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4469,34 +4570,43 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>2081</v>
+        <v>103021</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Finnbodarna, Finnbodarna, Jmt</t>
+          <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>520266</v>
+        <v>519946</v>
       </c>
       <c r="R35" t="n">
-        <v>7035582</v>
+        <v>7035240</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4555,10 +4665,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122720548</v>
+        <v>122717873</v>
       </c>
       <c r="B36" t="n">
-        <v>90962</v>
+        <v>79847</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4571,37 +4681,42 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>519847</v>
+        <v>520033</v>
       </c>
       <c r="R36" t="n">
-        <v>7035432</v>
+        <v>7035301</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4641,6 +4756,31 @@
       </c>
       <c r="AG36" t="b">
         <v>0</v>
+      </c>
+      <c r="AH36" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ36" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK36" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM36" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO36" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
@@ -4657,7 +4797,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122721035</v>
+        <v>122717616</v>
       </c>
       <c r="B37" t="n">
         <v>78766</v>
@@ -4697,13 +4837,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>519897</v>
+        <v>520019</v>
       </c>
       <c r="R37" t="n">
-        <v>7035374</v>
+        <v>7035352</v>
       </c>
       <c r="S37" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4735,6 +4875,11 @@
           <t>2025-02-23</t>
         </is>
       </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Rikligt.</t>
+        </is>
+      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
@@ -4751,12 +4896,12 @@
       </c>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>garnlav</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM37" t="inlineStr">
@@ -4766,7 +4911,7 @@
       </c>
       <c r="AO37" t="inlineStr">
         <is>
-          <t>Branch on living tree # Alectoria sarmentosa</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -4784,10 +4929,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122721333</v>
+        <v>122716216</v>
       </c>
       <c r="B38" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4800,37 +4945,42 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Spejkmyren, Spejkmyren, Jmt</t>
+          <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>519906</v>
+        <v>520368</v>
       </c>
       <c r="R38" t="n">
-        <v>7035389</v>
+        <v>7035513</v>
       </c>
       <c r="S38" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4864,7 +5014,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Ymnigt på flera granar.</t>
+          <t>På en gammal grovbarkad sälg.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4883,22 +5033,22 @@
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK38" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM38" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO38" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -4916,10 +5066,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122715569</v>
+        <v>122716269</v>
       </c>
       <c r="B39" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4932,34 +5082,39 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Djupmyren, Djupmyren, Jmt</t>
+          <t>Finnbodarna, Hammerdal, Finnbodarna, Hammerdal, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>520115</v>
+        <v>520256</v>
       </c>
       <c r="R39" t="n">
-        <v>7035562</v>
+        <v>7035380</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4996,7 +5151,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5007,31 +5162,6 @@
       </c>
       <c r="AG39" t="b">
         <v>0</v>
-      </c>
-      <c r="AH39" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ39" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK39" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM39" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO39" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
@@ -5048,10 +5178,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122720558</v>
+        <v>122716303</v>
       </c>
       <c r="B40" t="n">
-        <v>57494</v>
+        <v>57478</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5064,16 +5194,16 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -5089,14 +5219,14 @@
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Spejkmyren, Spejkmyren, Jmt</t>
+          <t>Finnbodarna, Hammerdal, Finnbodarna, Hammerdal, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>519949</v>
+        <v>520250</v>
       </c>
       <c r="R40" t="n">
-        <v>7035254</v>
+        <v>7035363</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5133,7 +5263,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Äldre hackspår i stambasen.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5144,31 +5274,6 @@
       </c>
       <c r="AG40" t="b">
         <v>0</v>
-      </c>
-      <c r="AH40" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ40" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK40" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM40" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO40" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
@@ -5297,10 +5402,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122715949</v>
+        <v>122715874</v>
       </c>
       <c r="B42" t="n">
-        <v>79847</v>
+        <v>79876</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5309,25 +5414,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5337,10 +5442,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>520254</v>
+        <v>520265</v>
       </c>
       <c r="R42" t="n">
-        <v>7035555</v>
+        <v>7035574</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5399,10 +5504,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122719979</v>
+        <v>122715953</v>
       </c>
       <c r="B43" t="n">
-        <v>57631</v>
+        <v>79848</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5415,43 +5520,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>103021</v>
+        <v>2081</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>par i lämplig häckbiotop</t>
-        </is>
-      </c>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Spejkmyren, Spejkmyren, Jmt</t>
+          <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>519946</v>
+        <v>520254</v>
       </c>
       <c r="R43" t="n">
-        <v>7035240</v>
+        <v>7035555</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5510,10 +5606,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122716850</v>
+        <v>122715868</v>
       </c>
       <c r="B44" t="n">
-        <v>90962</v>
+        <v>79847</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5526,34 +5622,39 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Spejkmyren, Spejkmyren, Jmt</t>
+          <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>520101</v>
+        <v>520265</v>
       </c>
       <c r="R44" t="n">
-        <v>7035388</v>
+        <v>7035574</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5612,10 +5713,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122716293</v>
+        <v>122715841</v>
       </c>
       <c r="B45" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5628,42 +5729,42 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Finnbodarna, Hammerdal, Finnbodarna, Hammerdal, Jmt</t>
+          <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>520249</v>
+        <v>520229</v>
       </c>
       <c r="R45" t="n">
-        <v>7035364</v>
+        <v>7035608</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5697,7 +5798,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>På en björk.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5708,6 +5809,31 @@
       </c>
       <c r="AG45" t="b">
         <v>0</v>
+      </c>
+      <c r="AH45" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ45" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK45" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AM45" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO45" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Betula</t>
+        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
@@ -5724,10 +5850,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122719648</v>
+        <v>122717468</v>
       </c>
       <c r="B46" t="n">
-        <v>57478</v>
+        <v>57494</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5740,16 +5866,16 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -5757,10 +5883,14 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr"/>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
@@ -5769,10 +5899,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>519939</v>
+        <v>520020</v>
       </c>
       <c r="R46" t="n">
-        <v>7035194</v>
+        <v>7035330</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5805,11 +5935,6 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-02-23</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5836,10 +5961,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122719371</v>
+        <v>122715648</v>
       </c>
       <c r="B47" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5852,37 +5977,42 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Spejkmyren, Spejkmyren, Jmt</t>
+          <t>Finnbodarna, Hammerdal, Finnbodarna, Hammerdal, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>519943</v>
+        <v>520219</v>
       </c>
       <c r="R47" t="n">
-        <v>7035270</v>
+        <v>7035597</v>
       </c>
       <c r="S47" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5914,6 +6044,11 @@
           <t>2025-02-23</t>
         </is>
       </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD47" t="b">
         <v>0</v>
       </c>
@@ -5922,31 +6057,6 @@
       </c>
       <c r="AG47" t="b">
         <v>0</v>
-      </c>
-      <c r="AH47" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ47" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK47" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM47" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO47" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
@@ -5963,10 +6073,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122720959</v>
+        <v>122720454</v>
       </c>
       <c r="B48" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5979,34 +6089,39 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>519917</v>
+        <v>519849</v>
       </c>
       <c r="R48" t="n">
-        <v>7035339</v>
+        <v>7035406</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6043,7 +6158,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Långväxta bålar på flertalet granar.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6054,31 +6169,6 @@
       </c>
       <c r="AG48" t="b">
         <v>0</v>
-      </c>
-      <c r="AH48" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ48" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK48" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM48" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO48" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
@@ -6095,10 +6185,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122721463</v>
+        <v>122720474</v>
       </c>
       <c r="B49" t="n">
-        <v>78766</v>
+        <v>57494</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6111,34 +6201,48 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>519841</v>
+        <v>519848</v>
       </c>
       <c r="R49" t="n">
-        <v>7035417</v>
+        <v>7035394</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6173,11 +6277,6 @@
           <t>2025-02-23</t>
         </is>
       </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
-        </is>
-      </c>
       <c r="AD49" t="b">
         <v>0</v>
       </c>
@@ -6186,31 +6285,6 @@
       </c>
       <c r="AG49" t="b">
         <v>0</v>
-      </c>
-      <c r="AH49" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ49" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK49" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM49" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO49" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
@@ -6227,10 +6301,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122720686</v>
+        <v>122717446</v>
       </c>
       <c r="B50" t="n">
-        <v>78766</v>
+        <v>90970</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6243,21 +6317,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6267,10 +6341,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>519903</v>
+        <v>520006</v>
       </c>
       <c r="R50" t="n">
-        <v>7035224</v>
+        <v>7035303</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6313,31 +6387,6 @@
       </c>
       <c r="AG50" t="b">
         <v>0</v>
-      </c>
-      <c r="AH50" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ50" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK50" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM50" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO50" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
@@ -6354,10 +6403,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122716216</v>
+        <v>122717294</v>
       </c>
       <c r="B51" t="n">
-        <v>79847</v>
+        <v>90970</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6370,39 +6419,34 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Finnbodarna, Finnbodarna, Jmt</t>
+          <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>520368</v>
+        <v>520013</v>
       </c>
       <c r="R51" t="n">
-        <v>7035513</v>
+        <v>7035340</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6437,11 +6481,6 @@
           <t>2025-02-23</t>
         </is>
       </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>På en gammal grovbarkad sälg.</t>
-        </is>
-      </c>
       <c r="AD51" t="b">
         <v>0</v>
       </c>
@@ -6450,31 +6489,6 @@
       </c>
       <c r="AG51" t="b">
         <v>0</v>
-      </c>
-      <c r="AH51" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ51" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK51" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM51" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO51" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
@@ -6491,7 +6505,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122720065</v>
+        <v>122715934</v>
       </c>
       <c r="B52" t="n">
         <v>78766</v>
@@ -6527,17 +6541,17 @@
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Spejkmyren, Spejkmyren, Jmt</t>
+          <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>520062</v>
+        <v>520303</v>
       </c>
       <c r="R52" t="n">
-        <v>7035232</v>
+        <v>7035598</v>
       </c>
       <c r="S52" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6567,6 +6581,11 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-02-23</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6618,10 +6637,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122716443</v>
+        <v>122715779</v>
       </c>
       <c r="B53" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6634,36 +6653,27 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
       <c r="K53" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
@@ -6672,13 +6682,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>520251</v>
+        <v>520223</v>
       </c>
       <c r="R53" t="n">
-        <v>7035394</v>
+        <v>7035609</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6710,11 +6720,6 @@
           <t>2025-02-23</t>
         </is>
       </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Garnlavsrikt</t>
-        </is>
-      </c>
       <c r="AD53" t="b">
         <v>0</v>
       </c>
@@ -6723,6 +6728,31 @@
       </c>
       <c r="AG53" t="b">
         <v>0</v>
+      </c>
+      <c r="AH53" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ53" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK53" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM53" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO53" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
@@ -6851,7 +6881,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122715757</v>
+        <v>122717164</v>
       </c>
       <c r="B55" t="n">
         <v>78766</v>
@@ -6887,14 +6917,14 @@
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Finnbodarna, Finnbodarna, Jmt</t>
+          <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>520234</v>
+        <v>520120</v>
       </c>
       <c r="R55" t="n">
-        <v>7035595</v>
+        <v>7035405</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6927,11 +6957,6 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-02-23</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6983,7 +7008,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122717284</v>
+        <v>122720065</v>
       </c>
       <c r="B56" t="n">
         <v>78766</v>
@@ -7023,13 +7048,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>520031</v>
+        <v>520062</v>
       </c>
       <c r="R56" t="n">
-        <v>7035353</v>
+        <v>7035232</v>
       </c>
       <c r="S56" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -7059,11 +7084,6 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-02-23</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Långväxta bålar på flertalet granar.</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7115,10 +7135,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122715778</v>
+        <v>122716160</v>
       </c>
       <c r="B57" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -7131,39 +7151,34 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="K57" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>520259</v>
+        <v>520349</v>
       </c>
       <c r="R57" t="n">
-        <v>7035574</v>
+        <v>7035517</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7206,6 +7221,31 @@
       </c>
       <c r="AG57" t="b">
         <v>0</v>
+      </c>
+      <c r="AH57" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ57" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK57" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM57" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO57" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
@@ -7222,10 +7262,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122715756</v>
+        <v>122720281</v>
       </c>
       <c r="B58" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7238,34 +7278,39 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Finnbodarna, Finnbodarna, Jmt</t>
+          <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>520256</v>
+        <v>519850</v>
       </c>
       <c r="R58" t="n">
-        <v>7035593</v>
+        <v>7035373</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7298,6 +7343,11 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-02-23</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7324,10 +7374,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122720427</v>
+        <v>122716295</v>
       </c>
       <c r="B59" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7340,39 +7390,39 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Spejkmyren, Spejkmyren, Jmt</t>
+          <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>519846</v>
+        <v>520378</v>
       </c>
       <c r="R59" t="n">
-        <v>7035407</v>
+        <v>7035512</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7409,7 +7459,7 @@
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ymnig påväxt på en grovbarkad gammal sälg. Fertila bålar med apothecier.</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7420,6 +7470,31 @@
       </c>
       <c r="AG59" t="b">
         <v>0</v>
+      </c>
+      <c r="AH59" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ59" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK59" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM59" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO59" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
@@ -7436,10 +7511,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122715868</v>
+        <v>122719371</v>
       </c>
       <c r="B60" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7452,42 +7527,37 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="K60" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Finnbodarna, Finnbodarna, Jmt</t>
+          <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>520265</v>
+        <v>519943</v>
       </c>
       <c r="R60" t="n">
-        <v>7035574</v>
+        <v>7035270</v>
       </c>
       <c r="S60" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7527,6 +7597,31 @@
       </c>
       <c r="AG60" t="b">
         <v>0</v>
+      </c>
+      <c r="AH60" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ60" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK60" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM60" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO60" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
@@ -7543,10 +7638,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122715780</v>
+        <v>122716392</v>
       </c>
       <c r="B61" t="n">
-        <v>79847</v>
+        <v>79848</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7559,37 +7654,42 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>520259</v>
+        <v>520385</v>
       </c>
       <c r="R61" t="n">
-        <v>7035569</v>
+        <v>7035518</v>
       </c>
       <c r="S61" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7623,7 +7723,7 @@
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>På björk</t>
+          <t>På gran intill en gammal sälg.</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7634,6 +7734,31 @@
       </c>
       <c r="AG61" t="b">
         <v>0</v>
+      </c>
+      <c r="AH61" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ61" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK61" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM61" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO61" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
@@ -7650,10 +7775,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122715874</v>
+        <v>122715756</v>
       </c>
       <c r="B62" t="n">
-        <v>79876</v>
+        <v>79847</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7662,25 +7787,25 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7690,10 +7815,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>520265</v>
+        <v>520256</v>
       </c>
       <c r="R62" t="n">
-        <v>7035574</v>
+        <v>7035593</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7752,10 +7877,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122716427</v>
+        <v>122716801</v>
       </c>
       <c r="B63" t="n">
-        <v>78767</v>
+        <v>57631</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7768,37 +7893,46 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>230405</v>
+        <v>103021</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Finnbodarna, Finnbodarna, Jmt</t>
+          <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>520388</v>
+        <v>520083</v>
       </c>
       <c r="R63" t="n">
-        <v>7035490</v>
+        <v>7035403</v>
       </c>
       <c r="S63" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7830,11 +7964,6 @@
           <t>2025-02-23</t>
         </is>
       </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
-        </is>
-      </c>
       <c r="AD63" t="b">
         <v>0</v>
       </c>
@@ -7843,31 +7972,6 @@
       </c>
       <c r="AG63" t="b">
         <v>0</v>
-      </c>
-      <c r="AH63" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ63" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK63" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM63" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO63" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
@@ -7884,10 +7988,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122716234</v>
+        <v>122715573</v>
       </c>
       <c r="B64" t="n">
-        <v>79847</v>
+        <v>79848</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7900,21 +8004,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7924,10 +8028,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>520362</v>
+        <v>520214</v>
       </c>
       <c r="R64" t="n">
-        <v>7035500</v>
+        <v>7035583</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7962,11 +8066,6 @@
           <t>2025-02-23</t>
         </is>
       </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>På en klen gran intill en gammal sälg med lunglav.</t>
-        </is>
-      </c>
       <c r="AD64" t="b">
         <v>0</v>
       </c>
@@ -7975,31 +8074,6 @@
       </c>
       <c r="AG64" t="b">
         <v>0</v>
-      </c>
-      <c r="AH64" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ64" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK64" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM64" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO64" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
@@ -8016,10 +8090,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122715779</v>
+        <v>122719533</v>
       </c>
       <c r="B65" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -8032,42 +8106,42 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="K65" t="inlineStr">
-        <is>
-          <t>med soral</t>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Finnbodarna, Finnbodarna, Jmt</t>
+          <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>520223</v>
+        <v>519948</v>
       </c>
       <c r="R65" t="n">
-        <v>7035609</v>
+        <v>7035187</v>
       </c>
       <c r="S65" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -8099,6 +8173,11 @@
           <t>2025-02-23</t>
         </is>
       </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD65" t="b">
         <v>0</v>
       </c>
@@ -8107,31 +8186,6 @@
       </c>
       <c r="AG65" t="b">
         <v>0</v>
-      </c>
-      <c r="AH65" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ65" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK65" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM65" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO65" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
@@ -8148,10 +8202,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122715795</v>
+        <v>122721035</v>
       </c>
       <c r="B66" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -8164,34 +8218,34 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Finnbodarna, Finnbodarna, Jmt</t>
+          <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>520214</v>
+        <v>519897</v>
       </c>
       <c r="R66" t="n">
-        <v>7035599</v>
+        <v>7035374</v>
       </c>
       <c r="S66" t="n">
         <v>8</v>
@@ -8226,11 +8280,6 @@
           <t>2025-02-23</t>
         </is>
       </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>På en klen gran intill en lunglavssälg.</t>
-        </is>
-      </c>
       <c r="AD66" t="b">
         <v>0</v>
       </c>
@@ -8247,12 +8296,12 @@
       </c>
       <c r="AJ66" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>garnlav</t>
         </is>
       </c>
       <c r="AK66" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="AM66" t="inlineStr">
@@ -8262,7 +8311,7 @@
       </c>
       <c r="AO66" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Branch on living tree # Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="AT66" t="inlineStr"/>
@@ -8280,7 +8329,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>122715999</v>
+        <v>122716443</v>
       </c>
       <c r="B67" t="n">
         <v>78766</v>
@@ -8313,20 +8362,34 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I67" t="inlineStr"/>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>520311</v>
+        <v>520251</v>
       </c>
       <c r="R67" t="n">
-        <v>7035566</v>
+        <v>7035394</v>
       </c>
       <c r="S67" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -8358,6 +8421,11 @@
           <t>2025-02-23</t>
         </is>
       </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Garnlavsrikt</t>
+        </is>
+      </c>
       <c r="AD67" t="b">
         <v>0</v>
       </c>
@@ -8366,31 +8434,6 @@
       </c>
       <c r="AG67" t="b">
         <v>0</v>
-      </c>
-      <c r="AH67" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ67" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK67" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM67" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO67" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
@@ -8407,7 +8450,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>122715934</v>
+        <v>122720629</v>
       </c>
       <c r="B68" t="n">
         <v>78766</v>
@@ -8443,17 +8486,17 @@
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Finnbodarna, Finnbodarna, Jmt</t>
+          <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>520303</v>
+        <v>519935</v>
       </c>
       <c r="R68" t="n">
-        <v>7035598</v>
+        <v>7035246</v>
       </c>
       <c r="S68" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8539,10 +8582,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>122717989</v>
+        <v>122715870</v>
       </c>
       <c r="B69" t="n">
-        <v>57494</v>
+        <v>79848</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8555,43 +8598,34 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100049</v>
+        <v>2081</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Spejkmyren, Spejkmyren, Jmt</t>
+          <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>519951</v>
+        <v>520265</v>
       </c>
       <c r="R69" t="n">
-        <v>7035320</v>
+        <v>7035574</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8624,11 +8658,6 @@
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-02-23</t>
-        </is>
-      </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>Trummande</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8655,10 +8684,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>122716547</v>
+        <v>122720959</v>
       </c>
       <c r="B70" t="n">
-        <v>98263</v>
+        <v>78766</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8667,55 +8696,41 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>504</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J70" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K70" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Finnbodarna, Finnbodarna, Jmt</t>
+          <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>520386</v>
+        <v>519917</v>
       </c>
       <c r="R70" t="n">
-        <v>7035492</v>
+        <v>7035339</v>
       </c>
       <c r="S70" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8749,7 +8764,7 @@
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>En vinterståndare på till synes fuktig mark i en lucka.</t>
+          <t>Långväxta bålar på flertalet granar.</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8764,6 +8779,26 @@
       <c r="AH70" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ70" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK70" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM70" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO70" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT70" t="inlineStr"/>
@@ -8781,10 +8816,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>122716757</v>
+        <v>122716234</v>
       </c>
       <c r="B71" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8797,21 +8832,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8821,13 +8856,13 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>520316</v>
+        <v>520362</v>
       </c>
       <c r="R71" t="n">
-        <v>7035491</v>
+        <v>7035500</v>
       </c>
       <c r="S71" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8857,6 +8892,11 @@
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-02-23</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>På en klen gran intill en gammal sälg med lunglav.</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8908,7 +8948,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>122716645</v>
+        <v>122719648</v>
       </c>
       <c r="B72" t="n">
         <v>57478</v>
@@ -8953,10 +8993,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>520129</v>
+        <v>519939</v>
       </c>
       <c r="R72" t="n">
-        <v>7035444</v>
+        <v>7035194</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -9020,10 +9060,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>122720823</v>
+        <v>122721463</v>
       </c>
       <c r="B73" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -9036,53 +9076,34 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K73" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L73" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
           <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>519842</v>
+        <v>519841</v>
       </c>
       <c r="R73" t="n">
-        <v>7035388</v>
+        <v>7035417</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -9119,7 +9140,7 @@
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>Trummande</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -9130,6 +9151,31 @@
       </c>
       <c r="AG73" t="b">
         <v>0</v>
+      </c>
+      <c r="AH73" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ73" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK73" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM73" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO73" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
@@ -9146,10 +9192,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>122715648</v>
+        <v>122715780</v>
       </c>
       <c r="B74" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -9162,39 +9208,34 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
-      <c r="M74" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Finnbodarna, Hammerdal, Finnbodarna, Hammerdal, Jmt</t>
+          <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>520219</v>
+        <v>520259</v>
       </c>
       <c r="R74" t="n">
-        <v>7035597</v>
+        <v>7035569</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -9231,7 +9272,7 @@
       </c>
       <c r="AC74" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>På björk</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9258,10 +9299,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>122716392</v>
+        <v>122717488</v>
       </c>
       <c r="B75" t="n">
-        <v>79848</v>
+        <v>79847</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -9274,42 +9315,37 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
-      <c r="K75" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Finnbodarna, Finnbodarna, Jmt</t>
+          <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>520385</v>
+        <v>520000</v>
       </c>
       <c r="R75" t="n">
-        <v>7035518</v>
+        <v>7035297</v>
       </c>
       <c r="S75" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -9341,11 +9377,6 @@
           <t>2025-02-23</t>
         </is>
       </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>På gran intill en gammal sälg.</t>
-        </is>
-      </c>
       <c r="AD75" t="b">
         <v>0</v>
       </c>
@@ -9354,31 +9385,6 @@
       </c>
       <c r="AG75" t="b">
         <v>0</v>
-      </c>
-      <c r="AH75" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ75" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK75" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM75" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO75" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
@@ -9395,7 +9401,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>122715978</v>
+        <v>122715795</v>
       </c>
       <c r="B76" t="n">
         <v>79847</v>
@@ -9429,24 +9435,19 @@
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
-      <c r="K76" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P76" t="inlineStr">
         <is>
           <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>520243</v>
+        <v>520214</v>
       </c>
       <c r="R76" t="n">
-        <v>7035552</v>
+        <v>7035599</v>
       </c>
       <c r="S76" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -9478,6 +9479,11 @@
           <t>2025-02-23</t>
         </is>
       </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>På en klen gran intill en lunglavssälg.</t>
+        </is>
+      </c>
       <c r="AD76" t="b">
         <v>0</v>
       </c>
@@ -9486,6 +9492,31 @@
       </c>
       <c r="AG76" t="b">
         <v>0</v>
+      </c>
+      <c r="AH76" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ76" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK76" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM76" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO76" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
@@ -9502,10 +9533,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>122715502</v>
+        <v>122720823</v>
       </c>
       <c r="B77" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -9518,42 +9549,56 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Djupmyren, Djupmyren, Jmt</t>
+          <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>520110</v>
+        <v>519842</v>
       </c>
       <c r="R77" t="n">
-        <v>7035585</v>
+        <v>7035388</v>
       </c>
       <c r="S77" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -9587,7 +9632,7 @@
       </c>
       <c r="AC77" t="inlineStr">
         <is>
-          <t>Gott om långväxt garnlav på många granar. Vissa bålar är här fertila.</t>
+          <t>Trummande</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9598,31 +9643,6 @@
       </c>
       <c r="AG77" t="b">
         <v>0</v>
-      </c>
-      <c r="AH77" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ77" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK77" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM77" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO77" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
@@ -9639,10 +9659,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>122720869</v>
+        <v>122720427</v>
       </c>
       <c r="B78" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -9655,34 +9675,39 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P78" t="inlineStr">
         <is>
           <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>519960</v>
+        <v>519846</v>
       </c>
       <c r="R78" t="n">
-        <v>7035342</v>
+        <v>7035407</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9717,6 +9742,11 @@
           <t>2025-02-23</t>
         </is>
       </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD78" t="b">
         <v>0</v>
       </c>
@@ -9725,31 +9755,6 @@
       </c>
       <c r="AG78" t="b">
         <v>0</v>
-      </c>
-      <c r="AH78" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ78" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK78" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM78" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO78" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
@@ -9766,10 +9771,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>122717359</v>
+        <v>122717636</v>
       </c>
       <c r="B79" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -9782,34 +9787,39 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P79" t="inlineStr">
         <is>
           <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>520030</v>
+        <v>519970</v>
       </c>
       <c r="R79" t="n">
-        <v>7035341</v>
+        <v>7035297</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9842,6 +9852,11 @@
       <c r="AA79" t="inlineStr">
         <is>
           <t>2025-02-23</t>
+        </is>
+      </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9868,10 +9883,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>122719697</v>
+        <v>122715669</v>
       </c>
       <c r="B80" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -9884,37 +9899,42 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Spejkmyren, Spejkmyren, Jmt</t>
+          <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>520026</v>
+        <v>520221</v>
       </c>
       <c r="R80" t="n">
-        <v>7035233</v>
+        <v>7035600</v>
       </c>
       <c r="S80" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -9954,31 +9974,6 @@
       </c>
       <c r="AG80" t="b">
         <v>0</v>
-      </c>
-      <c r="AH80" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ80" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK80" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM80" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO80" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
@@ -9995,10 +9990,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>122715677</v>
+        <v>122716387</v>
       </c>
       <c r="B81" t="n">
-        <v>79848</v>
+        <v>57478</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -10011,34 +10006,39 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Finnbodarna, Finnbodarna, Jmt</t>
+          <t>Finnbodarna, Hammerdal, Finnbodarna, Hammerdal, Jmt</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>520221</v>
+        <v>520278</v>
       </c>
       <c r="R81" t="n">
-        <v>7035600</v>
+        <v>7035397</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -10075,7 +10075,7 @@
       </c>
       <c r="AC81" t="inlineStr">
         <is>
-          <t>På gran</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -10102,10 +10102,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>122717616</v>
+        <v>122716850</v>
       </c>
       <c r="B82" t="n">
-        <v>78766</v>
+        <v>90970</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -10118,21 +10118,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -10142,10 +10142,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>520019</v>
+        <v>520101</v>
       </c>
       <c r="R82" t="n">
-        <v>7035352</v>
+        <v>7035388</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -10180,11 +10180,6 @@
           <t>2025-02-23</t>
         </is>
       </c>
-      <c r="AC82" t="inlineStr">
-        <is>
-          <t>Rikligt.</t>
-        </is>
-      </c>
       <c r="AD82" t="b">
         <v>0</v>
       </c>
@@ -10193,31 +10188,6 @@
       </c>
       <c r="AG82" t="b">
         <v>0</v>
-      </c>
-      <c r="AH82" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ82" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK82" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM82" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO82" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
@@ -10234,10 +10204,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>122720474</v>
+        <v>122716293</v>
       </c>
       <c r="B83" t="n">
-        <v>57494</v>
+        <v>57478</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -10250,16 +10220,16 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -10267,31 +10237,22 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I83" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L83" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="I83" t="inlineStr"/>
       <c r="M83" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Spejkmyren, Spejkmyren, Jmt</t>
+          <t>Finnbodarna, Hammerdal, Finnbodarna, Hammerdal, Jmt</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>519848</v>
+        <v>520249</v>
       </c>
       <c r="R83" t="n">
-        <v>7035394</v>
+        <v>7035364</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -10324,6 +10285,11 @@
       <c r="AA83" t="inlineStr">
         <is>
           <t>2025-02-23</t>
+        </is>
+      </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -10350,10 +10316,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>122716964</v>
+        <v>122715849</v>
       </c>
       <c r="B84" t="n">
-        <v>90962</v>
+        <v>79876</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -10362,38 +10328,38 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>5432</v>
+        <v>6462</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Spejkmyren, Spejkmyren, Jmt</t>
+          <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>520115</v>
+        <v>520268</v>
       </c>
       <c r="R84" t="n">
-        <v>7035402</v>
+        <v>7035575</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -10452,10 +10418,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>122717446</v>
+        <v>122717929</v>
       </c>
       <c r="B85" t="n">
-        <v>90962</v>
+        <v>79876</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -10464,41 +10430,46 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>5432</v>
+        <v>6462</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P85" t="inlineStr">
         <is>
           <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>520006</v>
+        <v>520029</v>
       </c>
       <c r="R85" t="n">
-        <v>7035303</v>
+        <v>7035292</v>
       </c>
       <c r="S85" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -10538,6 +10509,31 @@
       </c>
       <c r="AG85" t="b">
         <v>0</v>
+      </c>
+      <c r="AH85" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ85" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK85" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM85" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO85" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
@@ -10554,10 +10550,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>122716303</v>
+        <v>122715801</v>
       </c>
       <c r="B86" t="n">
-        <v>57478</v>
+        <v>79848</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -10570,39 +10566,34 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
-      <c r="M86" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Finnbodarna, Hammerdal, Finnbodarna, Hammerdal, Jmt</t>
+          <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>520250</v>
+        <v>520266</v>
       </c>
       <c r="R86" t="n">
-        <v>7035363</v>
+        <v>7035582</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -10635,11 +10626,6 @@
       <c r="AA86" t="inlineStr">
         <is>
           <t>2025-02-23</t>
-        </is>
-      </c>
-      <c r="AC86" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10666,10 +10652,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>122717164</v>
+        <v>122716547</v>
       </c>
       <c r="B87" t="n">
-        <v>78766</v>
+        <v>98271</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -10678,41 +10664,55 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6425</v>
+        <v>504</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Spejkmyren, Spejkmyren, Jmt</t>
+          <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>520120</v>
+        <v>520386</v>
       </c>
       <c r="R87" t="n">
-        <v>7035405</v>
+        <v>7035492</v>
       </c>
       <c r="S87" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -10744,6 +10744,11 @@
           <t>2025-02-23</t>
         </is>
       </c>
+      <c r="AC87" t="inlineStr">
+        <is>
+          <t>En vinterståndare på till synes fuktig mark i en lucka.</t>
+        </is>
+      </c>
       <c r="AD87" t="b">
         <v>0</v>
       </c>
@@ -10756,26 +10761,6 @@
       <c r="AH87" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ87" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK87" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM87" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO87" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT87" t="inlineStr"/>
@@ -10793,10 +10778,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>122715849</v>
+        <v>122720869</v>
       </c>
       <c r="B88" t="n">
-        <v>79876</v>
+        <v>78766</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -10805,38 +10790,38 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Finnbodarna, Finnbodarna, Jmt</t>
+          <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>520268</v>
+        <v>519960</v>
       </c>
       <c r="R88" t="n">
-        <v>7035575</v>
+        <v>7035342</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10879,6 +10864,31 @@
       </c>
       <c r="AG88" t="b">
         <v>0</v>
+      </c>
+      <c r="AH88" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ88" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK88" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM88" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO88" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
@@ -10895,10 +10905,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>122716329</v>
+        <v>122721333</v>
       </c>
       <c r="B89" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -10911,42 +10921,37 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
-      <c r="K89" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Finnbodarna, Finnbodarna, Jmt</t>
+          <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>520374</v>
+        <v>519906</v>
       </c>
       <c r="R89" t="n">
-        <v>7035511</v>
+        <v>7035389</v>
       </c>
       <c r="S89" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -10980,7 +10985,7 @@
       </c>
       <c r="AC89" t="inlineStr">
         <is>
-          <t>På gran intill en gammal lunglavssälg.</t>
+          <t>Ymnigt på flera granar.</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -11032,10 +11037,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>122720327</v>
+        <v>122715790</v>
       </c>
       <c r="B90" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -11048,39 +11053,39 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
-      <c r="M90" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Spejkmyren, Spejkmyren, Jmt</t>
+          <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>519838</v>
+        <v>520267</v>
       </c>
       <c r="R90" t="n">
-        <v>7035393</v>
+        <v>7035581</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -11113,11 +11118,6 @@
       <c r="AA90" t="inlineStr">
         <is>
           <t>2025-02-23</t>
-        </is>
-      </c>
-      <c r="AC90" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD90" t="b">

--- a/artfynd/A 1625-2025 artfynd.xlsx
+++ b/artfynd/A 1625-2025 artfynd.xlsx
@@ -2019,10 +2019,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122716427</v>
+        <v>122715766</v>
       </c>
       <c r="B14" t="n">
-        <v>78767</v>
+        <v>90970</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2035,21 +2035,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>230405</v>
+        <v>5432</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2059,13 +2059,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>520388</v>
+        <v>520252</v>
       </c>
       <c r="R14" t="n">
-        <v>7035490</v>
+        <v>7035591</v>
       </c>
       <c r="S14" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2097,11 +2097,6 @@
           <t>2025-02-23</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2110,31 +2105,6 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
-      </c>
-      <c r="AH14" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ14" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK14" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
@@ -2151,7 +2121,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122716645</v>
+        <v>122720368</v>
       </c>
       <c r="B15" t="n">
         <v>57478</v>
@@ -2196,10 +2166,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>520129</v>
+        <v>519852</v>
       </c>
       <c r="R15" t="n">
-        <v>7035444</v>
+        <v>7035392</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2263,10 +2233,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122716682</v>
+        <v>122716645</v>
       </c>
       <c r="B16" t="n">
-        <v>57631</v>
+        <v>57478</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2279,31 +2249,27 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
-          <t>par i lämplig häckbiotop</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2312,10 +2278,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>520101</v>
+        <v>520129</v>
       </c>
       <c r="R16" t="n">
-        <v>7035453</v>
+        <v>7035444</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2348,6 +2314,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-02-23</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2374,10 +2345,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122715766</v>
+        <v>122716682</v>
       </c>
       <c r="B17" t="n">
-        <v>90970</v>
+        <v>57631</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2390,34 +2361,43 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5432</v>
+        <v>103021</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Finnbodarna, Finnbodarna, Jmt</t>
+          <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>520252</v>
+        <v>520101</v>
       </c>
       <c r="R17" t="n">
-        <v>7035591</v>
+        <v>7035453</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2476,10 +2456,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122720368</v>
+        <v>122716427</v>
       </c>
       <c r="B18" t="n">
-        <v>57478</v>
+        <v>78767</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2492,42 +2472,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>230405</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Spejkmyren, Spejkmyren, Jmt</t>
+          <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>519852</v>
+        <v>520388</v>
       </c>
       <c r="R18" t="n">
-        <v>7035392</v>
+        <v>7035490</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2561,7 +2536,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2572,6 +2547,31 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM18" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -3319,10 +3319,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122720558</v>
+        <v>122719697</v>
       </c>
       <c r="B25" t="n">
-        <v>57494</v>
+        <v>78766</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3335,42 +3335,37 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>519949</v>
+        <v>520026</v>
       </c>
       <c r="R25" t="n">
-        <v>7035254</v>
+        <v>7035233</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3402,11 +3397,6 @@
           <t>2025-02-23</t>
         </is>
       </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Äldre hackspår i stambasen.</t>
-        </is>
-      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
@@ -3433,12 +3423,12 @@
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>Stående död trädstam/högstubbe</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
-          <t>Standing dead tree/snags # Picea abies</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3456,10 +3446,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122720889</v>
+        <v>122717284</v>
       </c>
       <c r="B26" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3472,42 +3462,37 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>519841</v>
+        <v>520031</v>
       </c>
       <c r="R26" t="n">
-        <v>7035390</v>
+        <v>7035353</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3541,7 +3526,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Långväxta bålar på flertalet granar.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3552,6 +3537,31 @@
       </c>
       <c r="AG26" t="b">
         <v>0</v>
+      </c>
+      <c r="AH26" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK26" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM26" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
@@ -3568,10 +3578,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122719554</v>
+        <v>122715775</v>
       </c>
       <c r="B27" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3584,44 +3594,39 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Spejkmyren, Spejkmyren, Jmt</t>
+          <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>519981</v>
+        <v>520252</v>
       </c>
       <c r="R27" t="n">
-        <v>7035221</v>
+        <v>7035576</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3658,7 +3663,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Äldre ringhack som bedöms vara 5 - 10 år gamla.</t>
+          <t>På björk</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3669,31 +3674,6 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
-      </c>
-      <c r="AH27" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ27" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK27" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM27" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO27" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
@@ -3710,10 +3690,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122719829</v>
+        <v>122720558</v>
       </c>
       <c r="B28" t="n">
-        <v>57478</v>
+        <v>57494</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3726,16 +3706,16 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -3755,10 +3735,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>519930</v>
+        <v>519949</v>
       </c>
       <c r="R28" t="n">
-        <v>7035181</v>
+        <v>7035254</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3795,7 +3775,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Äldre hackspår i stambasen.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3806,6 +3786,31 @@
       </c>
       <c r="AG28" t="b">
         <v>0</v>
+      </c>
+      <c r="AH28" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM28" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
@@ -3822,10 +3827,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122719697</v>
+        <v>122719829</v>
       </c>
       <c r="B29" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3838,37 +3843,42 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>520026</v>
+        <v>519930</v>
       </c>
       <c r="R29" t="n">
-        <v>7035233</v>
+        <v>7035181</v>
       </c>
       <c r="S29" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3900,6 +3910,11 @@
           <t>2025-02-23</t>
         </is>
       </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
@@ -3908,31 +3923,6 @@
       </c>
       <c r="AG29" t="b">
         <v>0</v>
-      </c>
-      <c r="AH29" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ29" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK29" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM29" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO29" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
@@ -3949,10 +3939,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122717284</v>
+        <v>122719554</v>
       </c>
       <c r="B30" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3965,37 +3955,47 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>520031</v>
+        <v>519981</v>
       </c>
       <c r="R30" t="n">
-        <v>7035353</v>
+        <v>7035221</v>
       </c>
       <c r="S30" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4029,7 +4029,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Långväxta bålar på flertalet granar.</t>
+          <t>Äldre ringhack som bedöms vara 5 - 10 år gamla.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4058,12 +4058,12 @@
       </c>
       <c r="AM30" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4081,10 +4081,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122715775</v>
+        <v>122720889</v>
       </c>
       <c r="B31" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4097,39 +4097,39 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Finnbodarna, Finnbodarna, Jmt</t>
+          <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>520252</v>
+        <v>519841</v>
       </c>
       <c r="R31" t="n">
-        <v>7035576</v>
+        <v>7035390</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4166,7 +4166,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>På björk</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4665,7 +4665,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122717873</v>
+        <v>122716216</v>
       </c>
       <c r="B36" t="n">
         <v>79847</v>
@@ -4706,17 +4706,17 @@
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Spejkmyren, Spejkmyren, Jmt</t>
+          <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>520033</v>
+        <v>520368</v>
       </c>
       <c r="R36" t="n">
-        <v>7035301</v>
+        <v>7035513</v>
       </c>
       <c r="S36" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4746,6 +4746,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-02-23</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>På en gammal grovbarkad sälg.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4929,7 +4934,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122716216</v>
+        <v>122717873</v>
       </c>
       <c r="B38" t="n">
         <v>79847</v>
@@ -4970,17 +4975,17 @@
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Finnbodarna, Finnbodarna, Jmt</t>
+          <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>520368</v>
+        <v>520033</v>
       </c>
       <c r="R38" t="n">
-        <v>7035513</v>
+        <v>7035301</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5010,11 +5015,6 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-02-23</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>På en gammal grovbarkad sälg.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5713,10 +5713,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122715841</v>
+        <v>122717468</v>
       </c>
       <c r="B45" t="n">
-        <v>79847</v>
+        <v>57494</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5729,42 +5729,46 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>med soral</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Finnbodarna, Finnbodarna, Jmt</t>
+          <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>520229</v>
+        <v>520020</v>
       </c>
       <c r="R45" t="n">
-        <v>7035608</v>
+        <v>7035330</v>
       </c>
       <c r="S45" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5796,11 +5800,6 @@
           <t>2025-02-23</t>
         </is>
       </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>På en björk.</t>
-        </is>
-      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
@@ -5809,31 +5808,6 @@
       </c>
       <c r="AG45" t="b">
         <v>0</v>
-      </c>
-      <c r="AH45" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ45" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK45" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AM45" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO45" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Betula</t>
-        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
@@ -5850,10 +5824,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122717468</v>
+        <v>122715841</v>
       </c>
       <c r="B46" t="n">
-        <v>57494</v>
+        <v>79847</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5866,46 +5840,42 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Spejkmyren, Spejkmyren, Jmt</t>
+          <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>520020</v>
+        <v>520229</v>
       </c>
       <c r="R46" t="n">
-        <v>7035330</v>
+        <v>7035608</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5937,6 +5907,11 @@
           <t>2025-02-23</t>
         </is>
       </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>På en björk.</t>
+        </is>
+      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
@@ -5945,6 +5920,31 @@
       </c>
       <c r="AG46" t="b">
         <v>0</v>
+      </c>
+      <c r="AH46" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ46" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK46" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AM46" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO46" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Betula</t>
+        </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
@@ -6185,10 +6185,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122720474</v>
+        <v>122717446</v>
       </c>
       <c r="B49" t="n">
-        <v>57494</v>
+        <v>90970</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6201,48 +6201,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L49" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>519848</v>
+        <v>520006</v>
       </c>
       <c r="R49" t="n">
-        <v>7035394</v>
+        <v>7035303</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6301,7 +6287,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122717446</v>
+        <v>122717294</v>
       </c>
       <c r="B50" t="n">
         <v>90970</v>
@@ -6341,10 +6327,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>520006</v>
+        <v>520013</v>
       </c>
       <c r="R50" t="n">
-        <v>7035303</v>
+        <v>7035340</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6403,10 +6389,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122717294</v>
+        <v>122715934</v>
       </c>
       <c r="B51" t="n">
-        <v>90970</v>
+        <v>78766</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6419,37 +6405,37 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Spejkmyren, Spejkmyren, Jmt</t>
+          <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>520013</v>
+        <v>520303</v>
       </c>
       <c r="R51" t="n">
-        <v>7035340</v>
+        <v>7035598</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6481,6 +6467,11 @@
           <t>2025-02-23</t>
         </is>
       </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
+        </is>
+      </c>
       <c r="AD51" t="b">
         <v>0</v>
       </c>
@@ -6489,6 +6480,31 @@
       </c>
       <c r="AG51" t="b">
         <v>0</v>
+      </c>
+      <c r="AH51" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ51" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK51" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM51" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO51" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
@@ -6505,10 +6521,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122715934</v>
+        <v>122715779</v>
       </c>
       <c r="B52" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6521,37 +6537,42 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>520303</v>
+        <v>520223</v>
       </c>
       <c r="R52" t="n">
-        <v>7035598</v>
+        <v>7035609</v>
       </c>
       <c r="S52" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6583,11 +6604,6 @@
           <t>2025-02-23</t>
         </is>
       </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
-        </is>
-      </c>
       <c r="AD52" t="b">
         <v>0</v>
       </c>
@@ -6604,22 +6620,22 @@
       </c>
       <c r="AJ52" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK52" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM52" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO52" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT52" t="inlineStr"/>
@@ -6637,10 +6653,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122715779</v>
+        <v>122720474</v>
       </c>
       <c r="B53" t="n">
-        <v>79847</v>
+        <v>57494</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6653,42 +6669,51 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t>med soral</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Finnbodarna, Finnbodarna, Jmt</t>
+          <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>520223</v>
+        <v>519848</v>
       </c>
       <c r="R53" t="n">
-        <v>7035609</v>
+        <v>7035394</v>
       </c>
       <c r="S53" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6728,31 +6753,6 @@
       </c>
       <c r="AG53" t="b">
         <v>0</v>
-      </c>
-      <c r="AH53" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ53" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK53" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM53" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO53" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
@@ -7775,10 +7775,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122715756</v>
+        <v>122716801</v>
       </c>
       <c r="B62" t="n">
-        <v>79847</v>
+        <v>57631</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7791,34 +7791,43 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Finnbodarna, Finnbodarna, Jmt</t>
+          <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>520256</v>
+        <v>520083</v>
       </c>
       <c r="R62" t="n">
-        <v>7035593</v>
+        <v>7035403</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7877,10 +7886,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122716801</v>
+        <v>122715756</v>
       </c>
       <c r="B63" t="n">
-        <v>57631</v>
+        <v>79847</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7893,43 +7902,34 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>par i lämplig häckbiotop</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Spejkmyren, Spejkmyren, Jmt</t>
+          <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>520083</v>
+        <v>520256</v>
       </c>
       <c r="R63" t="n">
-        <v>7035403</v>
+        <v>7035593</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -8582,10 +8582,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>122715870</v>
+        <v>122720959</v>
       </c>
       <c r="B69" t="n">
-        <v>79848</v>
+        <v>78766</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8598,34 +8598,34 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Finnbodarna, Finnbodarna, Jmt</t>
+          <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>520265</v>
+        <v>519917</v>
       </c>
       <c r="R69" t="n">
-        <v>7035574</v>
+        <v>7035339</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8660,6 +8660,11 @@
           <t>2025-02-23</t>
         </is>
       </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Långväxta bålar på flertalet granar.</t>
+        </is>
+      </c>
       <c r="AD69" t="b">
         <v>0</v>
       </c>
@@ -8668,6 +8673,31 @@
       </c>
       <c r="AG69" t="b">
         <v>0</v>
+      </c>
+      <c r="AH69" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ69" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK69" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM69" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO69" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
@@ -8684,10 +8714,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>122720959</v>
+        <v>122716234</v>
       </c>
       <c r="B70" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8700,34 +8730,34 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Spejkmyren, Spejkmyren, Jmt</t>
+          <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>519917</v>
+        <v>520362</v>
       </c>
       <c r="R70" t="n">
-        <v>7035339</v>
+        <v>7035500</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8764,7 +8794,7 @@
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>Långväxta bålar på flertalet granar.</t>
+          <t>På en klen gran intill en gammal sälg med lunglav.</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8816,10 +8846,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>122716234</v>
+        <v>122715870</v>
       </c>
       <c r="B71" t="n">
-        <v>79847</v>
+        <v>79848</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8832,21 +8862,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8856,10 +8886,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>520362</v>
+        <v>520265</v>
       </c>
       <c r="R71" t="n">
-        <v>7035500</v>
+        <v>7035574</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8894,11 +8924,6 @@
           <t>2025-02-23</t>
         </is>
       </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>På en klen gran intill en gammal sälg med lunglav.</t>
-        </is>
-      </c>
       <c r="AD71" t="b">
         <v>0</v>
       </c>
@@ -8907,31 +8932,6 @@
       </c>
       <c r="AG71" t="b">
         <v>0</v>
-      </c>
-      <c r="AH71" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ71" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK71" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM71" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO71" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
@@ -9299,10 +9299,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>122717488</v>
+        <v>122720427</v>
       </c>
       <c r="B75" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -9315,34 +9315,39 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P75" t="inlineStr">
         <is>
           <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>520000</v>
+        <v>519846</v>
       </c>
       <c r="R75" t="n">
-        <v>7035297</v>
+        <v>7035407</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -9375,6 +9380,11 @@
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-02-23</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9401,10 +9411,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>122715795</v>
+        <v>122717636</v>
       </c>
       <c r="B76" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -9417,37 +9427,42 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Finnbodarna, Finnbodarna, Jmt</t>
+          <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>520214</v>
+        <v>519970</v>
       </c>
       <c r="R76" t="n">
-        <v>7035599</v>
+        <v>7035297</v>
       </c>
       <c r="S76" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -9481,7 +9496,7 @@
       </c>
       <c r="AC76" t="inlineStr">
         <is>
-          <t>På en klen gran intill en lunglavssälg.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9492,31 +9507,6 @@
       </c>
       <c r="AG76" t="b">
         <v>0</v>
-      </c>
-      <c r="AH76" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ76" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK76" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM76" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO76" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
@@ -9533,10 +9523,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>122720823</v>
+        <v>122717488</v>
       </c>
       <c r="B77" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -9549,53 +9539,34 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K77" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L77" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M77" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
           <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>519842</v>
+        <v>520000</v>
       </c>
       <c r="R77" t="n">
-        <v>7035388</v>
+        <v>7035297</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9628,11 +9599,6 @@
       <c r="AA77" t="inlineStr">
         <is>
           <t>2025-02-23</t>
-        </is>
-      </c>
-      <c r="AC77" t="inlineStr">
-        <is>
-          <t>Trummande</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9659,10 +9625,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>122720427</v>
+        <v>122715795</v>
       </c>
       <c r="B78" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -9675,42 +9641,37 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
-      <c r="M78" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Spejkmyren, Spejkmyren, Jmt</t>
+          <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>519846</v>
+        <v>520214</v>
       </c>
       <c r="R78" t="n">
-        <v>7035407</v>
+        <v>7035599</v>
       </c>
       <c r="S78" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -9744,7 +9705,7 @@
       </c>
       <c r="AC78" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>På en klen gran intill en lunglavssälg.</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9755,6 +9716,31 @@
       </c>
       <c r="AG78" t="b">
         <v>0</v>
+      </c>
+      <c r="AH78" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ78" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK78" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM78" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO78" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
@@ -9771,7 +9757,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>122717636</v>
+        <v>122720823</v>
       </c>
       <c r="B79" t="n">
         <v>57478</v>
@@ -9804,10 +9790,24 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I79" t="inlineStr"/>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P79" t="inlineStr">
@@ -9816,10 +9816,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>519970</v>
+        <v>519842</v>
       </c>
       <c r="R79" t="n">
-        <v>7035297</v>
+        <v>7035388</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9856,7 +9856,7 @@
       </c>
       <c r="AC79" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Trummande</t>
         </is>
       </c>
       <c r="AD79" t="b">

--- a/artfynd/A 1625-2025 artfynd.xlsx
+++ b/artfynd/A 1625-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122720686</v>
+        <v>122715801</v>
       </c>
       <c r="B2" t="n">
-        <v>78766</v>
+        <v>79848</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Spejkmyren, Spejkmyren, Jmt</t>
+          <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>519903</v>
+        <v>520266</v>
       </c>
       <c r="R2" t="n">
-        <v>7035224</v>
+        <v>7035582</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -761,31 +761,6 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -802,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122715757</v>
+        <v>122721035</v>
       </c>
       <c r="B3" t="n">
         <v>78766</v>
@@ -838,17 +813,17 @@
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Finnbodarna, Finnbodarna, Jmt</t>
+          <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>520234</v>
+        <v>519897</v>
       </c>
       <c r="R3" t="n">
-        <v>7035595</v>
+        <v>7035374</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -880,11 +855,6 @@
           <t>2025-02-23</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -901,12 +871,12 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>garnlav</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
@@ -916,7 +886,7 @@
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Branch on living tree # Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -934,7 +904,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122715571</v>
+        <v>122715841</v>
       </c>
       <c r="B4" t="n">
         <v>79847</v>
@@ -968,19 +938,24 @@
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>520216</v>
+        <v>520229</v>
       </c>
       <c r="R4" t="n">
-        <v>7035583</v>
+        <v>7035608</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1012,6 +987,11 @@
           <t>2025-02-23</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>På en björk.</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1020,6 +1000,31 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Betula</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1036,7 +1041,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122715778</v>
+        <v>122715779</v>
       </c>
       <c r="B5" t="n">
         <v>79847</v>
@@ -1072,7 +1077,7 @@
       <c r="I5" t="inlineStr"/>
       <c r="K5" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1081,13 +1086,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>520259</v>
+        <v>520223</v>
       </c>
       <c r="R5" t="n">
-        <v>7035574</v>
+        <v>7035609</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1127,6 +1132,31 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1143,10 +1173,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122715677</v>
+        <v>122715949</v>
       </c>
       <c r="B6" t="n">
-        <v>79848</v>
+        <v>79847</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1159,21 +1189,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1183,10 +1213,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>520221</v>
+        <v>520254</v>
       </c>
       <c r="R6" t="n">
-        <v>7035600</v>
+        <v>7035555</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1219,11 +1249,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-02-23</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>På gran</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1250,10 +1275,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122717359</v>
+        <v>122717446</v>
       </c>
       <c r="B7" t="n">
-        <v>79847</v>
+        <v>90970</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1266,21 +1291,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1290,10 +1315,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>520030</v>
+        <v>520006</v>
       </c>
       <c r="R7" t="n">
-        <v>7035341</v>
+        <v>7035303</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1352,10 +1377,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122717343</v>
+        <v>122720065</v>
       </c>
       <c r="B8" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1368,42 +1393,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>520034</v>
+        <v>520062</v>
       </c>
       <c r="R8" t="n">
-        <v>7035339</v>
+        <v>7035232</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1435,11 +1455,6 @@
           <t>2025-02-23</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1448,6 +1463,31 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1464,7 +1504,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122719875</v>
+        <v>122716293</v>
       </c>
       <c r="B9" t="n">
         <v>57478</v>
@@ -1505,14 +1545,14 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Spejkmyren, Spejkmyren, Jmt</t>
+          <t>Finnbodarna, Hammerdal, Finnbodarna, Hammerdal, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>519983</v>
+        <v>520249</v>
       </c>
       <c r="R9" t="n">
-        <v>7035206</v>
+        <v>7035364</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1678,7 +1718,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122715999</v>
+        <v>122720629</v>
       </c>
       <c r="B11" t="n">
         <v>78766</v>
@@ -1714,17 +1754,17 @@
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Finnbodarna, Finnbodarna, Jmt</t>
+          <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>520311</v>
+        <v>519935</v>
       </c>
       <c r="R11" t="n">
-        <v>7035566</v>
+        <v>7035246</v>
       </c>
       <c r="S11" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1754,6 +1794,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-02-23</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1805,10 +1850,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122715836</v>
+        <v>122716673</v>
       </c>
       <c r="B12" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1821,39 +1866,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Finnbodarna, Finnbodarna, Jmt</t>
+          <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>520269</v>
+        <v>520108</v>
       </c>
       <c r="R12" t="n">
-        <v>7035574</v>
+        <v>7035462</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1886,6 +1931,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-02-23</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1912,10 +1962,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122715978</v>
+        <v>122715849</v>
       </c>
       <c r="B13" t="n">
-        <v>79847</v>
+        <v>79876</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1924,43 +1974,38 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>520243</v>
+        <v>520268</v>
       </c>
       <c r="R13" t="n">
-        <v>7035552</v>
+        <v>7035575</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2019,10 +2064,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122715766</v>
+        <v>122715795</v>
       </c>
       <c r="B14" t="n">
-        <v>90970</v>
+        <v>79847</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2035,21 +2080,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2059,13 +2104,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>520252</v>
+        <v>520214</v>
       </c>
       <c r="R14" t="n">
-        <v>7035591</v>
+        <v>7035599</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2097,6 +2142,11 @@
           <t>2025-02-23</t>
         </is>
       </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>På en klen gran intill en lunglavssälg.</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2105,6 +2155,31 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM14" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
@@ -2121,10 +2196,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122720368</v>
+        <v>122716682</v>
       </c>
       <c r="B15" t="n">
-        <v>57478</v>
+        <v>57631</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2137,27 +2212,31 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>par i lämplig häckbiotop</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2166,10 +2245,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>519852</v>
+        <v>520101</v>
       </c>
       <c r="R15" t="n">
-        <v>7035392</v>
+        <v>7035453</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2202,11 +2281,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-02-23</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2233,10 +2307,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122716645</v>
+        <v>122719371</v>
       </c>
       <c r="B16" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2249,42 +2323,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>520129</v>
+        <v>519943</v>
       </c>
       <c r="R16" t="n">
-        <v>7035444</v>
+        <v>7035270</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2316,11 +2385,6 @@
           <t>2025-02-23</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
@@ -2329,6 +2393,31 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM16" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
@@ -2345,10 +2434,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122716682</v>
+        <v>122715757</v>
       </c>
       <c r="B17" t="n">
-        <v>57631</v>
+        <v>78766</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2361,43 +2450,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>par i lämplig häckbiotop</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Spejkmyren, Spejkmyren, Jmt</t>
+          <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>520101</v>
+        <v>520234</v>
       </c>
       <c r="R17" t="n">
-        <v>7035453</v>
+        <v>7035595</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2432,6 +2512,11 @@
           <t>2025-02-23</t>
         </is>
       </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
@@ -2440,6 +2525,31 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM17" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
@@ -2456,10 +2566,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122716427</v>
+        <v>122717359</v>
       </c>
       <c r="B18" t="n">
-        <v>78767</v>
+        <v>79847</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2472,37 +2582,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>230405</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Finnbodarna, Finnbodarna, Jmt</t>
+          <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>520388</v>
+        <v>520030</v>
       </c>
       <c r="R18" t="n">
-        <v>7035490</v>
+        <v>7035341</v>
       </c>
       <c r="S18" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2534,11 +2644,6 @@
           <t>2025-02-23</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
-        </is>
-      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -2547,31 +2652,6 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
-      </c>
-      <c r="AH18" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2588,10 +2668,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122717989</v>
+        <v>122715870</v>
       </c>
       <c r="B19" t="n">
-        <v>57494</v>
+        <v>79848</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2604,43 +2684,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>2081</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Spejkmyren, Spejkmyren, Jmt</t>
+          <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>519951</v>
+        <v>520265</v>
       </c>
       <c r="R19" t="n">
-        <v>7035320</v>
+        <v>7035574</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2673,11 +2744,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-02-23</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Trummande</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2704,10 +2770,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122720327</v>
+        <v>122716392</v>
       </c>
       <c r="B20" t="n">
-        <v>57478</v>
+        <v>79848</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2720,42 +2786,42 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Spejkmyren, Spejkmyren, Jmt</t>
+          <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>519838</v>
+        <v>520385</v>
       </c>
       <c r="R20" t="n">
-        <v>7035393</v>
+        <v>7035518</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2789,7 +2855,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>På gran intill en gammal sälg.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2800,6 +2866,31 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM20" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
@@ -2816,7 +2907,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122716964</v>
+        <v>122717294</v>
       </c>
       <c r="B21" t="n">
         <v>90970</v>
@@ -2856,10 +2947,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>520115</v>
+        <v>520013</v>
       </c>
       <c r="R21" t="n">
-        <v>7035402</v>
+        <v>7035340</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2918,7 +3009,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122715502</v>
+        <v>122720869</v>
       </c>
       <c r="B22" t="n">
         <v>78766</v>
@@ -2952,24 +3043,19 @@
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Djupmyren, Djupmyren, Jmt</t>
+          <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>520110</v>
+        <v>519960</v>
       </c>
       <c r="R22" t="n">
-        <v>7035585</v>
+        <v>7035342</v>
       </c>
       <c r="S22" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2999,11 +3085,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-02-23</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Gott om långväxt garnlav på många granar. Vissa bålar är här fertila.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3055,10 +3136,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122720469</v>
+        <v>122715571</v>
       </c>
       <c r="B23" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3071,34 +3152,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Spejkmyren, Spejkmyren, Jmt</t>
+          <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>519996</v>
+        <v>520216</v>
       </c>
       <c r="R23" t="n">
-        <v>7035241</v>
+        <v>7035583</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3141,31 +3222,6 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
-      </c>
-      <c r="AH23" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
@@ -3182,7 +3238,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122716329</v>
+        <v>122715780</v>
       </c>
       <c r="B24" t="n">
         <v>79847</v>
@@ -3216,24 +3272,19 @@
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>520374</v>
+        <v>520259</v>
       </c>
       <c r="R24" t="n">
-        <v>7035511</v>
+        <v>7035569</v>
       </c>
       <c r="S24" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3267,7 +3318,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>På gran intill en gammal lunglavssälg.</t>
+          <t>På björk</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3278,31 +3329,6 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
-      </c>
-      <c r="AH24" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ24" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK24" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
@@ -3319,10 +3345,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122719697</v>
+        <v>122717989</v>
       </c>
       <c r="B25" t="n">
-        <v>78766</v>
+        <v>57494</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3335,37 +3361,46 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>520026</v>
+        <v>519951</v>
       </c>
       <c r="R25" t="n">
-        <v>7035233</v>
+        <v>7035320</v>
       </c>
       <c r="S25" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3397,6 +3432,11 @@
           <t>2025-02-23</t>
         </is>
       </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Trummande</t>
+        </is>
+      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
@@ -3405,31 +3445,6 @@
       </c>
       <c r="AG25" t="b">
         <v>0</v>
-      </c>
-      <c r="AH25" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ25" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK25" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM25" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO25" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
@@ -3446,10 +3461,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122717284</v>
+        <v>122720368</v>
       </c>
       <c r="B26" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3462,37 +3477,42 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>520031</v>
+        <v>519852</v>
       </c>
       <c r="R26" t="n">
-        <v>7035353</v>
+        <v>7035392</v>
       </c>
       <c r="S26" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3526,7 +3546,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Långväxta bålar på flertalet granar.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3537,31 +3557,6 @@
       </c>
       <c r="AG26" t="b">
         <v>0</v>
-      </c>
-      <c r="AH26" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ26" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK26" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM26" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO26" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
@@ -3578,7 +3573,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122715775</v>
+        <v>122717873</v>
       </c>
       <c r="B27" t="n">
         <v>79847</v>
@@ -3614,22 +3609,22 @@
       <c r="I27" t="inlineStr"/>
       <c r="K27" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Finnbodarna, Finnbodarna, Jmt</t>
+          <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>520252</v>
+        <v>520033</v>
       </c>
       <c r="R27" t="n">
-        <v>7035576</v>
+        <v>7035301</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3661,11 +3656,6 @@
           <t>2025-02-23</t>
         </is>
       </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>På björk</t>
-        </is>
-      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
@@ -3674,6 +3664,31 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
+      </c>
+      <c r="AH27" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM27" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
@@ -3690,10 +3705,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122720558</v>
+        <v>122719829</v>
       </c>
       <c r="B28" t="n">
-        <v>57494</v>
+        <v>57478</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3706,16 +3721,16 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -3735,10 +3750,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>519949</v>
+        <v>519930</v>
       </c>
       <c r="R28" t="n">
-        <v>7035254</v>
+        <v>7035181</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3775,7 +3790,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Äldre hackspår i stambasen.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3786,31 +3801,6 @@
       </c>
       <c r="AG28" t="b">
         <v>0</v>
-      </c>
-      <c r="AH28" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ28" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK28" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM28" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO28" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
@@ -3827,10 +3817,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122719829</v>
+        <v>122716427</v>
       </c>
       <c r="B29" t="n">
-        <v>57478</v>
+        <v>78767</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3843,42 +3833,37 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>230405</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Spejkmyren, Spejkmyren, Jmt</t>
+          <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>519930</v>
+        <v>520388</v>
       </c>
       <c r="R29" t="n">
-        <v>7035181</v>
+        <v>7035490</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3912,7 +3897,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3923,6 +3908,31 @@
       </c>
       <c r="AG29" t="b">
         <v>0</v>
+      </c>
+      <c r="AH29" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM29" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
@@ -3939,10 +3949,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122719554</v>
+        <v>122715669</v>
       </c>
       <c r="B30" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3955,44 +3965,39 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Spejkmyren, Spejkmyren, Jmt</t>
+          <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>519981</v>
+        <v>520221</v>
       </c>
       <c r="R30" t="n">
-        <v>7035221</v>
+        <v>7035600</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4027,11 +4032,6 @@
           <t>2025-02-23</t>
         </is>
       </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Äldre ringhack som bedöms vara 5 - 10 år gamla.</t>
-        </is>
-      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
@@ -4040,31 +4040,6 @@
       </c>
       <c r="AG30" t="b">
         <v>0</v>
-      </c>
-      <c r="AH30" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ30" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK30" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM30" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO30" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
@@ -4081,7 +4056,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122720889</v>
+        <v>122719875</v>
       </c>
       <c r="B31" t="n">
         <v>57478</v>
@@ -4126,10 +4101,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>519841</v>
+        <v>519983</v>
       </c>
       <c r="R31" t="n">
-        <v>7035390</v>
+        <v>7035206</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4193,10 +4168,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122715949</v>
+        <v>122721333</v>
       </c>
       <c r="B32" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4209,37 +4184,37 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Finnbodarna, Finnbodarna, Jmt</t>
+          <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>520254</v>
+        <v>519906</v>
       </c>
       <c r="R32" t="n">
-        <v>7035555</v>
+        <v>7035389</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4271,6 +4246,11 @@
           <t>2025-02-23</t>
         </is>
       </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Ymnigt på flera granar.</t>
+        </is>
+      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
@@ -4279,6 +4259,31 @@
       </c>
       <c r="AG32" t="b">
         <v>0</v>
+      </c>
+      <c r="AH32" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM32" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
@@ -4295,10 +4300,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122716757</v>
+        <v>122715677</v>
       </c>
       <c r="B33" t="n">
-        <v>78766</v>
+        <v>79848</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4311,21 +4316,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4335,13 +4340,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>520316</v>
+        <v>520221</v>
       </c>
       <c r="R33" t="n">
-        <v>7035491</v>
+        <v>7035600</v>
       </c>
       <c r="S33" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4373,6 +4378,11 @@
           <t>2025-02-23</t>
         </is>
       </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>På gran</t>
+        </is>
+      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
@@ -4381,31 +4391,6 @@
       </c>
       <c r="AG33" t="b">
         <v>0</v>
-      </c>
-      <c r="AH33" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ33" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK33" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO33" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
@@ -4422,10 +4407,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122715569</v>
+        <v>122716801</v>
       </c>
       <c r="B34" t="n">
-        <v>78766</v>
+        <v>57631</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4438,34 +4423,43 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Djupmyren, Djupmyren, Jmt</t>
+          <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>520115</v>
+        <v>520083</v>
       </c>
       <c r="R34" t="n">
-        <v>7035562</v>
+        <v>7035403</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4500,11 +4494,6 @@
           <t>2025-02-23</t>
         </is>
       </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
-        </is>
-      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
@@ -4513,31 +4502,6 @@
       </c>
       <c r="AG34" t="b">
         <v>0</v>
-      </c>
-      <c r="AH34" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ34" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK34" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM34" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO34" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
@@ -4554,10 +4518,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122719979</v>
+        <v>122715756</v>
       </c>
       <c r="B35" t="n">
-        <v>57631</v>
+        <v>79847</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4570,43 +4534,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>par i lämplig häckbiotop</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Spejkmyren, Spejkmyren, Jmt</t>
+          <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>519946</v>
+        <v>520256</v>
       </c>
       <c r="R35" t="n">
-        <v>7035240</v>
+        <v>7035593</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4665,10 +4620,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122716216</v>
+        <v>122715502</v>
       </c>
       <c r="B36" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4681,42 +4636,42 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="K36" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Finnbodarna, Finnbodarna, Jmt</t>
+          <t>Djupmyren, Djupmyren, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>520368</v>
+        <v>520110</v>
       </c>
       <c r="R36" t="n">
-        <v>7035513</v>
+        <v>7035585</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4750,7 +4705,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>På en gammal grovbarkad sälg.</t>
+          <t>Gott om långväxt garnlav på många granar. Vissa bålar är här fertila.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4769,22 +4724,22 @@
       </c>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK36" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM36" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -4802,10 +4757,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122717616</v>
+        <v>122716964</v>
       </c>
       <c r="B37" t="n">
-        <v>78766</v>
+        <v>90970</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4818,21 +4773,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4842,10 +4797,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>520019</v>
+        <v>520115</v>
       </c>
       <c r="R37" t="n">
-        <v>7035352</v>
+        <v>7035402</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4880,11 +4835,6 @@
           <t>2025-02-23</t>
         </is>
       </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Rikligt.</t>
-        </is>
-      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
@@ -4893,31 +4843,6 @@
       </c>
       <c r="AG37" t="b">
         <v>0</v>
-      </c>
-      <c r="AH37" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ37" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK37" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM37" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO37" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
@@ -4934,10 +4859,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122717873</v>
+        <v>122721463</v>
       </c>
       <c r="B38" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4950,42 +4875,37 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>520033</v>
+        <v>519841</v>
       </c>
       <c r="R38" t="n">
-        <v>7035301</v>
+        <v>7035417</v>
       </c>
       <c r="S38" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5017,6 +4937,11 @@
           <t>2025-02-23</t>
         </is>
       </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
+        </is>
+      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
@@ -5033,22 +4958,22 @@
       </c>
       <c r="AJ38" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK38" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM38" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO38" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -5066,10 +4991,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122716269</v>
+        <v>122715569</v>
       </c>
       <c r="B39" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5082,39 +5007,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Finnbodarna, Hammerdal, Finnbodarna, Hammerdal, Jmt</t>
+          <t>Djupmyren, Djupmyren, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>520256</v>
+        <v>520115</v>
       </c>
       <c r="R39" t="n">
-        <v>7035380</v>
+        <v>7035562</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5151,7 +5071,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5162,6 +5082,31 @@
       </c>
       <c r="AG39" t="b">
         <v>0</v>
+      </c>
+      <c r="AH39" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ39" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK39" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM39" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO39" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
@@ -5178,10 +5123,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122716303</v>
+        <v>122715836</v>
       </c>
       <c r="B40" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5194,39 +5139,39 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Finnbodarna, Hammerdal, Finnbodarna, Hammerdal, Jmt</t>
+          <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>520250</v>
+        <v>520269</v>
       </c>
       <c r="R40" t="n">
-        <v>7035363</v>
+        <v>7035574</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5259,11 +5204,6 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-02-23</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5290,10 +5230,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122718013</v>
+        <v>122716234</v>
       </c>
       <c r="B41" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5306,39 +5246,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Spejkmyren, Spejkmyren, Jmt</t>
+          <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>519948</v>
+        <v>520362</v>
       </c>
       <c r="R41" t="n">
-        <v>7035313</v>
+        <v>7035500</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5375,7 +5310,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>På en klen gran intill en gammal sälg med lunglav.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5386,6 +5321,31 @@
       </c>
       <c r="AG41" t="b">
         <v>0</v>
+      </c>
+      <c r="AH41" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ41" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK41" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM41" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO41" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
@@ -5402,10 +5362,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122715874</v>
+        <v>122716216</v>
       </c>
       <c r="B42" t="n">
-        <v>79876</v>
+        <v>79847</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5414,38 +5374,43 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>520265</v>
+        <v>520368</v>
       </c>
       <c r="R42" t="n">
-        <v>7035574</v>
+        <v>7035513</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5480,6 +5445,11 @@
           <t>2025-02-23</t>
         </is>
       </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>På en gammal grovbarkad sälg.</t>
+        </is>
+      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
@@ -5488,6 +5458,31 @@
       </c>
       <c r="AG42" t="b">
         <v>0</v>
+      </c>
+      <c r="AH42" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ42" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK42" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM42" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO42" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
@@ -5504,10 +5499,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122715953</v>
+        <v>122715648</v>
       </c>
       <c r="B43" t="n">
-        <v>79848</v>
+        <v>57478</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5520,34 +5515,39 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Finnbodarna, Finnbodarna, Jmt</t>
+          <t>Finnbodarna, Hammerdal, Finnbodarna, Hammerdal, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>520254</v>
+        <v>520219</v>
       </c>
       <c r="R43" t="n">
-        <v>7035555</v>
+        <v>7035597</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5580,6 +5580,11 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-02-23</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5606,10 +5611,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122715868</v>
+        <v>122719533</v>
       </c>
       <c r="B44" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5622,39 +5627,39 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Finnbodarna, Finnbodarna, Jmt</t>
+          <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>520265</v>
+        <v>519948</v>
       </c>
       <c r="R44" t="n">
-        <v>7035574</v>
+        <v>7035187</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5687,6 +5692,11 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-02-23</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5713,10 +5723,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122717468</v>
+        <v>122717929</v>
       </c>
       <c r="B45" t="n">
-        <v>57494</v>
+        <v>79876</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5725,35 +5735,31 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100049</v>
+        <v>6462</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
@@ -5762,13 +5768,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>520020</v>
+        <v>520029</v>
       </c>
       <c r="R45" t="n">
-        <v>7035330</v>
+        <v>7035292</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5808,6 +5814,31 @@
       </c>
       <c r="AG45" t="b">
         <v>0</v>
+      </c>
+      <c r="AH45" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ45" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK45" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM45" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO45" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
@@ -5824,10 +5855,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122715841</v>
+        <v>122716269</v>
       </c>
       <c r="B46" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5840,42 +5871,42 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>med soral</t>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Finnbodarna, Finnbodarna, Jmt</t>
+          <t>Finnbodarna, Hammerdal, Finnbodarna, Hammerdal, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>520229</v>
+        <v>520256</v>
       </c>
       <c r="R46" t="n">
-        <v>7035608</v>
+        <v>7035380</v>
       </c>
       <c r="S46" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5909,7 +5940,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>På en björk.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5920,31 +5951,6 @@
       </c>
       <c r="AG46" t="b">
         <v>0</v>
-      </c>
-      <c r="AH46" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ46" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK46" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AM46" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO46" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Betula</t>
-        </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
@@ -5961,7 +5967,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122715648</v>
+        <v>122720823</v>
       </c>
       <c r="B47" t="n">
         <v>57478</v>
@@ -5994,22 +6000,36 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I47" t="inlineStr"/>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Finnbodarna, Hammerdal, Finnbodarna, Hammerdal, Jmt</t>
+          <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>520219</v>
+        <v>519842</v>
       </c>
       <c r="R47" t="n">
-        <v>7035597</v>
+        <v>7035388</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6046,7 +6066,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Trummande</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6073,7 +6093,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122720454</v>
+        <v>122717636</v>
       </c>
       <c r="B48" t="n">
         <v>57478</v>
@@ -6118,10 +6138,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>519849</v>
+        <v>519970</v>
       </c>
       <c r="R48" t="n">
-        <v>7035406</v>
+        <v>7035297</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6185,10 +6205,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122717446</v>
+        <v>122719554</v>
       </c>
       <c r="B49" t="n">
-        <v>90970</v>
+        <v>57478</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6201,34 +6221,44 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>520006</v>
+        <v>519981</v>
       </c>
       <c r="R49" t="n">
-        <v>7035303</v>
+        <v>7035221</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6263,6 +6293,11 @@
           <t>2025-02-23</t>
         </is>
       </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Äldre ringhack som bedöms vara 5 - 10 år gamla.</t>
+        </is>
+      </c>
       <c r="AD49" t="b">
         <v>0</v>
       </c>
@@ -6271,6 +6306,31 @@
       </c>
       <c r="AG49" t="b">
         <v>0</v>
+      </c>
+      <c r="AH49" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ49" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK49" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM49" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO49" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
@@ -6287,10 +6347,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122717294</v>
+        <v>122715978</v>
       </c>
       <c r="B50" t="n">
-        <v>90970</v>
+        <v>79847</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6303,34 +6363,39 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Spejkmyren, Spejkmyren, Jmt</t>
+          <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>520013</v>
+        <v>520243</v>
       </c>
       <c r="R50" t="n">
-        <v>7035340</v>
+        <v>7035552</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6389,10 +6454,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122715934</v>
+        <v>122720281</v>
       </c>
       <c r="B51" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6405,37 +6470,42 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Finnbodarna, Finnbodarna, Jmt</t>
+          <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>520303</v>
+        <v>519850</v>
       </c>
       <c r="R51" t="n">
-        <v>7035598</v>
+        <v>7035373</v>
       </c>
       <c r="S51" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6469,7 +6539,7 @@
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6480,31 +6550,6 @@
       </c>
       <c r="AG51" t="b">
         <v>0</v>
-      </c>
-      <c r="AH51" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ51" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK51" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM51" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO51" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
@@ -6521,10 +6566,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122715779</v>
+        <v>122720474</v>
       </c>
       <c r="B52" t="n">
-        <v>79847</v>
+        <v>57494</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6537,42 +6582,51 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>med soral</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Finnbodarna, Finnbodarna, Jmt</t>
+          <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>520223</v>
+        <v>519848</v>
       </c>
       <c r="R52" t="n">
-        <v>7035609</v>
+        <v>7035394</v>
       </c>
       <c r="S52" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6612,31 +6666,6 @@
       </c>
       <c r="AG52" t="b">
         <v>0</v>
-      </c>
-      <c r="AH52" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ52" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK52" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM52" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO52" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
@@ -6653,10 +6682,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122720474</v>
+        <v>122720889</v>
       </c>
       <c r="B53" t="n">
-        <v>57494</v>
+        <v>57478</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6669,16 +6698,16 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -6686,19 +6715,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L53" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="I53" t="inlineStr"/>
       <c r="M53" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
@@ -6707,10 +6727,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>519848</v>
+        <v>519841</v>
       </c>
       <c r="R53" t="n">
-        <v>7035394</v>
+        <v>7035390</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6743,6 +6763,11 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-02-23</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6769,7 +6794,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122716673</v>
+        <v>122720427</v>
       </c>
       <c r="B54" t="n">
         <v>57478</v>
@@ -6805,7 +6830,7 @@
       <c r="I54" t="inlineStr"/>
       <c r="M54" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
@@ -6814,10 +6839,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>520108</v>
+        <v>519846</v>
       </c>
       <c r="R54" t="n">
-        <v>7035462</v>
+        <v>7035407</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6881,10 +6906,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122717164</v>
+        <v>122716387</v>
       </c>
       <c r="B55" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6897,34 +6922,39 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Spejkmyren, Spejkmyren, Jmt</t>
+          <t>Finnbodarna, Hammerdal, Finnbodarna, Hammerdal, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>520120</v>
+        <v>520278</v>
       </c>
       <c r="R55" t="n">
-        <v>7035405</v>
+        <v>7035397</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6959,6 +6989,11 @@
           <t>2025-02-23</t>
         </is>
       </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD55" t="b">
         <v>0</v>
       </c>
@@ -6967,31 +7002,6 @@
       </c>
       <c r="AG55" t="b">
         <v>0</v>
-      </c>
-      <c r="AH55" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ55" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK55" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM55" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO55" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
@@ -7008,7 +7018,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122720065</v>
+        <v>122720686</v>
       </c>
       <c r="B56" t="n">
         <v>78766</v>
@@ -7048,13 +7058,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>520062</v>
+        <v>519903</v>
       </c>
       <c r="R56" t="n">
-        <v>7035232</v>
+        <v>7035224</v>
       </c>
       <c r="S56" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -7135,10 +7145,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122716160</v>
+        <v>122715766</v>
       </c>
       <c r="B57" t="n">
-        <v>78766</v>
+        <v>90970</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -7151,21 +7161,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -7175,10 +7185,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>520349</v>
+        <v>520252</v>
       </c>
       <c r="R57" t="n">
-        <v>7035517</v>
+        <v>7035591</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7221,31 +7231,6 @@
       </c>
       <c r="AG57" t="b">
         <v>0</v>
-      </c>
-      <c r="AH57" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ57" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK57" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM57" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO57" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
@@ -7262,10 +7247,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122720281</v>
+        <v>122717284</v>
       </c>
       <c r="B58" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7278,42 +7263,37 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>519850</v>
+        <v>520031</v>
       </c>
       <c r="R58" t="n">
-        <v>7035373</v>
+        <v>7035353</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7347,7 +7327,7 @@
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Långväxta bålar på flertalet granar.</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7358,6 +7338,31 @@
       </c>
       <c r="AG58" t="b">
         <v>0</v>
+      </c>
+      <c r="AH58" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ58" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK58" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM58" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO58" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
@@ -7374,10 +7379,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122716295</v>
+        <v>122720959</v>
       </c>
       <c r="B59" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7390,39 +7395,34 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="K59" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Finnbodarna, Finnbodarna, Jmt</t>
+          <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>520378</v>
+        <v>519917</v>
       </c>
       <c r="R59" t="n">
-        <v>7035512</v>
+        <v>7035339</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7459,7 +7459,7 @@
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>Ymnig påväxt på en grovbarkad gammal sälg. Fertila bålar med apothecier.</t>
+          <t>Långväxta bålar på flertalet granar.</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7478,22 +7478,22 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK59" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM59" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO59" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT59" t="inlineStr"/>
@@ -7511,10 +7511,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122719371</v>
+        <v>122717488</v>
       </c>
       <c r="B60" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7527,21 +7527,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7551,13 +7551,13 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>519943</v>
+        <v>520000</v>
       </c>
       <c r="R60" t="n">
-        <v>7035270</v>
+        <v>7035297</v>
       </c>
       <c r="S60" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7597,31 +7597,6 @@
       </c>
       <c r="AG60" t="b">
         <v>0</v>
-      </c>
-      <c r="AH60" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ60" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK60" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM60" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO60" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
@@ -7638,10 +7613,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122716392</v>
+        <v>122716443</v>
       </c>
       <c r="B61" t="n">
-        <v>79848</v>
+        <v>78766</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7654,27 +7629,36 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
@@ -7683,13 +7667,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>520385</v>
+        <v>520251</v>
       </c>
       <c r="R61" t="n">
-        <v>7035518</v>
+        <v>7035394</v>
       </c>
       <c r="S61" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7723,7 +7707,7 @@
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>På gran intill en gammal sälg.</t>
+          <t>Garnlavsrikt</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7734,31 +7718,6 @@
       </c>
       <c r="AG61" t="b">
         <v>0</v>
-      </c>
-      <c r="AH61" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ61" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK61" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM61" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO61" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
@@ -7775,10 +7734,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122716801</v>
+        <v>122720558</v>
       </c>
       <c r="B62" t="n">
-        <v>57631</v>
+        <v>57494</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7791,31 +7750,27 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
       <c r="M62" t="inlineStr">
         <is>
-          <t>par i lämplig häckbiotop</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
@@ -7824,10 +7779,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>520083</v>
+        <v>519949</v>
       </c>
       <c r="R62" t="n">
-        <v>7035403</v>
+        <v>7035254</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7862,6 +7817,11 @@
           <t>2025-02-23</t>
         </is>
       </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Äldre hackspår i stambasen.</t>
+        </is>
+      </c>
       <c r="AD62" t="b">
         <v>0</v>
       </c>
@@ -7870,6 +7830,31 @@
       </c>
       <c r="AG62" t="b">
         <v>0</v>
+      </c>
+      <c r="AH62" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ62" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK62" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM62" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO62" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
@@ -7886,7 +7871,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122715756</v>
+        <v>122715778</v>
       </c>
       <c r="B63" t="n">
         <v>79847</v>
@@ -7920,16 +7905,21 @@
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>520256</v>
+        <v>520259</v>
       </c>
       <c r="R63" t="n">
-        <v>7035593</v>
+        <v>7035574</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7988,10 +7978,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122715573</v>
+        <v>122716160</v>
       </c>
       <c r="B64" t="n">
-        <v>79848</v>
+        <v>78766</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -8004,21 +7994,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -8028,10 +8018,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>520214</v>
+        <v>520349</v>
       </c>
       <c r="R64" t="n">
-        <v>7035583</v>
+        <v>7035517</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -8074,6 +8064,31 @@
       </c>
       <c r="AG64" t="b">
         <v>0</v>
+      </c>
+      <c r="AH64" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ64" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK64" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM64" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO64" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
@@ -8090,10 +8105,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122719533</v>
+        <v>122716757</v>
       </c>
       <c r="B65" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -8106,42 +8121,37 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Spejkmyren, Spejkmyren, Jmt</t>
+          <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>519948</v>
+        <v>520316</v>
       </c>
       <c r="R65" t="n">
-        <v>7035187</v>
+        <v>7035491</v>
       </c>
       <c r="S65" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -8173,11 +8183,6 @@
           <t>2025-02-23</t>
         </is>
       </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD65" t="b">
         <v>0</v>
       </c>
@@ -8186,6 +8191,31 @@
       </c>
       <c r="AG65" t="b">
         <v>0</v>
+      </c>
+      <c r="AH65" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ65" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK65" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM65" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO65" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
@@ -8202,10 +8232,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122721035</v>
+        <v>122716645</v>
       </c>
       <c r="B66" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -8218,37 +8248,42 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>519897</v>
+        <v>520129</v>
       </c>
       <c r="R66" t="n">
-        <v>7035374</v>
+        <v>7035444</v>
       </c>
       <c r="S66" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -8280,6 +8315,11 @@
           <t>2025-02-23</t>
         </is>
       </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD66" t="b">
         <v>0</v>
       </c>
@@ -8288,31 +8328,6 @@
       </c>
       <c r="AG66" t="b">
         <v>0</v>
-      </c>
-      <c r="AH66" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ66" t="inlineStr">
-        <is>
-          <t>garnlav</t>
-        </is>
-      </c>
-      <c r="AK66" t="inlineStr">
-        <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="AM66" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO66" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Alectoria sarmentosa</t>
-        </is>
       </c>
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
@@ -8329,10 +8344,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>122716443</v>
+        <v>122718013</v>
       </c>
       <c r="B67" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8345,48 +8360,39 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
-      <c r="J67" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K67" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Finnbodarna, Finnbodarna, Jmt</t>
+          <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>520251</v>
+        <v>519948</v>
       </c>
       <c r="R67" t="n">
-        <v>7035394</v>
+        <v>7035313</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8423,7 +8429,7 @@
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>Garnlavsrikt</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8450,10 +8456,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>122720629</v>
+        <v>122719648</v>
       </c>
       <c r="B68" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8466,34 +8472,39 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>519935</v>
+        <v>519939</v>
       </c>
       <c r="R68" t="n">
-        <v>7035246</v>
+        <v>7035194</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8530,7 +8541,7 @@
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8541,31 +8552,6 @@
       </c>
       <c r="AG68" t="b">
         <v>0</v>
-      </c>
-      <c r="AH68" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ68" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK68" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM68" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO68" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
@@ -8582,7 +8568,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>122720959</v>
+        <v>122720469</v>
       </c>
       <c r="B69" t="n">
         <v>78766</v>
@@ -8622,10 +8608,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>519917</v>
+        <v>519996</v>
       </c>
       <c r="R69" t="n">
-        <v>7035339</v>
+        <v>7035241</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8658,11 +8644,6 @@
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-02-23</t>
-        </is>
-      </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>Långväxta bålar på flertalet granar.</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8714,10 +8695,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>122716234</v>
+        <v>122720454</v>
       </c>
       <c r="B70" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8730,34 +8711,39 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Finnbodarna, Finnbodarna, Jmt</t>
+          <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>520362</v>
+        <v>519849</v>
       </c>
       <c r="R70" t="n">
-        <v>7035500</v>
+        <v>7035406</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8794,7 +8780,7 @@
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>På en klen gran intill en gammal sälg med lunglav.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8805,31 +8791,6 @@
       </c>
       <c r="AG70" t="b">
         <v>0</v>
-      </c>
-      <c r="AH70" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ70" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK70" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM70" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO70" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
@@ -8846,10 +8807,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>122715870</v>
+        <v>122716329</v>
       </c>
       <c r="B71" t="n">
-        <v>79848</v>
+        <v>79847</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8862,37 +8823,42 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>520265</v>
+        <v>520374</v>
       </c>
       <c r="R71" t="n">
-        <v>7035574</v>
+        <v>7035511</v>
       </c>
       <c r="S71" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8924,6 +8890,11 @@
           <t>2025-02-23</t>
         </is>
       </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>På gran intill en gammal lunglavssälg.</t>
+        </is>
+      </c>
       <c r="AD71" t="b">
         <v>0</v>
       </c>
@@ -8932,6 +8903,31 @@
       </c>
       <c r="AG71" t="b">
         <v>0</v>
+      </c>
+      <c r="AH71" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ71" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK71" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM71" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO71" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
@@ -8948,10 +8944,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>122719648</v>
+        <v>122715874</v>
       </c>
       <c r="B72" t="n">
-        <v>57478</v>
+        <v>79876</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8960,43 +8956,38 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Spejkmyren, Spejkmyren, Jmt</t>
+          <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>519939</v>
+        <v>520265</v>
       </c>
       <c r="R72" t="n">
-        <v>7035194</v>
+        <v>7035574</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -9029,11 +9020,6 @@
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-02-23</t>
-        </is>
-      </c>
-      <c r="AC72" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -9060,10 +9046,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>122721463</v>
+        <v>122716303</v>
       </c>
       <c r="B73" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -9076,34 +9062,39 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Spejkmyren, Spejkmyren, Jmt</t>
+          <t>Finnbodarna, Hammerdal, Finnbodarna, Hammerdal, Jmt</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>519841</v>
+        <v>520250</v>
       </c>
       <c r="R73" t="n">
-        <v>7035417</v>
+        <v>7035363</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -9140,7 +9131,7 @@
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -9151,31 +9142,6 @@
       </c>
       <c r="AG73" t="b">
         <v>0</v>
-      </c>
-      <c r="AH73" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ73" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK73" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM73" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO73" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
@@ -9192,10 +9158,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>122715780</v>
+        <v>122716547</v>
       </c>
       <c r="B74" t="n">
-        <v>79847</v>
+        <v>98271</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -9204,41 +9170,55 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6458</v>
+        <v>504</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P74" t="inlineStr">
         <is>
           <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>520259</v>
+        <v>520386</v>
       </c>
       <c r="R74" t="n">
-        <v>7035569</v>
+        <v>7035492</v>
       </c>
       <c r="S74" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -9272,7 +9252,7 @@
       </c>
       <c r="AC74" t="inlineStr">
         <is>
-          <t>På björk</t>
+          <t>En vinterståndare på till synes fuktig mark i en lucka.</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9283,6 +9263,11 @@
       </c>
       <c r="AG74" t="b">
         <v>0</v>
+      </c>
+      <c r="AH74" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
@@ -9299,10 +9284,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>122720427</v>
+        <v>122719697</v>
       </c>
       <c r="B75" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -9315,42 +9300,37 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
-      <c r="M75" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P75" t="inlineStr">
         <is>
           <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>519846</v>
+        <v>520026</v>
       </c>
       <c r="R75" t="n">
-        <v>7035407</v>
+        <v>7035233</v>
       </c>
       <c r="S75" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -9382,11 +9362,6 @@
           <t>2025-02-23</t>
         </is>
       </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD75" t="b">
         <v>0</v>
       </c>
@@ -9395,6 +9370,31 @@
       </c>
       <c r="AG75" t="b">
         <v>0</v>
+      </c>
+      <c r="AH75" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK75" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM75" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO75" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
@@ -9411,10 +9411,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>122717636</v>
+        <v>122717164</v>
       </c>
       <c r="B76" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -9427,39 +9427,34 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
-      <c r="M76" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P76" t="inlineStr">
         <is>
           <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>519970</v>
+        <v>520120</v>
       </c>
       <c r="R76" t="n">
-        <v>7035297</v>
+        <v>7035405</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -9494,11 +9489,6 @@
           <t>2025-02-23</t>
         </is>
       </c>
-      <c r="AC76" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD76" t="b">
         <v>0</v>
       </c>
@@ -9507,6 +9497,31 @@
       </c>
       <c r="AG76" t="b">
         <v>0</v>
+      </c>
+      <c r="AH76" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ76" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK76" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM76" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO76" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
@@ -9523,10 +9538,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>122717488</v>
+        <v>122715999</v>
       </c>
       <c r="B77" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -9539,37 +9554,37 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Spejkmyren, Spejkmyren, Jmt</t>
+          <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>520000</v>
+        <v>520311</v>
       </c>
       <c r="R77" t="n">
-        <v>7035297</v>
+        <v>7035566</v>
       </c>
       <c r="S77" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -9609,6 +9624,31 @@
       </c>
       <c r="AG77" t="b">
         <v>0</v>
+      </c>
+      <c r="AH77" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ77" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK77" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM77" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO77" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
@@ -9625,10 +9665,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>122715795</v>
+        <v>122715934</v>
       </c>
       <c r="B78" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -9641,21 +9681,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -9665,13 +9705,13 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>520214</v>
+        <v>520303</v>
       </c>
       <c r="R78" t="n">
-        <v>7035599</v>
+        <v>7035598</v>
       </c>
       <c r="S78" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -9705,7 +9745,7 @@
       </c>
       <c r="AC78" t="inlineStr">
         <is>
-          <t>På en klen gran intill en lunglavssälg.</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9757,10 +9797,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>122720823</v>
+        <v>122715868</v>
       </c>
       <c r="B79" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -9773,53 +9813,39 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
       <c r="K79" t="inlineStr">
         <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L79" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M79" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Spejkmyren, Spejkmyren, Jmt</t>
+          <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>519842</v>
+        <v>520265</v>
       </c>
       <c r="R79" t="n">
-        <v>7035388</v>
+        <v>7035574</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9852,11 +9878,6 @@
       <c r="AA79" t="inlineStr">
         <is>
           <t>2025-02-23</t>
-        </is>
-      </c>
-      <c r="AC79" t="inlineStr">
-        <is>
-          <t>Trummande</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9883,7 +9904,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>122715669</v>
+        <v>122715790</v>
       </c>
       <c r="B80" t="n">
         <v>79847</v>
@@ -9928,10 +9949,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>520221</v>
+        <v>520267</v>
       </c>
       <c r="R80" t="n">
-        <v>7035600</v>
+        <v>7035581</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9990,10 +10011,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>122716387</v>
+        <v>122716295</v>
       </c>
       <c r="B81" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -10006,39 +10027,39 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
-      <c r="M81" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Finnbodarna, Hammerdal, Finnbodarna, Hammerdal, Jmt</t>
+          <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>520278</v>
+        <v>520378</v>
       </c>
       <c r="R81" t="n">
-        <v>7035397</v>
+        <v>7035512</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -10075,7 +10096,7 @@
       </c>
       <c r="AC81" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ymnig påväxt på en grovbarkad gammal sälg. Fertila bålar med apothecier.</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -10086,6 +10107,31 @@
       </c>
       <c r="AG81" t="b">
         <v>0</v>
+      </c>
+      <c r="AH81" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ81" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK81" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM81" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO81" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
@@ -10102,10 +10148,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>122716850</v>
+        <v>122715573</v>
       </c>
       <c r="B82" t="n">
-        <v>90970</v>
+        <v>79848</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -10118,34 +10164,34 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>5432</v>
+        <v>2081</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Spejkmyren, Spejkmyren, Jmt</t>
+          <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>520101</v>
+        <v>520214</v>
       </c>
       <c r="R82" t="n">
-        <v>7035388</v>
+        <v>7035583</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -10204,10 +10250,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>122716293</v>
+        <v>122717468</v>
       </c>
       <c r="B83" t="n">
-        <v>57478</v>
+        <v>57494</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -10220,16 +10266,16 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -10237,22 +10283,26 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I83" t="inlineStr"/>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Finnbodarna, Hammerdal, Finnbodarna, Hammerdal, Jmt</t>
+          <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>520249</v>
+        <v>520020</v>
       </c>
       <c r="R83" t="n">
-        <v>7035364</v>
+        <v>7035330</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -10285,11 +10335,6 @@
       <c r="AA83" t="inlineStr">
         <is>
           <t>2025-02-23</t>
-        </is>
-      </c>
-      <c r="AC83" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -10316,10 +10361,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>122715849</v>
+        <v>122720327</v>
       </c>
       <c r="B84" t="n">
-        <v>79876</v>
+        <v>57478</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -10328,38 +10373,43 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Finnbodarna, Finnbodarna, Jmt</t>
+          <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>520268</v>
+        <v>519838</v>
       </c>
       <c r="R84" t="n">
-        <v>7035575</v>
+        <v>7035393</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -10392,6 +10442,11 @@
       <c r="AA84" t="inlineStr">
         <is>
           <t>2025-02-23</t>
+        </is>
+      </c>
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -10418,10 +10473,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>122717929</v>
+        <v>122719979</v>
       </c>
       <c r="B85" t="n">
-        <v>79876</v>
+        <v>57631</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -10430,31 +10485,35 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6462</v>
+        <v>103021</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr"/>
-      <c r="K85" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
         </is>
       </c>
       <c r="P85" t="inlineStr">
@@ -10463,13 +10522,13 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>520029</v>
+        <v>519946</v>
       </c>
       <c r="R85" t="n">
-        <v>7035292</v>
+        <v>7035240</v>
       </c>
       <c r="S85" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -10509,31 +10568,6 @@
       </c>
       <c r="AG85" t="b">
         <v>0</v>
-      </c>
-      <c r="AH85" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ85" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK85" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM85" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO85" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
@@ -10550,10 +10584,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>122715801</v>
+        <v>122716850</v>
       </c>
       <c r="B86" t="n">
-        <v>79848</v>
+        <v>90970</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -10566,34 +10600,34 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>2081</v>
+        <v>5432</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Finnbodarna, Finnbodarna, Jmt</t>
+          <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>520266</v>
+        <v>520101</v>
       </c>
       <c r="R86" t="n">
-        <v>7035582</v>
+        <v>7035388</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -10652,10 +10686,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>122716547</v>
+        <v>122717616</v>
       </c>
       <c r="B87" t="n">
-        <v>98271</v>
+        <v>78766</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -10664,55 +10698,41 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>504</v>
+        <v>6425</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J87" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K87" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Finnbodarna, Finnbodarna, Jmt</t>
+          <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>520386</v>
+        <v>520019</v>
       </c>
       <c r="R87" t="n">
-        <v>7035492</v>
+        <v>7035352</v>
       </c>
       <c r="S87" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -10746,7 +10766,7 @@
       </c>
       <c r="AC87" t="inlineStr">
         <is>
-          <t>En vinterståndare på till synes fuktig mark i en lucka.</t>
+          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10761,6 +10781,26 @@
       <c r="AH87" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ87" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK87" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM87" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO87" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT87" t="inlineStr"/>
@@ -10778,10 +10818,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>122720869</v>
+        <v>122715775</v>
       </c>
       <c r="B88" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -10794,34 +10834,39 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Spejkmyren, Spejkmyren, Jmt</t>
+          <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>519960</v>
+        <v>520252</v>
       </c>
       <c r="R88" t="n">
-        <v>7035342</v>
+        <v>7035576</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10856,6 +10901,11 @@
           <t>2025-02-23</t>
         </is>
       </c>
+      <c r="AC88" t="inlineStr">
+        <is>
+          <t>På björk</t>
+        </is>
+      </c>
       <c r="AD88" t="b">
         <v>0</v>
       </c>
@@ -10864,31 +10914,6 @@
       </c>
       <c r="AG88" t="b">
         <v>0</v>
-      </c>
-      <c r="AH88" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ88" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK88" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM88" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO88" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
@@ -10905,10 +10930,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>122721333</v>
+        <v>122715953</v>
       </c>
       <c r="B89" t="n">
-        <v>78766</v>
+        <v>79848</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -10921,37 +10946,37 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Spejkmyren, Spejkmyren, Jmt</t>
+          <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>519906</v>
+        <v>520254</v>
       </c>
       <c r="R89" t="n">
-        <v>7035389</v>
+        <v>7035555</v>
       </c>
       <c r="S89" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -10983,11 +11008,6 @@
           <t>2025-02-23</t>
         </is>
       </c>
-      <c r="AC89" t="inlineStr">
-        <is>
-          <t>Ymnigt på flera granar.</t>
-        </is>
-      </c>
       <c r="AD89" t="b">
         <v>0</v>
       </c>
@@ -10996,31 +11016,6 @@
       </c>
       <c r="AG89" t="b">
         <v>0</v>
-      </c>
-      <c r="AH89" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ89" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK89" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM89" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO89" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
@@ -11037,10 +11032,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>122715790</v>
+        <v>122717343</v>
       </c>
       <c r="B90" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -11053,39 +11048,39 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
-      <c r="K90" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Finnbodarna, Finnbodarna, Jmt</t>
+          <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>520267</v>
+        <v>520034</v>
       </c>
       <c r="R90" t="n">
-        <v>7035581</v>
+        <v>7035339</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -11118,6 +11113,11 @@
       <c r="AA90" t="inlineStr">
         <is>
           <t>2025-02-23</t>
+        </is>
+      </c>
+      <c r="AC90" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD90" t="b">

--- a/artfynd/A 1625-2025 artfynd.xlsx
+++ b/artfynd/A 1625-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122715801</v>
+        <v>122721035</v>
       </c>
       <c r="B2" t="n">
-        <v>79848</v>
+        <v>78766</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,37 +691,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Finnbodarna, Finnbodarna, Jmt</t>
+          <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>520266</v>
+        <v>519897</v>
       </c>
       <c r="R2" t="n">
-        <v>7035582</v>
+        <v>7035374</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -761,6 +761,31 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>garnlav</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Alectoria sarmentosa</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -777,10 +802,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122721035</v>
+        <v>122715841</v>
       </c>
       <c r="B3" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,37 +818,42 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Spejkmyren, Spejkmyren, Jmt</t>
+          <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>519897</v>
+        <v>520229</v>
       </c>
       <c r="R3" t="n">
-        <v>7035374</v>
+        <v>7035608</v>
       </c>
       <c r="S3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -855,6 +885,11 @@
           <t>2025-02-23</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>På en björk.</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -871,22 +906,22 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>garnlav</t>
+          <t>björkar</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Betula</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Branch on living tree # Alectoria sarmentosa</t>
+          <t>Bark on living woody plant # Betula</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -904,7 +939,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122715841</v>
+        <v>122715779</v>
       </c>
       <c r="B4" t="n">
         <v>79847</v>
@@ -949,10 +984,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>520229</v>
+        <v>520223</v>
       </c>
       <c r="R4" t="n">
-        <v>7035608</v>
+        <v>7035609</v>
       </c>
       <c r="S4" t="n">
         <v>9</v>
@@ -987,11 +1022,6 @@
           <t>2025-02-23</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>På en björk.</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1008,12 +1038,12 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>björkar</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
@@ -1023,7 +1053,7 @@
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Betula</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1041,7 +1071,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122715779</v>
+        <v>122715949</v>
       </c>
       <c r="B5" t="n">
         <v>79847</v>
@@ -1075,24 +1105,19 @@
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>520223</v>
+        <v>520254</v>
       </c>
       <c r="R5" t="n">
-        <v>7035609</v>
+        <v>7035555</v>
       </c>
       <c r="S5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1132,31 +1157,6 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1173,10 +1173,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122715949</v>
+        <v>122715801</v>
       </c>
       <c r="B6" t="n">
-        <v>79847</v>
+        <v>79848</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1189,21 +1189,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1213,10 +1213,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>520254</v>
+        <v>520266</v>
       </c>
       <c r="R6" t="n">
-        <v>7035555</v>
+        <v>7035582</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1616,10 +1616,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122720548</v>
+        <v>122716682</v>
       </c>
       <c r="B10" t="n">
-        <v>90970</v>
+        <v>57631</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1632,34 +1632,43 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>103021</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>519847</v>
+        <v>520101</v>
       </c>
       <c r="R10" t="n">
-        <v>7035432</v>
+        <v>7035453</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1718,10 +1727,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122720629</v>
+        <v>122720548</v>
       </c>
       <c r="B11" t="n">
-        <v>78766</v>
+        <v>90970</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1734,21 +1743,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1758,10 +1767,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>519935</v>
+        <v>519847</v>
       </c>
       <c r="R11" t="n">
-        <v>7035246</v>
+        <v>7035432</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1796,11 +1805,6 @@
           <t>2025-02-23</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1809,31 +1813,6 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
-      </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -1850,10 +1829,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122716673</v>
+        <v>122720629</v>
       </c>
       <c r="B12" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1866,39 +1845,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>520108</v>
+        <v>519935</v>
       </c>
       <c r="R12" t="n">
-        <v>7035462</v>
+        <v>7035246</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1935,7 +1909,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1946,6 +1920,31 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -2196,10 +2195,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122716682</v>
+        <v>122716673</v>
       </c>
       <c r="B15" t="n">
-        <v>57631</v>
+        <v>57478</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2212,31 +2211,27 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
-          <t>par i lämplig häckbiotop</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2245,10 +2240,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>520101</v>
+        <v>520108</v>
       </c>
       <c r="R15" t="n">
-        <v>7035453</v>
+        <v>7035462</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2281,6 +2276,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-02-23</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2307,10 +2307,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122719371</v>
+        <v>122717359</v>
       </c>
       <c r="B16" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2323,21 +2323,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2347,13 +2347,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>519943</v>
+        <v>520030</v>
       </c>
       <c r="R16" t="n">
-        <v>7035270</v>
+        <v>7035341</v>
       </c>
       <c r="S16" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2393,31 +2393,6 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
-      </c>
-      <c r="AH16" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
@@ -2434,10 +2409,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122715757</v>
+        <v>122715870</v>
       </c>
       <c r="B17" t="n">
-        <v>78766</v>
+        <v>79848</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2450,21 +2425,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2474,10 +2449,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>520234</v>
+        <v>520265</v>
       </c>
       <c r="R17" t="n">
-        <v>7035595</v>
+        <v>7035574</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2512,11 +2487,6 @@
           <t>2025-02-23</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
@@ -2525,31 +2495,6 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
-      </c>
-      <c r="AH17" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
@@ -2566,10 +2511,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122717359</v>
+        <v>122716392</v>
       </c>
       <c r="B18" t="n">
-        <v>79847</v>
+        <v>79848</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2582,37 +2527,42 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Spejkmyren, Spejkmyren, Jmt</t>
+          <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>520030</v>
+        <v>520385</v>
       </c>
       <c r="R18" t="n">
-        <v>7035341</v>
+        <v>7035518</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2644,6 +2594,11 @@
           <t>2025-02-23</t>
         </is>
       </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>På gran intill en gammal sälg.</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -2652,6 +2607,31 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM18" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2668,10 +2648,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122715870</v>
+        <v>122719371</v>
       </c>
       <c r="B19" t="n">
-        <v>79848</v>
+        <v>78766</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2684,37 +2664,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Finnbodarna, Finnbodarna, Jmt</t>
+          <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>520265</v>
+        <v>519943</v>
       </c>
       <c r="R19" t="n">
-        <v>7035574</v>
+        <v>7035270</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2754,6 +2734,31 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM19" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -2770,10 +2775,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122716392</v>
+        <v>122715757</v>
       </c>
       <c r="B20" t="n">
-        <v>79848</v>
+        <v>78766</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2786,42 +2791,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>520385</v>
+        <v>520234</v>
       </c>
       <c r="R20" t="n">
-        <v>7035518</v>
+        <v>7035595</v>
       </c>
       <c r="S20" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2855,7 +2855,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>På gran intill en gammal sälg.</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3573,10 +3573,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122717873</v>
+        <v>122716427</v>
       </c>
       <c r="B27" t="n">
-        <v>79847</v>
+        <v>78767</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3589,42 +3589,37 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6458</v>
+        <v>230405</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Spejkmyren, Spejkmyren, Jmt</t>
+          <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>520033</v>
+        <v>520388</v>
       </c>
       <c r="R27" t="n">
-        <v>7035301</v>
+        <v>7035490</v>
       </c>
       <c r="S27" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3656,6 +3651,11 @@
           <t>2025-02-23</t>
         </is>
       </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
+        </is>
+      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
@@ -3672,22 +3672,22 @@
       </c>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT27" t="inlineStr"/>
@@ -3705,10 +3705,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122719829</v>
+        <v>122717873</v>
       </c>
       <c r="B28" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3721,27 +3721,27 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -3750,13 +3750,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>519930</v>
+        <v>520033</v>
       </c>
       <c r="R28" t="n">
-        <v>7035181</v>
+        <v>7035301</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3788,11 +3788,6 @@
           <t>2025-02-23</t>
         </is>
       </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
@@ -3801,6 +3796,31 @@
       </c>
       <c r="AG28" t="b">
         <v>0</v>
+      </c>
+      <c r="AH28" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM28" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
@@ -3817,10 +3837,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122716427</v>
+        <v>122719829</v>
       </c>
       <c r="B29" t="n">
-        <v>78767</v>
+        <v>57478</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3833,37 +3853,42 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>230405</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Finnbodarna, Finnbodarna, Jmt</t>
+          <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>520388</v>
+        <v>519930</v>
       </c>
       <c r="R29" t="n">
-        <v>7035490</v>
+        <v>7035181</v>
       </c>
       <c r="S29" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3897,7 +3922,7 @@
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3908,31 +3933,6 @@
       </c>
       <c r="AG29" t="b">
         <v>0</v>
-      </c>
-      <c r="AH29" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ29" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK29" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM29" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO29" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
@@ -4407,10 +4407,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122716801</v>
+        <v>122715502</v>
       </c>
       <c r="B34" t="n">
-        <v>57631</v>
+        <v>78766</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4423,46 +4423,42 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>par i lämplig häckbiotop</t>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Spejkmyren, Spejkmyren, Jmt</t>
+          <t>Djupmyren, Djupmyren, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>520083</v>
+        <v>520110</v>
       </c>
       <c r="R34" t="n">
-        <v>7035403</v>
+        <v>7035585</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4494,6 +4490,11 @@
           <t>2025-02-23</t>
         </is>
       </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Gott om långväxt garnlav på många granar. Vissa bålar är här fertila.</t>
+        </is>
+      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
@@ -4502,6 +4503,31 @@
       </c>
       <c r="AG34" t="b">
         <v>0</v>
+      </c>
+      <c r="AH34" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ34" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK34" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM34" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO34" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
@@ -4620,10 +4646,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122715502</v>
+        <v>122716801</v>
       </c>
       <c r="B36" t="n">
-        <v>78766</v>
+        <v>57631</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4636,42 +4662,46 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Djupmyren, Djupmyren, Jmt</t>
+          <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>520110</v>
+        <v>520083</v>
       </c>
       <c r="R36" t="n">
-        <v>7035585</v>
+        <v>7035403</v>
       </c>
       <c r="S36" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4703,11 +4733,6 @@
           <t>2025-02-23</t>
         </is>
       </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Gott om långväxt garnlav på många granar. Vissa bålar är här fertila.</t>
-        </is>
-      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
@@ -4716,31 +4741,6 @@
       </c>
       <c r="AG36" t="b">
         <v>0</v>
-      </c>
-      <c r="AH36" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ36" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK36" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM36" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO36" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
@@ -4757,10 +4757,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122716964</v>
+        <v>122715569</v>
       </c>
       <c r="B37" t="n">
-        <v>90970</v>
+        <v>78766</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4773,34 +4773,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Spejkmyren, Spejkmyren, Jmt</t>
+          <t>Djupmyren, Djupmyren, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
         <v>520115</v>
       </c>
       <c r="R37" t="n">
-        <v>7035402</v>
+        <v>7035562</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4835,6 +4835,11 @@
           <t>2025-02-23</t>
         </is>
       </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
+        </is>
+      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
@@ -4843,6 +4848,31 @@
       </c>
       <c r="AG37" t="b">
         <v>0</v>
+      </c>
+      <c r="AH37" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ37" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK37" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM37" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO37" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
@@ -4859,10 +4889,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122721463</v>
+        <v>122716964</v>
       </c>
       <c r="B38" t="n">
-        <v>78766</v>
+        <v>90970</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4875,21 +4905,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4899,10 +4929,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>519841</v>
+        <v>520115</v>
       </c>
       <c r="R38" t="n">
-        <v>7035417</v>
+        <v>7035402</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4937,11 +4967,6 @@
           <t>2025-02-23</t>
         </is>
       </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
-        </is>
-      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
@@ -4950,31 +4975,6 @@
       </c>
       <c r="AG38" t="b">
         <v>0</v>
-      </c>
-      <c r="AH38" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ38" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK38" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM38" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO38" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
@@ -4991,7 +4991,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122715569</v>
+        <v>122721463</v>
       </c>
       <c r="B39" t="n">
         <v>78766</v>
@@ -5027,14 +5027,14 @@
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Djupmyren, Djupmyren, Jmt</t>
+          <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>520115</v>
+        <v>519841</v>
       </c>
       <c r="R39" t="n">
-        <v>7035562</v>
+        <v>7035417</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -10686,10 +10686,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>122717616</v>
+        <v>122717343</v>
       </c>
       <c r="B87" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -10702,34 +10702,39 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P87" t="inlineStr">
         <is>
           <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>520019</v>
+        <v>520034</v>
       </c>
       <c r="R87" t="n">
-        <v>7035352</v>
+        <v>7035339</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10766,7 +10771,7 @@
       </c>
       <c r="AC87" t="inlineStr">
         <is>
-          <t>Rikligt.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10777,31 +10782,6 @@
       </c>
       <c r="AG87" t="b">
         <v>0</v>
-      </c>
-      <c r="AH87" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ87" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK87" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM87" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO87" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
@@ -10818,10 +10798,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>122715775</v>
+        <v>122717616</v>
       </c>
       <c r="B88" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -10834,39 +10814,34 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
-      <c r="K88" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Finnbodarna, Finnbodarna, Jmt</t>
+          <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>520252</v>
+        <v>520019</v>
       </c>
       <c r="R88" t="n">
-        <v>7035576</v>
+        <v>7035352</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10903,7 +10878,7 @@
       </c>
       <c r="AC88" t="inlineStr">
         <is>
-          <t>På björk</t>
+          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10914,6 +10889,31 @@
       </c>
       <c r="AG88" t="b">
         <v>0</v>
+      </c>
+      <c r="AH88" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ88" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK88" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM88" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO88" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
@@ -10930,10 +10930,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>122715953</v>
+        <v>122715775</v>
       </c>
       <c r="B89" t="n">
-        <v>79848</v>
+        <v>79847</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -10946,34 +10946,39 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P89" t="inlineStr">
         <is>
           <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>520254</v>
+        <v>520252</v>
       </c>
       <c r="R89" t="n">
-        <v>7035555</v>
+        <v>7035576</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -11006,6 +11011,11 @@
       <c r="AA89" t="inlineStr">
         <is>
           <t>2025-02-23</t>
+        </is>
+      </c>
+      <c r="AC89" t="inlineStr">
+        <is>
+          <t>På björk</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -11032,10 +11042,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>122717343</v>
+        <v>122715953</v>
       </c>
       <c r="B90" t="n">
-        <v>57478</v>
+        <v>79848</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -11048,39 +11058,34 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
-      <c r="M90" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Spejkmyren, Spejkmyren, Jmt</t>
+          <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>520034</v>
+        <v>520254</v>
       </c>
       <c r="R90" t="n">
-        <v>7035339</v>
+        <v>7035555</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -11113,11 +11118,6 @@
       <c r="AA90" t="inlineStr">
         <is>
           <t>2025-02-23</t>
-        </is>
-      </c>
-      <c r="AC90" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD90" t="b">

--- a/artfynd/A 1625-2025 artfynd.xlsx
+++ b/artfynd/A 1625-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122721035</v>
+        <v>122715801</v>
       </c>
       <c r="B2" t="n">
-        <v>78766</v>
+        <v>79848</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,37 +691,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Spejkmyren, Spejkmyren, Jmt</t>
+          <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>519897</v>
+        <v>520266</v>
       </c>
       <c r="R2" t="n">
-        <v>7035374</v>
+        <v>7035582</v>
       </c>
       <c r="S2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -761,31 +761,6 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>garnlav</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Alectoria sarmentosa</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -802,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122715841</v>
+        <v>122721035</v>
       </c>
       <c r="B3" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -818,42 +793,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Finnbodarna, Finnbodarna, Jmt</t>
+          <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>520229</v>
+        <v>519897</v>
       </c>
       <c r="R3" t="n">
-        <v>7035608</v>
+        <v>7035374</v>
       </c>
       <c r="S3" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -885,11 +855,6 @@
           <t>2025-02-23</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>På en björk.</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -906,22 +871,22 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>björkar</t>
+          <t>garnlav</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Betula</t>
+          <t>Branch on living tree # Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -939,7 +904,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122715779</v>
+        <v>122715841</v>
       </c>
       <c r="B4" t="n">
         <v>79847</v>
@@ -984,10 +949,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>520223</v>
+        <v>520229</v>
       </c>
       <c r="R4" t="n">
-        <v>7035609</v>
+        <v>7035608</v>
       </c>
       <c r="S4" t="n">
         <v>9</v>
@@ -1022,6 +987,11 @@
           <t>2025-02-23</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>På en björk.</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1038,12 +1008,12 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>björkar</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Betula</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
@@ -1053,7 +1023,7 @@
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Bark on living woody plant # Betula</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1071,7 +1041,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122715949</v>
+        <v>122715779</v>
       </c>
       <c r="B5" t="n">
         <v>79847</v>
@@ -1105,19 +1075,24 @@
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>520254</v>
+        <v>520223</v>
       </c>
       <c r="R5" t="n">
-        <v>7035555</v>
+        <v>7035609</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1157,6 +1132,31 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1173,10 +1173,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122715801</v>
+        <v>122715949</v>
       </c>
       <c r="B6" t="n">
-        <v>79848</v>
+        <v>79847</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1189,21 +1189,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1213,10 +1213,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>520266</v>
+        <v>520254</v>
       </c>
       <c r="R6" t="n">
-        <v>7035582</v>
+        <v>7035555</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -3949,10 +3949,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122715669</v>
+        <v>122721333</v>
       </c>
       <c r="B30" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3965,42 +3965,37 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Finnbodarna, Finnbodarna, Jmt</t>
+          <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>520221</v>
+        <v>519906</v>
       </c>
       <c r="R30" t="n">
-        <v>7035600</v>
+        <v>7035389</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4032,6 +4027,11 @@
           <t>2025-02-23</t>
         </is>
       </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Ymnigt på flera granar.</t>
+        </is>
+      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
@@ -4040,6 +4040,31 @@
       </c>
       <c r="AG30" t="b">
         <v>0</v>
+      </c>
+      <c r="AH30" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM30" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
@@ -4056,10 +4081,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122719875</v>
+        <v>122715677</v>
       </c>
       <c r="B31" t="n">
-        <v>57478</v>
+        <v>79848</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4072,39 +4097,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Spejkmyren, Spejkmyren, Jmt</t>
+          <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>519983</v>
+        <v>520221</v>
       </c>
       <c r="R31" t="n">
-        <v>7035206</v>
+        <v>7035600</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4141,7 +4161,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4168,10 +4188,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122721333</v>
+        <v>122719875</v>
       </c>
       <c r="B32" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4184,37 +4204,42 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>519906</v>
+        <v>519983</v>
       </c>
       <c r="R32" t="n">
-        <v>7035389</v>
+        <v>7035206</v>
       </c>
       <c r="S32" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4248,7 +4273,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Ymnigt på flera granar.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4259,31 +4284,6 @@
       </c>
       <c r="AG32" t="b">
         <v>0</v>
-      </c>
-      <c r="AH32" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ32" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK32" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM32" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO32" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
@@ -4300,10 +4300,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122715677</v>
+        <v>122715669</v>
       </c>
       <c r="B33" t="n">
-        <v>79848</v>
+        <v>79847</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4316,24 +4316,29 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Finnbodarna, Finnbodarna, Jmt</t>
@@ -4376,11 +4381,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-02-23</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>På gran</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -5967,7 +5967,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122720823</v>
+        <v>122717636</v>
       </c>
       <c r="B47" t="n">
         <v>57478</v>
@@ -6000,24 +6000,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L47" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="M47" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
@@ -6026,10 +6012,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>519842</v>
+        <v>519970</v>
       </c>
       <c r="R47" t="n">
-        <v>7035388</v>
+        <v>7035297</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6066,7 +6052,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Trummande</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6093,7 +6079,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122717636</v>
+        <v>122719554</v>
       </c>
       <c r="B48" t="n">
         <v>57478</v>
@@ -6132,16 +6118,21 @@
           <t>äldre spår</t>
         </is>
       </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>519970</v>
+        <v>519981</v>
       </c>
       <c r="R48" t="n">
-        <v>7035297</v>
+        <v>7035221</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6178,7 +6169,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Äldre ringhack som bedöms vara 5 - 10 år gamla.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6189,6 +6180,31 @@
       </c>
       <c r="AG48" t="b">
         <v>0</v>
+      </c>
+      <c r="AH48" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ48" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK48" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM48" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO48" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
@@ -6205,7 +6221,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122719554</v>
+        <v>122720823</v>
       </c>
       <c r="B49" t="n">
         <v>57478</v>
@@ -6238,15 +6254,24 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I49" t="inlineStr"/>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N49" t="inlineStr">
-        <is>
-          <t>observerad</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
@@ -6255,10 +6280,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>519981</v>
+        <v>519842</v>
       </c>
       <c r="R49" t="n">
-        <v>7035221</v>
+        <v>7035388</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6295,7 +6320,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Äldre ringhack som bedöms vara 5 - 10 år gamla.</t>
+          <t>Trummande</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6306,31 +6331,6 @@
       </c>
       <c r="AG49" t="b">
         <v>0</v>
-      </c>
-      <c r="AH49" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ49" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK49" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM49" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO49" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
@@ -7734,10 +7734,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122720558</v>
+        <v>122715778</v>
       </c>
       <c r="B62" t="n">
-        <v>57494</v>
+        <v>79847</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7750,39 +7750,39 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Spejkmyren, Spejkmyren, Jmt</t>
+          <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>519949</v>
+        <v>520259</v>
       </c>
       <c r="R62" t="n">
-        <v>7035254</v>
+        <v>7035574</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7817,11 +7817,6 @@
           <t>2025-02-23</t>
         </is>
       </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>Äldre hackspår i stambasen.</t>
-        </is>
-      </c>
       <c r="AD62" t="b">
         <v>0</v>
       </c>
@@ -7830,31 +7825,6 @@
       </c>
       <c r="AG62" t="b">
         <v>0</v>
-      </c>
-      <c r="AH62" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ62" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK62" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM62" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO62" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
@@ -7871,10 +7841,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122715778</v>
+        <v>122720558</v>
       </c>
       <c r="B63" t="n">
-        <v>79847</v>
+        <v>57494</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7887,39 +7857,39 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="K63" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Finnbodarna, Finnbodarna, Jmt</t>
+          <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>520259</v>
+        <v>519949</v>
       </c>
       <c r="R63" t="n">
-        <v>7035574</v>
+        <v>7035254</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7954,6 +7924,11 @@
           <t>2025-02-23</t>
         </is>
       </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Äldre hackspår i stambasen.</t>
+        </is>
+      </c>
       <c r="AD63" t="b">
         <v>0</v>
       </c>
@@ -7962,6 +7937,31 @@
       </c>
       <c r="AG63" t="b">
         <v>0</v>
+      </c>
+      <c r="AH63" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ63" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK63" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM63" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO63" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
@@ -7978,10 +7978,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122716160</v>
+        <v>122716645</v>
       </c>
       <c r="B64" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7994,34 +7994,39 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Finnbodarna, Finnbodarna, Jmt</t>
+          <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>520349</v>
+        <v>520129</v>
       </c>
       <c r="R64" t="n">
-        <v>7035517</v>
+        <v>7035444</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -8056,6 +8061,11 @@
           <t>2025-02-23</t>
         </is>
       </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD64" t="b">
         <v>0</v>
       </c>
@@ -8064,31 +8074,6 @@
       </c>
       <c r="AG64" t="b">
         <v>0</v>
-      </c>
-      <c r="AH64" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ64" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK64" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM64" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO64" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
@@ -8105,10 +8090,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122716757</v>
+        <v>122718013</v>
       </c>
       <c r="B65" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -8121,37 +8106,42 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Finnbodarna, Finnbodarna, Jmt</t>
+          <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>520316</v>
+        <v>519948</v>
       </c>
       <c r="R65" t="n">
-        <v>7035491</v>
+        <v>7035313</v>
       </c>
       <c r="S65" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -8183,6 +8173,11 @@
           <t>2025-02-23</t>
         </is>
       </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD65" t="b">
         <v>0</v>
       </c>
@@ -8191,31 +8186,6 @@
       </c>
       <c r="AG65" t="b">
         <v>0</v>
-      </c>
-      <c r="AH65" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ65" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK65" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM65" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO65" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
@@ -8232,7 +8202,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122716645</v>
+        <v>122719648</v>
       </c>
       <c r="B66" t="n">
         <v>57478</v>
@@ -8277,10 +8247,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>520129</v>
+        <v>519939</v>
       </c>
       <c r="R66" t="n">
-        <v>7035444</v>
+        <v>7035194</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -8344,10 +8314,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>122718013</v>
+        <v>122716160</v>
       </c>
       <c r="B67" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8360,39 +8330,34 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Spejkmyren, Spejkmyren, Jmt</t>
+          <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>519948</v>
+        <v>520349</v>
       </c>
       <c r="R67" t="n">
-        <v>7035313</v>
+        <v>7035517</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8427,11 +8392,6 @@
           <t>2025-02-23</t>
         </is>
       </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD67" t="b">
         <v>0</v>
       </c>
@@ -8440,6 +8400,31 @@
       </c>
       <c r="AG67" t="b">
         <v>0</v>
+      </c>
+      <c r="AH67" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ67" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK67" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM67" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO67" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
@@ -8456,10 +8441,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>122719648</v>
+        <v>122716757</v>
       </c>
       <c r="B68" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8472,42 +8457,37 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Spejkmyren, Spejkmyren, Jmt</t>
+          <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>519939</v>
+        <v>520316</v>
       </c>
       <c r="R68" t="n">
-        <v>7035194</v>
+        <v>7035491</v>
       </c>
       <c r="S68" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8539,11 +8519,6 @@
           <t>2025-02-23</t>
         </is>
       </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD68" t="b">
         <v>0</v>
       </c>
@@ -8552,6 +8527,31 @@
       </c>
       <c r="AG68" t="b">
         <v>0</v>
+      </c>
+      <c r="AH68" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ68" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK68" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM68" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO68" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">

--- a/artfynd/A 1625-2025 artfynd.xlsx
+++ b/artfynd/A 1625-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122715801</v>
+        <v>122719614</v>
       </c>
       <c r="B2" t="n">
-        <v>79848</v>
+        <v>57478</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,39 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Finnbodarna, Finnbodarna, Jmt</t>
+          <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>520266</v>
+        <v>519930</v>
       </c>
       <c r="R2" t="n">
-        <v>7035582</v>
+        <v>7035181</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,6 +756,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-02-23</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Färska och äldre ringhack på samma gran.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,7 +787,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122721035</v>
+        <v>122717616</v>
       </c>
       <c r="B3" t="n">
         <v>78766</v>
@@ -817,13 +827,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>519897</v>
+        <v>520019</v>
       </c>
       <c r="R3" t="n">
-        <v>7035374</v>
+        <v>7035352</v>
       </c>
       <c r="S3" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -855,6 +865,11 @@
           <t>2025-02-23</t>
         </is>
       </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Rikligt.</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -871,12 +886,12 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>garnlav</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
@@ -886,7 +901,7 @@
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>Branch on living tree # Alectoria sarmentosa</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -904,10 +919,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122715841</v>
+        <v>122717284</v>
       </c>
       <c r="B4" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -920,39 +935,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Finnbodarna, Finnbodarna, Jmt</t>
+          <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>520229</v>
+        <v>520031</v>
       </c>
       <c r="R4" t="n">
-        <v>7035608</v>
+        <v>7035353</v>
       </c>
       <c r="S4" t="n">
         <v>9</v>
@@ -989,7 +999,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>På en björk.</t>
+          <t>Långväxta bålar på flertalet granar.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1008,22 +1018,22 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>björkar</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Betula</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1041,10 +1051,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122715779</v>
+        <v>122720469</v>
       </c>
       <c r="B5" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1057,42 +1067,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Finnbodarna, Finnbodarna, Jmt</t>
+          <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>520223</v>
+        <v>519996</v>
       </c>
       <c r="R5" t="n">
-        <v>7035609</v>
+        <v>7035241</v>
       </c>
       <c r="S5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1140,22 +1145,22 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1173,10 +1178,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122715949</v>
+        <v>122717952</v>
       </c>
       <c r="B6" t="n">
-        <v>79847</v>
+        <v>57494</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1189,34 +1194,43 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Finnbodarna, Finnbodarna, Jmt</t>
+          <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>520254</v>
+        <v>519951</v>
       </c>
       <c r="R6" t="n">
-        <v>7035555</v>
+        <v>7035320</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1275,10 +1289,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122717446</v>
+        <v>122715870</v>
       </c>
       <c r="B7" t="n">
-        <v>90970</v>
+        <v>79848</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1291,34 +1305,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>2081</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Spejkmyren, Spejkmyren, Jmt</t>
+          <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>520006</v>
+        <v>520265</v>
       </c>
       <c r="R7" t="n">
-        <v>7035303</v>
+        <v>7035574</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1377,10 +1391,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122720065</v>
+        <v>122715573</v>
       </c>
       <c r="B8" t="n">
-        <v>78766</v>
+        <v>79848</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1393,37 +1407,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Spejkmyren, Spejkmyren, Jmt</t>
+          <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>520062</v>
+        <v>520214</v>
       </c>
       <c r="R8" t="n">
-        <v>7035232</v>
+        <v>7035583</v>
       </c>
       <c r="S8" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1463,31 +1477,6 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1504,7 +1493,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122716293</v>
+        <v>122719648</v>
       </c>
       <c r="B9" t="n">
         <v>57478</v>
@@ -1545,14 +1534,14 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Finnbodarna, Hammerdal, Finnbodarna, Hammerdal, Jmt</t>
+          <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>520249</v>
+        <v>519939</v>
       </c>
       <c r="R9" t="n">
-        <v>7035364</v>
+        <v>7035194</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1616,10 +1605,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122716682</v>
+        <v>122719554</v>
       </c>
       <c r="B10" t="n">
-        <v>57631</v>
+        <v>57478</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1632,31 +1621,32 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>par i lämplig häckbiotop</t>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1665,10 +1655,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>520101</v>
+        <v>519981</v>
       </c>
       <c r="R10" t="n">
-        <v>7035453</v>
+        <v>7035221</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1703,6 +1693,11 @@
           <t>2025-02-23</t>
         </is>
       </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Äldre ringhack som bedöms vara 5 - 10 år gamla.</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1711,6 +1706,31 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1727,10 +1747,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122720548</v>
+        <v>122717343</v>
       </c>
       <c r="B11" t="n">
-        <v>90970</v>
+        <v>57478</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1743,34 +1763,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>519847</v>
+        <v>520034</v>
       </c>
       <c r="R11" t="n">
-        <v>7035432</v>
+        <v>7035339</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1803,6 +1828,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-02-23</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1829,10 +1859,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122720629</v>
+        <v>122719979</v>
       </c>
       <c r="B12" t="n">
-        <v>78766</v>
+        <v>57631</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1845,34 +1875,43 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>519935</v>
+        <v>519946</v>
       </c>
       <c r="R12" t="n">
-        <v>7035246</v>
+        <v>7035240</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1907,11 +1946,6 @@
           <t>2025-02-23</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -1920,31 +1954,6 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AH12" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -1961,10 +1970,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122715849</v>
+        <v>122717446</v>
       </c>
       <c r="B13" t="n">
-        <v>79876</v>
+        <v>90970</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1973,38 +1982,38 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6462</v>
+        <v>5432</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Finnbodarna, Finnbodarna, Jmt</t>
+          <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>520268</v>
+        <v>520006</v>
       </c>
       <c r="R13" t="n">
-        <v>7035575</v>
+        <v>7035303</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2063,7 +2072,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122715795</v>
+        <v>122715756</v>
       </c>
       <c r="B14" t="n">
         <v>79847</v>
@@ -2103,13 +2112,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>520214</v>
+        <v>520256</v>
       </c>
       <c r="R14" t="n">
-        <v>7035599</v>
+        <v>7035593</v>
       </c>
       <c r="S14" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2141,11 +2150,6 @@
           <t>2025-02-23</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>På en klen gran intill en lunglavssälg.</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2154,31 +2158,6 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
-      </c>
-      <c r="AH14" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ14" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK14" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
@@ -2195,10 +2174,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122716673</v>
+        <v>122716295</v>
       </c>
       <c r="B15" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2211,39 +2190,39 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Spejkmyren, Spejkmyren, Jmt</t>
+          <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>520108</v>
+        <v>520378</v>
       </c>
       <c r="R15" t="n">
-        <v>7035462</v>
+        <v>7035512</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2280,7 +2259,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ymnig påväxt på en grovbarkad gammal sälg. Fertila bålar med apothecier.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2291,6 +2270,31 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM15" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
@@ -2307,10 +2311,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122717359</v>
+        <v>122716645</v>
       </c>
       <c r="B16" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2323,34 +2327,39 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>520030</v>
+        <v>520129</v>
       </c>
       <c r="R16" t="n">
-        <v>7035341</v>
+        <v>7035444</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2383,6 +2392,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-02-23</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2409,10 +2423,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122715870</v>
+        <v>122720548</v>
       </c>
       <c r="B17" t="n">
-        <v>79848</v>
+        <v>90970</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2425,34 +2439,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2081</v>
+        <v>5432</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Finnbodarna, Finnbodarna, Jmt</t>
+          <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>520265</v>
+        <v>519847</v>
       </c>
       <c r="R17" t="n">
-        <v>7035574</v>
+        <v>7035432</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2511,10 +2525,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122716392</v>
+        <v>122719697</v>
       </c>
       <c r="B18" t="n">
-        <v>79848</v>
+        <v>78766</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2527,42 +2541,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Finnbodarna, Finnbodarna, Jmt</t>
+          <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>520385</v>
+        <v>520026</v>
       </c>
       <c r="R18" t="n">
-        <v>7035518</v>
+        <v>7035233</v>
       </c>
       <c r="S18" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2592,11 +2601,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-02-23</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>På gran intill en gammal sälg.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2648,7 +2652,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122719371</v>
+        <v>122720869</v>
       </c>
       <c r="B19" t="n">
         <v>78766</v>
@@ -2688,13 +2692,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>519943</v>
+        <v>519960</v>
       </c>
       <c r="R19" t="n">
-        <v>7035270</v>
+        <v>7035342</v>
       </c>
       <c r="S19" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2775,7 +2779,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122715757</v>
+        <v>122720629</v>
       </c>
       <c r="B20" t="n">
         <v>78766</v>
@@ -2811,14 +2815,14 @@
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Finnbodarna, Finnbodarna, Jmt</t>
+          <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>520234</v>
+        <v>519935</v>
       </c>
       <c r="R20" t="n">
-        <v>7035595</v>
+        <v>7035246</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2907,10 +2911,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122717294</v>
+        <v>122715569</v>
       </c>
       <c r="B21" t="n">
-        <v>90970</v>
+        <v>78766</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2923,34 +2927,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Spejkmyren, Spejkmyren, Jmt</t>
+          <t>Djupmyren, Djupmyren, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>520013</v>
+        <v>520115</v>
       </c>
       <c r="R21" t="n">
-        <v>7035340</v>
+        <v>7035562</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2985,6 +2989,11 @@
           <t>2025-02-23</t>
         </is>
       </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
+        </is>
+      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
@@ -2993,6 +3002,31 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM21" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -3009,10 +3043,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122720869</v>
+        <v>122716392</v>
       </c>
       <c r="B22" t="n">
-        <v>78766</v>
+        <v>79848</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3025,37 +3059,42 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Spejkmyren, Spejkmyren, Jmt</t>
+          <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>519960</v>
+        <v>520385</v>
       </c>
       <c r="R22" t="n">
-        <v>7035342</v>
+        <v>7035518</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3085,6 +3124,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-02-23</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>På gran intill en gammal sälg.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3136,7 +3180,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122715571</v>
+        <v>122716234</v>
       </c>
       <c r="B23" t="n">
         <v>79847</v>
@@ -3176,10 +3220,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>520216</v>
+        <v>520362</v>
       </c>
       <c r="R23" t="n">
-        <v>7035583</v>
+        <v>7035500</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3214,6 +3258,11 @@
           <t>2025-02-23</t>
         </is>
       </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>På en klen gran intill en gammal sälg med lunglav.</t>
+        </is>
+      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
@@ -3222,6 +3271,31 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM23" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
@@ -3238,7 +3312,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122715780</v>
+        <v>122715978</v>
       </c>
       <c r="B24" t="n">
         <v>79847</v>
@@ -3272,16 +3346,21 @@
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>520259</v>
+        <v>520243</v>
       </c>
       <c r="R24" t="n">
-        <v>7035569</v>
+        <v>7035552</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3314,11 +3393,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-02-23</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>På björk</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3345,10 +3419,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122717989</v>
+        <v>122716443</v>
       </c>
       <c r="B25" t="n">
-        <v>57494</v>
+        <v>78766</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3361,43 +3435,48 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Spejkmyren, Spejkmyren, Jmt</t>
+          <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>519951</v>
+        <v>520251</v>
       </c>
       <c r="R25" t="n">
-        <v>7035320</v>
+        <v>7035394</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3434,7 +3513,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Trummande</t>
+          <t>Garnlavsrikt</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3461,7 +3540,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122720368</v>
+        <v>122720427</v>
       </c>
       <c r="B26" t="n">
         <v>57478</v>
@@ -3497,7 +3576,7 @@
       <c r="I26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3506,10 +3585,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>519852</v>
+        <v>519846</v>
       </c>
       <c r="R26" t="n">
-        <v>7035392</v>
+        <v>7035407</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3573,10 +3652,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122716427</v>
+        <v>122720327</v>
       </c>
       <c r="B27" t="n">
-        <v>78767</v>
+        <v>57478</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3589,37 +3668,42 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>230405</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Finnbodarna, Finnbodarna, Jmt</t>
+          <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>520388</v>
+        <v>519838</v>
       </c>
       <c r="R27" t="n">
-        <v>7035490</v>
+        <v>7035393</v>
       </c>
       <c r="S27" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3653,7 +3737,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3664,31 +3748,6 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
-      </c>
-      <c r="AH27" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ27" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK27" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM27" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO27" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
@@ -3705,10 +3764,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122717873</v>
+        <v>122716387</v>
       </c>
       <c r="B28" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3721,42 +3780,42 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>med soral</t>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Spejkmyren, Spejkmyren, Jmt</t>
+          <t>Finnbodarna, Hammerdal, Finnbodarna, Hammerdal, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>520033</v>
+        <v>520278</v>
       </c>
       <c r="R28" t="n">
-        <v>7035301</v>
+        <v>7035397</v>
       </c>
       <c r="S28" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3788,6 +3847,11 @@
           <t>2025-02-23</t>
         </is>
       </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
@@ -3796,31 +3860,6 @@
       </c>
       <c r="AG28" t="b">
         <v>0</v>
-      </c>
-      <c r="AH28" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ28" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK28" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM28" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO28" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
@@ -3837,10 +3876,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122719829</v>
+        <v>122716850</v>
       </c>
       <c r="B29" t="n">
-        <v>57478</v>
+        <v>90970</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3853,39 +3892,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>519930</v>
+        <v>520101</v>
       </c>
       <c r="R29" t="n">
-        <v>7035181</v>
+        <v>7035388</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3918,11 +3952,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-02-23</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3949,10 +3978,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122721333</v>
+        <v>122715841</v>
       </c>
       <c r="B30" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3965,37 +3994,42 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Spejkmyren, Spejkmyren, Jmt</t>
+          <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>519906</v>
+        <v>520229</v>
       </c>
       <c r="R30" t="n">
-        <v>7035389</v>
+        <v>7035608</v>
       </c>
       <c r="S30" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4029,7 +4063,7 @@
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Ymnigt på flera granar.</t>
+          <t>På en björk.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4048,22 +4082,22 @@
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>björkar</t>
         </is>
       </c>
       <c r="AK30" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Betula</t>
         </is>
       </c>
       <c r="AM30" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Betula</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -4081,10 +4115,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122715677</v>
+        <v>122715780</v>
       </c>
       <c r="B31" t="n">
-        <v>79848</v>
+        <v>79847</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4097,21 +4131,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4121,10 +4155,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>520221</v>
+        <v>520259</v>
       </c>
       <c r="R31" t="n">
-        <v>7035600</v>
+        <v>7035569</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4161,7 +4195,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>På gran</t>
+          <t>På björk</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4188,10 +4222,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122719875</v>
+        <v>122715757</v>
       </c>
       <c r="B32" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4204,39 +4238,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Spejkmyren, Spejkmyren, Jmt</t>
+          <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>519983</v>
+        <v>520234</v>
       </c>
       <c r="R32" t="n">
-        <v>7035206</v>
+        <v>7035595</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4273,7 +4302,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4284,6 +4313,31 @@
       </c>
       <c r="AG32" t="b">
         <v>0</v>
+      </c>
+      <c r="AH32" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM32" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
@@ -4300,10 +4354,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122715669</v>
+        <v>122720558</v>
       </c>
       <c r="B33" t="n">
-        <v>79847</v>
+        <v>57494</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4316,39 +4370,39 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Finnbodarna, Finnbodarna, Jmt</t>
+          <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>520221</v>
+        <v>519949</v>
       </c>
       <c r="R33" t="n">
-        <v>7035600</v>
+        <v>7035254</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4383,6 +4437,11 @@
           <t>2025-02-23</t>
         </is>
       </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Äldre hackspår i stambasen.</t>
+        </is>
+      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
@@ -4391,6 +4450,31 @@
       </c>
       <c r="AG33" t="b">
         <v>0</v>
+      </c>
+      <c r="AH33" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM33" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
@@ -4407,10 +4491,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122715502</v>
+        <v>122715949</v>
       </c>
       <c r="B34" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4423,42 +4507,37 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Djupmyren, Djupmyren, Jmt</t>
+          <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>520110</v>
+        <v>520254</v>
       </c>
       <c r="R34" t="n">
-        <v>7035585</v>
+        <v>7035555</v>
       </c>
       <c r="S34" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4490,11 +4569,6 @@
           <t>2025-02-23</t>
         </is>
       </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Gott om långväxt garnlav på många granar. Vissa bålar är här fertila.</t>
-        </is>
-      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
@@ -4503,31 +4577,6 @@
       </c>
       <c r="AG34" t="b">
         <v>0</v>
-      </c>
-      <c r="AH34" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ34" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK34" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM34" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO34" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
@@ -4544,10 +4593,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122715756</v>
+        <v>122720474</v>
       </c>
       <c r="B35" t="n">
-        <v>79847</v>
+        <v>57494</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4560,34 +4609,48 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Finnbodarna, Finnbodarna, Jmt</t>
+          <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>520256</v>
+        <v>519848</v>
       </c>
       <c r="R35" t="n">
-        <v>7035593</v>
+        <v>7035394</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4646,10 +4709,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122716801</v>
+        <v>122717294</v>
       </c>
       <c r="B36" t="n">
-        <v>57631</v>
+        <v>90970</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4662,43 +4725,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>103021</v>
+        <v>5432</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>par i lämplig häckbiotop</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>520083</v>
+        <v>520013</v>
       </c>
       <c r="R36" t="n">
-        <v>7035403</v>
+        <v>7035340</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4757,7 +4811,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122715569</v>
+        <v>122716757</v>
       </c>
       <c r="B37" t="n">
         <v>78766</v>
@@ -4793,17 +4847,17 @@
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Djupmyren, Djupmyren, Jmt</t>
+          <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>520115</v>
+        <v>520316</v>
       </c>
       <c r="R37" t="n">
-        <v>7035562</v>
+        <v>7035491</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4833,11 +4887,6 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-02-23</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4889,10 +4938,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122716964</v>
+        <v>122716547</v>
       </c>
       <c r="B38" t="n">
-        <v>90970</v>
+        <v>98271</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4901,41 +4950,55 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>5432</v>
+        <v>504</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Spejkmyren, Spejkmyren, Jmt</t>
+          <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>520115</v>
+        <v>520386</v>
       </c>
       <c r="R38" t="n">
-        <v>7035402</v>
+        <v>7035492</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4967,6 +5030,11 @@
           <t>2025-02-23</t>
         </is>
       </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>En vinterståndare på till synes fuktig mark i en lucka.</t>
+        </is>
+      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
@@ -4975,6 +5043,11 @@
       </c>
       <c r="AG38" t="b">
         <v>0</v>
+      </c>
+      <c r="AH38" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
@@ -4991,10 +5064,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122721463</v>
+        <v>122715953</v>
       </c>
       <c r="B39" t="n">
-        <v>78766</v>
+        <v>79848</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5007,34 +5080,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Spejkmyren, Spejkmyren, Jmt</t>
+          <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>519841</v>
+        <v>520254</v>
       </c>
       <c r="R39" t="n">
-        <v>7035417</v>
+        <v>7035555</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5069,11 +5142,6 @@
           <t>2025-02-23</t>
         </is>
       </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
-        </is>
-      </c>
       <c r="AD39" t="b">
         <v>0</v>
       </c>
@@ -5082,31 +5150,6 @@
       </c>
       <c r="AG39" t="b">
         <v>0</v>
-      </c>
-      <c r="AH39" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ39" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK39" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM39" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO39" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
@@ -5123,7 +5166,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122715836</v>
+        <v>122715868</v>
       </c>
       <c r="B40" t="n">
         <v>79847</v>
@@ -5168,7 +5211,7 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>520269</v>
+        <v>520265</v>
       </c>
       <c r="R40" t="n">
         <v>7035574</v>
@@ -5230,7 +5273,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122716234</v>
+        <v>122717359</v>
       </c>
       <c r="B41" t="n">
         <v>79847</v>
@@ -5266,14 +5309,14 @@
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Finnbodarna, Finnbodarna, Jmt</t>
+          <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>520362</v>
+        <v>520030</v>
       </c>
       <c r="R41" t="n">
-        <v>7035500</v>
+        <v>7035341</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5308,11 +5351,6 @@
           <t>2025-02-23</t>
         </is>
       </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>På en klen gran intill en gammal sälg med lunglav.</t>
-        </is>
-      </c>
       <c r="AD41" t="b">
         <v>0</v>
       </c>
@@ -5321,31 +5359,6 @@
       </c>
       <c r="AG41" t="b">
         <v>0</v>
-      </c>
-      <c r="AH41" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ41" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK41" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM41" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO41" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
@@ -5362,10 +5375,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122716216</v>
+        <v>122715874</v>
       </c>
       <c r="B42" t="n">
-        <v>79847</v>
+        <v>79876</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5374,43 +5387,38 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>520368</v>
+        <v>520265</v>
       </c>
       <c r="R42" t="n">
-        <v>7035513</v>
+        <v>7035574</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5445,11 +5453,6 @@
           <t>2025-02-23</t>
         </is>
       </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>På en gammal grovbarkad sälg.</t>
-        </is>
-      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
@@ -5458,31 +5461,6 @@
       </c>
       <c r="AG42" t="b">
         <v>0</v>
-      </c>
-      <c r="AH42" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ42" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK42" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM42" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO42" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
@@ -5499,10 +5477,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122715648</v>
+        <v>122719371</v>
       </c>
       <c r="B43" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5515,42 +5493,37 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Finnbodarna, Hammerdal, Finnbodarna, Hammerdal, Jmt</t>
+          <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>520219</v>
+        <v>519943</v>
       </c>
       <c r="R43" t="n">
-        <v>7035597</v>
+        <v>7035270</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5582,11 +5555,6 @@
           <t>2025-02-23</t>
         </is>
       </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
@@ -5595,6 +5563,31 @@
       </c>
       <c r="AG43" t="b">
         <v>0</v>
+      </c>
+      <c r="AH43" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ43" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK43" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM43" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO43" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
@@ -5611,10 +5604,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122719533</v>
+        <v>122720959</v>
       </c>
       <c r="B44" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5627,39 +5620,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>519948</v>
+        <v>519917</v>
       </c>
       <c r="R44" t="n">
-        <v>7035187</v>
+        <v>7035339</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5696,7 +5684,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Långväxta bålar på flertalet granar.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5707,6 +5695,31 @@
       </c>
       <c r="AG44" t="b">
         <v>0</v>
+      </c>
+      <c r="AH44" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ44" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK44" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM44" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO44" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
@@ -5723,10 +5736,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122717929</v>
+        <v>122717164</v>
       </c>
       <c r="B45" t="n">
-        <v>79876</v>
+        <v>78766</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5735,46 +5748,41 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>520029</v>
+        <v>520120</v>
       </c>
       <c r="R45" t="n">
-        <v>7035292</v>
+        <v>7035405</v>
       </c>
       <c r="S45" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5822,22 +5830,22 @@
       </c>
       <c r="AJ45" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK45" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM45" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO45" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>
@@ -5855,10 +5863,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122716269</v>
+        <v>122715677</v>
       </c>
       <c r="B46" t="n">
-        <v>57478</v>
+        <v>79848</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5871,39 +5879,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Finnbodarna, Hammerdal, Finnbodarna, Hammerdal, Jmt</t>
+          <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>520256</v>
+        <v>520221</v>
       </c>
       <c r="R46" t="n">
-        <v>7035380</v>
+        <v>7035600</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5940,7 +5943,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5967,10 +5970,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122717636</v>
+        <v>122715836</v>
       </c>
       <c r="B47" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5983,39 +5986,39 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Spejkmyren, Spejkmyren, Jmt</t>
+          <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>519970</v>
+        <v>520269</v>
       </c>
       <c r="R47" t="n">
-        <v>7035297</v>
+        <v>7035574</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6048,11 +6051,6 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-02-23</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6079,10 +6077,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122719554</v>
+        <v>122715669</v>
       </c>
       <c r="B48" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6095,44 +6093,39 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N48" t="inlineStr">
-        <is>
-          <t>observerad</t>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Spejkmyren, Spejkmyren, Jmt</t>
+          <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>519981</v>
+        <v>520221</v>
       </c>
       <c r="R48" t="n">
-        <v>7035221</v>
+        <v>7035600</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6167,11 +6160,6 @@
           <t>2025-02-23</t>
         </is>
       </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Äldre ringhack som bedöms vara 5 - 10 år gamla.</t>
-        </is>
-      </c>
       <c r="AD48" t="b">
         <v>0</v>
       </c>
@@ -6180,31 +6168,6 @@
       </c>
       <c r="AG48" t="b">
         <v>0</v>
-      </c>
-      <c r="AH48" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ48" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK48" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM48" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO48" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
@@ -6221,10 +6184,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122720823</v>
+        <v>122716964</v>
       </c>
       <c r="B49" t="n">
-        <v>57478</v>
+        <v>90970</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6237,53 +6200,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L49" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>519842</v>
+        <v>520115</v>
       </c>
       <c r="R49" t="n">
-        <v>7035388</v>
+        <v>7035402</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6316,11 +6260,6 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-02-23</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Trummande</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6347,7 +6286,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122715978</v>
+        <v>122716329</v>
       </c>
       <c r="B50" t="n">
         <v>79847</v>
@@ -6383,7 +6322,7 @@
       <c r="I50" t="inlineStr"/>
       <c r="K50" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
@@ -6392,13 +6331,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>520243</v>
+        <v>520374</v>
       </c>
       <c r="R50" t="n">
-        <v>7035552</v>
+        <v>7035511</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6430,6 +6369,11 @@
           <t>2025-02-23</t>
         </is>
       </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>På gran intill en gammal lunglavssälg.</t>
+        </is>
+      </c>
       <c r="AD50" t="b">
         <v>0</v>
       </c>
@@ -6438,6 +6382,31 @@
       </c>
       <c r="AG50" t="b">
         <v>0</v>
+      </c>
+      <c r="AH50" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ50" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK50" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM50" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO50" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
@@ -6454,10 +6423,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122720281</v>
+        <v>122717929</v>
       </c>
       <c r="B51" t="n">
-        <v>57478</v>
+        <v>79876</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6466,31 +6435,31 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
@@ -6499,13 +6468,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>519850</v>
+        <v>520029</v>
       </c>
       <c r="R51" t="n">
-        <v>7035373</v>
+        <v>7035292</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6537,11 +6506,6 @@
           <t>2025-02-23</t>
         </is>
       </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD51" t="b">
         <v>0</v>
       </c>
@@ -6550,6 +6514,31 @@
       </c>
       <c r="AG51" t="b">
         <v>0</v>
+      </c>
+      <c r="AH51" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ51" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK51" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM51" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO51" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
@@ -6566,10 +6555,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122720474</v>
+        <v>122721333</v>
       </c>
       <c r="B52" t="n">
-        <v>57494</v>
+        <v>78766</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6582,51 +6571,37 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L52" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>519848</v>
+        <v>519906</v>
       </c>
       <c r="R52" t="n">
-        <v>7035394</v>
+        <v>7035389</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6658,6 +6633,11 @@
           <t>2025-02-23</t>
         </is>
       </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Ymnigt på flera granar.</t>
+        </is>
+      </c>
       <c r="AD52" t="b">
         <v>0</v>
       </c>
@@ -6666,6 +6646,31 @@
       </c>
       <c r="AG52" t="b">
         <v>0</v>
+      </c>
+      <c r="AH52" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ52" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK52" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM52" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO52" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
@@ -6682,10 +6687,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122720889</v>
+        <v>122715801</v>
       </c>
       <c r="B53" t="n">
-        <v>57478</v>
+        <v>79848</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6698,39 +6703,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Spejkmyren, Spejkmyren, Jmt</t>
+          <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>519841</v>
+        <v>520266</v>
       </c>
       <c r="R53" t="n">
-        <v>7035390</v>
+        <v>7035582</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6763,11 +6763,6 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-02-23</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6794,10 +6789,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122720427</v>
+        <v>122717873</v>
       </c>
       <c r="B54" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6810,27 +6805,27 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
@@ -6839,13 +6834,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>519846</v>
+        <v>520033</v>
       </c>
       <c r="R54" t="n">
-        <v>7035407</v>
+        <v>7035301</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6877,11 +6872,6 @@
           <t>2025-02-23</t>
         </is>
       </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD54" t="b">
         <v>0</v>
       </c>
@@ -6890,6 +6880,31 @@
       </c>
       <c r="AG54" t="b">
         <v>0</v>
+      </c>
+      <c r="AH54" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ54" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK54" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM54" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO54" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
@@ -6906,10 +6921,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122716387</v>
+        <v>122715790</v>
       </c>
       <c r="B55" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6922,39 +6937,39 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Finnbodarna, Hammerdal, Finnbodarna, Hammerdal, Jmt</t>
+          <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>520278</v>
+        <v>520267</v>
       </c>
       <c r="R55" t="n">
-        <v>7035397</v>
+        <v>7035581</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6987,11 +7002,6 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-02-23</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7018,10 +7028,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122720686</v>
+        <v>122715795</v>
       </c>
       <c r="B56" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -7034,37 +7044,37 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Spejkmyren, Spejkmyren, Jmt</t>
+          <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>519903</v>
+        <v>520214</v>
       </c>
       <c r="R56" t="n">
-        <v>7035224</v>
+        <v>7035599</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -7094,6 +7104,11 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-02-23</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>På en klen gran intill en lunglavssälg.</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7145,10 +7160,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122715766</v>
+        <v>122720686</v>
       </c>
       <c r="B57" t="n">
-        <v>90970</v>
+        <v>78766</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -7161,34 +7176,34 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Finnbodarna, Finnbodarna, Jmt</t>
+          <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>520252</v>
+        <v>519903</v>
       </c>
       <c r="R57" t="n">
-        <v>7035591</v>
+        <v>7035224</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7231,6 +7246,31 @@
       </c>
       <c r="AG57" t="b">
         <v>0</v>
+      </c>
+      <c r="AH57" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ57" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK57" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM57" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO57" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
@@ -7247,10 +7287,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122717284</v>
+        <v>122716303</v>
       </c>
       <c r="B58" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7263,37 +7303,42 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Spejkmyren, Spejkmyren, Jmt</t>
+          <t>Finnbodarna, Hammerdal, Finnbodarna, Hammerdal, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>520031</v>
+        <v>520250</v>
       </c>
       <c r="R58" t="n">
-        <v>7035353</v>
+        <v>7035363</v>
       </c>
       <c r="S58" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7327,7 +7372,7 @@
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>Långväxta bålar på flertalet granar.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7338,31 +7383,6 @@
       </c>
       <c r="AG58" t="b">
         <v>0</v>
-      </c>
-      <c r="AH58" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ58" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK58" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM58" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO58" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
@@ -7379,10 +7399,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122720959</v>
+        <v>122716673</v>
       </c>
       <c r="B59" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7395,34 +7415,39 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>519917</v>
+        <v>520108</v>
       </c>
       <c r="R59" t="n">
-        <v>7035339</v>
+        <v>7035462</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7459,7 +7484,7 @@
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>Långväxta bålar på flertalet granar.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7470,31 +7495,6 @@
       </c>
       <c r="AG59" t="b">
         <v>0</v>
-      </c>
-      <c r="AH59" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ59" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK59" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM59" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO59" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
@@ -7511,10 +7511,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122717488</v>
+        <v>122720454</v>
       </c>
       <c r="B60" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7527,34 +7527,39 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
           <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>520000</v>
+        <v>519849</v>
       </c>
       <c r="R60" t="n">
-        <v>7035297</v>
+        <v>7035406</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7587,6 +7592,11 @@
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-02-23</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7613,7 +7623,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122716443</v>
+        <v>122720065</v>
       </c>
       <c r="B61" t="n">
         <v>78766</v>
@@ -7646,34 +7656,20 @@
           <t>(Ach.) Ach.</t>
         </is>
       </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K61" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Finnbodarna, Finnbodarna, Jmt</t>
+          <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>520251</v>
+        <v>520062</v>
       </c>
       <c r="R61" t="n">
-        <v>7035394</v>
+        <v>7035232</v>
       </c>
       <c r="S61" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7705,11 +7701,6 @@
           <t>2025-02-23</t>
         </is>
       </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>Garnlavsrikt</t>
-        </is>
-      </c>
       <c r="AD61" t="b">
         <v>0</v>
       </c>
@@ -7718,6 +7709,31 @@
       </c>
       <c r="AG61" t="b">
         <v>0</v>
+      </c>
+      <c r="AH61" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ61" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK61" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM61" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO61" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
@@ -7734,10 +7750,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122715778</v>
+        <v>122715999</v>
       </c>
       <c r="B62" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7750,42 +7766,37 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="K62" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>520259</v>
+        <v>520311</v>
       </c>
       <c r="R62" t="n">
-        <v>7035574</v>
+        <v>7035566</v>
       </c>
       <c r="S62" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7825,6 +7836,31 @@
       </c>
       <c r="AG62" t="b">
         <v>0</v>
+      </c>
+      <c r="AH62" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ62" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK62" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM62" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO62" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
@@ -7841,10 +7877,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122720558</v>
+        <v>122720823</v>
       </c>
       <c r="B63" t="n">
-        <v>57494</v>
+        <v>57478</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7857,16 +7893,16 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -7874,10 +7910,24 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I63" t="inlineStr"/>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P63" t="inlineStr">
@@ -7886,10 +7936,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>519949</v>
+        <v>519842</v>
       </c>
       <c r="R63" t="n">
-        <v>7035254</v>
+        <v>7035388</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7926,7 +7976,7 @@
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>Äldre hackspår i stambasen.</t>
+          <t>Trummande</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7937,31 +7987,6 @@
       </c>
       <c r="AG63" t="b">
         <v>0</v>
-      </c>
-      <c r="AH63" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ63" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK63" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM63" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO63" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
@@ -7978,7 +8003,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122716645</v>
+        <v>122720368</v>
       </c>
       <c r="B64" t="n">
         <v>57478</v>
@@ -8023,10 +8048,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>520129</v>
+        <v>519852</v>
       </c>
       <c r="R64" t="n">
-        <v>7035444</v>
+        <v>7035392</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -8090,7 +8115,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122718013</v>
+        <v>122719875</v>
       </c>
       <c r="B65" t="n">
         <v>57478</v>
@@ -8135,10 +8160,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>519948</v>
+        <v>519983</v>
       </c>
       <c r="R65" t="n">
-        <v>7035313</v>
+        <v>7035206</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -8202,7 +8227,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122719648</v>
+        <v>122719533</v>
       </c>
       <c r="B66" t="n">
         <v>57478</v>
@@ -8247,10 +8272,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>519939</v>
+        <v>519948</v>
       </c>
       <c r="R66" t="n">
-        <v>7035194</v>
+        <v>7035187</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -8314,10 +8339,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>122716160</v>
+        <v>122716682</v>
       </c>
       <c r="B67" t="n">
-        <v>78766</v>
+        <v>57631</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8330,34 +8355,43 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Finnbodarna, Finnbodarna, Jmt</t>
+          <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>520349</v>
+        <v>520101</v>
       </c>
       <c r="R67" t="n">
-        <v>7035517</v>
+        <v>7035453</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8400,31 +8434,6 @@
       </c>
       <c r="AG67" t="b">
         <v>0</v>
-      </c>
-      <c r="AH67" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ67" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK67" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM67" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO67" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
@@ -8441,10 +8450,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>122716757</v>
+        <v>122716216</v>
       </c>
       <c r="B68" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8457,37 +8466,42 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>520316</v>
+        <v>520368</v>
       </c>
       <c r="R68" t="n">
-        <v>7035491</v>
+        <v>7035513</v>
       </c>
       <c r="S68" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8519,6 +8533,11 @@
           <t>2025-02-23</t>
         </is>
       </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>På en gammal grovbarkad sälg.</t>
+        </is>
+      </c>
       <c r="AD68" t="b">
         <v>0</v>
       </c>
@@ -8535,22 +8554,22 @@
       </c>
       <c r="AJ68" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK68" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM68" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO68" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT68" t="inlineStr"/>
@@ -8568,10 +8587,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>122720469</v>
+        <v>122716293</v>
       </c>
       <c r="B69" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8584,34 +8603,39 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Spejkmyren, Spejkmyren, Jmt</t>
+          <t>Finnbodarna, Hammerdal, Finnbodarna, Hammerdal, Jmt</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>519996</v>
+        <v>520249</v>
       </c>
       <c r="R69" t="n">
-        <v>7035241</v>
+        <v>7035364</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8646,6 +8670,11 @@
           <t>2025-02-23</t>
         </is>
       </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD69" t="b">
         <v>0</v>
       </c>
@@ -8654,31 +8683,6 @@
       </c>
       <c r="AG69" t="b">
         <v>0</v>
-      </c>
-      <c r="AH69" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ69" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK69" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM69" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO69" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
@@ -8695,10 +8699,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>122720454</v>
+        <v>122717488</v>
       </c>
       <c r="B70" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8711,39 +8715,34 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>519849</v>
+        <v>520000</v>
       </c>
       <c r="R70" t="n">
-        <v>7035406</v>
+        <v>7035297</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8776,11 +8775,6 @@
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-02-23</t>
-        </is>
-      </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8807,10 +8801,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>122716329</v>
+        <v>122721463</v>
       </c>
       <c r="B71" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8823,42 +8817,37 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="K71" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Finnbodarna, Finnbodarna, Jmt</t>
+          <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>520374</v>
+        <v>519841</v>
       </c>
       <c r="R71" t="n">
-        <v>7035511</v>
+        <v>7035417</v>
       </c>
       <c r="S71" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8892,7 +8881,7 @@
       </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>På gran intill en gammal lunglavssälg.</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8944,10 +8933,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>122715874</v>
+        <v>122716269</v>
       </c>
       <c r="B72" t="n">
-        <v>79876</v>
+        <v>57478</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8956,38 +8945,43 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Finnbodarna, Finnbodarna, Jmt</t>
+          <t>Finnbodarna, Hammerdal, Finnbodarna, Hammerdal, Jmt</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>520265</v>
+        <v>520256</v>
       </c>
       <c r="R72" t="n">
-        <v>7035574</v>
+        <v>7035380</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -9020,6 +9014,11 @@
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-02-23</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -9046,7 +9045,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>122716303</v>
+        <v>122718013</v>
       </c>
       <c r="B73" t="n">
         <v>57478</v>
@@ -9087,14 +9086,14 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Finnbodarna, Hammerdal, Finnbodarna, Hammerdal, Jmt</t>
+          <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>520250</v>
+        <v>519948</v>
       </c>
       <c r="R73" t="n">
-        <v>7035363</v>
+        <v>7035313</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -9158,10 +9157,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>122716547</v>
+        <v>122715934</v>
       </c>
       <c r="B74" t="n">
-        <v>98271</v>
+        <v>78766</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -9170,55 +9169,41 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>504</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J74" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K74" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>520386</v>
+        <v>520303</v>
       </c>
       <c r="R74" t="n">
-        <v>7035492</v>
+        <v>7035598</v>
       </c>
       <c r="S74" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -9252,7 +9237,7 @@
       </c>
       <c r="AC74" t="inlineStr">
         <is>
-          <t>En vinterståndare på till synes fuktig mark i en lucka.</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9267,6 +9252,26 @@
       <c r="AH74" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ74" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK74" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM74" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO74" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT74" t="inlineStr"/>
@@ -9284,7 +9289,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>122719697</v>
+        <v>122716160</v>
       </c>
       <c r="B75" t="n">
         <v>78766</v>
@@ -9320,17 +9325,17 @@
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Spejkmyren, Spejkmyren, Jmt</t>
+          <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>520026</v>
+        <v>520349</v>
       </c>
       <c r="R75" t="n">
-        <v>7035233</v>
+        <v>7035517</v>
       </c>
       <c r="S75" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -9411,10 +9416,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>122717164</v>
+        <v>122716801</v>
       </c>
       <c r="B76" t="n">
-        <v>78766</v>
+        <v>57631</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -9427,34 +9432,43 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
       <c r="P76" t="inlineStr">
         <is>
           <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>520120</v>
+        <v>520083</v>
       </c>
       <c r="R76" t="n">
-        <v>7035405</v>
+        <v>7035403</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -9497,31 +9511,6 @@
       </c>
       <c r="AG76" t="b">
         <v>0</v>
-      </c>
-      <c r="AH76" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ76" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK76" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM76" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO76" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
@@ -9538,10 +9527,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>122715999</v>
+        <v>122715775</v>
       </c>
       <c r="B77" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -9554,37 +9543,42 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P77" t="inlineStr">
         <is>
           <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>520311</v>
+        <v>520252</v>
       </c>
       <c r="R77" t="n">
-        <v>7035566</v>
+        <v>7035576</v>
       </c>
       <c r="S77" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -9616,6 +9610,11 @@
           <t>2025-02-23</t>
         </is>
       </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>På björk</t>
+        </is>
+      </c>
       <c r="AD77" t="b">
         <v>0</v>
       </c>
@@ -9624,31 +9623,6 @@
       </c>
       <c r="AG77" t="b">
         <v>0</v>
-      </c>
-      <c r="AH77" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ77" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK77" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM77" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO77" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
@@ -9665,10 +9639,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>122715934</v>
+        <v>122715778</v>
       </c>
       <c r="B78" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -9681,37 +9655,42 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P78" t="inlineStr">
         <is>
           <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>520303</v>
+        <v>520259</v>
       </c>
       <c r="R78" t="n">
-        <v>7035598</v>
+        <v>7035574</v>
       </c>
       <c r="S78" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -9743,11 +9722,6 @@
           <t>2025-02-23</t>
         </is>
       </c>
-      <c r="AC78" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
-        </is>
-      </c>
       <c r="AD78" t="b">
         <v>0</v>
       </c>
@@ -9756,31 +9730,6 @@
       </c>
       <c r="AG78" t="b">
         <v>0</v>
-      </c>
-      <c r="AH78" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ78" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK78" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM78" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO78" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
@@ -9797,10 +9746,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>122715868</v>
+        <v>122715766</v>
       </c>
       <c r="B79" t="n">
-        <v>79847</v>
+        <v>90970</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -9813,39 +9762,34 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
-      <c r="K79" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P79" t="inlineStr">
         <is>
           <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>520265</v>
+        <v>520252</v>
       </c>
       <c r="R79" t="n">
-        <v>7035574</v>
+        <v>7035591</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9904,10 +9848,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>122715790</v>
+        <v>122715849</v>
       </c>
       <c r="B80" t="n">
-        <v>79847</v>
+        <v>79876</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -9916,43 +9860,38 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
-      <c r="K80" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P80" t="inlineStr">
         <is>
           <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>520267</v>
+        <v>520268</v>
       </c>
       <c r="R80" t="n">
-        <v>7035581</v>
+        <v>7035575</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -10011,7 +9950,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>122716295</v>
+        <v>122715779</v>
       </c>
       <c r="B81" t="n">
         <v>79847</v>
@@ -10047,7 +9986,7 @@
       <c r="I81" t="inlineStr"/>
       <c r="K81" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P81" t="inlineStr">
@@ -10056,13 +9995,13 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>520378</v>
+        <v>520223</v>
       </c>
       <c r="R81" t="n">
-        <v>7035512</v>
+        <v>7035609</v>
       </c>
       <c r="S81" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -10092,11 +10031,6 @@
       <c r="AA81" t="inlineStr">
         <is>
           <t>2025-02-23</t>
-        </is>
-      </c>
-      <c r="AC81" t="inlineStr">
-        <is>
-          <t>Ymnig påväxt på en grovbarkad gammal sälg. Fertila bålar med apothecier.</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -10148,10 +10082,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>122715573</v>
+        <v>122717468</v>
       </c>
       <c r="B82" t="n">
-        <v>79848</v>
+        <v>57494</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -10164,34 +10098,43 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>2081</v>
+        <v>100049</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Finnbodarna, Finnbodarna, Jmt</t>
+          <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>520214</v>
+        <v>520020</v>
       </c>
       <c r="R82" t="n">
-        <v>7035583</v>
+        <v>7035330</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -10250,10 +10193,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>122717468</v>
+        <v>122716427</v>
       </c>
       <c r="B83" t="n">
-        <v>57494</v>
+        <v>78767</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -10266,46 +10209,37 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>100049</v>
+        <v>230405</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M83" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Spejkmyren, Spejkmyren, Jmt</t>
+          <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>520020</v>
+        <v>520388</v>
       </c>
       <c r="R83" t="n">
-        <v>7035330</v>
+        <v>7035490</v>
       </c>
       <c r="S83" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -10337,6 +10271,11 @@
           <t>2025-02-23</t>
         </is>
       </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
+        </is>
+      </c>
       <c r="AD83" t="b">
         <v>0</v>
       </c>
@@ -10345,6 +10284,31 @@
       </c>
       <c r="AG83" t="b">
         <v>0</v>
+      </c>
+      <c r="AH83" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ83" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK83" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM83" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO83" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
@@ -10361,7 +10325,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>122720327</v>
+        <v>122720889</v>
       </c>
       <c r="B84" t="n">
         <v>57478</v>
@@ -10406,10 +10370,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>519838</v>
+        <v>519841</v>
       </c>
       <c r="R84" t="n">
-        <v>7035393</v>
+        <v>7035390</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -10473,10 +10437,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>122719979</v>
+        <v>122715648</v>
       </c>
       <c r="B85" t="n">
-        <v>57631</v>
+        <v>57478</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -10489,43 +10453,39 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
       <c r="M85" t="inlineStr">
         <is>
-          <t>par i lämplig häckbiotop</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Spejkmyren, Spejkmyren, Jmt</t>
+          <t>Finnbodarna, Hammerdal, Finnbodarna, Hammerdal, Jmt</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>519946</v>
+        <v>520219</v>
       </c>
       <c r="R85" t="n">
-        <v>7035240</v>
+        <v>7035597</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -10558,6 +10518,11 @@
       <c r="AA85" t="inlineStr">
         <is>
           <t>2025-02-23</t>
+        </is>
+      </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -10584,10 +10549,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>122716850</v>
+        <v>122717636</v>
       </c>
       <c r="B86" t="n">
-        <v>90970</v>
+        <v>57478</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -10600,34 +10565,39 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P86" t="inlineStr">
         <is>
           <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>520101</v>
+        <v>519970</v>
       </c>
       <c r="R86" t="n">
-        <v>7035388</v>
+        <v>7035297</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -10660,6 +10630,11 @@
       <c r="AA86" t="inlineStr">
         <is>
           <t>2025-02-23</t>
+        </is>
+      </c>
+      <c r="AC86" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10686,10 +10661,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>122717343</v>
+        <v>122715571</v>
       </c>
       <c r="B87" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -10702,39 +10677,34 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
-      <c r="M87" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Spejkmyren, Spejkmyren, Jmt</t>
+          <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>520034</v>
+        <v>520216</v>
       </c>
       <c r="R87" t="n">
-        <v>7035339</v>
+        <v>7035583</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10767,11 +10737,6 @@
       <c r="AA87" t="inlineStr">
         <is>
           <t>2025-02-23</t>
-        </is>
-      </c>
-      <c r="AC87" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10798,7 +10763,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>122717616</v>
+        <v>122721035</v>
       </c>
       <c r="B88" t="n">
         <v>78766</v>
@@ -10838,13 +10803,13 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>520019</v>
+        <v>519897</v>
       </c>
       <c r="R88" t="n">
-        <v>7035352</v>
+        <v>7035374</v>
       </c>
       <c r="S88" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -10876,11 +10841,6 @@
           <t>2025-02-23</t>
         </is>
       </c>
-      <c r="AC88" t="inlineStr">
-        <is>
-          <t>Rikligt.</t>
-        </is>
-      </c>
       <c r="AD88" t="b">
         <v>0</v>
       </c>
@@ -10897,12 +10857,12 @@
       </c>
       <c r="AJ88" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>garnlav</t>
         </is>
       </c>
       <c r="AK88" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="AM88" t="inlineStr">
@@ -10912,7 +10872,7 @@
       </c>
       <c r="AO88" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Branch on living tree # Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="AT88" t="inlineStr"/>
@@ -10930,10 +10890,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>122715775</v>
+        <v>122715502</v>
       </c>
       <c r="B89" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -10946,21 +10906,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -10971,17 +10931,17 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Finnbodarna, Finnbodarna, Jmt</t>
+          <t>Djupmyren, Djupmyren, Jmt</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>520252</v>
+        <v>520110</v>
       </c>
       <c r="R89" t="n">
-        <v>7035576</v>
+        <v>7035585</v>
       </c>
       <c r="S89" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -11015,7 +10975,7 @@
       </c>
       <c r="AC89" t="inlineStr">
         <is>
-          <t>På björk</t>
+          <t>Gott om långväxt garnlav på många granar. Vissa bålar är här fertila.</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -11026,6 +10986,31 @@
       </c>
       <c r="AG89" t="b">
         <v>0</v>
+      </c>
+      <c r="AH89" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ89" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK89" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM89" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO89" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
@@ -11042,10 +11027,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>122715953</v>
+        <v>122720281</v>
       </c>
       <c r="B90" t="n">
-        <v>79848</v>
+        <v>57478</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -11058,34 +11043,39 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Finnbodarna, Finnbodarna, Jmt</t>
+          <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>520254</v>
+        <v>519850</v>
       </c>
       <c r="R90" t="n">
-        <v>7035555</v>
+        <v>7035373</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -11118,6 +11108,11 @@
       <c r="AA90" t="inlineStr">
         <is>
           <t>2025-02-23</t>
+        </is>
+      </c>
+      <c r="AC90" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD90" t="b">

--- a/artfynd/A 1625-2025 artfynd.xlsx
+++ b/artfynd/A 1625-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122719614</v>
+        <v>122715978</v>
       </c>
       <c r="B2" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,39 +691,39 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Spejkmyren, Spejkmyren, Jmt</t>
+          <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>519930</v>
+        <v>520243</v>
       </c>
       <c r="R2" t="n">
-        <v>7035181</v>
+        <v>7035552</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -756,11 +756,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-02-23</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Färska och äldre ringhack på samma gran.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122717616</v>
+        <v>122716269</v>
       </c>
       <c r="B3" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,34 +798,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Spejkmyren, Spejkmyren, Jmt</t>
+          <t>Finnbodarna, Hammerdal, Finnbodarna, Hammerdal, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>520019</v>
+        <v>520256</v>
       </c>
       <c r="R3" t="n">
-        <v>7035352</v>
+        <v>7035380</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -867,7 +867,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Rikligt.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -878,31 +878,6 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -919,7 +894,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122717284</v>
+        <v>122717164</v>
       </c>
       <c r="B4" t="n">
         <v>78766</v>
@@ -959,13 +934,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>520031</v>
+        <v>520120</v>
       </c>
       <c r="R4" t="n">
-        <v>7035353</v>
+        <v>7035405</v>
       </c>
       <c r="S4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -995,11 +970,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-02-23</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Långväxta bålar på flertalet granar.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1051,7 +1021,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122720469</v>
+        <v>122717284</v>
       </c>
       <c r="B5" t="n">
         <v>78766</v>
@@ -1091,13 +1061,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>519996</v>
+        <v>520031</v>
       </c>
       <c r="R5" t="n">
-        <v>7035241</v>
+        <v>7035353</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1127,6 +1097,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-02-23</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Långväxta bålar på flertalet granar.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1178,10 +1153,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122717952</v>
+        <v>122715870</v>
       </c>
       <c r="B6" t="n">
-        <v>57494</v>
+        <v>79848</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1194,43 +1169,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>2081</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
-        </is>
-      </c>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Spejkmyren, Spejkmyren, Jmt</t>
+          <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>519951</v>
+        <v>520265</v>
       </c>
       <c r="R6" t="n">
-        <v>7035320</v>
+        <v>7035574</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1289,10 +1255,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122715870</v>
+        <v>122715756</v>
       </c>
       <c r="B7" t="n">
-        <v>79848</v>
+        <v>79847</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1305,21 +1271,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1329,10 +1295,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>520265</v>
+        <v>520256</v>
       </c>
       <c r="R7" t="n">
-        <v>7035574</v>
+        <v>7035593</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1391,10 +1357,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122715573</v>
+        <v>122716329</v>
       </c>
       <c r="B8" t="n">
-        <v>79848</v>
+        <v>79847</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1407,37 +1373,42 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>520214</v>
+        <v>520374</v>
       </c>
       <c r="R8" t="n">
-        <v>7035583</v>
+        <v>7035511</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1469,6 +1440,11 @@
           <t>2025-02-23</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>På gran intill en gammal lunglavssälg.</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1477,6 +1453,31 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1493,7 +1494,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122719648</v>
+        <v>122720889</v>
       </c>
       <c r="B9" t="n">
         <v>57478</v>
@@ -1538,10 +1539,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>519939</v>
+        <v>519841</v>
       </c>
       <c r="R9" t="n">
-        <v>7035194</v>
+        <v>7035390</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1605,7 +1606,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122719554</v>
+        <v>122719829</v>
       </c>
       <c r="B10" t="n">
         <v>57478</v>
@@ -1644,21 +1645,16 @@
           <t>äldre spår</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>519981</v>
+        <v>519930</v>
       </c>
       <c r="R10" t="n">
-        <v>7035221</v>
+        <v>7035181</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1695,7 +1691,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Äldre ringhack som bedöms vara 5 - 10 år gamla.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1706,31 +1702,6 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1747,10 +1718,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122717343</v>
+        <v>122715677</v>
       </c>
       <c r="B11" t="n">
-        <v>57478</v>
+        <v>79848</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1763,39 +1734,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Spejkmyren, Spejkmyren, Jmt</t>
+          <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>520034</v>
+        <v>520221</v>
       </c>
       <c r="R11" t="n">
-        <v>7035339</v>
+        <v>7035600</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1832,7 +1798,7 @@
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1859,10 +1825,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122719979</v>
+        <v>122716964</v>
       </c>
       <c r="B12" t="n">
-        <v>57631</v>
+        <v>90970</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1875,43 +1841,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103021</v>
+        <v>5432</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>par i lämplig häckbiotop</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>519946</v>
+        <v>520115</v>
       </c>
       <c r="R12" t="n">
-        <v>7035240</v>
+        <v>7035402</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1970,10 +1927,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122717446</v>
+        <v>122720823</v>
       </c>
       <c r="B13" t="n">
-        <v>90970</v>
+        <v>57478</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1986,34 +1943,53 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>520006</v>
+        <v>519842</v>
       </c>
       <c r="R13" t="n">
-        <v>7035303</v>
+        <v>7035388</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2046,6 +2022,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-02-23</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Trummande</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2072,10 +2053,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122715756</v>
+        <v>122716673</v>
       </c>
       <c r="B14" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2088,34 +2069,39 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Finnbodarna, Finnbodarna, Jmt</t>
+          <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>520256</v>
+        <v>520108</v>
       </c>
       <c r="R14" t="n">
-        <v>7035593</v>
+        <v>7035462</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2148,6 +2134,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-02-23</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2174,10 +2165,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122716295</v>
+        <v>122719554</v>
       </c>
       <c r="B15" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2190,39 +2181,44 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Finnbodarna, Finnbodarna, Jmt</t>
+          <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>520378</v>
+        <v>519981</v>
       </c>
       <c r="R15" t="n">
-        <v>7035512</v>
+        <v>7035221</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2259,7 +2255,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Ymnig påväxt på en grovbarkad gammal sälg. Fertila bålar med apothecier.</t>
+          <t>Äldre ringhack som bedöms vara 5 - 10 år gamla.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2278,22 +2274,22 @@
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2311,10 +2307,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122716645</v>
+        <v>122715841</v>
       </c>
       <c r="B16" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2327,42 +2323,42 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Spejkmyren, Spejkmyren, Jmt</t>
+          <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>520129</v>
+        <v>520229</v>
       </c>
       <c r="R16" t="n">
-        <v>7035444</v>
+        <v>7035608</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2396,7 +2392,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>På en björk.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2407,6 +2403,31 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AM16" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Betula</t>
+        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
@@ -2423,10 +2444,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122720548</v>
+        <v>122717952</v>
       </c>
       <c r="B17" t="n">
-        <v>90970</v>
+        <v>57494</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2439,34 +2460,43 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>519847</v>
+        <v>519951</v>
       </c>
       <c r="R17" t="n">
-        <v>7035432</v>
+        <v>7035320</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2525,10 +2555,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122719697</v>
+        <v>122720281</v>
       </c>
       <c r="B18" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2541,37 +2571,42 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>520026</v>
+        <v>519850</v>
       </c>
       <c r="R18" t="n">
-        <v>7035233</v>
+        <v>7035373</v>
       </c>
       <c r="S18" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2603,6 +2638,11 @@
           <t>2025-02-23</t>
         </is>
       </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
@@ -2611,31 +2651,6 @@
       </c>
       <c r="AG18" t="b">
         <v>0</v>
-      </c>
-      <c r="AH18" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
@@ -2652,10 +2667,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122720869</v>
+        <v>122716547</v>
       </c>
       <c r="B19" t="n">
-        <v>78766</v>
+        <v>98271</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2664,41 +2679,55 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>504</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Spejkmyren, Spejkmyren, Jmt</t>
+          <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>519960</v>
+        <v>520386</v>
       </c>
       <c r="R19" t="n">
-        <v>7035342</v>
+        <v>7035492</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2730,6 +2759,11 @@
           <t>2025-02-23</t>
         </is>
       </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>En vinterståndare på till synes fuktig mark i en lucka.</t>
+        </is>
+      </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
@@ -2742,26 +2776,6 @@
       <c r="AH19" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2779,10 +2793,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122720629</v>
+        <v>122715795</v>
       </c>
       <c r="B20" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2795,37 +2809,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Spejkmyren, Spejkmyren, Jmt</t>
+          <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>519935</v>
+        <v>520214</v>
       </c>
       <c r="R20" t="n">
-        <v>7035246</v>
+        <v>7035599</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2859,7 +2873,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>På en klen gran intill en lunglavssälg.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2911,7 +2925,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122715569</v>
+        <v>122720469</v>
       </c>
       <c r="B21" t="n">
         <v>78766</v>
@@ -2947,14 +2961,14 @@
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Djupmyren, Djupmyren, Jmt</t>
+          <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>520115</v>
+        <v>519996</v>
       </c>
       <c r="R21" t="n">
-        <v>7035562</v>
+        <v>7035241</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2987,11 +3001,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-02-23</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3043,10 +3052,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122716392</v>
+        <v>122715999</v>
       </c>
       <c r="B22" t="n">
-        <v>79848</v>
+        <v>78766</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3059,42 +3068,37 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>520385</v>
+        <v>520311</v>
       </c>
       <c r="R22" t="n">
-        <v>7035518</v>
+        <v>7035566</v>
       </c>
       <c r="S22" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3124,11 +3128,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-02-23</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>På gran intill en gammal sälg.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3180,10 +3179,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122716234</v>
+        <v>122716160</v>
       </c>
       <c r="B23" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3196,21 +3195,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3220,10 +3219,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>520362</v>
+        <v>520349</v>
       </c>
       <c r="R23" t="n">
-        <v>7035500</v>
+        <v>7035517</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3256,11 +3255,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-02-23</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>På en klen gran intill en gammal sälg med lunglav.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3312,10 +3306,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122715978</v>
+        <v>122720629</v>
       </c>
       <c r="B24" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3328,39 +3322,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Finnbodarna, Finnbodarna, Jmt</t>
+          <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>520243</v>
+        <v>519935</v>
       </c>
       <c r="R24" t="n">
-        <v>7035552</v>
+        <v>7035246</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3395,6 +3384,11 @@
           <t>2025-02-23</t>
         </is>
       </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
+        </is>
+      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
@@ -3403,6 +3397,31 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
+      </c>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM24" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
@@ -3419,10 +3438,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122716443</v>
+        <v>122715778</v>
       </c>
       <c r="B25" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3435,33 +3454,24 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="K25" t="inlineStr">
         <is>
           <t>med apothecier</t>
@@ -3473,10 +3483,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>520251</v>
+        <v>520259</v>
       </c>
       <c r="R25" t="n">
-        <v>7035394</v>
+        <v>7035574</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3509,11 +3519,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-02-23</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Garnlavsrikt</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3540,10 +3545,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122720427</v>
+        <v>122715502</v>
       </c>
       <c r="B26" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3556,42 +3561,42 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Spejkmyren, Spejkmyren, Jmt</t>
+          <t>Djupmyren, Djupmyren, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>519846</v>
+        <v>520110</v>
       </c>
       <c r="R26" t="n">
-        <v>7035407</v>
+        <v>7035585</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3625,7 +3630,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Gott om långväxt garnlav på många granar. Vissa bålar är här fertila.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3636,6 +3641,31 @@
       </c>
       <c r="AG26" t="b">
         <v>0</v>
+      </c>
+      <c r="AH26" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK26" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM26" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
@@ -3652,10 +3682,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122720327</v>
+        <v>122720065</v>
       </c>
       <c r="B27" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3668,42 +3698,37 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>519838</v>
+        <v>520062</v>
       </c>
       <c r="R27" t="n">
-        <v>7035393</v>
+        <v>7035232</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3735,11 +3760,6 @@
           <t>2025-02-23</t>
         </is>
       </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
@@ -3748,6 +3768,31 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
+      </c>
+      <c r="AH27" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM27" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
@@ -3764,7 +3809,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122716387</v>
+        <v>122720368</v>
       </c>
       <c r="B28" t="n">
         <v>57478</v>
@@ -3805,14 +3850,14 @@
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Finnbodarna, Hammerdal, Finnbodarna, Hammerdal, Jmt</t>
+          <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>520278</v>
+        <v>519852</v>
       </c>
       <c r="R28" t="n">
-        <v>7035397</v>
+        <v>7035392</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3876,10 +3921,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122716850</v>
+        <v>122716427</v>
       </c>
       <c r="B29" t="n">
-        <v>90970</v>
+        <v>78767</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3892,37 +3937,37 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5432</v>
+        <v>230405</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Spejkmyren, Spejkmyren, Jmt</t>
+          <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>520101</v>
+        <v>520388</v>
       </c>
       <c r="R29" t="n">
-        <v>7035388</v>
+        <v>7035490</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3954,6 +3999,11 @@
           <t>2025-02-23</t>
         </is>
       </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
+        </is>
+      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
@@ -3962,6 +4012,31 @@
       </c>
       <c r="AG29" t="b">
         <v>0</v>
+      </c>
+      <c r="AH29" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM29" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
@@ -3978,10 +4053,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122715841</v>
+        <v>122716682</v>
       </c>
       <c r="B30" t="n">
-        <v>79847</v>
+        <v>57631</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3994,42 +4069,46 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>med soral</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Finnbodarna, Finnbodarna, Jmt</t>
+          <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>520229</v>
+        <v>520101</v>
       </c>
       <c r="R30" t="n">
-        <v>7035608</v>
+        <v>7035453</v>
       </c>
       <c r="S30" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4061,11 +4140,6 @@
           <t>2025-02-23</t>
         </is>
       </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>På en björk.</t>
-        </is>
-      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
@@ -4074,31 +4148,6 @@
       </c>
       <c r="AG30" t="b">
         <v>0</v>
-      </c>
-      <c r="AH30" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ30" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK30" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AM30" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO30" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Betula</t>
-        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
@@ -4115,10 +4164,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122715780</v>
+        <v>122715953</v>
       </c>
       <c r="B31" t="n">
-        <v>79847</v>
+        <v>79848</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4131,21 +4180,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4155,10 +4204,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>520259</v>
+        <v>520254</v>
       </c>
       <c r="R31" t="n">
-        <v>7035569</v>
+        <v>7035555</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4191,11 +4240,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-02-23</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>På björk</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4222,10 +4266,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122715757</v>
+        <v>122715766</v>
       </c>
       <c r="B32" t="n">
-        <v>78766</v>
+        <v>90970</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4238,21 +4282,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4262,10 +4306,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>520234</v>
+        <v>520252</v>
       </c>
       <c r="R32" t="n">
-        <v>7035595</v>
+        <v>7035591</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4300,11 +4344,6 @@
           <t>2025-02-23</t>
         </is>
       </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
-        </is>
-      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
@@ -4313,31 +4352,6 @@
       </c>
       <c r="AG32" t="b">
         <v>0</v>
-      </c>
-      <c r="AH32" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ32" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK32" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM32" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO32" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
@@ -4354,10 +4368,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122720558</v>
+        <v>122719533</v>
       </c>
       <c r="B33" t="n">
-        <v>57494</v>
+        <v>57478</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4370,16 +4384,16 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -4399,10 +4413,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>519949</v>
+        <v>519948</v>
       </c>
       <c r="R33" t="n">
-        <v>7035254</v>
+        <v>7035187</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4439,7 +4453,7 @@
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Äldre hackspår i stambasen.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4450,31 +4464,6 @@
       </c>
       <c r="AG33" t="b">
         <v>0</v>
-      </c>
-      <c r="AH33" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ33" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK33" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO33" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
@@ -4491,7 +4480,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122715949</v>
+        <v>122717873</v>
       </c>
       <c r="B34" t="n">
         <v>79847</v>
@@ -4525,19 +4514,24 @@
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Finnbodarna, Finnbodarna, Jmt</t>
+          <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>520254</v>
+        <v>520033</v>
       </c>
       <c r="R34" t="n">
-        <v>7035555</v>
+        <v>7035301</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4577,6 +4571,31 @@
       </c>
       <c r="AG34" t="b">
         <v>0</v>
+      </c>
+      <c r="AH34" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ34" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK34" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM34" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO34" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
@@ -4593,10 +4612,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122720474</v>
+        <v>122715949</v>
       </c>
       <c r="B35" t="n">
-        <v>57494</v>
+        <v>79847</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4609,48 +4628,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L35" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Spejkmyren, Spejkmyren, Jmt</t>
+          <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>519848</v>
+        <v>520254</v>
       </c>
       <c r="R35" t="n">
-        <v>7035394</v>
+        <v>7035555</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4709,10 +4714,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122717294</v>
+        <v>122721035</v>
       </c>
       <c r="B36" t="n">
-        <v>90970</v>
+        <v>78766</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4725,21 +4730,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4749,13 +4754,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>520013</v>
+        <v>519897</v>
       </c>
       <c r="R36" t="n">
-        <v>7035340</v>
+        <v>7035374</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4795,6 +4800,31 @@
       </c>
       <c r="AG36" t="b">
         <v>0</v>
+      </c>
+      <c r="AH36" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ36" t="inlineStr">
+        <is>
+          <t>garnlav</t>
+        </is>
+      </c>
+      <c r="AK36" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="AM36" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO36" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Alectoria sarmentosa</t>
+        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
@@ -4811,7 +4841,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122716757</v>
+        <v>122720686</v>
       </c>
       <c r="B37" t="n">
         <v>78766</v>
@@ -4847,17 +4877,17 @@
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Finnbodarna, Finnbodarna, Jmt</t>
+          <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>520316</v>
+        <v>519903</v>
       </c>
       <c r="R37" t="n">
-        <v>7035491</v>
+        <v>7035224</v>
       </c>
       <c r="S37" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4938,10 +4968,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122716547</v>
+        <v>122715934</v>
       </c>
       <c r="B38" t="n">
-        <v>98271</v>
+        <v>78766</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4950,55 +4980,41 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>504</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>vinterståndare</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>520386</v>
+        <v>520303</v>
       </c>
       <c r="R38" t="n">
-        <v>7035492</v>
+        <v>7035598</v>
       </c>
       <c r="S38" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5032,7 +5048,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>En vinterståndare på till synes fuktig mark i en lucka.</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5047,6 +5063,26 @@
       <c r="AH38" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ38" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK38" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM38" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO38" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -5064,10 +5100,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122715953</v>
+        <v>122715780</v>
       </c>
       <c r="B39" t="n">
-        <v>79848</v>
+        <v>79847</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5080,21 +5116,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -5104,10 +5140,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>520254</v>
+        <v>520259</v>
       </c>
       <c r="R39" t="n">
-        <v>7035555</v>
+        <v>7035569</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5140,6 +5176,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-02-23</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>På björk</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5166,10 +5207,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122715868</v>
+        <v>122720327</v>
       </c>
       <c r="B40" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5182,39 +5223,39 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Finnbodarna, Finnbodarna, Jmt</t>
+          <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>520265</v>
+        <v>519838</v>
       </c>
       <c r="R40" t="n">
-        <v>7035574</v>
+        <v>7035393</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5247,6 +5288,11 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-02-23</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5273,10 +5319,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122717359</v>
+        <v>122720454</v>
       </c>
       <c r="B41" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5289,34 +5335,39 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>520030</v>
+        <v>519849</v>
       </c>
       <c r="R41" t="n">
-        <v>7035341</v>
+        <v>7035406</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5349,6 +5400,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-02-23</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5375,10 +5431,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122715874</v>
+        <v>122719697</v>
       </c>
       <c r="B42" t="n">
-        <v>79876</v>
+        <v>78766</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5387,41 +5443,41 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Finnbodarna, Finnbodarna, Jmt</t>
+          <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>520265</v>
+        <v>520026</v>
       </c>
       <c r="R42" t="n">
-        <v>7035574</v>
+        <v>7035233</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5461,6 +5517,31 @@
       </c>
       <c r="AG42" t="b">
         <v>0</v>
+      </c>
+      <c r="AH42" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ42" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK42" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM42" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO42" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
@@ -5477,7 +5558,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122719371</v>
+        <v>122717616</v>
       </c>
       <c r="B43" t="n">
         <v>78766</v>
@@ -5517,13 +5598,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>519943</v>
+        <v>520019</v>
       </c>
       <c r="R43" t="n">
-        <v>7035270</v>
+        <v>7035352</v>
       </c>
       <c r="S43" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5553,6 +5634,11 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-02-23</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5604,10 +5690,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122720959</v>
+        <v>122717359</v>
       </c>
       <c r="B44" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5620,21 +5706,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5644,10 +5730,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>519917</v>
+        <v>520030</v>
       </c>
       <c r="R44" t="n">
-        <v>7035339</v>
+        <v>7035341</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5682,11 +5768,6 @@
           <t>2025-02-23</t>
         </is>
       </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Långväxta bålar på flertalet granar.</t>
-        </is>
-      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
@@ -5695,31 +5776,6 @@
       </c>
       <c r="AG44" t="b">
         <v>0</v>
-      </c>
-      <c r="AH44" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ44" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK44" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM44" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO44" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
@@ -5736,7 +5792,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122717164</v>
+        <v>122721333</v>
       </c>
       <c r="B45" t="n">
         <v>78766</v>
@@ -5776,13 +5832,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>520120</v>
+        <v>519906</v>
       </c>
       <c r="R45" t="n">
-        <v>7035405</v>
+        <v>7035389</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5812,6 +5868,11 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-02-23</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Ymnigt på flera granar.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5863,10 +5924,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122715677</v>
+        <v>122720959</v>
       </c>
       <c r="B46" t="n">
-        <v>79848</v>
+        <v>78766</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5879,34 +5940,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Finnbodarna, Finnbodarna, Jmt</t>
+          <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>520221</v>
+        <v>519917</v>
       </c>
       <c r="R46" t="n">
-        <v>7035600</v>
+        <v>7035339</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5943,7 +6004,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>På gran</t>
+          <t>Långväxta bålar på flertalet granar.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5954,6 +6015,31 @@
       </c>
       <c r="AG46" t="b">
         <v>0</v>
+      </c>
+      <c r="AH46" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ46" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK46" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM46" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO46" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
@@ -5970,10 +6056,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122715836</v>
+        <v>122718013</v>
       </c>
       <c r="B47" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5986,39 +6072,39 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Finnbodarna, Finnbodarna, Jmt</t>
+          <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>520269</v>
+        <v>519948</v>
       </c>
       <c r="R47" t="n">
-        <v>7035574</v>
+        <v>7035313</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6051,6 +6137,11 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-02-23</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6077,10 +6168,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122715669</v>
+        <v>122716850</v>
       </c>
       <c r="B48" t="n">
-        <v>79847</v>
+        <v>90970</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6093,39 +6184,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Finnbodarna, Finnbodarna, Jmt</t>
+          <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>520221</v>
+        <v>520101</v>
       </c>
       <c r="R48" t="n">
-        <v>7035600</v>
+        <v>7035388</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6184,10 +6270,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122716964</v>
+        <v>122716801</v>
       </c>
       <c r="B49" t="n">
-        <v>90970</v>
+        <v>57631</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6200,34 +6286,43 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>5432</v>
+        <v>103021</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>520115</v>
+        <v>520083</v>
       </c>
       <c r="R49" t="n">
-        <v>7035402</v>
+        <v>7035403</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6286,10 +6381,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122716329</v>
+        <v>122715801</v>
       </c>
       <c r="B50" t="n">
-        <v>79847</v>
+        <v>79848</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6302,42 +6397,37 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>520374</v>
+        <v>520266</v>
       </c>
       <c r="R50" t="n">
-        <v>7035511</v>
+        <v>7035582</v>
       </c>
       <c r="S50" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6369,11 +6459,6 @@
           <t>2025-02-23</t>
         </is>
       </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>På gran intill en gammal lunglavssälg.</t>
-        </is>
-      </c>
       <c r="AD50" t="b">
         <v>0</v>
       </c>
@@ -6382,31 +6467,6 @@
       </c>
       <c r="AG50" t="b">
         <v>0</v>
-      </c>
-      <c r="AH50" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ50" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK50" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM50" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO50" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
@@ -6423,10 +6483,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122717929</v>
+        <v>122715648</v>
       </c>
       <c r="B51" t="n">
-        <v>79876</v>
+        <v>57478</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6435,46 +6495,46 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Spejkmyren, Spejkmyren, Jmt</t>
+          <t>Finnbodarna, Hammerdal, Finnbodarna, Hammerdal, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>520029</v>
+        <v>520219</v>
       </c>
       <c r="R51" t="n">
-        <v>7035292</v>
+        <v>7035597</v>
       </c>
       <c r="S51" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6506,6 +6566,11 @@
           <t>2025-02-23</t>
         </is>
       </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD51" t="b">
         <v>0</v>
       </c>
@@ -6514,31 +6579,6 @@
       </c>
       <c r="AG51" t="b">
         <v>0</v>
-      </c>
-      <c r="AH51" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ51" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK51" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM51" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO51" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
@@ -6555,10 +6595,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122721333</v>
+        <v>122716293</v>
       </c>
       <c r="B52" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6571,37 +6611,42 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Spejkmyren, Spejkmyren, Jmt</t>
+          <t>Finnbodarna, Hammerdal, Finnbodarna, Hammerdal, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>519906</v>
+        <v>520249</v>
       </c>
       <c r="R52" t="n">
-        <v>7035389</v>
+        <v>7035364</v>
       </c>
       <c r="S52" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6635,7 +6680,7 @@
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>Ymnigt på flera granar.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6646,31 +6691,6 @@
       </c>
       <c r="AG52" t="b">
         <v>0</v>
-      </c>
-      <c r="AH52" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ52" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK52" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM52" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO52" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
@@ -6687,10 +6707,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122715801</v>
+        <v>122719648</v>
       </c>
       <c r="B53" t="n">
-        <v>79848</v>
+        <v>57478</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6703,34 +6723,39 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Finnbodarna, Finnbodarna, Jmt</t>
+          <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>520266</v>
+        <v>519939</v>
       </c>
       <c r="R53" t="n">
-        <v>7035582</v>
+        <v>7035194</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6763,6 +6788,11 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-02-23</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6789,7 +6819,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122717873</v>
+        <v>122716216</v>
       </c>
       <c r="B54" t="n">
         <v>79847</v>
@@ -6830,17 +6860,17 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Spejkmyren, Spejkmyren, Jmt</t>
+          <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>520033</v>
+        <v>520368</v>
       </c>
       <c r="R54" t="n">
-        <v>7035301</v>
+        <v>7035513</v>
       </c>
       <c r="S54" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6870,6 +6900,11 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-02-23</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>På en gammal grovbarkad sälg.</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6921,10 +6956,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122715790</v>
+        <v>122716303</v>
       </c>
       <c r="B55" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6937,39 +6972,39 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Finnbodarna, Finnbodarna, Jmt</t>
+          <t>Finnbodarna, Hammerdal, Finnbodarna, Hammerdal, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>520267</v>
+        <v>520250</v>
       </c>
       <c r="R55" t="n">
-        <v>7035581</v>
+        <v>7035363</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -7002,6 +7037,11 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-02-23</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7028,10 +7068,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122715795</v>
+        <v>122720427</v>
       </c>
       <c r="B56" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -7044,37 +7084,42 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Finnbodarna, Finnbodarna, Jmt</t>
+          <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>520214</v>
+        <v>519846</v>
       </c>
       <c r="R56" t="n">
-        <v>7035599</v>
+        <v>7035407</v>
       </c>
       <c r="S56" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -7108,7 +7153,7 @@
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>På en klen gran intill en lunglavssälg.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7119,31 +7164,6 @@
       </c>
       <c r="AG56" t="b">
         <v>0</v>
-      </c>
-      <c r="AH56" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ56" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK56" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM56" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO56" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
@@ -7160,10 +7180,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122720686</v>
+        <v>122715849</v>
       </c>
       <c r="B57" t="n">
-        <v>78766</v>
+        <v>79876</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -7172,38 +7192,38 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Spejkmyren, Spejkmyren, Jmt</t>
+          <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>519903</v>
+        <v>520268</v>
       </c>
       <c r="R57" t="n">
-        <v>7035224</v>
+        <v>7035575</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7246,31 +7266,6 @@
       </c>
       <c r="AG57" t="b">
         <v>0</v>
-      </c>
-      <c r="AH57" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ57" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK57" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM57" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO57" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
@@ -7287,10 +7282,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122716303</v>
+        <v>122720558</v>
       </c>
       <c r="B58" t="n">
-        <v>57478</v>
+        <v>57494</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7303,16 +7298,16 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -7328,14 +7323,14 @@
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Finnbodarna, Hammerdal, Finnbodarna, Hammerdal, Jmt</t>
+          <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>520250</v>
+        <v>519949</v>
       </c>
       <c r="R58" t="n">
-        <v>7035363</v>
+        <v>7035254</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7372,7 +7367,7 @@
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Äldre hackspår i stambasen.</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7383,6 +7378,31 @@
       </c>
       <c r="AG58" t="b">
         <v>0</v>
+      </c>
+      <c r="AH58" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ58" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK58" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM58" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO58" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
@@ -7399,10 +7419,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122716673</v>
+        <v>122716757</v>
       </c>
       <c r="B59" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7415,42 +7435,37 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Spejkmyren, Spejkmyren, Jmt</t>
+          <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>520108</v>
+        <v>520316</v>
       </c>
       <c r="R59" t="n">
-        <v>7035462</v>
+        <v>7035491</v>
       </c>
       <c r="S59" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7482,11 +7497,6 @@
           <t>2025-02-23</t>
         </is>
       </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD59" t="b">
         <v>0</v>
       </c>
@@ -7495,6 +7505,31 @@
       </c>
       <c r="AG59" t="b">
         <v>0</v>
+      </c>
+      <c r="AH59" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ59" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK59" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM59" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO59" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
@@ -7511,10 +7546,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122720454</v>
+        <v>122715569</v>
       </c>
       <c r="B60" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7527,39 +7562,34 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Spejkmyren, Spejkmyren, Jmt</t>
+          <t>Djupmyren, Djupmyren, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>519849</v>
+        <v>520115</v>
       </c>
       <c r="R60" t="n">
-        <v>7035406</v>
+        <v>7035562</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7596,7 +7626,7 @@
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7607,6 +7637,31 @@
       </c>
       <c r="AG60" t="b">
         <v>0</v>
+      </c>
+      <c r="AH60" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ60" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK60" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM60" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO60" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
@@ -7623,10 +7678,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122720065</v>
+        <v>122716392</v>
       </c>
       <c r="B61" t="n">
-        <v>78766</v>
+        <v>79848</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7639,34 +7694,39 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Spejkmyren, Spejkmyren, Jmt</t>
+          <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>520062</v>
+        <v>520385</v>
       </c>
       <c r="R61" t="n">
-        <v>7035232</v>
+        <v>7035518</v>
       </c>
       <c r="S61" t="n">
         <v>8</v>
@@ -7699,6 +7759,11 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-02-23</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>På gran intill en gammal sälg.</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7750,10 +7815,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122715999</v>
+        <v>122717343</v>
       </c>
       <c r="B62" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7766,37 +7831,42 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Finnbodarna, Finnbodarna, Jmt</t>
+          <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>520311</v>
+        <v>520034</v>
       </c>
       <c r="R62" t="n">
-        <v>7035566</v>
+        <v>7035339</v>
       </c>
       <c r="S62" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7828,6 +7898,11 @@
           <t>2025-02-23</t>
         </is>
       </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD62" t="b">
         <v>0</v>
       </c>
@@ -7836,31 +7911,6 @@
       </c>
       <c r="AG62" t="b">
         <v>0</v>
-      </c>
-      <c r="AH62" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ62" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK62" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM62" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO62" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
@@ -7877,10 +7927,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122720823</v>
+        <v>122715836</v>
       </c>
       <c r="B63" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7893,53 +7943,39 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
       <c r="K63" t="inlineStr">
         <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L63" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Spejkmyren, Spejkmyren, Jmt</t>
+          <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>519842</v>
+        <v>520269</v>
       </c>
       <c r="R63" t="n">
-        <v>7035388</v>
+        <v>7035574</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7972,11 +8008,6 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-02-23</t>
-        </is>
-      </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>Trummande</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -8003,10 +8034,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122720368</v>
+        <v>122716234</v>
       </c>
       <c r="B64" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -8019,39 +8050,34 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Spejkmyren, Spejkmyren, Jmt</t>
+          <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>519852</v>
+        <v>520362</v>
       </c>
       <c r="R64" t="n">
-        <v>7035392</v>
+        <v>7035500</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -8088,7 +8114,7 @@
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>På en klen gran intill en gammal sälg med lunglav.</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8099,6 +8125,31 @@
       </c>
       <c r="AG64" t="b">
         <v>0</v>
+      </c>
+      <c r="AH64" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ64" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK64" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM64" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO64" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
@@ -8115,10 +8166,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122719875</v>
+        <v>122717488</v>
       </c>
       <c r="B65" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -8131,39 +8182,34 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>519983</v>
+        <v>520000</v>
       </c>
       <c r="R65" t="n">
-        <v>7035206</v>
+        <v>7035297</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -8196,11 +8242,6 @@
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-02-23</t>
-        </is>
-      </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8227,10 +8268,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122719533</v>
+        <v>122716295</v>
       </c>
       <c r="B66" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -8243,39 +8284,39 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Spejkmyren, Spejkmyren, Jmt</t>
+          <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>519948</v>
+        <v>520378</v>
       </c>
       <c r="R66" t="n">
-        <v>7035187</v>
+        <v>7035512</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -8312,7 +8353,7 @@
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ymnig påväxt på en grovbarkad gammal sälg. Fertila bålar med apothecier.</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8323,6 +8364,31 @@
       </c>
       <c r="AG66" t="b">
         <v>0</v>
+      </c>
+      <c r="AH66" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ66" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK66" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM66" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO66" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
@@ -8339,10 +8405,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>122716682</v>
+        <v>122720548</v>
       </c>
       <c r="B67" t="n">
-        <v>57631</v>
+        <v>90970</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8355,43 +8421,34 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>103021</v>
+        <v>5432</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>par i lämplig häckbiotop</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>520101</v>
+        <v>519847</v>
       </c>
       <c r="R67" t="n">
-        <v>7035453</v>
+        <v>7035432</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8450,10 +8507,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>122716216</v>
+        <v>122717294</v>
       </c>
       <c r="B68" t="n">
-        <v>79847</v>
+        <v>90970</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8466,39 +8523,34 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="K68" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Finnbodarna, Finnbodarna, Jmt</t>
+          <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>520368</v>
+        <v>520013</v>
       </c>
       <c r="R68" t="n">
-        <v>7035513</v>
+        <v>7035340</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8533,11 +8585,6 @@
           <t>2025-02-23</t>
         </is>
       </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>På en gammal grovbarkad sälg.</t>
-        </is>
-      </c>
       <c r="AD68" t="b">
         <v>0</v>
       </c>
@@ -8546,31 +8593,6 @@
       </c>
       <c r="AG68" t="b">
         <v>0</v>
-      </c>
-      <c r="AH68" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ68" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK68" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM68" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO68" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
@@ -8587,10 +8609,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>122716293</v>
+        <v>122715790</v>
       </c>
       <c r="B69" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8603,39 +8625,39 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Finnbodarna, Hammerdal, Finnbodarna, Hammerdal, Jmt</t>
+          <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>520249</v>
+        <v>520267</v>
       </c>
       <c r="R69" t="n">
-        <v>7035364</v>
+        <v>7035581</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8668,11 +8690,6 @@
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-02-23</t>
-        </is>
-      </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8699,10 +8716,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>122717488</v>
+        <v>122721463</v>
       </c>
       <c r="B70" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8715,21 +8732,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8739,10 +8756,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>520000</v>
+        <v>519841</v>
       </c>
       <c r="R70" t="n">
-        <v>7035297</v>
+        <v>7035417</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8777,6 +8794,11 @@
           <t>2025-02-23</t>
         </is>
       </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
+        </is>
+      </c>
       <c r="AD70" t="b">
         <v>0</v>
       </c>
@@ -8785,6 +8807,31 @@
       </c>
       <c r="AG70" t="b">
         <v>0</v>
+      </c>
+      <c r="AH70" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ70" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK70" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM70" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO70" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
@@ -8801,7 +8848,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>122721463</v>
+        <v>122715757</v>
       </c>
       <c r="B71" t="n">
         <v>78766</v>
@@ -8837,14 +8884,14 @@
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Spejkmyren, Spejkmyren, Jmt</t>
+          <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>519841</v>
+        <v>520234</v>
       </c>
       <c r="R71" t="n">
-        <v>7035417</v>
+        <v>7035595</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8933,7 +8980,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>122716269</v>
+        <v>122719875</v>
       </c>
       <c r="B72" t="n">
         <v>57478</v>
@@ -8974,14 +9021,14 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Finnbodarna, Hammerdal, Finnbodarna, Hammerdal, Jmt</t>
+          <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>520256</v>
+        <v>519983</v>
       </c>
       <c r="R72" t="n">
-        <v>7035380</v>
+        <v>7035206</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -9045,10 +9092,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>122718013</v>
+        <v>122716443</v>
       </c>
       <c r="B73" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -9061,39 +9108,48 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr"/>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Spejkmyren, Spejkmyren, Jmt</t>
+          <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>519948</v>
+        <v>520251</v>
       </c>
       <c r="R73" t="n">
-        <v>7035313</v>
+        <v>7035394</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -9130,7 +9186,7 @@
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Garnlavsrikt</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -9157,10 +9213,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>122715934</v>
+        <v>122719979</v>
       </c>
       <c r="B74" t="n">
-        <v>78766</v>
+        <v>57631</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -9173,37 +9229,46 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Finnbodarna, Finnbodarna, Jmt</t>
+          <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>520303</v>
+        <v>519946</v>
       </c>
       <c r="R74" t="n">
-        <v>7035598</v>
+        <v>7035240</v>
       </c>
       <c r="S74" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -9235,11 +9300,6 @@
           <t>2025-02-23</t>
         </is>
       </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
-        </is>
-      </c>
       <c r="AD74" t="b">
         <v>0</v>
       </c>
@@ -9248,31 +9308,6 @@
       </c>
       <c r="AG74" t="b">
         <v>0</v>
-      </c>
-      <c r="AH74" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ74" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK74" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM74" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO74" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
@@ -9289,10 +9324,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>122716160</v>
+        <v>122715573</v>
       </c>
       <c r="B75" t="n">
-        <v>78766</v>
+        <v>79848</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -9305,21 +9340,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -9329,10 +9364,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>520349</v>
+        <v>520214</v>
       </c>
       <c r="R75" t="n">
-        <v>7035517</v>
+        <v>7035583</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -9375,31 +9410,6 @@
       </c>
       <c r="AG75" t="b">
         <v>0</v>
-      </c>
-      <c r="AH75" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ75" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK75" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM75" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO75" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
@@ -9416,10 +9426,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>122716801</v>
+        <v>122715874</v>
       </c>
       <c r="B76" t="n">
-        <v>57631</v>
+        <v>79876</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -9428,47 +9438,38 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>103021</v>
+        <v>6462</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M76" t="inlineStr">
-        <is>
-          <t>par i lämplig häckbiotop</t>
-        </is>
-      </c>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Spejkmyren, Spejkmyren, Jmt</t>
+          <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>520083</v>
+        <v>520265</v>
       </c>
       <c r="R76" t="n">
-        <v>7035403</v>
+        <v>7035574</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -9527,10 +9528,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>122715775</v>
+        <v>122719371</v>
       </c>
       <c r="B77" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -9543,42 +9544,37 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
-      <c r="K77" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Finnbodarna, Finnbodarna, Jmt</t>
+          <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>520252</v>
+        <v>519943</v>
       </c>
       <c r="R77" t="n">
-        <v>7035576</v>
+        <v>7035270</v>
       </c>
       <c r="S77" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -9610,11 +9606,6 @@
           <t>2025-02-23</t>
         </is>
       </c>
-      <c r="AC77" t="inlineStr">
-        <is>
-          <t>På björk</t>
-        </is>
-      </c>
       <c r="AD77" t="b">
         <v>0</v>
       </c>
@@ -9623,6 +9614,31 @@
       </c>
       <c r="AG77" t="b">
         <v>0</v>
+      </c>
+      <c r="AH77" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ77" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK77" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM77" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO77" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
@@ -9639,10 +9655,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>122715778</v>
+        <v>122716645</v>
       </c>
       <c r="B78" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -9655,39 +9671,39 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
-      <c r="K78" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Finnbodarna, Finnbodarna, Jmt</t>
+          <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>520259</v>
+        <v>520129</v>
       </c>
       <c r="R78" t="n">
-        <v>7035574</v>
+        <v>7035444</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9720,6 +9736,11 @@
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-02-23</t>
+        </is>
+      </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9746,10 +9767,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>122715766</v>
+        <v>122720869</v>
       </c>
       <c r="B79" t="n">
-        <v>90970</v>
+        <v>78766</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -9762,34 +9783,34 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Finnbodarna, Finnbodarna, Jmt</t>
+          <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>520252</v>
+        <v>519960</v>
       </c>
       <c r="R79" t="n">
-        <v>7035591</v>
+        <v>7035342</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9832,6 +9853,31 @@
       </c>
       <c r="AG79" t="b">
         <v>0</v>
+      </c>
+      <c r="AH79" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ79" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK79" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM79" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO79" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
@@ -9848,10 +9894,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>122715849</v>
+        <v>122717636</v>
       </c>
       <c r="B80" t="n">
-        <v>79876</v>
+        <v>57478</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -9860,38 +9906,43 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Finnbodarna, Finnbodarna, Jmt</t>
+          <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>520268</v>
+        <v>519970</v>
       </c>
       <c r="R80" t="n">
-        <v>7035575</v>
+        <v>7035297</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9924,6 +9975,11 @@
       <c r="AA80" t="inlineStr">
         <is>
           <t>2025-02-23</t>
+        </is>
+      </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9950,10 +10006,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>122715779</v>
+        <v>122716387</v>
       </c>
       <c r="B81" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9966,42 +10022,42 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
-      <c r="K81" t="inlineStr">
-        <is>
-          <t>med soral</t>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Finnbodarna, Finnbodarna, Jmt</t>
+          <t>Finnbodarna, Hammerdal, Finnbodarna, Hammerdal, Jmt</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>520223</v>
+        <v>520278</v>
       </c>
       <c r="R81" t="n">
-        <v>7035609</v>
+        <v>7035397</v>
       </c>
       <c r="S81" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -10033,6 +10089,11 @@
           <t>2025-02-23</t>
         </is>
       </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD81" t="b">
         <v>0</v>
       </c>
@@ -10041,31 +10102,6 @@
       </c>
       <c r="AG81" t="b">
         <v>0</v>
-      </c>
-      <c r="AH81" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ81" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK81" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM81" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO81" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
@@ -10082,10 +10118,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>122717468</v>
+        <v>122715775</v>
       </c>
       <c r="B82" t="n">
-        <v>57494</v>
+        <v>79847</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -10098,43 +10134,39 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Spejkmyren, Spejkmyren, Jmt</t>
+          <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>520020</v>
+        <v>520252</v>
       </c>
       <c r="R82" t="n">
-        <v>7035330</v>
+        <v>7035576</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -10167,6 +10199,11 @@
       <c r="AA82" t="inlineStr">
         <is>
           <t>2025-02-23</t>
+        </is>
+      </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>På björk</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -10193,10 +10230,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>122716427</v>
+        <v>122715868</v>
       </c>
       <c r="B83" t="n">
-        <v>78767</v>
+        <v>79847</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -10209,37 +10246,42 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>230405</v>
+        <v>6458</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P83" t="inlineStr">
         <is>
           <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>520388</v>
+        <v>520265</v>
       </c>
       <c r="R83" t="n">
-        <v>7035490</v>
+        <v>7035574</v>
       </c>
       <c r="S83" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -10271,11 +10313,6 @@
           <t>2025-02-23</t>
         </is>
       </c>
-      <c r="AC83" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
-        </is>
-      </c>
       <c r="AD83" t="b">
         <v>0</v>
       </c>
@@ -10284,31 +10321,6 @@
       </c>
       <c r="AG83" t="b">
         <v>0</v>
-      </c>
-      <c r="AH83" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ83" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK83" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM83" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO83" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
@@ -10325,10 +10337,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>122720889</v>
+        <v>122717446</v>
       </c>
       <c r="B84" t="n">
-        <v>57478</v>
+        <v>90970</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -10341,39 +10353,34 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
-      <c r="M84" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P84" t="inlineStr">
         <is>
           <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>519841</v>
+        <v>520006</v>
       </c>
       <c r="R84" t="n">
-        <v>7035390</v>
+        <v>7035303</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -10406,11 +10413,6 @@
       <c r="AA84" t="inlineStr">
         <is>
           <t>2025-02-23</t>
-        </is>
-      </c>
-      <c r="AC84" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -10437,10 +10439,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>122715648</v>
+        <v>122717929</v>
       </c>
       <c r="B85" t="n">
-        <v>57478</v>
+        <v>79876</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -10449,46 +10451,46 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
-      <c r="M85" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Finnbodarna, Hammerdal, Finnbodarna, Hammerdal, Jmt</t>
+          <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>520219</v>
+        <v>520029</v>
       </c>
       <c r="R85" t="n">
-        <v>7035597</v>
+        <v>7035292</v>
       </c>
       <c r="S85" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -10520,11 +10522,6 @@
           <t>2025-02-23</t>
         </is>
       </c>
-      <c r="AC85" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD85" t="b">
         <v>0</v>
       </c>
@@ -10533,6 +10530,31 @@
       </c>
       <c r="AG85" t="b">
         <v>0</v>
+      </c>
+      <c r="AH85" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ85" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK85" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM85" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO85" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
@@ -10549,10 +10571,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>122717636</v>
+        <v>122715669</v>
       </c>
       <c r="B86" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -10565,39 +10587,39 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
-      <c r="M86" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Spejkmyren, Spejkmyren, Jmt</t>
+          <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>519970</v>
+        <v>520221</v>
       </c>
       <c r="R86" t="n">
-        <v>7035297</v>
+        <v>7035600</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -10630,11 +10652,6 @@
       <c r="AA86" t="inlineStr">
         <is>
           <t>2025-02-23</t>
-        </is>
-      </c>
-      <c r="AC86" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -10763,10 +10780,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>122721035</v>
+        <v>122715779</v>
       </c>
       <c r="B88" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -10779,37 +10796,42 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Spejkmyren, Spejkmyren, Jmt</t>
+          <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>519897</v>
+        <v>520223</v>
       </c>
       <c r="R88" t="n">
-        <v>7035374</v>
+        <v>7035609</v>
       </c>
       <c r="S88" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -10857,22 +10879,22 @@
       </c>
       <c r="AJ88" t="inlineStr">
         <is>
-          <t>garnlav</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK88" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AM88" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO88" t="inlineStr">
         <is>
-          <t>Branch on living tree # Alectoria sarmentosa</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT88" t="inlineStr"/>
@@ -10890,10 +10912,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>122715502</v>
+        <v>122720474</v>
       </c>
       <c r="B89" t="n">
-        <v>78766</v>
+        <v>57494</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -10906,42 +10928,51 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr"/>
-      <c r="K89" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Djupmyren, Djupmyren, Jmt</t>
+          <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>520110</v>
+        <v>519848</v>
       </c>
       <c r="R89" t="n">
-        <v>7035585</v>
+        <v>7035394</v>
       </c>
       <c r="S89" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -10973,11 +11004,6 @@
           <t>2025-02-23</t>
         </is>
       </c>
-      <c r="AC89" t="inlineStr">
-        <is>
-          <t>Gott om långväxt garnlav på många granar. Vissa bålar är här fertila.</t>
-        </is>
-      </c>
       <c r="AD89" t="b">
         <v>0</v>
       </c>
@@ -10986,31 +11012,6 @@
       </c>
       <c r="AG89" t="b">
         <v>0</v>
-      </c>
-      <c r="AH89" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ89" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK89" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM89" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO89" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
@@ -11027,10 +11028,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>122720281</v>
+        <v>122717468</v>
       </c>
       <c r="B90" t="n">
-        <v>57478</v>
+        <v>57494</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -11043,16 +11044,16 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -11060,10 +11061,14 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I90" t="inlineStr"/>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P90" t="inlineStr">
@@ -11072,10 +11077,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>519850</v>
+        <v>520020</v>
       </c>
       <c r="R90" t="n">
-        <v>7035373</v>
+        <v>7035330</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -11108,11 +11113,6 @@
       <c r="AA90" t="inlineStr">
         <is>
           <t>2025-02-23</t>
-        </is>
-      </c>
-      <c r="AC90" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD90" t="b">

--- a/artfynd/A 1625-2025 artfynd.xlsx
+++ b/artfynd/A 1625-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122715978</v>
+        <v>122717164</v>
       </c>
       <c r="B2" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,39 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Finnbodarna, Finnbodarna, Jmt</t>
+          <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>520243</v>
+        <v>520120</v>
       </c>
       <c r="R2" t="n">
-        <v>7035552</v>
+        <v>7035405</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -766,6 +761,31 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -782,10 +802,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122716269</v>
+        <v>122717284</v>
       </c>
       <c r="B3" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,42 +818,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Finnbodarna, Hammerdal, Finnbodarna, Hammerdal, Jmt</t>
+          <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>520256</v>
+        <v>520031</v>
       </c>
       <c r="R3" t="n">
-        <v>7035380</v>
+        <v>7035353</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -867,7 +882,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Långväxta bålar på flertalet granar.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -878,6 +893,31 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -894,10 +934,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122717164</v>
+        <v>122715978</v>
       </c>
       <c r="B4" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -910,34 +950,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Spejkmyren, Spejkmyren, Jmt</t>
+          <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>520120</v>
+        <v>520243</v>
       </c>
       <c r="R4" t="n">
-        <v>7035405</v>
+        <v>7035552</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -980,31 +1025,6 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1021,10 +1041,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122717284</v>
+        <v>122716269</v>
       </c>
       <c r="B5" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1037,37 +1057,42 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Spejkmyren, Spejkmyren, Jmt</t>
+          <t>Finnbodarna, Hammerdal, Finnbodarna, Hammerdal, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>520031</v>
+        <v>520256</v>
       </c>
       <c r="R5" t="n">
-        <v>7035353</v>
+        <v>7035380</v>
       </c>
       <c r="S5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1101,7 +1126,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Långväxta bålar på flertalet granar.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1112,31 +1137,6 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -2307,10 +2307,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122715841</v>
+        <v>122720281</v>
       </c>
       <c r="B16" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2323,42 +2323,42 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>med soral</t>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Finnbodarna, Finnbodarna, Jmt</t>
+          <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>520229</v>
+        <v>519850</v>
       </c>
       <c r="R16" t="n">
-        <v>7035608</v>
+        <v>7035373</v>
       </c>
       <c r="S16" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2392,7 +2392,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>På en björk.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2403,31 +2403,6 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
-      </c>
-      <c r="AH16" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Betula</t>
-        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
@@ -2444,10 +2419,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122717952</v>
+        <v>122715841</v>
       </c>
       <c r="B17" t="n">
-        <v>57494</v>
+        <v>79847</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2460,46 +2435,42 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Spejkmyren, Spejkmyren, Jmt</t>
+          <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>519951</v>
+        <v>520229</v>
       </c>
       <c r="R17" t="n">
-        <v>7035320</v>
+        <v>7035608</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2531,6 +2502,11 @@
           <t>2025-02-23</t>
         </is>
       </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>På en björk.</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
@@ -2539,6 +2515,31 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AM17" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Betula</t>
+        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
@@ -2555,10 +2556,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122720281</v>
+        <v>122717952</v>
       </c>
       <c r="B18" t="n">
-        <v>57478</v>
+        <v>57494</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2571,16 +2572,16 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2588,10 +2589,14 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr"/>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2600,10 +2605,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>519850</v>
+        <v>519951</v>
       </c>
       <c r="R18" t="n">
-        <v>7035373</v>
+        <v>7035320</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2636,11 +2641,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-02-23</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -3306,10 +3306,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122720629</v>
+        <v>122715778</v>
       </c>
       <c r="B24" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3322,34 +3322,39 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Spejkmyren, Spejkmyren, Jmt</t>
+          <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>519935</v>
+        <v>520259</v>
       </c>
       <c r="R24" t="n">
-        <v>7035246</v>
+        <v>7035574</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3384,11 +3389,6 @@
           <t>2025-02-23</t>
         </is>
       </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
-        </is>
-      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
@@ -3397,31 +3397,6 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
-      </c>
-      <c r="AH24" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ24" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK24" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
@@ -3438,10 +3413,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122715778</v>
+        <v>122720368</v>
       </c>
       <c r="B25" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3454,39 +3429,39 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Finnbodarna, Finnbodarna, Jmt</t>
+          <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>520259</v>
+        <v>519852</v>
       </c>
       <c r="R25" t="n">
-        <v>7035574</v>
+        <v>7035392</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3519,6 +3494,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-02-23</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3809,10 +3789,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122720368</v>
+        <v>122720629</v>
       </c>
       <c r="B28" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3825,39 +3805,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>519852</v>
+        <v>519935</v>
       </c>
       <c r="R28" t="n">
-        <v>7035392</v>
+        <v>7035246</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3894,7 +3869,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3905,6 +3880,31 @@
       </c>
       <c r="AG28" t="b">
         <v>0</v>
+      </c>
+      <c r="AH28" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM28" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">

--- a/artfynd/A 1625-2025 artfynd.xlsx
+++ b/artfynd/A 1625-2025 artfynd.xlsx
@@ -3413,10 +3413,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122720368</v>
+        <v>122715502</v>
       </c>
       <c r="B25" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3429,42 +3429,42 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Spejkmyren, Spejkmyren, Jmt</t>
+          <t>Djupmyren, Djupmyren, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>519852</v>
+        <v>520110</v>
       </c>
       <c r="R25" t="n">
-        <v>7035392</v>
+        <v>7035585</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3498,7 +3498,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Gott om långväxt garnlav på många granar. Vissa bålar är här fertila.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3509,6 +3509,31 @@
       </c>
       <c r="AG25" t="b">
         <v>0</v>
+      </c>
+      <c r="AH25" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM25" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
@@ -3525,7 +3550,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122715502</v>
+        <v>122720065</v>
       </c>
       <c r="B26" t="n">
         <v>78766</v>
@@ -3559,24 +3584,19 @@
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Djupmyren, Djupmyren, Jmt</t>
+          <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>520110</v>
+        <v>520062</v>
       </c>
       <c r="R26" t="n">
-        <v>7035585</v>
+        <v>7035232</v>
       </c>
       <c r="S26" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3606,11 +3626,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-02-23</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Gott om långväxt garnlav på många granar. Vissa bålar är här fertila.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3662,10 +3677,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122720065</v>
+        <v>122720368</v>
       </c>
       <c r="B27" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3678,37 +3693,42 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>520062</v>
+        <v>519852</v>
       </c>
       <c r="R27" t="n">
-        <v>7035232</v>
+        <v>7035392</v>
       </c>
       <c r="S27" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3740,6 +3760,11 @@
           <t>2025-02-23</t>
         </is>
       </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
@@ -3748,31 +3773,6 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
-      </c>
-      <c r="AH27" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ27" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK27" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM27" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO27" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
@@ -6270,10 +6270,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122716801</v>
+        <v>122715648</v>
       </c>
       <c r="B49" t="n">
-        <v>57631</v>
+        <v>57478</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6286,43 +6286,39 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="M49" t="inlineStr">
         <is>
-          <t>par i lämplig häckbiotop</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Spejkmyren, Spejkmyren, Jmt</t>
+          <t>Finnbodarna, Hammerdal, Finnbodarna, Hammerdal, Jmt</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>520083</v>
+        <v>520219</v>
       </c>
       <c r="R49" t="n">
-        <v>7035403</v>
+        <v>7035597</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6355,6 +6351,11 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-02-23</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6381,10 +6382,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122715801</v>
+        <v>122716293</v>
       </c>
       <c r="B50" t="n">
-        <v>79848</v>
+        <v>57478</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6397,34 +6398,39 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Finnbodarna, Finnbodarna, Jmt</t>
+          <t>Finnbodarna, Hammerdal, Finnbodarna, Hammerdal, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>520266</v>
+        <v>520249</v>
       </c>
       <c r="R50" t="n">
-        <v>7035582</v>
+        <v>7035364</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6457,6 +6463,11 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-02-23</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6483,7 +6494,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122715648</v>
+        <v>122719648</v>
       </c>
       <c r="B51" t="n">
         <v>57478</v>
@@ -6524,14 +6535,14 @@
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Finnbodarna, Hammerdal, Finnbodarna, Hammerdal, Jmt</t>
+          <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>520219</v>
+        <v>519939</v>
       </c>
       <c r="R51" t="n">
-        <v>7035597</v>
+        <v>7035194</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6595,10 +6606,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122716293</v>
+        <v>122716801</v>
       </c>
       <c r="B52" t="n">
-        <v>57478</v>
+        <v>57631</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6611,39 +6622,43 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>par i lämplig häckbiotop</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Finnbodarna, Hammerdal, Finnbodarna, Hammerdal, Jmt</t>
+          <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>520249</v>
+        <v>520083</v>
       </c>
       <c r="R52" t="n">
-        <v>7035364</v>
+        <v>7035403</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6676,11 +6691,6 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-02-23</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6707,10 +6717,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122719648</v>
+        <v>122715801</v>
       </c>
       <c r="B53" t="n">
-        <v>57478</v>
+        <v>79848</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6723,39 +6733,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Spejkmyren, Spejkmyren, Jmt</t>
+          <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>519939</v>
+        <v>520266</v>
       </c>
       <c r="R53" t="n">
-        <v>7035194</v>
+        <v>7035582</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6788,11 +6793,6 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-02-23</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD53" t="b">

--- a/artfynd/A 1625-2025 artfynd.xlsx
+++ b/artfynd/A 1625-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122717164</v>
+        <v>122715978</v>
       </c>
       <c r="B2" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,39 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Spejkmyren, Spejkmyren, Jmt</t>
+          <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>520120</v>
+        <v>520243</v>
       </c>
       <c r="R2" t="n">
-        <v>7035405</v>
+        <v>7035552</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -761,31 +766,6 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -802,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122717284</v>
+        <v>122716269</v>
       </c>
       <c r="B3" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -818,37 +798,42 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Spejkmyren, Spejkmyren, Jmt</t>
+          <t>Finnbodarna, Hammerdal, Finnbodarna, Hammerdal, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>520031</v>
+        <v>520256</v>
       </c>
       <c r="R3" t="n">
-        <v>7035353</v>
+        <v>7035380</v>
       </c>
       <c r="S3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -882,7 +867,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Långväxta bålar på flertalet granar.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -893,31 +878,6 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -934,10 +894,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122715978</v>
+        <v>122717164</v>
       </c>
       <c r="B4" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -950,39 +910,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Finnbodarna, Finnbodarna, Jmt</t>
+          <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>520243</v>
+        <v>520120</v>
       </c>
       <c r="R4" t="n">
-        <v>7035552</v>
+        <v>7035405</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1025,6 +980,31 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1041,10 +1021,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122716269</v>
+        <v>122717284</v>
       </c>
       <c r="B5" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1057,42 +1037,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Finnbodarna, Hammerdal, Finnbodarna, Hammerdal, Jmt</t>
+          <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>520256</v>
+        <v>520031</v>
       </c>
       <c r="R5" t="n">
-        <v>7035380</v>
+        <v>7035353</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1126,7 +1101,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Långväxta bålar på flertalet granar.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1137,6 +1112,31 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -3921,10 +3921,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122716427</v>
+        <v>122715953</v>
       </c>
       <c r="B29" t="n">
-        <v>78767</v>
+        <v>79848</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3937,21 +3937,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>230405</v>
+        <v>2081</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3961,13 +3961,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>520388</v>
+        <v>520254</v>
       </c>
       <c r="R29" t="n">
-        <v>7035490</v>
+        <v>7035555</v>
       </c>
       <c r="S29" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3999,11 +3999,6 @@
           <t>2025-02-23</t>
         </is>
       </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
-        </is>
-      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
@@ -4012,31 +4007,6 @@
       </c>
       <c r="AG29" t="b">
         <v>0</v>
-      </c>
-      <c r="AH29" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ29" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK29" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM29" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO29" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
@@ -4053,10 +4023,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122716682</v>
+        <v>122715766</v>
       </c>
       <c r="B30" t="n">
-        <v>57631</v>
+        <v>90970</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4069,43 +4039,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>103021</v>
+        <v>5432</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>par i lämplig häckbiotop</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Spejkmyren, Spejkmyren, Jmt</t>
+          <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>520101</v>
+        <v>520252</v>
       </c>
       <c r="R30" t="n">
-        <v>7035453</v>
+        <v>7035591</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4164,10 +4125,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122715953</v>
+        <v>122717873</v>
       </c>
       <c r="B31" t="n">
-        <v>79848</v>
+        <v>79847</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4180,37 +4141,42 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Finnbodarna, Finnbodarna, Jmt</t>
+          <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>520254</v>
+        <v>520033</v>
       </c>
       <c r="R31" t="n">
-        <v>7035555</v>
+        <v>7035301</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4250,6 +4216,31 @@
       </c>
       <c r="AG31" t="b">
         <v>0</v>
+      </c>
+      <c r="AH31" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM31" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
@@ -4266,10 +4257,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122715766</v>
+        <v>122715949</v>
       </c>
       <c r="B32" t="n">
-        <v>90970</v>
+        <v>79847</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4282,21 +4273,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4306,10 +4297,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>520252</v>
+        <v>520254</v>
       </c>
       <c r="R32" t="n">
-        <v>7035591</v>
+        <v>7035555</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4368,10 +4359,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122719533</v>
+        <v>122721035</v>
       </c>
       <c r="B33" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4384,42 +4375,37 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>519948</v>
+        <v>519897</v>
       </c>
       <c r="R33" t="n">
-        <v>7035187</v>
+        <v>7035374</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4451,11 +4437,6 @@
           <t>2025-02-23</t>
         </is>
       </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
@@ -4464,6 +4445,31 @@
       </c>
       <c r="AG33" t="b">
         <v>0</v>
+      </c>
+      <c r="AH33" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>garnlav</t>
+        </is>
+      </c>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="AM33" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Alectoria sarmentosa</t>
+        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
@@ -4480,10 +4486,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122717873</v>
+        <v>122720686</v>
       </c>
       <c r="B34" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4496,42 +4502,37 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>520033</v>
+        <v>519903</v>
       </c>
       <c r="R34" t="n">
-        <v>7035301</v>
+        <v>7035224</v>
       </c>
       <c r="S34" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4579,22 +4580,22 @@
       </c>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK34" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM34" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT34" t="inlineStr"/>
@@ -4612,10 +4613,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122715949</v>
+        <v>122715934</v>
       </c>
       <c r="B35" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4628,21 +4629,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4652,13 +4653,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>520254</v>
+        <v>520303</v>
       </c>
       <c r="R35" t="n">
-        <v>7035555</v>
+        <v>7035598</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4690,6 +4691,11 @@
           <t>2025-02-23</t>
         </is>
       </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
+        </is>
+      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
@@ -4698,6 +4704,31 @@
       </c>
       <c r="AG35" t="b">
         <v>0</v>
+      </c>
+      <c r="AH35" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ35" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK35" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM35" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO35" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
@@ -4714,10 +4745,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122721035</v>
+        <v>122719533</v>
       </c>
       <c r="B36" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4730,37 +4761,42 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>519897</v>
+        <v>519948</v>
       </c>
       <c r="R36" t="n">
-        <v>7035374</v>
+        <v>7035187</v>
       </c>
       <c r="S36" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4792,6 +4828,11 @@
           <t>2025-02-23</t>
         </is>
       </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
@@ -4800,31 +4841,6 @@
       </c>
       <c r="AG36" t="b">
         <v>0</v>
-      </c>
-      <c r="AH36" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ36" t="inlineStr">
-        <is>
-          <t>garnlav</t>
-        </is>
-      </c>
-      <c r="AK36" t="inlineStr">
-        <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="AM36" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO36" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Alectoria sarmentosa</t>
-        </is>
       </c>
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
@@ -4841,10 +4857,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122720686</v>
+        <v>122716682</v>
       </c>
       <c r="B37" t="n">
-        <v>78766</v>
+        <v>57631</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4857,34 +4873,43 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>519903</v>
+        <v>520101</v>
       </c>
       <c r="R37" t="n">
-        <v>7035224</v>
+        <v>7035453</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4927,31 +4952,6 @@
       </c>
       <c r="AG37" t="b">
         <v>0</v>
-      </c>
-      <c r="AH37" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ37" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK37" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM37" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO37" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
@@ -4968,10 +4968,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122715934</v>
+        <v>122716427</v>
       </c>
       <c r="B38" t="n">
-        <v>78766</v>
+        <v>78767</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4984,16 +4984,16 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>230405</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -5008,13 +5008,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>520303</v>
+        <v>520388</v>
       </c>
       <c r="R38" t="n">
-        <v>7035598</v>
+        <v>7035490</v>
       </c>
       <c r="S38" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>

--- a/artfynd/A 1625-2025 artfynd.xlsx
+++ b/artfynd/A 1625-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122715978</v>
+        <v>122717164</v>
       </c>
       <c r="B2" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,39 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Finnbodarna, Finnbodarna, Jmt</t>
+          <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>520243</v>
+        <v>520120</v>
       </c>
       <c r="R2" t="n">
-        <v>7035552</v>
+        <v>7035405</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -766,6 +761,31 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -782,10 +802,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122716269</v>
+        <v>122717284</v>
       </c>
       <c r="B3" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -798,42 +818,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Finnbodarna, Hammerdal, Finnbodarna, Hammerdal, Jmt</t>
+          <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>520256</v>
+        <v>520031</v>
       </c>
       <c r="R3" t="n">
-        <v>7035380</v>
+        <v>7035353</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -867,7 +882,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Långväxta bålar på flertalet granar.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -878,6 +893,31 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -894,10 +934,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122717164</v>
+        <v>122715978</v>
       </c>
       <c r="B4" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -910,34 +950,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Spejkmyren, Spejkmyren, Jmt</t>
+          <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>520120</v>
+        <v>520243</v>
       </c>
       <c r="R4" t="n">
-        <v>7035405</v>
+        <v>7035552</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -980,31 +1025,6 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1021,10 +1041,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122717284</v>
+        <v>122716269</v>
       </c>
       <c r="B5" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1037,37 +1057,42 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Spejkmyren, Spejkmyren, Jmt</t>
+          <t>Finnbodarna, Hammerdal, Finnbodarna, Hammerdal, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>520031</v>
+        <v>520256</v>
       </c>
       <c r="R5" t="n">
-        <v>7035353</v>
+        <v>7035380</v>
       </c>
       <c r="S5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1101,7 +1126,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Långväxta bålar på flertalet granar.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1112,31 +1137,6 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -3413,10 +3413,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122715502</v>
+        <v>122720368</v>
       </c>
       <c r="B25" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3429,42 +3429,42 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Djupmyren, Djupmyren, Jmt</t>
+          <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>520110</v>
+        <v>519852</v>
       </c>
       <c r="R25" t="n">
-        <v>7035585</v>
+        <v>7035392</v>
       </c>
       <c r="S25" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3498,7 +3498,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Gott om långväxt garnlav på många granar. Vissa bålar är här fertila.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3509,31 +3509,6 @@
       </c>
       <c r="AG25" t="b">
         <v>0</v>
-      </c>
-      <c r="AH25" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ25" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK25" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM25" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO25" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
@@ -3550,7 +3525,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122720065</v>
+        <v>122715502</v>
       </c>
       <c r="B26" t="n">
         <v>78766</v>
@@ -3584,19 +3559,24 @@
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Spejkmyren, Spejkmyren, Jmt</t>
+          <t>Djupmyren, Djupmyren, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>520062</v>
+        <v>520110</v>
       </c>
       <c r="R26" t="n">
-        <v>7035232</v>
+        <v>7035585</v>
       </c>
       <c r="S26" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3626,6 +3606,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-02-23</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Gott om långväxt garnlav på många granar. Vissa bålar är här fertila.</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3677,10 +3662,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122720368</v>
+        <v>122720065</v>
       </c>
       <c r="B27" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3693,42 +3678,37 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>519852</v>
+        <v>520062</v>
       </c>
       <c r="R27" t="n">
-        <v>7035392</v>
+        <v>7035232</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3760,11 +3740,6 @@
           <t>2025-02-23</t>
         </is>
       </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD27" t="b">
         <v>0</v>
       </c>
@@ -3773,6 +3748,31 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
+      </c>
+      <c r="AH27" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM27" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">

--- a/artfynd/A 1625-2025 artfynd.xlsx
+++ b/artfynd/A 1625-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122717164</v>
+        <v>122715949</v>
       </c>
       <c r="B2" t="n">
-        <v>78766</v>
+        <v>79850</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Spejkmyren, Spejkmyren, Jmt</t>
+          <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>520120</v>
+        <v>520254</v>
       </c>
       <c r="R2" t="n">
-        <v>7035405</v>
+        <v>7035555</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -761,31 +761,6 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -802,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122717284</v>
+        <v>122715669</v>
       </c>
       <c r="B3" t="n">
-        <v>78766</v>
+        <v>79850</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -818,37 +793,42 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Spejkmyren, Spejkmyren, Jmt</t>
+          <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>520031</v>
+        <v>520221</v>
       </c>
       <c r="R3" t="n">
-        <v>7035353</v>
+        <v>7035600</v>
       </c>
       <c r="S3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -880,11 +860,6 @@
           <t>2025-02-23</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Långväxta bålar på flertalet granar.</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -893,31 +868,6 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -934,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122715978</v>
+        <v>122720469</v>
       </c>
       <c r="B4" t="n">
-        <v>79847</v>
+        <v>78769</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -950,39 +900,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Finnbodarna, Finnbodarna, Jmt</t>
+          <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>520243</v>
+        <v>519996</v>
       </c>
       <c r="R4" t="n">
-        <v>7035552</v>
+        <v>7035241</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1025,6 +970,31 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1041,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122716269</v>
+        <v>122715569</v>
       </c>
       <c r="B5" t="n">
-        <v>57478</v>
+        <v>78769</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1057,39 +1027,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Finnbodarna, Hammerdal, Finnbodarna, Hammerdal, Jmt</t>
+          <t>Djupmyren, Djupmyren, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>520256</v>
+        <v>520115</v>
       </c>
       <c r="R5" t="n">
-        <v>7035380</v>
+        <v>7035562</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1126,7 +1091,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1137,6 +1102,31 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1153,10 +1143,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122715870</v>
+        <v>122719554</v>
       </c>
       <c r="B6" t="n">
-        <v>79848</v>
+        <v>57481</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1169,34 +1159,44 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Finnbodarna, Finnbodarna, Jmt</t>
+          <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>520265</v>
+        <v>519981</v>
       </c>
       <c r="R6" t="n">
-        <v>7035574</v>
+        <v>7035221</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1231,6 +1231,11 @@
           <t>2025-02-23</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Äldre ringhack som bedöms vara 5 - 10 år gamla.</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1239,6 +1244,31 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1255,10 +1285,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122715756</v>
+        <v>122719979</v>
       </c>
       <c r="B7" t="n">
-        <v>79847</v>
+        <v>57634</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1271,34 +1301,43 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Finnbodarna, Finnbodarna, Jmt</t>
+          <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>520256</v>
+        <v>519946</v>
       </c>
       <c r="R7" t="n">
-        <v>7035593</v>
+        <v>7035240</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1357,10 +1396,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122716329</v>
+        <v>122715953</v>
       </c>
       <c r="B8" t="n">
-        <v>79847</v>
+        <v>79851</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1373,42 +1412,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>520374</v>
+        <v>520254</v>
       </c>
       <c r="R8" t="n">
-        <v>7035511</v>
+        <v>7035555</v>
       </c>
       <c r="S8" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1440,11 +1474,6 @@
           <t>2025-02-23</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>På gran intill en gammal lunglavssälg.</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1453,31 +1482,6 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1494,10 +1498,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122720889</v>
+        <v>122721463</v>
       </c>
       <c r="B9" t="n">
-        <v>57478</v>
+        <v>78769</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1510,29 +1514,24 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Spejkmyren, Spejkmyren, Jmt</t>
@@ -1542,7 +1541,7 @@
         <v>519841</v>
       </c>
       <c r="R9" t="n">
-        <v>7035390</v>
+        <v>7035417</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1579,7 +1578,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1590,6 +1589,31 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1606,10 +1630,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122719829</v>
+        <v>122721035</v>
       </c>
       <c r="B10" t="n">
-        <v>57478</v>
+        <v>78769</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1622,42 +1646,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>519930</v>
+        <v>519897</v>
       </c>
       <c r="R10" t="n">
-        <v>7035181</v>
+        <v>7035374</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1689,11 +1708,6 @@
           <t>2025-02-23</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1702,6 +1716,31 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>garnlav</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Alectoria sarmentosa</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1718,10 +1757,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122715677</v>
+        <v>122717164</v>
       </c>
       <c r="B11" t="n">
-        <v>79848</v>
+        <v>78769</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1734,34 +1773,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2081</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Finnbodarna, Finnbodarna, Jmt</t>
+          <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>520221</v>
+        <v>520120</v>
       </c>
       <c r="R11" t="n">
-        <v>7035600</v>
+        <v>7035405</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1796,11 +1835,6 @@
           <t>2025-02-23</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>På gran</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
@@ -1809,6 +1843,31 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
@@ -1825,10 +1884,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122716964</v>
+        <v>122719829</v>
       </c>
       <c r="B12" t="n">
-        <v>90970</v>
+        <v>57481</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1841,34 +1900,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>520115</v>
+        <v>519930</v>
       </c>
       <c r="R12" t="n">
-        <v>7035402</v>
+        <v>7035181</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1901,6 +1965,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-02-23</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1927,10 +1996,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122720823</v>
+        <v>122716293</v>
       </c>
       <c r="B13" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1960,36 +2029,22 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Spejkmyren, Spejkmyren, Jmt</t>
+          <t>Finnbodarna, Hammerdal, Finnbodarna, Hammerdal, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>519842</v>
+        <v>520249</v>
       </c>
       <c r="R13" t="n">
-        <v>7035388</v>
+        <v>7035364</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2026,7 +2081,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Trummande</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2053,10 +2108,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122716673</v>
+        <v>122715756</v>
       </c>
       <c r="B14" t="n">
-        <v>57478</v>
+        <v>79850</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2069,39 +2124,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Spejkmyren, Spejkmyren, Jmt</t>
+          <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>520108</v>
+        <v>520256</v>
       </c>
       <c r="R14" t="n">
-        <v>7035462</v>
+        <v>7035593</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2134,11 +2184,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-02-23</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2165,10 +2210,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122719554</v>
+        <v>122715780</v>
       </c>
       <c r="B15" t="n">
-        <v>57478</v>
+        <v>79850</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2181,44 +2226,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Spejkmyren, Spejkmyren, Jmt</t>
+          <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>519981</v>
+        <v>520259</v>
       </c>
       <c r="R15" t="n">
-        <v>7035221</v>
+        <v>7035569</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2255,7 +2290,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Äldre ringhack som bedöms vara 5 - 10 år gamla.</t>
+          <t>På björk</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2266,31 +2301,6 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
-      </c>
-      <c r="AH15" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
@@ -2307,10 +2317,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122720281</v>
+        <v>122716392</v>
       </c>
       <c r="B16" t="n">
-        <v>57478</v>
+        <v>79851</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2323,42 +2333,42 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Spejkmyren, Spejkmyren, Jmt</t>
+          <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>519850</v>
+        <v>520385</v>
       </c>
       <c r="R16" t="n">
-        <v>7035373</v>
+        <v>7035518</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2392,7 +2402,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>På gran intill en gammal sälg.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2403,6 +2413,31 @@
       </c>
       <c r="AG16" t="b">
         <v>0</v>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM16" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
@@ -2419,10 +2454,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122715841</v>
+        <v>122719533</v>
       </c>
       <c r="B17" t="n">
-        <v>79847</v>
+        <v>57481</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2435,42 +2470,42 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>med soral</t>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Finnbodarna, Finnbodarna, Jmt</t>
+          <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>520229</v>
+        <v>519948</v>
       </c>
       <c r="R17" t="n">
-        <v>7035608</v>
+        <v>7035187</v>
       </c>
       <c r="S17" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2504,7 +2539,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>På en björk.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2515,31 +2550,6 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
-      </c>
-      <c r="AH17" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Betula</t>
-        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
@@ -2556,10 +2566,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122717952</v>
+        <v>122715778</v>
       </c>
       <c r="B18" t="n">
-        <v>57494</v>
+        <v>79850</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2572,43 +2582,39 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Spejkmyren, Spejkmyren, Jmt</t>
+          <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>519951</v>
+        <v>520259</v>
       </c>
       <c r="R18" t="n">
-        <v>7035320</v>
+        <v>7035574</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2667,10 +2673,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122716547</v>
+        <v>122720823</v>
       </c>
       <c r="B19" t="n">
-        <v>98271</v>
+        <v>57481</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2679,25 +2685,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>504</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Guckusko</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Cypripedium calceolus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2705,29 +2711,34 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>vinterståndare</t>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Finnbodarna, Finnbodarna, Jmt</t>
+          <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>520386</v>
+        <v>519842</v>
       </c>
       <c r="R19" t="n">
-        <v>7035492</v>
+        <v>7035388</v>
       </c>
       <c r="S19" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2761,7 +2772,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>En vinterståndare på till synes fuktig mark i en lucka.</t>
+          <t>Trummande</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2772,11 +2783,6 @@
       </c>
       <c r="AG19" t="b">
         <v>0</v>
-      </c>
-      <c r="AH19" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
@@ -2793,10 +2799,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122715795</v>
+        <v>122720869</v>
       </c>
       <c r="B20" t="n">
-        <v>79847</v>
+        <v>78769</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2809,37 +2815,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Finnbodarna, Finnbodarna, Jmt</t>
+          <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>520214</v>
+        <v>519960</v>
       </c>
       <c r="R20" t="n">
-        <v>7035599</v>
+        <v>7035342</v>
       </c>
       <c r="S20" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2869,11 +2875,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-02-23</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>På en klen gran intill en lunglavssälg.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2925,10 +2926,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122720469</v>
+        <v>122717952</v>
       </c>
       <c r="B21" t="n">
-        <v>78766</v>
+        <v>57497</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2941,34 +2942,43 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>519996</v>
+        <v>519951</v>
       </c>
       <c r="R21" t="n">
-        <v>7035241</v>
+        <v>7035320</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3011,31 +3021,6 @@
       </c>
       <c r="AG21" t="b">
         <v>0</v>
-      </c>
-      <c r="AH21" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
@@ -3052,10 +3037,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122715999</v>
+        <v>122715790</v>
       </c>
       <c r="B22" t="n">
-        <v>78766</v>
+        <v>79850</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3068,37 +3053,42 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>520311</v>
+        <v>520267</v>
       </c>
       <c r="R22" t="n">
-        <v>7035566</v>
+        <v>7035581</v>
       </c>
       <c r="S22" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3138,31 +3128,6 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
-      </c>
-      <c r="AH22" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
@@ -3179,10 +3144,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122716160</v>
+        <v>122715757</v>
       </c>
       <c r="B23" t="n">
-        <v>78766</v>
+        <v>78769</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3219,10 +3184,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>520349</v>
+        <v>520234</v>
       </c>
       <c r="R23" t="n">
-        <v>7035517</v>
+        <v>7035595</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3255,6 +3220,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-02-23</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3306,10 +3276,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122715778</v>
+        <v>122720327</v>
       </c>
       <c r="B24" t="n">
-        <v>79847</v>
+        <v>57481</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3322,39 +3292,39 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Finnbodarna, Finnbodarna, Jmt</t>
+          <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>520259</v>
+        <v>519838</v>
       </c>
       <c r="R24" t="n">
-        <v>7035574</v>
+        <v>7035393</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3387,6 +3357,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-02-23</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3413,10 +3388,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122720368</v>
+        <v>122720454</v>
       </c>
       <c r="B25" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3458,10 +3433,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>519852</v>
+        <v>519849</v>
       </c>
       <c r="R25" t="n">
-        <v>7035392</v>
+        <v>7035406</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3525,10 +3500,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122715502</v>
+        <v>122720474</v>
       </c>
       <c r="B26" t="n">
-        <v>78766</v>
+        <v>57497</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3541,42 +3516,51 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Djupmyren, Djupmyren, Jmt</t>
+          <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>520110</v>
+        <v>519848</v>
       </c>
       <c r="R26" t="n">
-        <v>7035585</v>
+        <v>7035394</v>
       </c>
       <c r="S26" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3608,11 +3592,6 @@
           <t>2025-02-23</t>
         </is>
       </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Gott om långväxt garnlav på många granar. Vissa bålar är här fertila.</t>
-        </is>
-      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
@@ -3621,31 +3600,6 @@
       </c>
       <c r="AG26" t="b">
         <v>0</v>
-      </c>
-      <c r="AH26" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ26" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK26" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM26" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO26" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
@@ -3662,10 +3616,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122720065</v>
+        <v>122715766</v>
       </c>
       <c r="B27" t="n">
-        <v>78766</v>
+        <v>90973</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3678,37 +3632,37 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Spejkmyren, Spejkmyren, Jmt</t>
+          <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>520062</v>
+        <v>520252</v>
       </c>
       <c r="R27" t="n">
-        <v>7035232</v>
+        <v>7035591</v>
       </c>
       <c r="S27" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3748,31 +3702,6 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
-      </c>
-      <c r="AH27" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ27" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK27" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM27" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO27" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
@@ -3789,10 +3718,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122720629</v>
+        <v>122720548</v>
       </c>
       <c r="B28" t="n">
-        <v>78766</v>
+        <v>90973</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3805,21 +3734,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3829,10 +3758,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>519935</v>
+        <v>519847</v>
       </c>
       <c r="R28" t="n">
-        <v>7035246</v>
+        <v>7035432</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3867,11 +3796,6 @@
           <t>2025-02-23</t>
         </is>
       </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
-        </is>
-      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
@@ -3880,31 +3804,6 @@
       </c>
       <c r="AG28" t="b">
         <v>0</v>
-      </c>
-      <c r="AH28" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ28" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK28" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM28" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO28" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
@@ -3921,10 +3820,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122715953</v>
+        <v>122717294</v>
       </c>
       <c r="B29" t="n">
-        <v>79848</v>
+        <v>90973</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3937,34 +3836,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>2081</v>
+        <v>5432</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Finnbodarna, Finnbodarna, Jmt</t>
+          <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>520254</v>
+        <v>520013</v>
       </c>
       <c r="R29" t="n">
-        <v>7035555</v>
+        <v>7035340</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4023,10 +3922,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122715766</v>
+        <v>122715795</v>
       </c>
       <c r="B30" t="n">
-        <v>90970</v>
+        <v>79850</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4039,21 +3938,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -4063,13 +3962,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>520252</v>
+        <v>520214</v>
       </c>
       <c r="R30" t="n">
-        <v>7035591</v>
+        <v>7035599</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4101,6 +4000,11 @@
           <t>2025-02-23</t>
         </is>
       </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>På en klen gran intill en lunglavssälg.</t>
+        </is>
+      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
@@ -4109,6 +4013,31 @@
       </c>
       <c r="AG30" t="b">
         <v>0</v>
+      </c>
+      <c r="AH30" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM30" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
@@ -4125,10 +4054,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122717873</v>
+        <v>122720629</v>
       </c>
       <c r="B31" t="n">
-        <v>79847</v>
+        <v>78769</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4141,42 +4070,37 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>520033</v>
+        <v>519935</v>
       </c>
       <c r="R31" t="n">
-        <v>7035301</v>
+        <v>7035246</v>
       </c>
       <c r="S31" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4208,6 +4132,11 @@
           <t>2025-02-23</t>
         </is>
       </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
+        </is>
+      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
@@ -4224,22 +4153,22 @@
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>sälg</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK31" t="inlineStr">
         <is>
-          <t>Salix caprea</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM31" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Salix caprea</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -4257,10 +4186,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122715949</v>
+        <v>122716757</v>
       </c>
       <c r="B32" t="n">
-        <v>79847</v>
+        <v>78769</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4273,21 +4202,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4297,13 +4226,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>520254</v>
+        <v>520316</v>
       </c>
       <c r="R32" t="n">
-        <v>7035555</v>
+        <v>7035491</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4343,6 +4272,31 @@
       </c>
       <c r="AG32" t="b">
         <v>0</v>
+      </c>
+      <c r="AH32" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM32" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
@@ -4359,10 +4313,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122721035</v>
+        <v>122720558</v>
       </c>
       <c r="B33" t="n">
-        <v>78766</v>
+        <v>57497</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4375,37 +4329,42 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>519897</v>
+        <v>519949</v>
       </c>
       <c r="R33" t="n">
-        <v>7035374</v>
+        <v>7035254</v>
       </c>
       <c r="S33" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4437,6 +4396,11 @@
           <t>2025-02-23</t>
         </is>
       </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Äldre hackspår i stambasen.</t>
+        </is>
+      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
@@ -4453,22 +4417,22 @@
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>garnlav</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM33" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Stående död trädstam/högstubbe</t>
         </is>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
-          <t>Branch on living tree # Alectoria sarmentosa</t>
+          <t>Standing dead tree/snags # Picea abies</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4486,10 +4450,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122720686</v>
+        <v>122715934</v>
       </c>
       <c r="B34" t="n">
-        <v>78766</v>
+        <v>78769</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4522,17 +4486,17 @@
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Spejkmyren, Spejkmyren, Jmt</t>
+          <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>519903</v>
+        <v>520303</v>
       </c>
       <c r="R34" t="n">
-        <v>7035224</v>
+        <v>7035598</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4562,6 +4526,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-02-23</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4613,10 +4582,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122715934</v>
+        <v>122720368</v>
       </c>
       <c r="B35" t="n">
-        <v>78766</v>
+        <v>57481</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4629,37 +4598,42 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Finnbodarna, Finnbodarna, Jmt</t>
+          <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>520303</v>
+        <v>519852</v>
       </c>
       <c r="R35" t="n">
-        <v>7035598</v>
+        <v>7035392</v>
       </c>
       <c r="S35" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4693,7 +4667,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4704,31 +4678,6 @@
       </c>
       <c r="AG35" t="b">
         <v>0</v>
-      </c>
-      <c r="AH35" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ35" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK35" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM35" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO35" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
@@ -4745,10 +4694,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122719533</v>
+        <v>122715648</v>
       </c>
       <c r="B36" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4786,14 +4735,14 @@
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Spejkmyren, Spejkmyren, Jmt</t>
+          <t>Finnbodarna, Hammerdal, Finnbodarna, Hammerdal, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>519948</v>
+        <v>520219</v>
       </c>
       <c r="R36" t="n">
-        <v>7035187</v>
+        <v>7035597</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4857,10 +4806,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122716682</v>
+        <v>122717446</v>
       </c>
       <c r="B37" t="n">
-        <v>57631</v>
+        <v>90973</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4873,43 +4822,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>103021</v>
+        <v>5432</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>par i lämplig häckbiotop</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>520101</v>
+        <v>520006</v>
       </c>
       <c r="R37" t="n">
-        <v>7035453</v>
+        <v>7035303</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4968,10 +4908,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122716427</v>
+        <v>122716329</v>
       </c>
       <c r="B38" t="n">
-        <v>78767</v>
+        <v>79850</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4984,37 +4924,42 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>230405</v>
+        <v>6458</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>520388</v>
+        <v>520374</v>
       </c>
       <c r="R38" t="n">
-        <v>7035490</v>
+        <v>7035511</v>
       </c>
       <c r="S38" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5048,7 +4993,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>På gran intill en gammal lunglavssälg.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5100,10 +5045,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122715780</v>
+        <v>122715870</v>
       </c>
       <c r="B39" t="n">
-        <v>79847</v>
+        <v>79851</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5116,21 +5061,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -5140,10 +5085,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>520259</v>
+        <v>520265</v>
       </c>
       <c r="R39" t="n">
-        <v>7035569</v>
+        <v>7035574</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5176,11 +5121,6 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-02-23</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>På björk</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5207,10 +5147,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122720327</v>
+        <v>122718013</v>
       </c>
       <c r="B40" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5252,10 +5192,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>519838</v>
+        <v>519948</v>
       </c>
       <c r="R40" t="n">
-        <v>7035393</v>
+        <v>7035313</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5319,10 +5259,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122720454</v>
+        <v>122716673</v>
       </c>
       <c r="B41" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5364,10 +5304,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>519849</v>
+        <v>520108</v>
       </c>
       <c r="R41" t="n">
-        <v>7035406</v>
+        <v>7035462</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5431,10 +5371,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122719697</v>
+        <v>122719648</v>
       </c>
       <c r="B42" t="n">
-        <v>78766</v>
+        <v>57481</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5447,37 +5387,42 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>520026</v>
+        <v>519939</v>
       </c>
       <c r="R42" t="n">
-        <v>7035233</v>
+        <v>7035194</v>
       </c>
       <c r="S42" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5509,6 +5454,11 @@
           <t>2025-02-23</t>
         </is>
       </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD42" t="b">
         <v>0</v>
       </c>
@@ -5517,31 +5467,6 @@
       </c>
       <c r="AG42" t="b">
         <v>0</v>
-      </c>
-      <c r="AH42" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ42" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK42" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM42" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO42" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
@@ -5558,10 +5483,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122717616</v>
+        <v>122717343</v>
       </c>
       <c r="B43" t="n">
-        <v>78766</v>
+        <v>57481</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5574,34 +5499,39 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
           <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>520019</v>
+        <v>520034</v>
       </c>
       <c r="R43" t="n">
-        <v>7035352</v>
+        <v>7035339</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5638,7 +5568,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Rikligt.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5649,31 +5579,6 @@
       </c>
       <c r="AG43" t="b">
         <v>0</v>
-      </c>
-      <c r="AH43" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ43" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK43" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM43" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO43" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
@@ -5690,10 +5595,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122717359</v>
+        <v>122715775</v>
       </c>
       <c r="B44" t="n">
-        <v>79847</v>
+        <v>79850</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5724,16 +5629,21 @@
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Spejkmyren, Spejkmyren, Jmt</t>
+          <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>520030</v>
+        <v>520252</v>
       </c>
       <c r="R44" t="n">
-        <v>7035341</v>
+        <v>7035576</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5766,6 +5676,11 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-02-23</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>På björk</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5792,10 +5707,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122721333</v>
+        <v>122715978</v>
       </c>
       <c r="B45" t="n">
-        <v>78766</v>
+        <v>79850</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5808,37 +5723,42 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Spejkmyren, Spejkmyren, Jmt</t>
+          <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>519906</v>
+        <v>520243</v>
       </c>
       <c r="R45" t="n">
-        <v>7035389</v>
+        <v>7035552</v>
       </c>
       <c r="S45" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5870,11 +5790,6 @@
           <t>2025-02-23</t>
         </is>
       </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Ymnigt på flera granar.</t>
-        </is>
-      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
@@ -5883,31 +5798,6 @@
       </c>
       <c r="AG45" t="b">
         <v>0</v>
-      </c>
-      <c r="AH45" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ45" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK45" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM45" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO45" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
@@ -5924,10 +5814,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122720959</v>
+        <v>122716547</v>
       </c>
       <c r="B46" t="n">
-        <v>78766</v>
+        <v>98274</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5936,41 +5826,55 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>504</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Spejkmyren, Spejkmyren, Jmt</t>
+          <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>519917</v>
+        <v>520386</v>
       </c>
       <c r="R46" t="n">
-        <v>7035339</v>
+        <v>7035492</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -6004,7 +5908,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Långväxta bålar på flertalet granar.</t>
+          <t>En vinterståndare på till synes fuktig mark i en lucka.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6019,26 +5923,6 @@
       <c r="AH46" t="inlineStr">
         <is>
           <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ46" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK46" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM46" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO46" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT46" t="inlineStr"/>
@@ -6056,10 +5940,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>122718013</v>
+        <v>122715849</v>
       </c>
       <c r="B47" t="n">
-        <v>57478</v>
+        <v>79879</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6068,43 +5952,38 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Spejkmyren, Spejkmyren, Jmt</t>
+          <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>519948</v>
+        <v>520268</v>
       </c>
       <c r="R47" t="n">
-        <v>7035313</v>
+        <v>7035575</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6137,11 +6016,6 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-02-23</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6168,10 +6042,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122716850</v>
+        <v>122716645</v>
       </c>
       <c r="B48" t="n">
-        <v>90970</v>
+        <v>57481</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6184,34 +6058,39 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>520101</v>
+        <v>520129</v>
       </c>
       <c r="R48" t="n">
-        <v>7035388</v>
+        <v>7035444</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6244,6 +6123,11 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-02-23</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6270,10 +6154,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>122715648</v>
+        <v>122716269</v>
       </c>
       <c r="B49" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6315,10 +6199,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>520219</v>
+        <v>520256</v>
       </c>
       <c r="R49" t="n">
-        <v>7035597</v>
+        <v>7035380</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6382,10 +6266,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122716293</v>
+        <v>122715677</v>
       </c>
       <c r="B50" t="n">
-        <v>57478</v>
+        <v>79851</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6398,39 +6282,34 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Finnbodarna, Hammerdal, Finnbodarna, Hammerdal, Jmt</t>
+          <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>520249</v>
+        <v>520221</v>
       </c>
       <c r="R50" t="n">
-        <v>7035364</v>
+        <v>7035600</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6467,7 +6346,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6494,10 +6373,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122719648</v>
+        <v>122717488</v>
       </c>
       <c r="B51" t="n">
-        <v>57478</v>
+        <v>79850</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6510,39 +6389,34 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>519939</v>
+        <v>520000</v>
       </c>
       <c r="R51" t="n">
-        <v>7035194</v>
+        <v>7035297</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6575,11 +6449,6 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-02-23</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6606,10 +6475,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122716801</v>
+        <v>122716850</v>
       </c>
       <c r="B52" t="n">
-        <v>57631</v>
+        <v>90973</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6622,43 +6491,34 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>103021</v>
+        <v>5432</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>par i lämplig häckbiotop</t>
-        </is>
-      </c>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>520083</v>
+        <v>520101</v>
       </c>
       <c r="R52" t="n">
-        <v>7035403</v>
+        <v>7035388</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6717,10 +6577,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122715801</v>
+        <v>122715868</v>
       </c>
       <c r="B53" t="n">
-        <v>79848</v>
+        <v>79850</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6733,34 +6593,39 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>520266</v>
+        <v>520265</v>
       </c>
       <c r="R53" t="n">
-        <v>7035582</v>
+        <v>7035574</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6819,10 +6684,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>122716216</v>
+        <v>122716295</v>
       </c>
       <c r="B54" t="n">
-        <v>79847</v>
+        <v>79850</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6855,7 +6720,7 @@
       <c r="I54" t="inlineStr"/>
       <c r="K54" t="inlineStr">
         <is>
-          <t>med soral</t>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
@@ -6864,10 +6729,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>520368</v>
+        <v>520378</v>
       </c>
       <c r="R54" t="n">
-        <v>7035513</v>
+        <v>7035512</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6904,7 +6769,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>På en gammal grovbarkad sälg.</t>
+          <t>Ymnig påväxt på en grovbarkad gammal sälg. Fertila bålar med apothecier.</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6956,10 +6821,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122716303</v>
+        <v>122715571</v>
       </c>
       <c r="B55" t="n">
-        <v>57478</v>
+        <v>79850</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6972,39 +6837,34 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Finnbodarna, Hammerdal, Finnbodarna, Hammerdal, Jmt</t>
+          <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>520250</v>
+        <v>520216</v>
       </c>
       <c r="R55" t="n">
-        <v>7035363</v>
+        <v>7035583</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -7037,11 +6897,6 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-02-23</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7068,10 +6923,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122720427</v>
+        <v>122715573</v>
       </c>
       <c r="B56" t="n">
-        <v>57478</v>
+        <v>79851</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -7084,39 +6939,34 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Spejkmyren, Spejkmyren, Jmt</t>
+          <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>519846</v>
+        <v>520214</v>
       </c>
       <c r="R56" t="n">
-        <v>7035407</v>
+        <v>7035583</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7149,11 +6999,6 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-02-23</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7180,10 +7025,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122715849</v>
+        <v>122720065</v>
       </c>
       <c r="B57" t="n">
-        <v>79876</v>
+        <v>78769</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -7192,41 +7037,41 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Finnbodarna, Finnbodarna, Jmt</t>
+          <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>520268</v>
+        <v>520062</v>
       </c>
       <c r="R57" t="n">
-        <v>7035575</v>
+        <v>7035232</v>
       </c>
       <c r="S57" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -7266,6 +7111,31 @@
       </c>
       <c r="AG57" t="b">
         <v>0</v>
+      </c>
+      <c r="AH57" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ57" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK57" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM57" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO57" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
@@ -7282,10 +7152,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122720558</v>
+        <v>122717359</v>
       </c>
       <c r="B58" t="n">
-        <v>57494</v>
+        <v>79850</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7298,39 +7168,34 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>519949</v>
+        <v>520030</v>
       </c>
       <c r="R58" t="n">
-        <v>7035254</v>
+        <v>7035341</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7365,11 +7230,6 @@
           <t>2025-02-23</t>
         </is>
       </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Äldre hackspår i stambasen.</t>
-        </is>
-      </c>
       <c r="AD58" t="b">
         <v>0</v>
       </c>
@@ -7378,31 +7238,6 @@
       </c>
       <c r="AG58" t="b">
         <v>0</v>
-      </c>
-      <c r="AH58" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ58" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK58" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM58" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO58" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
@@ -7419,10 +7254,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122716757</v>
+        <v>122715801</v>
       </c>
       <c r="B59" t="n">
-        <v>78766</v>
+        <v>79851</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7435,21 +7270,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>2081</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -7459,13 +7294,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>520316</v>
+        <v>520266</v>
       </c>
       <c r="R59" t="n">
-        <v>7035491</v>
+        <v>7035582</v>
       </c>
       <c r="S59" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7505,31 +7340,6 @@
       </c>
       <c r="AG59" t="b">
         <v>0</v>
-      </c>
-      <c r="AH59" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ59" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK59" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM59" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO59" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
@@ -7546,10 +7356,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122715569</v>
+        <v>122716801</v>
       </c>
       <c r="B60" t="n">
-        <v>78766</v>
+        <v>57634</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7562,34 +7372,43 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Djupmyren, Djupmyren, Jmt</t>
+          <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>520115</v>
+        <v>520083</v>
       </c>
       <c r="R60" t="n">
-        <v>7035562</v>
+        <v>7035403</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7624,11 +7443,6 @@
           <t>2025-02-23</t>
         </is>
       </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
-        </is>
-      </c>
       <c r="AD60" t="b">
         <v>0</v>
       </c>
@@ -7637,31 +7451,6 @@
       </c>
       <c r="AG60" t="b">
         <v>0</v>
-      </c>
-      <c r="AH60" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ60" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK60" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM60" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO60" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
@@ -7678,10 +7467,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122716392</v>
+        <v>122716303</v>
       </c>
       <c r="B61" t="n">
-        <v>79848</v>
+        <v>57481</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7694,42 +7483,42 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="K61" t="inlineStr">
-        <is>
-          <t>med soral</t>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Finnbodarna, Finnbodarna, Jmt</t>
+          <t>Finnbodarna, Hammerdal, Finnbodarna, Hammerdal, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>520385</v>
+        <v>520250</v>
       </c>
       <c r="R61" t="n">
-        <v>7035518</v>
+        <v>7035363</v>
       </c>
       <c r="S61" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7763,7 +7552,7 @@
       </c>
       <c r="AC61" t="inlineStr">
         <is>
-          <t>På gran intill en gammal sälg.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7774,31 +7563,6 @@
       </c>
       <c r="AG61" t="b">
         <v>0</v>
-      </c>
-      <c r="AH61" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ61" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK61" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM61" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO61" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
@@ -7815,10 +7579,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>122717343</v>
+        <v>122721333</v>
       </c>
       <c r="B62" t="n">
-        <v>57478</v>
+        <v>78769</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7831,42 +7595,37 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>520034</v>
+        <v>519906</v>
       </c>
       <c r="R62" t="n">
-        <v>7035339</v>
+        <v>7035389</v>
       </c>
       <c r="S62" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7900,7 +7659,7 @@
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ymnigt på flera granar.</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7911,6 +7670,31 @@
       </c>
       <c r="AG62" t="b">
         <v>0</v>
+      </c>
+      <c r="AH62" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ62" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK62" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM62" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO62" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
@@ -7927,10 +7711,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>122715836</v>
+        <v>122716160</v>
       </c>
       <c r="B63" t="n">
-        <v>79847</v>
+        <v>78769</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7943,39 +7727,34 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="K63" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P63" t="inlineStr">
         <is>
           <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>520269</v>
+        <v>520349</v>
       </c>
       <c r="R63" t="n">
-        <v>7035574</v>
+        <v>7035517</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -8018,6 +7797,31 @@
       </c>
       <c r="AG63" t="b">
         <v>0</v>
+      </c>
+      <c r="AH63" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ63" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK63" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM63" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO63" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
@@ -8034,10 +7838,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>122716234</v>
+        <v>122720889</v>
       </c>
       <c r="B64" t="n">
-        <v>79847</v>
+        <v>57481</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -8050,34 +7854,39 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Finnbodarna, Finnbodarna, Jmt</t>
+          <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>520362</v>
+        <v>519841</v>
       </c>
       <c r="R64" t="n">
-        <v>7035500</v>
+        <v>7035390</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -8114,7 +7923,7 @@
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>På en klen gran intill en gammal sälg med lunglav.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8125,31 +7934,6 @@
       </c>
       <c r="AG64" t="b">
         <v>0</v>
-      </c>
-      <c r="AH64" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ64" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK64" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM64" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO64" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
@@ -8166,10 +7950,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>122717488</v>
+        <v>122717873</v>
       </c>
       <c r="B65" t="n">
-        <v>79847</v>
+        <v>79850</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -8200,19 +7984,24 @@
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>520000</v>
+        <v>520033</v>
       </c>
       <c r="R65" t="n">
-        <v>7035297</v>
+        <v>7035301</v>
       </c>
       <c r="S65" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -8252,6 +8041,31 @@
       </c>
       <c r="AG65" t="b">
         <v>0</v>
+      </c>
+      <c r="AH65" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ65" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK65" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM65" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO65" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
@@ -8268,10 +8082,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>122716295</v>
+        <v>122716216</v>
       </c>
       <c r="B66" t="n">
-        <v>79847</v>
+        <v>79850</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -8304,7 +8118,7 @@
       <c r="I66" t="inlineStr"/>
       <c r="K66" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
@@ -8313,10 +8127,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>520378</v>
+        <v>520368</v>
       </c>
       <c r="R66" t="n">
-        <v>7035512</v>
+        <v>7035513</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -8353,7 +8167,7 @@
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>Ymnig påväxt på en grovbarkad gammal sälg. Fertila bålar med apothecier.</t>
+          <t>På en gammal grovbarkad sälg.</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8405,10 +8219,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>122720548</v>
+        <v>122719697</v>
       </c>
       <c r="B67" t="n">
-        <v>90970</v>
+        <v>78769</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -8421,21 +8235,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -8445,13 +8259,13 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>519847</v>
+        <v>520026</v>
       </c>
       <c r="R67" t="n">
-        <v>7035432</v>
+        <v>7035233</v>
       </c>
       <c r="S67" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -8491,6 +8305,31 @@
       </c>
       <c r="AG67" t="b">
         <v>0</v>
+      </c>
+      <c r="AH67" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ67" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK67" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM67" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO67" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
@@ -8507,10 +8346,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>122717294</v>
+        <v>122715502</v>
       </c>
       <c r="B68" t="n">
-        <v>90970</v>
+        <v>78769</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -8523,37 +8362,42 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Spejkmyren, Spejkmyren, Jmt</t>
+          <t>Djupmyren, Djupmyren, Jmt</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>520013</v>
+        <v>520110</v>
       </c>
       <c r="R68" t="n">
-        <v>7035340</v>
+        <v>7035585</v>
       </c>
       <c r="S68" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8585,6 +8429,11 @@
           <t>2025-02-23</t>
         </is>
       </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Gott om långväxt garnlav på många granar. Vissa bålar är här fertila.</t>
+        </is>
+      </c>
       <c r="AD68" t="b">
         <v>0</v>
       </c>
@@ -8593,6 +8442,31 @@
       </c>
       <c r="AG68" t="b">
         <v>0</v>
+      </c>
+      <c r="AH68" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ68" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK68" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM68" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO68" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
@@ -8609,10 +8483,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>122715790</v>
+        <v>122715999</v>
       </c>
       <c r="B69" t="n">
-        <v>79847</v>
+        <v>78769</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -8625,42 +8499,37 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="K69" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>520267</v>
+        <v>520311</v>
       </c>
       <c r="R69" t="n">
-        <v>7035581</v>
+        <v>7035566</v>
       </c>
       <c r="S69" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8700,6 +8569,31 @@
       </c>
       <c r="AG69" t="b">
         <v>0</v>
+      </c>
+      <c r="AH69" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ69" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK69" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM69" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO69" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
@@ -8716,10 +8610,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>122721463</v>
+        <v>122717284</v>
       </c>
       <c r="B70" t="n">
-        <v>78766</v>
+        <v>78769</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -8756,13 +8650,13 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>519841</v>
+        <v>520031</v>
       </c>
       <c r="R70" t="n">
-        <v>7035417</v>
+        <v>7035353</v>
       </c>
       <c r="S70" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8796,7 +8690,7 @@
       </c>
       <c r="AC70" t="inlineStr">
         <is>
-          <t>Långväxta bålar.</t>
+          <t>Långväxta bålar på flertalet granar.</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8848,10 +8742,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>122715757</v>
+        <v>122717468</v>
       </c>
       <c r="B71" t="n">
-        <v>78766</v>
+        <v>57497</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8864,34 +8758,43 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Finnbodarna, Finnbodarna, Jmt</t>
+          <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>520234</v>
+        <v>520020</v>
       </c>
       <c r="R71" t="n">
-        <v>7035595</v>
+        <v>7035330</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8926,11 +8829,6 @@
           <t>2025-02-23</t>
         </is>
       </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
-        </is>
-      </c>
       <c r="AD71" t="b">
         <v>0</v>
       </c>
@@ -8939,31 +8837,6 @@
       </c>
       <c r="AG71" t="b">
         <v>0</v>
-      </c>
-      <c r="AH71" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ71" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK71" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM71" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO71" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
@@ -8980,10 +8853,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>122719875</v>
+        <v>122720281</v>
       </c>
       <c r="B72" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -9025,10 +8898,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>519983</v>
+        <v>519850</v>
       </c>
       <c r="R72" t="n">
-        <v>7035206</v>
+        <v>7035373</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -9092,10 +8965,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>122716443</v>
+        <v>122715836</v>
       </c>
       <c r="B73" t="n">
-        <v>78766</v>
+        <v>79850</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -9108,33 +8981,24 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
-      <c r="J73" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
       <c r="K73" t="inlineStr">
         <is>
           <t>med apothecier</t>
@@ -9146,10 +9010,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>520251</v>
+        <v>520269</v>
       </c>
       <c r="R73" t="n">
-        <v>7035394</v>
+        <v>7035574</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -9182,11 +9046,6 @@
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-02-23</t>
-        </is>
-      </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>Garnlavsrikt</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -9213,10 +9072,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>122719979</v>
+        <v>122715779</v>
       </c>
       <c r="B74" t="n">
-        <v>57631</v>
+        <v>79850</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -9229,46 +9088,42 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M74" t="inlineStr">
-        <is>
-          <t>par i lämplig häckbiotop</t>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Spejkmyren, Spejkmyren, Jmt</t>
+          <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>519946</v>
+        <v>520223</v>
       </c>
       <c r="R74" t="n">
-        <v>7035240</v>
+        <v>7035609</v>
       </c>
       <c r="S74" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -9308,6 +9163,31 @@
       </c>
       <c r="AG74" t="b">
         <v>0</v>
+      </c>
+      <c r="AH74" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ74" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK74" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM74" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO74" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
@@ -9324,10 +9204,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>122715573</v>
+        <v>122716964</v>
       </c>
       <c r="B75" t="n">
-        <v>79848</v>
+        <v>90973</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -9340,34 +9220,34 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>2081</v>
+        <v>5432</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Finnbodarna, Finnbodarna, Jmt</t>
+          <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>520214</v>
+        <v>520115</v>
       </c>
       <c r="R75" t="n">
-        <v>7035583</v>
+        <v>7035402</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -9426,10 +9306,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>122715874</v>
+        <v>122720959</v>
       </c>
       <c r="B76" t="n">
-        <v>79876</v>
+        <v>78769</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -9438,38 +9318,38 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Finnbodarna, Finnbodarna, Jmt</t>
+          <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>520265</v>
+        <v>519917</v>
       </c>
       <c r="R76" t="n">
-        <v>7035574</v>
+        <v>7035339</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -9504,6 +9384,11 @@
           <t>2025-02-23</t>
         </is>
       </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>Långväxta bålar på flertalet granar.</t>
+        </is>
+      </c>
       <c r="AD76" t="b">
         <v>0</v>
       </c>
@@ -9512,6 +9397,31 @@
       </c>
       <c r="AG76" t="b">
         <v>0</v>
+      </c>
+      <c r="AH76" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ76" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK76" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM76" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO76" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
@@ -9528,10 +9438,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>122719371</v>
+        <v>122716234</v>
       </c>
       <c r="B77" t="n">
-        <v>78766</v>
+        <v>79850</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -9544,37 +9454,37 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Spejkmyren, Spejkmyren, Jmt</t>
+          <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>519943</v>
+        <v>520362</v>
       </c>
       <c r="R77" t="n">
-        <v>7035270</v>
+        <v>7035500</v>
       </c>
       <c r="S77" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -9604,6 +9514,11 @@
       <c r="AA77" t="inlineStr">
         <is>
           <t>2025-02-23</t>
+        </is>
+      </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>På en klen gran intill en gammal sälg med lunglav.</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -9655,10 +9570,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>122716645</v>
+        <v>122717929</v>
       </c>
       <c r="B78" t="n">
-        <v>57478</v>
+        <v>79879</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -9667,31 +9582,31 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
-      <c r="M78" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P78" t="inlineStr">
@@ -9700,13 +9615,13 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>520129</v>
+        <v>520029</v>
       </c>
       <c r="R78" t="n">
-        <v>7035444</v>
+        <v>7035292</v>
       </c>
       <c r="S78" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -9738,11 +9653,6 @@
           <t>2025-02-23</t>
         </is>
       </c>
-      <c r="AC78" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD78" t="b">
         <v>0</v>
       </c>
@@ -9751,6 +9661,31 @@
       </c>
       <c r="AG78" t="b">
         <v>0</v>
+      </c>
+      <c r="AH78" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ78" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK78" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM78" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO78" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
+        </is>
       </c>
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
@@ -9767,10 +9702,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>122720869</v>
+        <v>122715874</v>
       </c>
       <c r="B79" t="n">
-        <v>78766</v>
+        <v>79879</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -9779,38 +9714,38 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Spejkmyren, Spejkmyren, Jmt</t>
+          <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>519960</v>
+        <v>520265</v>
       </c>
       <c r="R79" t="n">
-        <v>7035342</v>
+        <v>7035574</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9853,31 +9788,6 @@
       </c>
       <c r="AG79" t="b">
         <v>0</v>
-      </c>
-      <c r="AH79" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ79" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK79" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM79" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO79" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
@@ -9894,10 +9804,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>122717636</v>
+        <v>122719371</v>
       </c>
       <c r="B80" t="n">
-        <v>57478</v>
+        <v>78769</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -9910,42 +9820,37 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
-      <c r="M80" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P80" t="inlineStr">
         <is>
           <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>519970</v>
+        <v>519943</v>
       </c>
       <c r="R80" t="n">
-        <v>7035297</v>
+        <v>7035270</v>
       </c>
       <c r="S80" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -9977,11 +9882,6 @@
           <t>2025-02-23</t>
         </is>
       </c>
-      <c r="AC80" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD80" t="b">
         <v>0</v>
       </c>
@@ -9990,6 +9890,31 @@
       </c>
       <c r="AG80" t="b">
         <v>0</v>
+      </c>
+      <c r="AH80" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ80" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK80" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM80" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO80" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
@@ -10006,10 +9931,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>122716387</v>
+        <v>122716443</v>
       </c>
       <c r="B81" t="n">
-        <v>57478</v>
+        <v>78769</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -10022,39 +9947,48 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr"/>
-      <c r="M81" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Finnbodarna, Hammerdal, Finnbodarna, Hammerdal, Jmt</t>
+          <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>520278</v>
+        <v>520251</v>
       </c>
       <c r="R81" t="n">
-        <v>7035397</v>
+        <v>7035394</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -10091,7 +10025,7 @@
       </c>
       <c r="AC81" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Garnlavsrikt</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -10118,10 +10052,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>122715775</v>
+        <v>122717616</v>
       </c>
       <c r="B82" t="n">
-        <v>79847</v>
+        <v>78769</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -10134,39 +10068,34 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
-      <c r="K82" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Finnbodarna, Finnbodarna, Jmt</t>
+          <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>520252</v>
+        <v>520019</v>
       </c>
       <c r="R82" t="n">
-        <v>7035576</v>
+        <v>7035352</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -10203,7 +10132,7 @@
       </c>
       <c r="AC82" t="inlineStr">
         <is>
-          <t>På björk</t>
+          <t>Rikligt.</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -10214,6 +10143,31 @@
       </c>
       <c r="AG82" t="b">
         <v>0</v>
+      </c>
+      <c r="AH82" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ82" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK82" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM82" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO82" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
@@ -10230,10 +10184,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>122715868</v>
+        <v>122719875</v>
       </c>
       <c r="B83" t="n">
-        <v>79847</v>
+        <v>57481</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -10246,39 +10200,39 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
-      <c r="K83" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Finnbodarna, Finnbodarna, Jmt</t>
+          <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>520265</v>
+        <v>519983</v>
       </c>
       <c r="R83" t="n">
-        <v>7035574</v>
+        <v>7035206</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -10311,6 +10265,11 @@
       <c r="AA83" t="inlineStr">
         <is>
           <t>2025-02-23</t>
+        </is>
+      </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -10337,10 +10296,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>122717446</v>
+        <v>122716387</v>
       </c>
       <c r="B84" t="n">
-        <v>90970</v>
+        <v>57481</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -10353,34 +10312,39 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Spejkmyren, Spejkmyren, Jmt</t>
+          <t>Finnbodarna, Hammerdal, Finnbodarna, Hammerdal, Jmt</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>520006</v>
+        <v>520278</v>
       </c>
       <c r="R84" t="n">
-        <v>7035303</v>
+        <v>7035397</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -10413,6 +10377,11 @@
       <c r="AA84" t="inlineStr">
         <is>
           <t>2025-02-23</t>
+        </is>
+      </c>
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -10439,10 +10408,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>122717929</v>
+        <v>122716682</v>
       </c>
       <c r="B85" t="n">
-        <v>79876</v>
+        <v>57634</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -10451,31 +10420,35 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6462</v>
+        <v>103021</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr"/>
-      <c r="K85" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
         </is>
       </c>
       <c r="P85" t="inlineStr">
@@ -10484,13 +10457,13 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>520029</v>
+        <v>520101</v>
       </c>
       <c r="R85" t="n">
-        <v>7035292</v>
+        <v>7035453</v>
       </c>
       <c r="S85" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -10530,31 +10503,6 @@
       </c>
       <c r="AG85" t="b">
         <v>0</v>
-      </c>
-      <c r="AH85" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ85" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK85" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM85" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO85" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
@@ -10571,10 +10519,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>122715669</v>
+        <v>122715841</v>
       </c>
       <c r="B86" t="n">
-        <v>79847</v>
+        <v>79850</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -10607,7 +10555,7 @@
       <c r="I86" t="inlineStr"/>
       <c r="K86" t="inlineStr">
         <is>
-          <t>med apothecier</t>
+          <t>med soral</t>
         </is>
       </c>
       <c r="P86" t="inlineStr">
@@ -10616,13 +10564,13 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>520221</v>
+        <v>520229</v>
       </c>
       <c r="R86" t="n">
-        <v>7035600</v>
+        <v>7035608</v>
       </c>
       <c r="S86" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -10654,6 +10602,11 @@
           <t>2025-02-23</t>
         </is>
       </c>
+      <c r="AC86" t="inlineStr">
+        <is>
+          <t>På en björk.</t>
+        </is>
+      </c>
       <c r="AD86" t="b">
         <v>0</v>
       </c>
@@ -10662,6 +10615,31 @@
       </c>
       <c r="AG86" t="b">
         <v>0</v>
+      </c>
+      <c r="AH86" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ86" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK86" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AM86" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO86" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Betula</t>
+        </is>
       </c>
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
@@ -10678,10 +10656,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>122715571</v>
+        <v>122720686</v>
       </c>
       <c r="B87" t="n">
-        <v>79847</v>
+        <v>78769</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -10694,34 +10672,34 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Finnbodarna, Finnbodarna, Jmt</t>
+          <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>520216</v>
+        <v>519903</v>
       </c>
       <c r="R87" t="n">
-        <v>7035583</v>
+        <v>7035224</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10764,6 +10742,31 @@
       </c>
       <c r="AG87" t="b">
         <v>0</v>
+      </c>
+      <c r="AH87" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ87" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK87" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM87" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO87" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
@@ -10780,10 +10783,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>122715779</v>
+        <v>122720427</v>
       </c>
       <c r="B88" t="n">
-        <v>79847</v>
+        <v>57481</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -10796,42 +10799,42 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
-      <c r="K88" t="inlineStr">
-        <is>
-          <t>med soral</t>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Finnbodarna, Finnbodarna, Jmt</t>
+          <t>Spejkmyren, Spejkmyren, Jmt</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>520223</v>
+        <v>519846</v>
       </c>
       <c r="R88" t="n">
-        <v>7035609</v>
+        <v>7035407</v>
       </c>
       <c r="S88" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -10863,6 +10866,11 @@
           <t>2025-02-23</t>
         </is>
       </c>
+      <c r="AC88" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD88" t="b">
         <v>0</v>
       </c>
@@ -10871,31 +10879,6 @@
       </c>
       <c r="AG88" t="b">
         <v>0</v>
-      </c>
-      <c r="AH88" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ88" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK88" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM88" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO88" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
-        </is>
       </c>
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
@@ -10912,10 +10895,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>122720474</v>
+        <v>122717636</v>
       </c>
       <c r="B89" t="n">
-        <v>57494</v>
+        <v>57481</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -10928,16 +10911,16 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -10945,19 +10928,10 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I89" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="L89" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="I89" t="inlineStr"/>
       <c r="M89" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P89" t="inlineStr">
@@ -10966,10 +10940,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>519848</v>
+        <v>519970</v>
       </c>
       <c r="R89" t="n">
-        <v>7035394</v>
+        <v>7035297</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -11002,6 +10976,11 @@
       <c r="AA89" t="inlineStr">
         <is>
           <t>2025-02-23</t>
+        </is>
+      </c>
+      <c r="AC89" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -11028,10 +11007,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>122717468</v>
+        <v>122716427</v>
       </c>
       <c r="B90" t="n">
-        <v>57494</v>
+        <v>78770</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -11044,46 +11023,37 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>100049</v>
+        <v>230405</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M90" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Spejkmyren, Spejkmyren, Jmt</t>
+          <t>Finnbodarna, Finnbodarna, Jmt</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>520020</v>
+        <v>520388</v>
       </c>
       <c r="R90" t="n">
-        <v>7035330</v>
+        <v>7035490</v>
       </c>
       <c r="S90" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -11115,6 +11085,11 @@
           <t>2025-02-23</t>
         </is>
       </c>
+      <c r="AC90" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
+        </is>
+      </c>
       <c r="AD90" t="b">
         <v>0</v>
       </c>
@@ -11123,6 +11098,31 @@
       </c>
       <c r="AG90" t="b">
         <v>0</v>
+      </c>
+      <c r="AH90" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ90" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK90" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM90" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO90" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
+        </is>
       </c>
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
@@ -11142,7 +11142,7 @@
         <v>122720789</v>
       </c>
       <c r="B91" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
